--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="H4" t="n">
         <v>1.57</v>
@@ -1377,7 +1377,7 @@
         <v>1.69</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
         <v>4.7</v>
@@ -1395,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q4" t="n">
         <v>1.83</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -1628,10 +1628,10 @@
         <v>2.12</v>
       </c>
       <c r="I5" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="J5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
         <v>4.1</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="G6" t="n">
         <v>1.93</v>
@@ -1882,7 +1882,7 @@
         <v>4.8</v>
       </c>
       <c r="I6" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="J6" t="n">
         <v>3.6</v>
@@ -1906,7 +1906,7 @@
         <v>1.88</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G7" t="n">
         <v>3.05</v>
@@ -2136,7 +2136,7 @@
         <v>2.74</v>
       </c>
       <c r="I7" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -2384,16 +2384,16 @@
         <v>2.44</v>
       </c>
       <c r="G8" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H8" t="n">
         <v>3.05</v>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J8" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
         <v>3.5</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -2635,28 +2635,28 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="G9" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
         <v>3.45</v>
       </c>
       <c r="K9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L9" t="n">
         <v>1.38</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N9" t="n">
         <v>3.2</v>
@@ -2665,13 +2665,13 @@
         <v>1.39</v>
       </c>
       <c r="P9" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q9" t="n">
         <v>2.14</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -2680,64 +2680,64 @@
         <v>1.94</v>
       </c>
       <c r="U9" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V9" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="X9" t="n">
         <v>14.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AA9" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AE9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI9" t="n">
         <v>75</v>
       </c>
-      <c r="AF9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>100</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AK9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AL9" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AM9" t="n">
         <v>160</v>
       </c>
       <c r="AN9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO9" t="n">
         <v>110</v>
@@ -2746,82 +2746,82 @@
         <v>10.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.3</v>
+        <v>7.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
       <c r="BD9" t="n">
         <v>36</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="BH9" t="n">
         <v>3.15</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BJ9" t="n">
         <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BN9" t="n">
         <v>4.6</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ9" t="n">
         <v>7.6</v>
@@ -2836,7 +2836,7 @@
         <v>7.8</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
@@ -2851,14 +2851,14 @@
         <v>12.5</v>
       </c>
       <c r="BZ9" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
         <v>10.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="G10" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="H10" t="n">
         <v>1.47</v>
       </c>
       <c r="I10" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="J10" t="n">
         <v>4.3</v>
@@ -2919,11 +2919,11 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1.92</v>
       </c>
-      <c r="Q10" t="n">
-        <v>1.97</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="G12" t="n">
         <v>7</v>
       </c>
       <c r="H12" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="J12" t="n">
         <v>4.3</v>
       </c>
       <c r="K12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3430,7 +3430,7 @@
         <v>2.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G14" t="n">
         <v>3.15</v>
       </c>
       <c r="H14" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="I14" t="n">
         <v>2.66</v>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q14" t="n">
         <v>1.71</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -4159,19 +4159,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="I15" t="n">
         <v>4.7</v>
       </c>
       <c r="J15" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K15" t="n">
         <v>3.9</v>
@@ -4189,7 +4189,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q15" t="n">
         <v>2.02</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
         <v>4.2</v>
       </c>
       <c r="I16" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
         <v>4.4</v>
@@ -4446,7 +4446,7 @@
         <v>3.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -4700,7 +4700,7 @@
         <v>2.22</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -4921,19 +4921,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G18" t="n">
         <v>1.6</v>
       </c>
       <c r="H18" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I18" t="n">
         <v>7.2</v>
       </c>
       <c r="J18" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K18" t="n">
         <v>5</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Y18" t="n">
         <v>25</v>
@@ -4987,16 +4987,16 @@
         <v>210</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AC18" t="n">
         <v>11</v>
       </c>
       <c r="AD18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE18" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF18" t="n">
         <v>10.5</v>
@@ -5008,7 +5008,7 @@
         <v>22</v>
       </c>
       <c r="AI18" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ18" t="n">
         <v>15</v>
@@ -5026,19 +5026,19 @@
         <v>7.4</v>
       </c>
       <c r="AO18" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP18" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>21</v>
       </c>
       <c r="AR18" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AS18" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT18" t="n">
         <v>8.6</v>
@@ -5047,10 +5047,10 @@
         <v>9.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AW18" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AX18" t="n">
         <v>9</v>
@@ -5062,7 +5062,7 @@
         <v>18.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB18" t="n">
         <v>13</v>
@@ -5074,13 +5074,13 @@
         <v>23</v>
       </c>
       <c r="BE18" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BF18" t="n">
         <v>6.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BH18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
         <v>3.65</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="K20" t="n">
         <v>3.95</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -6191,22 +6191,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="G23" t="n">
         <v>2.5</v>
       </c>
       <c r="H23" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="I23" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="J23" t="n">
         <v>4.1</v>
       </c>
       <c r="K23" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q24" t="n">
         <v>1.74</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -7715,22 +7715,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G29" t="n">
         <v>6.2</v>
       </c>
       <c r="H29" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="I29" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="J29" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K29" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -7745,10 +7745,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -8253,10 +8253,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -8477,23 +8477,23 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="G32" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K32" t="n">
         <v>3.5</v>
       </c>
-      <c r="H32" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K32" t="n">
-        <v>5.8</v>
-      </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
@@ -8507,10 +8507,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -8731,22 +8731,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="G33" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="H33" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="I33" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J33" t="n">
         <v>3.15</v>
       </c>
-      <c r="J33" t="n">
-        <v>3.05</v>
-      </c>
       <c r="K33" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -8761,10 +8761,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -9239,22 +9239,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.22</v>
+        <v>2.62</v>
       </c>
       <c r="G35" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="H35" t="n">
-        <v>1.43</v>
+        <v>2.8</v>
       </c>
       <c r="I35" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J35" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="K35" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="Q35" t="n">
         <v>2.16</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -9493,19 +9493,19 @@
         </is>
       </c>
       <c r="F36" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G36" t="n">
         <v>2.32</v>
       </c>
-      <c r="G36" t="n">
-        <v>2.46</v>
-      </c>
       <c r="H36" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="I36" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J36" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K36" t="n">
         <v>3.35</v>
@@ -9523,10 +9523,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
@@ -875,212 +875,212 @@
         <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P2" t="n">
         <v>1.07</v>
       </c>
       <c r="Q2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T2" t="n">
         <v>1.01</v>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -1129,212 +1129,212 @@
         <v>1000</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P3" t="n">
         <v>1.07</v>
       </c>
       <c r="Q3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T3" t="n">
         <v>1.01</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="H5" t="n">
         <v>2.12</v>
       </c>
       <c r="I5" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1649,7 +1649,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q5" t="n">
         <v>1.8</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
         <v>1.93</v>
       </c>
       <c r="H6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I6" t="n">
         <v>5.3</v>
@@ -1888,7 +1888,7 @@
         <v>3.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>1.88</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="G7" t="n">
         <v>3.05</v>
@@ -2157,7 +2157,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q7" t="n">
         <v>2.22</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G8" t="n">
         <v>2.64</v>
       </c>
       <c r="H8" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I8" t="n">
         <v>3.35</v>
@@ -2414,7 +2414,7 @@
         <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G9" t="n">
         <v>2.06</v>
@@ -2647,7 +2647,7 @@
         <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
         <v>3.7</v>
@@ -2665,7 +2665,7 @@
         <v>1.39</v>
       </c>
       <c r="P9" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q9" t="n">
         <v>2.14</v>
@@ -2701,13 +2701,13 @@
         <v>130</v>
       </c>
       <c r="AB9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AC9" t="n">
         <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AE9" t="n">
         <v>65</v>
@@ -2740,7 +2740,7 @@
         <v>22</v>
       </c>
       <c r="AO9" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AP9" t="n">
         <v>10.5</v>
@@ -2749,10 +2749,10 @@
         <v>12.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AT9" t="n">
         <v>7</v>
@@ -2764,7 +2764,7 @@
         <v>16</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX9" t="n">
         <v>10</v>
@@ -2776,25 +2776,25 @@
         <v>6</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD9" t="n">
         <v>36</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF9" t="n">
         <v>13</v>
       </c>
       <c r="BG9" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BH9" t="n">
         <v>3.15</v>
@@ -2812,7 +2812,7 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BN9" t="n">
         <v>4.6</v>
@@ -2842,23 +2842,23 @@
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA9" t="n">
         <v>10.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="H10" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="I10" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="J10" t="n">
         <v>4.3</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="G12" t="n">
         <v>7</v>
@@ -3430,7 +3430,7 @@
         <v>2.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
         <v>1.62</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         <v>2.4</v>
       </c>
       <c r="I14" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J14" t="n">
         <v>3.6</v>
@@ -3938,7 +3938,7 @@
         <v>2.12</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G15" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H15" t="n">
         <v>3.95</v>
@@ -4171,7 +4171,7 @@
         <v>4.7</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K15" t="n">
         <v>3.9</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -4413,16 +4413,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G16" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="H16" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J16" t="n">
         <v>4.4</v>
@@ -4446,7 +4446,7 @@
         <v>3.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="Q17" t="n">
         <v>1.71</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G18" t="n">
         <v>1.6</v>
@@ -4933,7 +4933,7 @@
         <v>7.2</v>
       </c>
       <c r="J18" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="K18" t="n">
         <v>5</v>
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q18" t="n">
         <v>1.7</v>
@@ -5029,7 +5029,7 @@
         <v>110</v>
       </c>
       <c r="AP18" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AQ18" t="n">
         <v>21</v>
@@ -5065,7 +5065,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BB18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC18" t="n">
         <v>13.5</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -6191,16 +6191,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G23" t="n">
         <v>2.5</v>
       </c>
       <c r="H23" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="I23" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="J23" t="n">
         <v>4.1</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
         <v>4.2</v>
       </c>
       <c r="H24" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="I24" t="n">
         <v>2.06</v>
@@ -6460,7 +6460,7 @@
         <v>3.8</v>
       </c>
       <c r="K24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -6475,10 +6475,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6711,7 @@
         <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="K25" t="n">
         <v>1000</v>
@@ -6732,7 +6732,7 @@
         <v>1.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -7715,22 +7715,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G29" t="n">
         <v>6.2</v>
       </c>
       <c r="H29" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="I29" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="J29" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K29" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -7745,10 +7745,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -8480,16 +8480,16 @@
         <v>2.62</v>
       </c>
       <c r="G32" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="H32" t="n">
         <v>2.76</v>
       </c>
       <c r="I32" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="J32" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="K32" t="n">
         <v>3.5</v>
@@ -8507,10 +8507,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -9239,19 +9239,19 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="G35" t="n">
-        <v>3.05</v>
+        <v>2.52</v>
       </c>
       <c r="H35" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="I35" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="J35" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="K35" t="n">
         <v>3.45</v>
@@ -9272,7 +9272,7 @@
         <v>1.54</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G36" t="n">
         <v>2.32</v>
@@ -9508,7 +9508,7 @@
         <v>3.2</v>
       </c>
       <c r="K36" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -9526,7 +9526,7 @@
         <v>1.67</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB36"/>
+  <dimension ref="A1:CB38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="O2" t="n">
         <v>1.32</v>
       </c>
       <c r="P2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q2" t="n">
         <v>1.32</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1138,19 +1138,19 @@
         <v>1.07</v>
       </c>
       <c r="O3" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="R3" t="n">
         <v>1.07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -1383,16 +1383,16 @@
         <v>4.7</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P4" t="n">
         <v>1.99</v>
@@ -1401,194 +1401,194 @@
         <v>1.83</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -1628,221 +1628,221 @@
         <v>2.12</v>
       </c>
       <c r="I5" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
         <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -1891,212 +1891,212 @@
         <v>3.95</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P6" t="n">
         <v>1.88</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -2130,13 +2130,13 @@
         <v>2.68</v>
       </c>
       <c r="G7" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="H7" t="n">
         <v>2.74</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
@@ -2145,212 +2145,212 @@
         <v>3.55</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -2381,230 +2381,230 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G8" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H8" t="n">
         <v>3.1</v>
       </c>
       <c r="I8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J8" t="n">
         <v>3.35</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.25</v>
       </c>
       <c r="K8" t="n">
         <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -2650,10 +2650,10 @@
         <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L9" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="M9" t="n">
         <v>1.09</v>
@@ -2665,7 +2665,7 @@
         <v>1.39</v>
       </c>
       <c r="P9" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="Q9" t="n">
         <v>2.14</v>
@@ -2680,7 +2680,7 @@
         <v>1.94</v>
       </c>
       <c r="U9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V9" t="n">
         <v>1.27</v>
@@ -2692,37 +2692,37 @@
         <v>14.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AA9" t="n">
         <v>130</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AE9" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AF9" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AJ9" t="n">
         <v>29</v>
@@ -2731,7 +2731,7 @@
         <v>29</v>
       </c>
       <c r="AL9" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AM9" t="n">
         <v>160</v>
@@ -2740,19 +2740,19 @@
         <v>22</v>
       </c>
       <c r="AO9" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AP9" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.6</v>
+        <v>3.85</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.8</v>
+        <v>4.1</v>
       </c>
       <c r="AT9" t="n">
         <v>7</v>
@@ -2761,10 +2761,10 @@
         <v>7</v>
       </c>
       <c r="AV9" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.4</v>
+        <v>4</v>
       </c>
       <c r="AX9" t="n">
         <v>10</v>
@@ -2773,28 +2773,28 @@
         <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.6</v>
+        <v>4</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.4</v>
+        <v>3.75</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.4</v>
+        <v>17.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="BE9" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="BF9" t="n">
         <v>13</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="BH9" t="n">
         <v>3.15</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
         <v>9.4</v>
       </c>
       <c r="H10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I10" t="n">
         <v>1.53</v>
@@ -2907,212 +2907,212 @@
         <v>4.7</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P10" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BP10" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BY10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="G12" t="n">
         <v>7</v>
@@ -3430,7 +3430,7 @@
         <v>2.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Chinese League 1</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,31 +3642,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Hangzhou Linping Wuyue</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Foshan Nanshi FC</t>
+          <t>Wenzhou Professional</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.87</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>2.08</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.62</v>
+        <v>1.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -3896,31 +3896,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Foshan Nanshi FC</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.8</v>
+        <v>1.87</v>
       </c>
       <c r="G14" t="n">
-        <v>3.15</v>
+        <v>2.08</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="I14" t="n">
-        <v>2.64</v>
+        <v>5.7</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.7</v>
+        <v>2.14</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -4150,49 +4150,49 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dalian Kun City FC</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="G15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>2.1</v>
       </c>
-      <c r="H15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="I15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.79</v>
-      </c>
       <c r="Q15" t="n">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Chinese Super League</t>
+          <t>Chinese League 1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,36 +4399,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zhejiang Greentown</t>
+          <t>Dalian Kun City FC</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="H16" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="I16" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J16" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="K16" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.15</v>
+        <v>1.81</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.38</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4636,14 +4636,14 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,36 +4653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>IFK Goteborg</t>
+          <t>Guizhou Zhucheng Athletic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Jiangxi Lushan</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.28</v>
+        <v>1.04</v>
       </c>
       <c r="G17" t="n">
-        <v>2.48</v>
+        <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="I17" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.18</v>
+        <v>1.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,42 +4907,42 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orgryte</t>
+          <t>Zhejiang Greentown</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="H18" t="n">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="I18" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="J18" t="n">
         <v>4.4</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.26</v>
+        <v>3.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4963,10 +4963,10 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -4975,112 +4975,112 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BH18" t="n">
         <v>0</v>
@@ -5144,14 +5144,14 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,43 +5161,43 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SC Grobina</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FK Tukums 2000</t>
+          <t>Orgryte</t>
         </is>
       </c>
       <c r="F19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>1.04</v>
       </c>
-      <c r="G19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.07</v>
+        <v>2.26</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5217,10 +5217,10 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -5229,112 +5229,112 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BH19" t="n">
         <v>0</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,36 +5415,36 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ypiranga RS</t>
+          <t>IFK Goteborg</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="G20" t="n">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="H20" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="J20" t="n">
-        <v>2.82</v>
+        <v>3.75</v>
       </c>
       <c r="K20" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -5459,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,17 +5669,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FK Aktobe</t>
+          <t>SC Grobina</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Zhetysu</t>
+          <t>FK Tukums 2000</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -5713,7 +5713,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Q21" t="n">
         <v>1.01</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5928,31 +5928,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FK Atyrau</t>
+          <t>Ypiranga RS</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FK Kaspyi Aktau</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="J22" t="n">
-        <v>1.02</v>
+        <v>2.98</v>
       </c>
       <c r="K22" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -5967,10 +5967,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.1</v>
+        <v>1.96</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6182,31 +6182,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Odds BK</t>
+          <t>FK Aktobe</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>FC Zhetysu</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="G23" t="n">
-        <v>2.5</v>
+        <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="I23" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>4.1</v>
+        <v>1.02</v>
       </c>
       <c r="K23" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -6221,10 +6221,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>3.25</v>
+        <v>1.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -6414,14 +6414,14 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6431,36 +6431,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>11:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>FK Atyrau</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>FK Kaspyi Aktau</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="G24" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>1.93</v>
+        <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>2.06</v>
+        <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>3.8</v>
+        <v>1.02</v>
       </c>
       <c r="K24" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -6475,10 +6475,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.18</v>
+        <v>1.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -6668,14 +6668,14 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6685,36 +6685,36 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FC Ordabasy</t>
+          <t>Odds BK</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FK Ulytau Zhezkazgan</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.09</v>
+        <v>2.24</v>
       </c>
       <c r="G25" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="H25" t="n">
-        <v>3.7</v>
+        <v>2.72</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="J25" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="K25" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -6729,10 +6729,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.12</v>
+        <v>3.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.02</v>
+        <v>1.36</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -6922,14 +6922,14 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6939,36 +6939,36 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FK Kaisar</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Irtysh Pavlodar</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="G26" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="H26" t="n">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>2.06</v>
       </c>
       <c r="J26" t="n">
-        <v>1.02</v>
+        <v>3.8</v>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -6983,10 +6983,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -7176,14 +7176,14 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7193,17 +7193,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>12:45:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Fk Siauliai</t>
+          <t>FK Kaisar</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>VMFD Zalgiris</t>
+          <t>Irtysh Pavlodar</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -7237,7 +7237,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Q27" t="n">
         <v>1.01</v>
@@ -7430,14 +7430,14 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7447,55 +7447,55 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tammeka Tartu</t>
+          <t>FC Ordabasy</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>FK Ulytau Zhezkazgan</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G28" t="n">
-        <v>1000</v>
+        <v>1.4</v>
       </c>
       <c r="H28" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="I28" t="n">
         <v>1000</v>
       </c>
       <c r="J28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Q28" t="n">
         <v>1.02</v>
       </c>
-      <c r="K28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.01</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -7684,14 +7684,14 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7701,36 +7701,36 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:45:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FC Supra du Quebec</t>
+          <t>Fk Siauliai</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Forge</t>
+          <t>VMFD Zalgiris</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="G29" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>1.7</v>
+        <v>1.04</v>
       </c>
       <c r="I29" t="n">
-        <v>1.95</v>
+        <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>3.05</v>
+        <v>1.02</v>
       </c>
       <c r="K29" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -7745,10 +7745,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>1.07</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7955,17 +7955,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Centro Atletico Fenix</t>
+          <t>Tammeka Tartu</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Huracan del Paso</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Q30" t="n">
         <v>1.01</v>
@@ -8192,14 +8192,14 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8209,36 +8209,36 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>FC Supra du Quebec</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Forge</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="G31" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="H31" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="I31" t="n">
-        <v>2.72</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="K31" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -8253,10 +8253,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.32</v>
+        <v>1.73</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -8463,36 +8463,36 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tacuarembo</t>
+          <t>Centro Atletico Fenix</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cerrito</t>
+          <t>Huracan del Paso</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="G32" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="H32" t="n">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="I32" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="J32" t="n">
-        <v>2.72</v>
+        <v>1.02</v>
       </c>
       <c r="K32" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -8507,10 +8507,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -8700,14 +8700,14 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8717,36 +8717,36 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.66</v>
+        <v>3.15</v>
       </c>
       <c r="G33" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="H33" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="I33" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="J33" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K33" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -8761,10 +8761,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.98</v>
+        <v>1.6</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.68</v>
+        <v>2.32</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -8954,14 +8954,14 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8971,251 +8971,251 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Delfin</t>
+          <t>Tacuarembo</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Cerrito</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.09</v>
+        <v>2.62</v>
       </c>
       <c r="G34" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="H34" t="n">
-        <v>1.09</v>
+        <v>2.76</v>
       </c>
       <c r="I34" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="J34" t="n">
-        <v>1.03</v>
+        <v>2.74</v>
       </c>
       <c r="K34" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.53</v>
+        <v>2.08</v>
       </c>
       <c r="R34" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9225,36 +9225,36 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Colon FC</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Uruguay Montevideo FC</t>
+          <t>HFX Wanderers</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="G35" t="n">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="H35" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J35" t="n">
         <v>3.15</v>
       </c>
-      <c r="I35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2.88</v>
-      </c>
       <c r="K35" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -9269,10 +9269,10 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.54</v>
+        <v>2.14</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.22</v>
+        <v>1.68</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -9462,261 +9462,769 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Delfin</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Emelec</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB36" t="inlineStr">
+        <is>
+          <t>2026-07-03 07:47:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Colon FC</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Uruguay Montevideo FC</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB37" t="inlineStr">
+        <is>
+          <t>2026-07-03 07:47:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Nautico PE</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Juventude</t>
         </is>
       </c>
-      <c r="F36" t="n">
+      <c r="F38" t="n">
         <v>2.18</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G38" t="n">
         <v>2.32</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H38" t="n">
         <v>3.85</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I38" t="n">
         <v>4.2</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J38" t="n">
         <v>3.2</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K38" t="n">
         <v>3.4</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
         <v>1.67</v>
       </c>
-      <c r="Q36" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB36" t="inlineStr">
-        <is>
-          <t>2026-07-03 05:30:36</t>
+      <c r="Q38" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB38" t="inlineStr">
+        <is>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB38"/>
+  <dimension ref="A1:CB39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -905,10 +905,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1159,10 +1159,10 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>South Korean K2 League</t>
+          <t>South Korean K1 League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1356,246 +1356,246 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seoul E-Land FC</t>
+          <t>Incheon Utd</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>1.95</v>
       </c>
       <c r="G4" t="n">
-        <v>7.2</v>
+        <v>2.04</v>
       </c>
       <c r="H4" t="n">
-        <v>1.57</v>
+        <v>4.4</v>
       </c>
       <c r="I4" t="n">
-        <v>1.69</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="P4" t="n">
-        <v>1.99</v>
+        <v>1.77</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="R4" t="n">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>1.83</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V4" t="n">
-        <v>2.44</v>
+        <v>1.26</v>
       </c>
       <c r="W4" t="n">
-        <v>1.16</v>
+        <v>1.96</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="BJ4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
         <v>15</v>
       </c>
-      <c r="BK4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>22</v>
-      </c>
       <c r="BN4" t="n">
-        <v>13.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>22</v>
+        <v>7.6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BU4" t="n">
-        <v>2.92</v>
+        <v>5.8</v>
       </c>
       <c r="BV4" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="BX4" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ4" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>South Korean K2 League</t>
+          <t>South Korean K1 League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1610,246 +1610,246 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimcheon Sangmu</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan IPark</t>
+          <t>Jeju Utd</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.3</v>
+        <v>2.48</v>
       </c>
       <c r="G5" t="n">
-        <v>3.85</v>
+        <v>2.62</v>
       </c>
       <c r="H5" t="n">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="I5" t="n">
-        <v>2.34</v>
+        <v>3.35</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S5" t="n">
         <v>4</v>
       </c>
-      <c r="L5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.79</v>
-      </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U5" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V5" t="n">
-        <v>1.74</v>
+        <v>1.43</v>
       </c>
       <c r="W5" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>9.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BP5" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BQ5" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.55</v>
+        <v>5.5</v>
       </c>
       <c r="BV5" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="BY5" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>South Korean K2 League</t>
+          <t>South Korean K1 League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1864,239 +1864,239 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gwangju FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chungnam Asan</t>
+          <t>Ulsan Hyundai Horang-i</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.86</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>1.93</v>
+        <v>9.6</v>
       </c>
       <c r="H6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K6" t="n">
         <v>4.7</v>
       </c>
-      <c r="I6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X6" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>90</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>370</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>180</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>280</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>12</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>85</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT6" t="n">
         <v>3.95</v>
       </c>
-      <c r="L6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="X6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>85</v>
-      </c>
-      <c r="BF6" t="n">
+      <c r="BU6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BV6" t="n">
         <v>10</v>
       </c>
-      <c r="BG6" t="n">
-        <v>60</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK6" t="n">
+      <c r="BW6" t="n">
         <v>7</v>
       </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>17</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>38</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>22</v>
-      </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY6" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="CA6" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -2118,246 +2118,246 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Chungnam Asan</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.68</v>
+        <v>1.82</v>
       </c>
       <c r="G7" t="n">
-        <v>3.25</v>
+        <v>1.93</v>
       </c>
       <c r="H7" t="n">
-        <v>2.74</v>
+        <v>4.7</v>
       </c>
       <c r="I7" t="n">
-        <v>3.35</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="K7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N7" t="n">
         <v>3.55</v>
       </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.68</v>
-      </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="R7" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="T7" t="n">
         <v>1.86</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="W7" t="n">
-        <v>1.44</v>
+        <v>2.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.42</v>
+        <v>3.05</v>
       </c>
       <c r="BJ7" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BP7" t="n">
-        <v>32</v>
+        <v>13.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>14.5</v>
+        <v>8.6</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS7" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.95</v>
+        <v>5.6</v>
       </c>
       <c r="BV7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY7" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="CA7" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>South Korean K1 League</t>
+          <t>South Korean K2 League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2372,246 +2372,246 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Gimcheon Sangmu</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeju Utd</t>
+          <t>Busan IPark</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.48</v>
+        <v>3.3</v>
       </c>
       <c r="G8" t="n">
-        <v>2.62</v>
+        <v>3.85</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1</v>
+        <v>2.12</v>
       </c>
       <c r="I8" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="J8" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.16</v>
+        <v>1.79</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="U8" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="W8" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF8" t="n">
-        <v>18.5</v>
+        <v>32</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ8" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AK8" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.3</v>
+        <v>13</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.3</v>
+        <v>8.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.3</v>
+        <v>11</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.3</v>
+        <v>21</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.3</v>
+        <v>11.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.11</v>
+        <v>6.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.3</v>
+        <v>8.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.3</v>
+        <v>17</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.21</v>
+        <v>20</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.3</v>
+        <v>11.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.3</v>
+        <v>12.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.3</v>
+        <v>11</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BJ8" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>22</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="BO8" t="n">
         <v>4.3</v>
       </c>
       <c r="BP8" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="BR8" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>22</v>
+        <v>8.4</v>
       </c>
       <c r="BT8" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="BV8" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="BW8" t="n">
-        <v>20</v>
+        <v>6.4</v>
       </c>
       <c r="BX8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>22</v>
+        <v>7.8</v>
       </c>
       <c r="BZ8" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>21</v>
+        <v>7.2</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>South Korean K1 League</t>
+          <t>South Korean K2 League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,246 +2626,246 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Incheon Utd</t>
+          <t>Seoul E-Land FC</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.96</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>2.06</v>
+        <v>7.2</v>
       </c>
       <c r="H9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X9" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>220</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>140</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>60</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>85</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT9" t="n">
         <v>4.3</v>
       </c>
-      <c r="I9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="BU9" t="n">
         <v>3.65</v>
       </c>
-      <c r="L9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="X9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>14</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BW9" t="n">
-        <v>11</v>
+        <v>6.4</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY9" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>32</v>
+        <v>19.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>South Korean K1 League</t>
+          <t>South Korean K2 League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,246 +2880,246 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Gwangju FC</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulsan Hyundai Horang-i</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8.199999999999999</v>
+        <v>2.68</v>
       </c>
       <c r="G10" t="n">
-        <v>9.4</v>
+        <v>3.15</v>
       </c>
       <c r="H10" t="n">
-        <v>1.49</v>
+        <v>2.74</v>
       </c>
       <c r="I10" t="n">
-        <v>1.53</v>
+        <v>3.2</v>
       </c>
       <c r="J10" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="M10" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="P10" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.98</v>
+        <v>2.22</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="T10" t="n">
-        <v>2.16</v>
+        <v>1.88</v>
       </c>
       <c r="U10" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="V10" t="n">
-        <v>2.88</v>
+        <v>1.45</v>
       </c>
       <c r="W10" t="n">
-        <v>1.12</v>
+        <v>1.48</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y10" t="n">
         <v>10.5</v>
       </c>
       <c r="Z10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT10" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AA10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AG10" t="n">
+      <c r="AU10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>44</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ10" t="n">
         <v>40</v>
       </c>
-      <c r="AH10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>22</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>85</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>22</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>100</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>22</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>30</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>21</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>20</v>
-      </c>
       <c r="CA10" t="n">
-        <v>16</v>
+        <v>8.6</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Chinese League 2</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,246 +3134,246 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Taian Tiankuang</t>
+          <t>Qingdao Hainiu</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Changchun Xidu</t>
+          <t>Chengdu Rongcheng</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>1.69</v>
       </c>
       <c r="J11" t="n">
-        <v>1.02</v>
+        <v>4.3</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P11" t="n">
-        <v>1.07</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BH11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK11" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BO11" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BP11" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BV11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BX11" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BY11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Chinese Super League</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,239 +3388,239 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu</t>
+          <t>Dalian Yingbo II</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chengdu Rongcheng</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.59</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>1.69</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>4.3</v>
+        <v>1.02</v>
       </c>
       <c r="K12" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="P12" t="n">
-        <v>2.36</v>
+        <v>1.07</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -3637,17 +3637,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hangzhou Linping Wuyue</t>
+          <t>Taian Tiankuang</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wenzhou Professional</t>
+          <t>Changchun Xidu</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -3663,218 +3663,218 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P13" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -3908,227 +3908,227 @@
         <v>1.87</v>
       </c>
       <c r="G14" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I14" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K14" t="n">
         <v>3.8</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P14" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q14" t="n">
         <v>2.14</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -4177,16 +4177,16 @@
         <v>4.1</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P15" t="n">
         <v>2.1</v>
@@ -4195,194 +4195,194 @@
         <v>1.72</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP15" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT15" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV15" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -4431,16 +4431,16 @@
         <v>3.95</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P16" t="n">
         <v>1.81</v>
@@ -4449,194 +4449,194 @@
         <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BP16" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BY16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -4679,225 +4679,225 @@
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Chinese Super League</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,251 +4907,251 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Hangzhou Linping Wuyue</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zhejiang Greentown</t>
+          <t>Wenzhou Professional</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="K18" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P18" t="n">
-        <v>3.15</v>
+        <v>1.07</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.38</v>
+        <v>1.02</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,244 +5161,244 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Orgryte</t>
+          <t>Zhejiang Greentown</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="G19" t="n">
-        <v>1.59</v>
+        <v>1.89</v>
       </c>
       <c r="H19" t="n">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="I19" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="J19" t="n">
         <v>4.5</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P19" t="n">
-        <v>2.26</v>
+        <v>3.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.69</v>
+        <v>1.38</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="T19" t="n">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="U19" t="n">
-        <v>2.06</v>
+        <v>2.82</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X19" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>48</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AO19" t="n">
         <v>24</v>
       </c>
-      <c r="Y19" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z19" t="n">
+      <c r="AP19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>17</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL19" t="n">
         <v>60</v>
       </c>
-      <c r="AA19" t="n">
-        <v>210</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC19" t="n">
+      <c r="BM19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>18</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>29</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ19" t="n">
         <v>11</v>
       </c>
-      <c r="AD19" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>42</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ19" t="n">
-        <v>0</v>
-      </c>
       <c r="CA19" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -5420,246 +5420,246 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>IFK Goteborg</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Orgryte</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.32</v>
+        <v>1.52</v>
       </c>
       <c r="G20" t="n">
-        <v>2.48</v>
+        <v>1.58</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>6.2</v>
       </c>
       <c r="I20" t="n">
-        <v>3.35</v>
+        <v>7.2</v>
       </c>
       <c r="J20" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P20" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BO20" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BP20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BS20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BT20" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BU20" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BV20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CA20" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,251 +5669,251 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SC Grobina</t>
+          <t>IFK Goteborg</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FK Tukums 2000</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>2.42</v>
       </c>
       <c r="H21" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="J21" t="n">
-        <v>1.02</v>
+        <v>3.7</v>
       </c>
       <c r="K21" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P21" t="n">
-        <v>1.07</v>
+        <v>2.22</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BK21" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BL21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN21" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BO21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BP21" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BQ21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BR21" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BS21" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BT21" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BV21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BW21" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BX21" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BY21" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BZ21" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="CA21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,36 +5923,36 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ypiranga RS</t>
+          <t>SC Grobina</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>FK Tukums 2000</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="G22" t="n">
-        <v>2.64</v>
+        <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>2.92</v>
+        <v>1.04</v>
       </c>
       <c r="I22" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>2.98</v>
+        <v>1.02</v>
       </c>
       <c r="K22" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -5967,10 +5967,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.96</v>
+        <v>1.07</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6182,31 +6182,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FK Aktobe</t>
+          <t>Ypiranga RS</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FC Zhetysu</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="H23" t="n">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="J23" t="n">
-        <v>1.02</v>
+        <v>3.2</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -6221,10 +6221,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FK Atyrau</t>
+          <t>FK Aktobe</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FK Kaspyi Aktau</t>
+          <t>FC Zhetysu</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -6668,14 +6668,14 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6690,31 +6690,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Odds BK</t>
+          <t>FK Atyrau</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>FK Kaspyi Aktau</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="G25" t="n">
-        <v>2.5</v>
+        <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="I25" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>4.1</v>
+        <v>1.02</v>
       </c>
       <c r="K25" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -6729,10 +6729,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3.25</v>
+        <v>1.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -6922,14 +6922,14 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6939,36 +6939,36 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>11:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Odds BK</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.9</v>
+        <v>2.24</v>
       </c>
       <c r="G26" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="H26" t="n">
-        <v>1.93</v>
+        <v>2.72</v>
       </c>
       <c r="I26" t="n">
-        <v>2.06</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="K26" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -6983,10 +6983,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.18</v>
+        <v>3.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.74</v>
+        <v>1.36</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -7176,14 +7176,14 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7193,36 +7193,36 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FK Kaisar</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Irtysh Pavlodar</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="G27" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="H27" t="n">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="I27" t="n">
-        <v>1000</v>
+        <v>2.06</v>
       </c>
       <c r="J27" t="n">
-        <v>1.02</v>
+        <v>3.8</v>
       </c>
       <c r="K27" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -7237,10 +7237,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -7684,14 +7684,14 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7701,17 +7701,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>12:45:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Fk Siauliai</t>
+          <t>FK Kaisar</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>VMFD Zalgiris</t>
+          <t>Irtysh Pavlodar</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -7745,7 +7745,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Q29" t="n">
         <v>1.01</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7955,33 +7955,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:45:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Tammeka Tartu</t>
+          <t>Fk Siauliai</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>VMFD Zalgiris</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1.04</v>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="H30" t="n">
-        <v>1.04</v>
+        <v>1.51</v>
       </c>
       <c r="I30" t="n">
-        <v>1000</v>
+        <v>1.62</v>
       </c>
       <c r="J30" t="n">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="K30" t="n">
         <v>1000</v>
@@ -7999,10 +7999,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.07</v>
+        <v>2.36</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -8192,14 +8192,14 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8209,36 +8209,36 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FC Supra du Quebec</t>
+          <t>Tammeka Tartu</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Forge</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="G31" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="H31" t="n">
-        <v>1.7</v>
+        <v>1.04</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>2.94</v>
+        <v>1.02</v>
       </c>
       <c r="K31" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -8253,10 +8253,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>1.07</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -8446,14 +8446,14 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8468,31 +8468,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Centro Atletico Fenix</t>
+          <t>FC Supra du Quebec</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Huracan del Paso</t>
+          <t>Forge</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="G32" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="H32" t="n">
-        <v>1.04</v>
+        <v>1.7</v>
       </c>
       <c r="I32" t="n">
-        <v>1000</v>
+        <v>1.95</v>
       </c>
       <c r="J32" t="n">
-        <v>1.02</v>
+        <v>3.05</v>
       </c>
       <c r="K32" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -8507,10 +8507,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -8700,14 +8700,14 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8717,36 +8717,36 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>Centro Atletico Fenix</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Huracan del Paso</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="G33" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="H33" t="n">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="I33" t="n">
-        <v>2.72</v>
+        <v>1000</v>
       </c>
       <c r="J33" t="n">
-        <v>3.05</v>
+        <v>1.02</v>
       </c>
       <c r="K33" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -8761,10 +8761,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -8954,14 +8954,14 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8971,36 +8971,36 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tacuarembo</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cerrito</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="G34" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="J34" t="n">
         <v>3.05</v>
       </c>
-      <c r="H34" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="I34" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2.74</v>
-      </c>
       <c r="K34" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -9015,10 +9015,10 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -9208,14 +9208,14 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9225,36 +9225,36 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Tacuarembo</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>Cerrito</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="G35" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="H35" t="n">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="I35" t="n">
-        <v>2.76</v>
+        <v>3.25</v>
       </c>
       <c r="J35" t="n">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="K35" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -9269,10 +9269,10 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.14</v>
+        <v>1.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.68</v>
+        <v>2.08</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -9462,14 +9462,14 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9484,246 +9484,246 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Delfin</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>HFX Wanderers</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="G36" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="H36" t="n">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="I36" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="J36" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="K36" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.34</v>
+        <v>1.98</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="R36" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -9733,251 +9733,251 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Colon FC</t>
+          <t>Delfin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Uruguay Montevideo FC</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="G37" t="n">
-        <v>2.52</v>
+        <v>1000</v>
       </c>
       <c r="H37" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="I37" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="J37" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="K37" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P37" t="n">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.28</v>
+        <v>1.53</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9987,244 +9987,498 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Colon FC</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Uruguay Montevideo FC</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G38" t="n">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="H38" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="I38" t="n">
         <v>4.2</v>
       </c>
       <c r="J38" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB38" t="inlineStr">
+        <is>
+          <t>2026-07-03 10:04:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Nautico PE</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J39" t="n">
         <v>3.2</v>
       </c>
-      <c r="K38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
+      <c r="K39" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
         <v>1.67</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="Q39" t="n">
         <v>2.06</v>
       </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB38" t="inlineStr">
-        <is>
-          <t>2026-07-03 07:47:13</t>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB39" t="inlineStr">
+        <is>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H4" t="n">
         <v>4.4</v>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
         <v>3.75</v>
@@ -1395,13 +1395,13 @@
         <v>1.39</v>
       </c>
       <c r="P4" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
         <v>2.14</v>
       </c>
       <c r="R4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1410,7 +1410,7 @@
         <v>1.94</v>
       </c>
       <c r="U4" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V4" t="n">
         <v>1.26</v>
@@ -1422,67 +1422,67 @@
         <v>14.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AA4" t="n">
         <v>140</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK4" t="n">
         <v>23</v>
       </c>
-      <c r="AE4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>28</v>
-      </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AM4" t="n">
         <v>160</v>
       </c>
       <c r="AN4" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AO4" t="n">
         <v>110</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT4" t="n">
         <v>7</v>
@@ -1491,40 +1491,40 @@
         <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX4" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15.5</v>
+        <v>7</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.2</v>
+        <v>9.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.1</v>
+        <v>36</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="BF4" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.1</v>
+        <v>9.6</v>
       </c>
       <c r="BH4" t="n">
         <v>3.15</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -1625,10 +1625,10 @@
         <v>2.62</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J5" t="n">
         <v>3.35</v>
@@ -1640,7 +1640,7 @@
         <v>1.46</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
         <v>3.35</v>
@@ -1670,7 +1670,7 @@
         <v>1.43</v>
       </c>
       <c r="W5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X5" t="n">
         <v>14.5</v>
@@ -1685,7 +1685,7 @@
         <v>70</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AC5" t="n">
         <v>7.6</v>
@@ -1712,7 +1712,7 @@
         <v>44</v>
       </c>
       <c r="AK5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL5" t="n">
         <v>55</v>
@@ -1733,10 +1733,10 @@
         <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>17</v>
+        <v>4.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="AT5" t="n">
         <v>8.6</v>
@@ -1745,104 +1745,104 @@
         <v>6.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AW5" t="n">
-        <v>32</v>
+        <v>4.9</v>
       </c>
       <c r="AX5" t="n">
-        <v>11.5</v>
+        <v>4.2</v>
       </c>
       <c r="AY5" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16</v>
+        <v>4.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BE5" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BF5" t="n">
         <v>20</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="BH5" t="n">
         <v>3.15</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ5" t="n">
         <v>10</v>
       </c>
       <c r="BK5" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BN5" t="n">
         <v>5.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BP5" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BT5" t="n">
         <v>6.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BV5" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1876,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="H6" t="n">
         <v>1.47</v>
       </c>
       <c r="I6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="J6" t="n">
         <v>4.3</v>
       </c>
       <c r="K6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.39</v>
@@ -1897,10 +1897,10 @@
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P6" t="n">
         <v>1.91</v>
@@ -1909,28 +1909,28 @@
         <v>1.96</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S6" t="n">
         <v>3.55</v>
       </c>
       <c r="T6" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
         <v>1.79</v>
       </c>
       <c r="V6" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
         <v>16</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z6" t="n">
         <v>8.199999999999999</v>
@@ -1948,16 +1948,16 @@
         <v>10.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AG6" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AH6" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AI6" t="n">
         <v>50</v>
@@ -1990,13 +1990,13 @@
         <v>7.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT6" t="n">
         <v>20</v>
       </c>
       <c r="AU6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV6" t="n">
         <v>9</v>
@@ -2005,31 +2005,31 @@
         <v>15</v>
       </c>
       <c r="AX6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC6" t="n">
         <v>9</v>
       </c>
-      <c r="AY6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BD6" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BE6" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BF6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG6" t="n">
         <v>7.8</v>
@@ -2038,65 +2038,65 @@
         <v>3.55</v>
       </c>
       <c r="BI6" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="BJ6" t="n">
         <v>12.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN6" t="n">
         <v>12</v>
       </c>
       <c r="BO6" t="n">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="BP6" t="n">
         <v>85</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BT6" t="n">
         <v>3.95</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="BV6" t="n">
         <v>10</v>
       </c>
       <c r="BW6" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="BX6" t="n">
         <v>30</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BZ6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="G7" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="H7" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="I7" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L7" t="n">
         <v>1.36</v>
@@ -2157,10 +2157,10 @@
         <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R7" t="n">
         <v>1.33</v>
@@ -2169,188 +2169,188 @@
         <v>3.55</v>
       </c>
       <c r="T7" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V7" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="X7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN7" t="n">
         <v>16.5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>16</v>
       </c>
       <c r="AO7" t="n">
         <v>95</v>
       </c>
       <c r="AP7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.7</v>
+        <v>23</v>
       </c>
       <c r="AS7" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>14.5</v>
       </c>
-      <c r="AW7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY7" t="n">
+      <c r="BA7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD7" t="n">
         <v>8</v>
       </c>
-      <c r="AZ7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BE7" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="BH7" t="n">
         <v>3.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="BJ7" t="n">
         <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="BP7" t="n">
         <v>13.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR7" t="n">
         <v>29</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BT7" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BZ7" t="n">
         <v>25</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G8" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="H8" t="n">
         <v>2.12</v>
@@ -2393,10 +2393,10 @@
         <v>2.3</v>
       </c>
       <c r="J8" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L8" t="n">
         <v>1.32</v>
@@ -2414,7 +2414,7 @@
         <v>2.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R8" t="n">
         <v>1.4</v>
@@ -2546,7 +2546,7 @@
         <v>3.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ8" t="n">
         <v>9.6</v>
@@ -2564,7 +2564,7 @@
         <v>7.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>1.69</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="K9" t="n">
         <v>4.7</v>
@@ -2662,7 +2662,7 @@
         <v>3.85</v>
       </c>
       <c r="O9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P9" t="n">
         <v>1.99</v>
@@ -2692,13 +2692,13 @@
         <v>20</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Z9" t="n">
         <v>12</v>
       </c>
       <c r="AA9" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AB9" t="n">
         <v>26</v>
@@ -2710,7 +2710,7 @@
         <v>12</v>
       </c>
       <c r="AE9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AF9" t="n">
         <v>65</v>
@@ -2749,10 +2749,10 @@
         <v>6.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT9" t="n">
         <v>15.5</v>
@@ -2767,7 +2767,7 @@
         <v>12.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY9" t="n">
         <v>17.5</v>
@@ -2776,22 +2776,22 @@
         <v>15.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG9" t="n">
         <v>6.8</v>
@@ -2806,31 +2806,31 @@
         <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN9" t="n">
         <v>10</v>
       </c>
       <c r="BO9" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BP9" t="n">
         <v>60</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR9" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT9" t="n">
         <v>4.3</v>
@@ -2842,23 +2842,23 @@
         <v>11</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BX9" t="n">
         <v>26</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ9" t="n">
         <v>19.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G10" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="H10" t="n">
         <v>2.74</v>
       </c>
       <c r="I10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
@@ -2907,10 +2907,10 @@
         <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="M10" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -2922,7 +2922,7 @@
         <v>1.66</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
         <v>1.24</v>
@@ -2946,7 +2946,7 @@
         <v>12.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z10" t="n">
         <v>22</v>
@@ -2961,7 +2961,7 @@
         <v>8.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AE10" t="n">
         <v>44</v>
@@ -2985,7 +2985,7 @@
         <v>42</v>
       </c>
       <c r="AL10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM10" t="n">
         <v>150</v>
@@ -3000,25 +3000,25 @@
         <v>8.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR10" t="n">
         <v>14.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AU10" t="n">
         <v>5.7</v>
       </c>
       <c r="AV10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX10" t="n">
         <v>13.5</v>
@@ -3030,31 +3030,31 @@
         <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH10" t="n">
         <v>3.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
@@ -3072,7 +3072,7 @@
         <v>5.9</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BP10" t="n">
         <v>25</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>5.5</v>
       </c>
       <c r="G11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H11" t="n">
         <v>1.59</v>
@@ -3161,7 +3161,7 @@
         <v>4.9</v>
       </c>
       <c r="L11" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
@@ -3179,7 +3179,7 @@
         <v>1.63</v>
       </c>
       <c r="R11" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S11" t="n">
         <v>2.6</v>
@@ -3194,7 +3194,7 @@
         <v>2.44</v>
       </c>
       <c r="W11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X11" t="n">
         <v>27</v>
@@ -3203,7 +3203,7 @@
         <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AA11" t="n">
         <v>16.5</v>
@@ -3212,13 +3212,13 @@
         <v>29</v>
       </c>
       <c r="AC11" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AD11" t="n">
         <v>10.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF11" t="n">
         <v>60</v>
@@ -3230,16 +3230,16 @@
         <v>23</v>
       </c>
       <c r="AI11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ11" t="n">
         <v>160</v>
       </c>
       <c r="AK11" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AL11" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM11" t="n">
         <v>100</v>
@@ -3248,22 +3248,22 @@
         <v>80</v>
       </c>
       <c r="AO11" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AP11" t="n">
-        <v>17</v>
+        <v>6.2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AT11" t="n">
-        <v>18</v>
+        <v>6.2</v>
       </c>
       <c r="AU11" t="n">
         <v>9.199999999999999</v>
@@ -3272,49 +3272,49 @@
         <v>9</v>
       </c>
       <c r="AW11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB11" t="n">
         <v>8</v>
       </c>
-      <c r="AY11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BC11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BD11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG11" t="n">
         <v>5.7</v>
       </c>
       <c r="BH11" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3323,50 +3323,50 @@
         <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
         <v>1.01</v>
       </c>
       <c r="BR11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
         <v>1.01</v>
       </c>
       <c r="BT11" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BV11" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
         <v>1.02</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3421,10 +3421,10 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="O12" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="P12" t="n">
         <v>1.07</v>
@@ -3436,7 +3436,7 @@
         <v>1.07</v>
       </c>
       <c r="S12" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -3505,52 +3505,52 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
         <v>1.01</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -3675,19 +3675,19 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="O13" t="n">
         <v>1.34</v>
       </c>
       <c r="P13" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Q13" t="n">
         <v>1.34</v>
       </c>
       <c r="R13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S13" t="n">
         <v>1.34</v>
@@ -3699,10 +3699,10 @@
         <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -3908,49 +3908,49 @@
         <v>1.87</v>
       </c>
       <c r="G14" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
         <v>5.6</v>
       </c>
       <c r="J14" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="K14" t="n">
         <v>3.8</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="O14" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="R14" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="V14" t="n">
         <v>1.21</v>
@@ -4013,52 +4013,52 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
         <v>1.01</v>
@@ -4067,10 +4067,10 @@
         <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
@@ -4085,7 +4085,7 @@
         <v>1.01</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="G15" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="I15" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="J15" t="n">
         <v>3.6</v>
@@ -4177,55 +4177,55 @@
         <v>4.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U15" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="V15" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W15" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X15" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z15" t="n">
         <v>23</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>22</v>
       </c>
       <c r="AA15" t="n">
         <v>42</v>
       </c>
       <c r="AB15" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AC15" t="n">
         <v>11</v>
@@ -4234,7 +4234,7 @@
         <v>14.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF15" t="n">
         <v>27</v>
@@ -4246,143 +4246,143 @@
         <v>19</v>
       </c>
       <c r="AI15" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ15" t="n">
         <v>55</v>
       </c>
       <c r="AK15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL15" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM15" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO15" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BH15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BJ15" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BN15" t="n">
         <v>6.6</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP15" t="n">
         <v>22</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BR15" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BT15" t="n">
         <v>5.9</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BV15" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BZ15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -4413,52 +4413,52 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G16" t="n">
         <v>2.02</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I16" t="n">
         <v>4.7</v>
       </c>
       <c r="J16" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K16" t="n">
         <v>3.95</v>
       </c>
       <c r="L16" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="M16" t="n">
         <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="O16" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P16" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R16" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S16" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T16" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="U16" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="V16" t="n">
         <v>1.27</v>
@@ -4467,10 +4467,10 @@
         <v>1.98</v>
       </c>
       <c r="X16" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y16" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z16" t="n">
         <v>42</v>
@@ -4479,7 +4479,7 @@
         <v>130</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC16" t="n">
         <v>8.6</v>
@@ -4491,7 +4491,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG16" t="n">
         <v>12</v>
@@ -4500,7 +4500,7 @@
         <v>23</v>
       </c>
       <c r="AI16" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AJ16" t="n">
         <v>26</v>
@@ -4521,58 +4521,58 @@
         <v>95</v>
       </c>
       <c r="AP16" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.2</v>
+        <v>3.55</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.2</v>
+        <v>3.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>14.5</v>
+        <v>4.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AX16" t="n">
-        <v>9.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="AY16" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15</v>
+        <v>4.9</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>16.5</v>
+        <v>5</v>
       </c>
       <c r="BC16" t="n">
-        <v>16</v>
+        <v>4.9</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BF16" t="n">
-        <v>11.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BH16" t="n">
         <v>3.35</v>
@@ -4584,13 +4584,13 @@
         <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN16" t="n">
         <v>4.7</v>
@@ -4602,41 +4602,41 @@
         <v>14.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR16" t="n">
         <v>32</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT16" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV16" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX16" t="n">
         <v>55</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -4691,34 +4691,34 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="O17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="R17" t="n">
         <v>1.07</v>
       </c>
       <c r="S17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V17" t="n">
         <v>1.02</v>
       </c>
-      <c r="T17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4775,52 +4775,52 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
         <v>1.01</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="O18" t="n">
         <v>1.01</v>
@@ -4954,13 +4954,13 @@
         <v>1.07</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.02</v>
+        <v>1.51</v>
       </c>
       <c r="R18" t="n">
         <v>1.07</v>
       </c>
       <c r="S18" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="T18" t="n">
         <v>1.01</v>
@@ -4969,10 +4969,10 @@
         <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -5029,52 +5029,52 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
         <v>1.01</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -5178,19 +5178,19 @@
         <v>1.74</v>
       </c>
       <c r="G19" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="H19" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="I19" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J19" t="n">
         <v>4.5</v>
       </c>
       <c r="K19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L19" t="n">
         <v>1.19</v>
@@ -5226,7 +5226,7 @@
         <v>1.28</v>
       </c>
       <c r="W19" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X19" t="n">
         <v>40</v>
@@ -5247,7 +5247,7 @@
         <v>13</v>
       </c>
       <c r="AD19" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE19" t="n">
         <v>42</v>
@@ -5283,7 +5283,7 @@
         <v>24</v>
       </c>
       <c r="AP19" t="n">
-        <v>28</v>
+        <v>8.4</v>
       </c>
       <c r="AQ19" t="n">
         <v>7.8</v>
@@ -5292,7 +5292,7 @@
         <v>34</v>
       </c>
       <c r="AS19" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT19" t="n">
         <v>15.5</v>
@@ -5304,7 +5304,7 @@
         <v>16</v>
       </c>
       <c r="AW19" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AX19" t="n">
         <v>14.5</v>
@@ -5313,10 +5313,10 @@
         <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BA19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BB19" t="n">
         <v>18.5</v>
@@ -5325,16 +5325,16 @@
         <v>14</v>
       </c>
       <c r="BD19" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BE19" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BF19" t="n">
         <v>4.7</v>
       </c>
       <c r="BG19" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH19" t="n">
         <v>5.6</v>
@@ -5346,59 +5346,59 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK19" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BL19" t="n">
         <v>60</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN19" t="n">
         <v>5.4</v>
       </c>
       <c r="BO19" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BP19" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="BR19" t="n">
         <v>18</v>
       </c>
       <c r="BS19" t="n">
-        <v>11.5</v>
+        <v>6.8</v>
       </c>
       <c r="BT19" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU19" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BV19" t="n">
         <v>28</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BX19" t="n">
         <v>29</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ19" t="n">
         <v>11</v>
       </c>
       <c r="CA19" t="n">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>1.52</v>
       </c>
       <c r="G20" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H20" t="n">
         <v>6.2</v>
@@ -5441,13 +5441,13 @@
         <v>7.2</v>
       </c>
       <c r="J20" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
@@ -5456,7 +5456,7 @@
         <v>4.6</v>
       </c>
       <c r="O20" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P20" t="n">
         <v>2.26</v>
@@ -5468,7 +5468,7 @@
         <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T20" t="n">
         <v>1.83</v>
@@ -5477,13 +5477,13 @@
         <v>2.06</v>
       </c>
       <c r="V20" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W20" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="X20" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y20" t="n">
         <v>25</v>
@@ -5498,7 +5498,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD20" t="n">
         <v>25</v>
@@ -5519,7 +5519,7 @@
         <v>100</v>
       </c>
       <c r="AJ20" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK20" t="n">
         <v>16</v>
@@ -5543,22 +5543,22 @@
         <v>21</v>
       </c>
       <c r="AR20" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AS20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV20" t="n">
         <v>21</v>
       </c>
       <c r="AW20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX20" t="n">
         <v>8.800000000000001</v>
@@ -5570,7 +5570,7 @@
         <v>19</v>
       </c>
       <c r="BA20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB20" t="n">
         <v>12.5</v>
@@ -5582,31 +5582,31 @@
         <v>23</v>
       </c>
       <c r="BE20" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG20" t="n">
         <v>10.5</v>
       </c>
-      <c r="BF20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>10</v>
-      </c>
       <c r="BH20" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.84</v>
+        <v>2</v>
       </c>
       <c r="BJ20" t="n">
         <v>14.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>6.6</v>
+        <v>1.76</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="BN20" t="n">
         <v>5.6</v>
@@ -5618,41 +5618,41 @@
         <v>13</v>
       </c>
       <c r="BQ20" t="n">
-        <v>6.2</v>
+        <v>1.74</v>
       </c>
       <c r="BR20" t="n">
         <v>30</v>
       </c>
       <c r="BS20" t="n">
-        <v>14</v>
+        <v>1.88</v>
       </c>
       <c r="BT20" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BU20" t="n">
-        <v>6.6</v>
+        <v>1.76</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>21</v>
+        <v>1.95</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>21</v>
+        <v>1.95</v>
       </c>
       <c r="BZ20" t="n">
         <v>21</v>
       </c>
       <c r="CA20" t="n">
-        <v>9.6</v>
+        <v>1.83</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -5683,22 +5683,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="G21" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="I21" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="J21" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -5716,7 +5716,7 @@
         <v>2.22</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R21" t="n">
         <v>1.5</v>
@@ -5725,19 +5725,19 @@
         <v>2.78</v>
       </c>
       <c r="T21" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U21" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V21" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W21" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="X21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y21" t="n">
         <v>16.5</v>
@@ -5752,7 +5752,7 @@
         <v>13.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AD21" t="n">
         <v>14.5</v>
@@ -5788,10 +5788,10 @@
         <v>15.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AP21" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AQ21" t="n">
         <v>13</v>
@@ -5800,7 +5800,7 @@
         <v>20</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT21" t="n">
         <v>11</v>
@@ -5812,7 +5812,7 @@
         <v>11.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AX21" t="n">
         <v>14.5</v>
@@ -5824,19 +5824,19 @@
         <v>13</v>
       </c>
       <c r="BA21" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BC21" t="n">
         <v>19.5</v>
       </c>
       <c r="BD21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE21" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>7.6</v>
       </c>
       <c r="BF21" t="n">
         <v>12.5</v>
@@ -5848,65 +5848,65 @@
         <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.82</v>
+        <v>1.96</v>
       </c>
       <c r="BJ21" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.8</v>
+        <v>1.7</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>21</v>
+        <v>1.96</v>
       </c>
       <c r="BN21" t="n">
         <v>7.4</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BP21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ21" t="n">
-        <v>10</v>
+        <v>1.8</v>
       </c>
       <c r="BR21" t="n">
         <v>36</v>
       </c>
       <c r="BS21" t="n">
-        <v>16.5</v>
+        <v>1.87</v>
       </c>
       <c r="BT21" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW21" t="n">
-        <v>14</v>
+        <v>1.85</v>
       </c>
       <c r="BX21" t="n">
         <v>44</v>
       </c>
       <c r="BY21" t="n">
-        <v>19</v>
+        <v>1.88</v>
       </c>
       <c r="BZ21" t="n">
         <v>28</v>
       </c>
       <c r="CA21" t="n">
-        <v>12</v>
+        <v>1.84</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -5955,212 +5955,212 @@
         <v>1000</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P22" t="n">
         <v>1.07</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -6191,220 +6191,220 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G23" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="H23" t="n">
         <v>2.92</v>
       </c>
       <c r="I23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J23" t="n">
         <v>3.2</v>
       </c>
       <c r="K23" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P23" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="Q23" t="n">
         <v>1.84</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BI23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BL23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BN23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BP23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BR23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BT23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BV23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BX23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BZ23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -6463,212 +6463,212 @@
         <v>1000</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P24" t="n">
         <v>1.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -6717,212 +6717,212 @@
         <v>1000</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P25" t="n">
         <v>1.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -6959,10 +6959,10 @@
         <v>2.5</v>
       </c>
       <c r="H26" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J26" t="n">
         <v>4.1</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -7213,224 +7213,224 @@
         <v>4.2</v>
       </c>
       <c r="H27" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="I27" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J27" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K27" t="n">
         <v>4.2</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P27" t="n">
         <v>2.18</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BG27" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -7479,212 +7479,212 @@
         <v>1000</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P28" t="n">
         <v>1.12</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -7733,212 +7733,212 @@
         <v>1000</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P29" t="n">
         <v>1.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -7969,22 +7969,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="G30" t="n">
-        <v>12.5</v>
+        <v>6</v>
       </c>
       <c r="H30" t="n">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="I30" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="J30" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="K30" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -7999,10 +7999,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="G32" t="n">
         <v>6.2</v>
@@ -8486,10 +8486,10 @@
         <v>1.7</v>
       </c>
       <c r="I32" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="K32" t="n">
         <v>4.6</v>
@@ -8510,7 +8510,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -8991,10 +8991,10 @@
         <v>3.7</v>
       </c>
       <c r="H34" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="I34" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J34" t="n">
         <v>3.05</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
         <v>2.62</v>
       </c>
       <c r="G35" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H35" t="n">
         <v>2.76</v>
@@ -9251,7 +9251,7 @@
         <v>3.25</v>
       </c>
       <c r="J35" t="n">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="K35" t="n">
         <v>3.5</v>
@@ -9272,7 +9272,7 @@
         <v>1.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -9523,10 +9523,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -9771,13 +9771,13 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="O37" t="n">
         <v>1.45</v>
       </c>
       <c r="P37" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Q37" t="n">
         <v>1.53</v>
@@ -9786,7 +9786,7 @@
         <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="T37" t="n">
         <v>1.01</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -10013,10 +10013,10 @@
         <v>4.2</v>
       </c>
       <c r="J38" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="K38" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G39" t="n">
         <v>2.32</v>
@@ -10288,7 +10288,7 @@
         <v>1.67</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-03 10:04:25</t>
+          <t>2026-07-03 12:22:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB39"/>
+  <dimension ref="A1:CB40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>South Korean K1 League</t>
+          <t>South Korean K2 League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1356,246 +1356,246 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Incheon Utd</t>
+          <t>Seoul E-Land FC</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.96</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>2.06</v>
+        <v>7.2</v>
       </c>
       <c r="H4" t="n">
-        <v>4.4</v>
+        <v>1.57</v>
       </c>
       <c r="I4" t="n">
-        <v>4.9</v>
+        <v>1.69</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="L4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.38</v>
       </c>
-      <c r="M4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="S4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>220</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>140</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI4" t="n">
         <v>3.2</v>
       </c>
-      <c r="O4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="X4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="BJ4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK4" t="n">
         <v>8</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>60</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>26</v>
+      </c>
+      <c r="BY4" t="n">
         <v>8</v>
       </c>
-      <c r="AD4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC4" t="n">
+      <c r="BZ4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="CA4" t="n">
         <v>7.2</v>
       </c>
-      <c r="BD4" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>15</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>10.5</v>
-      </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>South Korean K1 League</t>
+          <t>South Korean K2 League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1610,246 +1610,246 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Gimcheon Sangmu</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeju Utd</t>
+          <t>Busan IPark</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.48</v>
+        <v>3.35</v>
       </c>
       <c r="G5" t="n">
-        <v>2.62</v>
+        <v>3.85</v>
       </c>
       <c r="H5" t="n">
-        <v>3.05</v>
+        <v>2.12</v>
       </c>
       <c r="I5" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="L5" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="P5" t="n">
-        <v>1.78</v>
+        <v>2.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="U5" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.43</v>
+        <v>1.76</v>
       </c>
       <c r="W5" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="X5" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y5" t="n">
         <v>13</v>
       </c>
       <c r="Z5" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AA5" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="AF5" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="AG5" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AJ5" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AK5" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AL5" t="n">
         <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="AN5" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AO5" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="AP5" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.1</v>
+        <v>21</v>
       </c>
       <c r="AT5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV5" t="n">
         <v>8.6</v>
       </c>
-      <c r="AU5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>12</v>
-      </c>
       <c r="AW5" t="n">
-        <v>4.9</v>
+        <v>17</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.2</v>
+        <v>20</v>
       </c>
       <c r="AY5" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.4</v>
+        <v>12.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK5" t="n">
         <v>5</v>
       </c>
-      <c r="BE5" t="n">
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT5" t="n">
         <v>5.3</v>
       </c>
-      <c r="BF5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>9</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BU5" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BW5" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>South Korean K1 League</t>
+          <t>South Korean K2 League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1864,239 +1864,239 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Gwangju FC</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ulsan Hyundai Horang-i</t>
+          <t>Chungnam Asan</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>8.199999999999999</v>
+        <v>1.91</v>
       </c>
       <c r="G6" t="n">
-        <v>9.4</v>
+        <v>2.04</v>
       </c>
       <c r="H6" t="n">
-        <v>1.47</v>
+        <v>4.4</v>
       </c>
       <c r="I6" t="n">
-        <v>1.54</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>4.8</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="O6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
         <v>3.55</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>1.84</v>
       </c>
       <c r="U6" t="n">
-        <v>1.79</v>
+        <v>2.02</v>
       </c>
       <c r="V6" t="n">
-        <v>2.86</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.96</v>
       </c>
       <c r="X6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y6" t="n">
         <v>16</v>
       </c>
-      <c r="Y6" t="n">
-        <v>7.4</v>
-      </c>
       <c r="Z6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC6" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AD6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV6" t="n">
         <v>14</v>
       </c>
-      <c r="AB6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="AW6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BJ6" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="BK6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
         <v>10.5</v>
       </c>
-      <c r="AE6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>85</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>370</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>180</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>280</v>
-      </c>
-      <c r="AO6" t="n">
+      <c r="BZ6" t="n">
+        <v>25</v>
+      </c>
+      <c r="CA6" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AP6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>85</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>30</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>21</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>7</v>
-      </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -2118,246 +2118,246 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chungnam Asan</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="G7" t="n">
-        <v>2.04</v>
+        <v>3.05</v>
       </c>
       <c r="H7" t="n">
-        <v>4.4</v>
+        <v>2.78</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="L7" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="P7" t="n">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="U7" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="V7" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="W7" t="n">
-        <v>1.96</v>
+        <v>1.48</v>
       </c>
       <c r="X7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD7" t="n">
         <v>15.5</v>
       </c>
-      <c r="Y7" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AE7" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="AF7" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AH7" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="AK7" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="AL7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO7" t="n">
         <v>46</v>
       </c>
-      <c r="AM7" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>95</v>
-      </c>
       <c r="AP7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV7" t="n">
         <v>10</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AW7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX7" t="n">
         <v>13.5</v>
       </c>
-      <c r="AR7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX7" t="n">
+      <c r="AY7" t="n">
         <v>10</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.4</v>
       </c>
       <c r="AZ7" t="n">
         <v>14.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB7" t="n">
-        <v>19</v>
+        <v>4.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>18.5</v>
+        <v>4.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>8</v>
+        <v>4.7</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="BF7" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.6</v>
+        <v>4.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="BJ7" t="n">
         <v>10.5</v>
       </c>
       <c r="BK7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN7" t="n">
         <v>5.9</v>
       </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BN7" t="n">
+      <c r="BO7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU7" t="n">
         <v>4.6</v>
       </c>
-      <c r="BO7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>29</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BV7" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="BW7" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY7" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ7" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>South Korean K2 League</t>
+          <t>South Korean K1 League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2372,246 +2372,246 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimcheon Sangmu</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Busan IPark</t>
+          <t>Jeju Utd</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J8" t="n">
         <v>3.35</v>
       </c>
-      <c r="G8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.65</v>
-      </c>
       <c r="K8" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S8" t="n">
         <v>4</v>
       </c>
-      <c r="O8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="T8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U8" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.2</v>
-      </c>
       <c r="V8" t="n">
-        <v>1.76</v>
+        <v>1.43</v>
       </c>
       <c r="W8" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="X8" t="n">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y8" t="n">
         <v>13</v>
       </c>
       <c r="Z8" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AA8" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="AB8" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE8" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="AF8" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="AG8" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AH8" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AJ8" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="AK8" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AL8" t="n">
         <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="AN8" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AO8" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="AP8" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AR8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
         <v>11</v>
       </c>
-      <c r="AS8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT8" t="n">
+      <c r="BT8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
         <v>11.5</v>
       </c>
-      <c r="AU8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG8" t="n">
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
         <v>11</v>
       </c>
-      <c r="BH8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>16</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>7.2</v>
-      </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>South Korean K2 League</t>
+          <t>South Korean K1 League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,246 +2626,246 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Seoul E-Land FC</t>
+          <t>Incheon Utd</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>1.96</v>
       </c>
       <c r="G9" t="n">
-        <v>7.2</v>
+        <v>2.06</v>
       </c>
       <c r="H9" t="n">
-        <v>1.57</v>
+        <v>4.4</v>
       </c>
       <c r="I9" t="n">
-        <v>1.69</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="K9" t="n">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="M9" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="P9" t="n">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="U9" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V9" t="n">
-        <v>2.44</v>
+        <v>1.26</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>1.96</v>
       </c>
       <c r="X9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB9" t="n">
         <v>20</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="BC9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ9" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>220</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>140</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ9" t="n">
+      <c r="BK9" t="n">
         <v>6.4</v>
       </c>
-      <c r="AR9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS9" t="n">
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
         <v>11.5</v>
       </c>
-      <c r="AT9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW9" t="n">
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
         <v>12.5</v>
       </c>
-      <c r="AX9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
         <v>10.5</v>
       </c>
-      <c r="BN9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>60</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>26</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>7.2</v>
-      </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>South Korean K2 League</t>
+          <t>South Korean K1 League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,187 +2880,187 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gwangju FC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ulsan Hyundai Horang-i</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>3.05</v>
+        <v>9.4</v>
       </c>
       <c r="H10" t="n">
-        <v>2.74</v>
+        <v>1.47</v>
       </c>
       <c r="I10" t="n">
-        <v>3.25</v>
+        <v>1.54</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="K10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S10" t="n">
         <v>3.55</v>
       </c>
-      <c r="L10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4.2</v>
-      </c>
       <c r="T10" t="n">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="U10" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="V10" t="n">
-        <v>1.45</v>
+        <v>2.86</v>
       </c>
       <c r="W10" t="n">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>370</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>180</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>280</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AP10" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AQ10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS10" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG10" t="n">
+      <c r="AT10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW10" t="n">
         <v>15</v>
       </c>
-      <c r="AH10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT10" t="n">
+      <c r="AX10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>7.4</v>
       </c>
-      <c r="AU10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BA10" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.52</v>
+        <v>2.82</v>
       </c>
       <c r="BJ10" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
@@ -3069,57 +3069,57 @@
         <v>10</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.9</v>
+        <v>12</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BP10" t="n">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT10" t="n">
-        <v>6</v>
+        <v>3.95</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="BV10" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="BX10" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BZ10" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="CA10" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Chinese Super League</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,31 +3134,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu</t>
+          <t>Dalian Yingbo II</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chengdu Rongcheng</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.59</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>1.69</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="K11" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3167,142 +3167,142 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>4.9</v>
+        <v>1.08</v>
       </c>
       <c r="O11" t="n">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>1.07</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="R11" t="n">
-        <v>1.55</v>
+        <v>1.07</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>1.51</v>
       </c>
       <c r="T11" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -3388,12 +3388,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Dalian Yingbo II</t>
+          <t>Taian Tiankuang</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Changchun Xidu</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3409,10 +3409,10 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3421,22 +3421,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="O12" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="P12" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="R12" t="n">
         <v>1.07</v>
       </c>
       <c r="S12" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -3445,10 +3445,10 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Chinese League 2</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,31 +3642,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Taian Tiankuang</t>
+          <t>Qingdao Hainiu</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Changchun Xidu</t>
+          <t>Chengdu Rongcheng</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>1.69</v>
       </c>
       <c r="J13" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -3675,142 +3675,142 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.11</v>
+        <v>4.9</v>
       </c>
       <c r="O13" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="P13" t="n">
-        <v>1.11</v>
+        <v>2.36</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="R13" t="n">
-        <v>1.08</v>
+        <v>1.54</v>
       </c>
       <c r="S13" t="n">
-        <v>1.34</v>
+        <v>2.6</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>2.44</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chinese League 1</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,67 +3896,67 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Hangzhou Linping Wuyue</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Foshan Nanshi FC</t>
+          <t>Wenzhou Professional</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.87</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>2.88</v>
+        <v>1.04</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N14" t="n">
         <v>1.09</v>
       </c>
-      <c r="N14" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O14" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="P14" t="n">
-        <v>1.65</v>
+        <v>1.07</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="S14" t="n">
-        <v>3.15</v>
+        <v>1.52</v>
       </c>
       <c r="T14" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.92</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4067,10 +4067,10 @@
         <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
@@ -4085,7 +4085,7 @@
         <v>1.01</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -4150,239 +4150,239 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Foshan Nanshi FC</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.78</v>
+        <v>1.87</v>
       </c>
       <c r="G15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S15" t="n">
         <v>3.15</v>
       </c>
-      <c r="H15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.56</v>
-      </c>
       <c r="T15" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.59</v>
+        <v>1.21</v>
       </c>
       <c r="W15" t="n">
-        <v>1.46</v>
+        <v>1.89</v>
       </c>
       <c r="X15" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.6</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.05</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH15" t="n">
         <v>3.7</v>
       </c>
-      <c r="AY15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BI15" t="n">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="BN15" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP15" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT15" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BV15" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -4404,246 +4404,246 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dalian Kun City FC</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.9</v>
+        <v>2.76</v>
       </c>
       <c r="G16" t="n">
-        <v>2.02</v>
+        <v>3.15</v>
       </c>
       <c r="H16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K16" t="n">
         <v>4.1</v>
       </c>
-      <c r="I16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X16" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>3.4</v>
       </c>
-      <c r="K16" t="n">
+      <c r="AR16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BB16" t="n">
         <v>3.95</v>
       </c>
-      <c r="L16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X16" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY16" t="n">
+      <c r="BC16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BH16" t="n">
         <v>4.1</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>3.35</v>
       </c>
       <c r="BI16" t="n">
         <v>2.94</v>
       </c>
       <c r="BJ16" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>10</v>
+        <v>2.86</v>
       </c>
       <c r="BN16" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BP16" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BR16" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BT16" t="n">
-        <v>8.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="BV16" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BX16" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="BY16" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BZ16" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="CA16" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Chinese League 2</t>
+          <t>Chinese League 1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,239 +4658,239 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Guizhou Zhucheng Athletic</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jiangxi Lushan</t>
+          <t>Dalian Kun City FC</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.04</v>
+        <v>1.88</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>2.04</v>
       </c>
       <c r="H17" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="J17" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>1.08</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="P17" t="n">
-        <v>1.08</v>
+        <v>1.77</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.43</v>
+        <v>2.04</v>
       </c>
       <c r="R17" t="n">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>1.42</v>
+        <v>3.7</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.97</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH17" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN17" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP17" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR17" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV17" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -4912,12 +4912,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hangzhou Linping Wuyue</t>
+          <t>Guizhou Zhucheng Athletic</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wenzhou Professional</t>
+          <t>Jiangxi Lushan</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4945,22 +4945,22 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="O18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P18" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="R18" t="n">
         <v>1.07</v>
       </c>
       <c r="S18" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="T18" t="n">
         <v>1.01</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5190,7 @@
         <v>4.5</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.19</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G20" t="n">
         <v>1.57</v>
@@ -5447,10 +5447,10 @@
         <v>5.2</v>
       </c>
       <c r="L20" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N20" t="n">
         <v>4.6</v>
@@ -5459,7 +5459,7 @@
         <v>1.23</v>
       </c>
       <c r="P20" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q20" t="n">
         <v>1.69</v>
@@ -5477,7 +5477,7 @@
         <v>2.06</v>
       </c>
       <c r="V20" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W20" t="n">
         <v>2.72</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -5686,13 +5686,13 @@
         <v>2.28</v>
       </c>
       <c r="G21" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H21" t="n">
         <v>3.2</v>
       </c>
       <c r="I21" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J21" t="n">
         <v>3.65</v>
@@ -5701,7 +5701,7 @@
         <v>3.95</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M21" t="n">
         <v>1.05</v>
@@ -5710,19 +5710,19 @@
         <v>4.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P21" t="n">
         <v>2.22</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R21" t="n">
         <v>1.5</v>
       </c>
       <c r="S21" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T21" t="n">
         <v>1.63</v>
@@ -5749,7 +5749,7 @@
         <v>55</v>
       </c>
       <c r="AB21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC21" t="n">
         <v>10.5</v>
@@ -5761,10 +5761,10 @@
         <v>34</v>
       </c>
       <c r="AF21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH21" t="n">
         <v>16</v>
@@ -5773,10 +5773,10 @@
         <v>40</v>
       </c>
       <c r="AJ21" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL21" t="n">
         <v>34</v>
@@ -5785,13 +5785,13 @@
         <v>70</v>
       </c>
       <c r="AN21" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO21" t="n">
         <v>27</v>
       </c>
       <c r="AP21" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ21" t="n">
         <v>13</v>
@@ -5800,7 +5800,7 @@
         <v>20</v>
       </c>
       <c r="AS21" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT21" t="n">
         <v>11</v>
@@ -5812,7 +5812,7 @@
         <v>11.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX21" t="n">
         <v>14.5</v>
@@ -5824,89 +5824,89 @@
         <v>13</v>
       </c>
       <c r="BA21" t="n">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="BB21" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC21" t="n">
         <v>19.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF21" t="n">
         <v>12.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>18</v>
+        <v>6.4</v>
       </c>
       <c r="BH21" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.96</v>
+        <v>3.25</v>
       </c>
       <c r="BJ21" t="n">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.7</v>
+        <v>6.8</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.96</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>27</v>
+      </c>
+      <c r="BS21" t="n">
         <v>7.4</v>
       </c>
-      <c r="BO21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP21" t="n">
+      <c r="BT21" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BZ21" t="n">
         <v>21</v>
       </c>
-      <c r="BQ21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BT21" t="n">
-        <v>9</v>
-      </c>
-      <c r="BU21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV21" t="n">
-        <v>32</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BX21" t="n">
-        <v>44</v>
-      </c>
-      <c r="BY21" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BZ21" t="n">
-        <v>28</v>
-      </c>
       <c r="CA21" t="n">
-        <v>1.84</v>
+        <v>6.8</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -5949,7 +5949,7 @@
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -5961,13 +5961,13 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="O22" t="n">
         <v>1.28</v>
       </c>
       <c r="P22" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Q22" t="n">
         <v>1.28</v>
@@ -5985,10 +5985,10 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -6212,7 +6212,7 @@
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N23" t="n">
         <v>3.25</v>
@@ -6254,7 +6254,7 @@
         <v>25</v>
       </c>
       <c r="AA23" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB23" t="n">
         <v>12</v>
@@ -6266,7 +6266,7 @@
         <v>15.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF23" t="n">
         <v>17.5</v>
@@ -6281,13 +6281,13 @@
         <v>50</v>
       </c>
       <c r="AJ23" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AK23" t="n">
         <v>29</v>
       </c>
       <c r="AL23" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -6296,7 +6296,7 @@
         <v>22</v>
       </c>
       <c r="AO23" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP23" t="n">
         <v>1.01</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
         <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K24" t="n">
         <v>1000</v>
@@ -6469,22 +6469,22 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="O24" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="R24" t="n">
         <v>1.07</v>
       </c>
       <c r="S24" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="T24" t="n">
         <v>1.01</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6711,7 @@
         <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K25" t="n">
         <v>1000</v>
@@ -6723,7 +6723,7 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="O25" t="n">
         <v>1.01</v>
@@ -6732,13 +6732,13 @@
         <v>1.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="R25" t="n">
         <v>1.07</v>
       </c>
       <c r="S25" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -6971,16 +6971,16 @@
         <v>5</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="P26" t="n">
         <v>3.3</v>
@@ -6989,194 +6989,194 @@
         <v>1.36</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BI26" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BK26" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BL26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BO26" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BP26" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BQ26" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR26" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BS26" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BT26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BU26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BV26" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BW26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BX26" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BY26" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BZ26" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="CA26" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -7213,19 +7213,19 @@
         <v>4.2</v>
       </c>
       <c r="H27" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="I27" t="n">
         <v>2.04</v>
       </c>
       <c r="J27" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K27" t="n">
         <v>4.2</v>
       </c>
       <c r="L27" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
         <v>1.05</v>
@@ -7249,10 +7249,10 @@
         <v>2.92</v>
       </c>
       <c r="T27" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="U27" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="V27" t="n">
         <v>1.96</v>
@@ -7261,112 +7261,112 @@
         <v>1.32</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y27" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z27" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA27" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AB27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE27" t="n">
         <v>20</v>
       </c>
-      <c r="AC27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>23</v>
-      </c>
       <c r="AF27" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AG27" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AI27" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ27" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AK27" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AL27" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM27" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO27" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AP27" t="n">
-        <v>3.6</v>
+        <v>16.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB27" t="n">
         <v>10.5</v>
       </c>
-      <c r="AS27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BC27" t="n">
-        <v>3.35</v>
+        <v>9.6</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>3.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>3.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG27" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -7452,28 +7452,28 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FC Ordabasy</t>
+          <t>FK Kaisar</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FK Ulytau Zhezkazgan</t>
+          <t>Irtysh Pavlodar</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G28" t="n">
-        <v>1.4</v>
+        <v>1000</v>
       </c>
       <c r="H28" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="I28" t="n">
         <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="K28" t="n">
         <v>1000</v>
@@ -7485,22 +7485,22 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="O28" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="P28" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="R28" t="n">
         <v>1.07</v>
       </c>
       <c r="S28" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="T28" t="n">
         <v>1.01</v>
@@ -7512,7 +7512,7 @@
         <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -7706,31 +7706,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FK Kaisar</t>
+          <t>FC Ordabasy</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Irtysh Pavlodar</t>
+          <t>FK Ulytau Zhezkazgan</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="G29" t="n">
-        <v>1000</v>
+        <v>1.4</v>
       </c>
       <c r="H29" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="I29" t="n">
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.02</v>
+        <v>4.4</v>
       </c>
       <c r="K29" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -7739,22 +7739,22 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="O29" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="P29" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.37</v>
+        <v>1.72</v>
       </c>
       <c r="R29" t="n">
         <v>1.07</v>
       </c>
       <c r="S29" t="n">
-        <v>1.37</v>
+        <v>1.72</v>
       </c>
       <c r="T29" t="n">
         <v>1.01</v>
@@ -7766,7 +7766,7 @@
         <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -7969,220 +7969,220 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="G30" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="H30" t="n">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="I30" t="n">
-        <v>1.89</v>
+        <v>2.28</v>
       </c>
       <c r="J30" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K30" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P30" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ30" t="n">
         <v>0</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -8235,218 +8235,218 @@
         <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K31" t="n">
         <v>1000</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P31" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
@@ -8477,237 +8477,237 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="G32" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="H32" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="J32" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="K32" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8722,229 +8722,229 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Centro Atletico Fenix</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Huracan del Paso</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="G33" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="H33" t="n">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="I33" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="J33" t="n">
-        <v>1.02</v>
+        <v>3.05</v>
       </c>
       <c r="K33" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P33" t="n">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BI33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BJ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ33" t="n">
         <v>0</v>
@@ -8954,14 +8954,14 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8971,234 +8971,234 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>Centro Atletico Fenix</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Huracan del Paso</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="G34" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="H34" t="n">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>2.74</v>
+        <v>1000</v>
       </c>
       <c r="J34" t="n">
-        <v>3.05</v>
+        <v>1.02</v>
       </c>
       <c r="K34" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P34" t="n">
-        <v>1.6</v>
+        <v>1.05</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.32</v>
+        <v>1.02</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ34" t="n">
         <v>0</v>
@@ -9208,14 +9208,14 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9225,36 +9225,36 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Tacuarembo</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cerrito</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="G35" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="H35" t="n">
-        <v>2.76</v>
+        <v>2.38</v>
       </c>
       <c r="I35" t="n">
-        <v>3.25</v>
+        <v>2.72</v>
       </c>
       <c r="J35" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="K35" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -9269,10 +9269,10 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -9462,14 +9462,14 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9479,36 +9479,36 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Tacuarembo</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>Cerrito</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="G36" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H36" t="n">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="I36" t="n">
-        <v>2.76</v>
+        <v>3.55</v>
       </c>
       <c r="J36" t="n">
-        <v>3.15</v>
+        <v>2.56</v>
       </c>
       <c r="K36" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -9523,10 +9523,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.14</v>
+        <v>1.54</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -9716,14 +9716,14 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -9738,246 +9738,246 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Delfin</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>HFX Wanderers</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="G37" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="H37" t="n">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="I37" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="J37" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="K37" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.36</v>
+        <v>1.98</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="R37" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9987,251 +9987,251 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Colon FC</t>
+          <t>Delfin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Uruguay Montevideo FC</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="G38" t="n">
-        <v>2.52</v>
+        <v>1000</v>
       </c>
       <c r="H38" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="I38" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="J38" t="n">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="K38" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P38" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.28</v>
+        <v>1.53</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-03 12:22:48</t>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -10241,244 +10241,498 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Colon FC</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Uruguay Montevideo FC</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G39" t="n">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="H39" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="I39" t="n">
         <v>4.2</v>
       </c>
       <c r="J39" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB39" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:41:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Nautico PE</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J40" t="n">
         <v>3.2</v>
       </c>
-      <c r="K39" t="n">
+      <c r="K40" t="n">
         <v>3.45</v>
       </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
         <v>1.67</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="Q40" t="n">
         <v>2.3</v>
       </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB39" t="inlineStr">
-        <is>
-          <t>2026-07-03 12:22:48</t>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB40" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:41:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -1138,13 +1138,13 @@
         <v>1.07</v>
       </c>
       <c r="O3" t="n">
-        <v>1.36</v>
+        <v>1.02</v>
       </c>
       <c r="P3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R3" t="n">
         <v>1.07</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -1368,22 +1368,22 @@
         <v>1.96</v>
       </c>
       <c r="G4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H4" t="n">
         <v>4.4</v>
       </c>
       <c r="I4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
         <v>3.75</v>
       </c>
       <c r="L4" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1392,7 +1392,7 @@
         <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P4" t="n">
         <v>1.75</v>
@@ -1407,70 +1407,70 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.94</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.93</v>
       </c>
       <c r="V4" t="n">
         <v>1.26</v>
       </c>
       <c r="W4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="X4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y4" t="n">
         <v>14.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AA4" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
         <v>8</v>
       </c>
       <c r="AC4" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE4" t="n">
         <v>970</v>
       </c>
-      <c r="AE4" t="n">
-        <v>70</v>
-      </c>
       <c r="AF4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG4" t="n">
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AI4" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AL4" t="n">
-        <v>44</v>
+        <v>170</v>
       </c>
       <c r="AM4" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AO4" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
         <v>10.5</v>
@@ -1479,13 +1479,13 @@
         <v>12.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.199999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="AT4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU4" t="n">
         <v>7</v>
@@ -1494,37 +1494,37 @@
         <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>9.4</v>
+        <v>30</v>
       </c>
       <c r="AX4" t="n">
         <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>7</v>
+        <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.4</v>
+        <v>34</v>
       </c>
       <c r="BB4" t="n">
         <v>20</v>
       </c>
       <c r="BC4" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="BD4" t="n">
         <v>36</v>
       </c>
       <c r="BE4" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="BF4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG4" t="n">
-        <v>9.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="BH4" t="n">
         <v>3.15</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -1634,16 +1634,16 @@
         <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.39</v>
@@ -1661,7 +1661,7 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U5" t="n">
         <v>2.04</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -1876,10 +1876,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I6" t="n">
         <v>1.54</v>
@@ -1903,7 +1903,7 @@
         <v>1.34</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q6" t="n">
         <v>1.97</v>
@@ -1915,10 +1915,10 @@
         <v>3.55</v>
       </c>
       <c r="T6" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V6" t="n">
         <v>2.86</v>
@@ -1933,13 +1933,13 @@
         <v>7.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AA6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC6" t="n">
         <v>10.5</v>
@@ -1948,13 +1948,13 @@
         <v>10.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF6" t="n">
         <v>85</v>
       </c>
       <c r="AG6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AH6" t="n">
         <v>32</v>
@@ -1966,22 +1966,22 @@
         <v>360</v>
       </c>
       <c r="AK6" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AP6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ6" t="n">
         <v>6.6</v>
@@ -1999,37 +1999,37 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6" t="n">
         <v>15</v>
       </c>
       <c r="AX6" t="n">
-        <v>8.6</v>
+        <v>30</v>
       </c>
       <c r="AY6" t="n">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7.4</v>
+        <v>24</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.199999999999999</v>
+        <v>50</v>
       </c>
       <c r="BC6" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="BD6" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="BE6" t="n">
-        <v>9.199999999999999</v>
+        <v>48</v>
       </c>
       <c r="BF6" t="n">
-        <v>9.199999999999999</v>
+        <v>48</v>
       </c>
       <c r="BG6" t="n">
         <v>7.8</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
         <v>3.85</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2546,7 @@
         <v>3.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="BJ8" t="n">
         <v>9.6</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2662,7 @@
         <v>3.85</v>
       </c>
       <c r="O9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P9" t="n">
         <v>1.99</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -2895,10 +2895,10 @@
         <v>3.05</v>
       </c>
       <c r="H10" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="I10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
@@ -2907,7 +2907,7 @@
         <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M10" t="n">
         <v>1.1</v>
@@ -2922,19 +2922,19 @@
         <v>1.66</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U10" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V10" t="n">
         <v>1.45</v>
@@ -3012,7 +3012,7 @@
         <v>7.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AV10" t="n">
         <v>10</v>
@@ -3054,7 +3054,7 @@
         <v>3.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="G13" t="n">
         <v>6.2</v>
@@ -3660,19 +3660,19 @@
         <v>1.61</v>
       </c>
       <c r="I13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
         <v>4.3</v>
       </c>
       <c r="K13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N13" t="n">
         <v>4.9</v>
@@ -3684,10 +3684,10 @@
         <v>2.34</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R13" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S13" t="n">
         <v>2.6</v>
@@ -3696,13 +3696,13 @@
         <v>1.72</v>
       </c>
       <c r="U13" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="V13" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="W13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X13" t="n">
         <v>27</v>
@@ -3711,7 +3711,7 @@
         <v>11</v>
       </c>
       <c r="Z13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA13" t="n">
         <v>16.5</v>
@@ -3720,7 +3720,7 @@
         <v>29</v>
       </c>
       <c r="AC13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD13" t="n">
         <v>10.5</v>
@@ -3759,7 +3759,7 @@
         <v>7.4</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ13" t="n">
         <v>9.6</v>
@@ -3801,13 +3801,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BD13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE13" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BE13" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BF13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG13" t="n">
         <v>6.4</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -3935,16 +3935,16 @@
         <v>1.01</v>
       </c>
       <c r="P14" t="n">
-        <v>1.07</v>
+        <v>1.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="R14" t="n">
         <v>1.07</v>
       </c>
       <c r="S14" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
         <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
         <v>1.19</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N19" t="n">
         <v>7.4</v>
@@ -5208,7 +5208,7 @@
         <v>3.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R19" t="n">
         <v>1.88</v>
@@ -5220,7 +5220,7 @@
         <v>1.45</v>
       </c>
       <c r="U19" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="V19" t="n">
         <v>1.27</v>
@@ -5340,22 +5340,22 @@
         <v>5.6</v>
       </c>
       <c r="BI19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BJ19" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK19" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL19" t="n">
         <v>60</v>
       </c>
       <c r="BM19" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BN19" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BO19" t="n">
         <v>4.2</v>
@@ -5364,41 +5364,41 @@
         <v>11.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR19" t="n">
         <v>18</v>
       </c>
       <c r="BS19" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT19" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV19" t="n">
         <v>28</v>
       </c>
       <c r="BW19" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BX19" t="n">
         <v>29</v>
       </c>
       <c r="BY19" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ19" t="n">
         <v>11</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -5435,16 +5435,16 @@
         <v>2.4</v>
       </c>
       <c r="H20" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J20" t="n">
         <v>3.65</v>
       </c>
       <c r="K20" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L20" t="n">
         <v>1.34</v>
@@ -5456,28 +5456,28 @@
         <v>4.5</v>
       </c>
       <c r="O20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="T20" t="n">
         <v>1.63</v>
       </c>
       <c r="U20" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="V20" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W20" t="n">
         <v>1.72</v>
@@ -5498,7 +5498,7 @@
         <v>13</v>
       </c>
       <c r="AC20" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD20" t="n">
         <v>14.5</v>
@@ -5537,7 +5537,7 @@
         <v>27</v>
       </c>
       <c r="AP20" t="n">
-        <v>6.2</v>
+        <v>16.5</v>
       </c>
       <c r="AQ20" t="n">
         <v>13</v>
@@ -5546,7 +5546,7 @@
         <v>20</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT20" t="n">
         <v>11</v>
@@ -5573,22 +5573,22 @@
         <v>30</v>
       </c>
       <c r="BB20" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BC20" t="n">
         <v>19.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BF20" t="n">
         <v>12.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH20" t="n">
         <v>4.1</v>
@@ -5618,7 +5618,7 @@
         <v>17</v>
       </c>
       <c r="BQ20" t="n">
-        <v>12</v>
+        <v>6.4</v>
       </c>
       <c r="BR20" t="n">
         <v>27</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="G21" t="n">
         <v>1.57</v>
@@ -5692,13 +5692,13 @@
         <v>6.2</v>
       </c>
       <c r="I21" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J21" t="n">
         <v>4.8</v>
       </c>
       <c r="K21" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -5731,7 +5731,7 @@
         <v>2.06</v>
       </c>
       <c r="V21" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W21" t="n">
         <v>2.72</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -6735,7 +6735,7 @@
         <v>1.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S25" t="n">
         <v>1.01</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -7061,16 +7061,16 @@
         <v>12</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AQ26" t="n">
         <v>20</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AT26" t="n">
         <v>18.5</v>
@@ -7097,7 +7097,7 @@
         <v>21</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC26" t="n">
         <v>17.5</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -7216,13 +7216,13 @@
         <v>1.98</v>
       </c>
       <c r="I27" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J27" t="n">
         <v>3.8</v>
       </c>
       <c r="K27" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -7255,7 +7255,7 @@
         <v>2.3</v>
       </c>
       <c r="V27" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="W27" t="n">
         <v>1.32</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="G28" t="n">
         <v>1.4</v>
@@ -7494,13 +7494,13 @@
         <v>1.12</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.27</v>
+        <v>1.72</v>
       </c>
       <c r="R28" t="n">
         <v>1.07</v>
       </c>
       <c r="S28" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="T28" t="n">
         <v>1.01</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -7739,13 +7739,13 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="O29" t="n">
         <v>1.37</v>
       </c>
       <c r="P29" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Q29" t="n">
         <v>1.37</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
         <v>1.05</v>
       </c>
       <c r="S34" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T34" t="n">
         <v>1.01</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -9251,7 +9251,7 @@
         <v>1000</v>
       </c>
       <c r="J35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K35" t="n">
         <v>1000</v>
@@ -9263,22 +9263,22 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="O35" t="n">
         <v>1.01</v>
       </c>
       <c r="P35" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R35" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S35" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="T35" t="n">
         <v>1.01</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -9505,7 +9505,7 @@
         <v>1000</v>
       </c>
       <c r="J36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K36" t="n">
         <v>1000</v>
@@ -9520,19 +9520,19 @@
         <v>1.08</v>
       </c>
       <c r="O36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P36" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="R36" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="S36" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="T36" t="n">
         <v>1.01</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -9756,7 +9756,7 @@
         <v>2.38</v>
       </c>
       <c r="I37" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J37" t="n">
         <v>3.05</v>
@@ -9765,212 +9765,212 @@
         <v>3.45</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="P37" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q37" t="n">
         <v>2.3</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BI37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BJ37" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BK37" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BL37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN37" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BO37" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BP37" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BQ37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BU37" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BV37" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BW37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ37" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="CA37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10013,7 @@
         <v>1000</v>
       </c>
       <c r="J38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K38" t="n">
         <v>1000</v>
@@ -10025,22 +10025,22 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P38" t="n">
         <v>1.08</v>
       </c>
-      <c r="O38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Q38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R38" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S38" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="T38" t="n">
         <v>1.01</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -10267,7 +10267,7 @@
         <v>1000</v>
       </c>
       <c r="J39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K39" t="n">
         <v>1000</v>
@@ -10279,22 +10279,22 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="O39" t="n">
         <v>1.01</v>
       </c>
       <c r="P39" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R39" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S39" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="T39" t="n">
         <v>1.01</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -10521,7 +10521,7 @@
         <v>1000</v>
       </c>
       <c r="J40" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K40" t="n">
         <v>1000</v>
@@ -10533,22 +10533,22 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P40" t="n">
         <v>1.08</v>
       </c>
-      <c r="O40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P40" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Q40" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R40" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S40" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="T40" t="n">
         <v>1.01</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -10775,7 +10775,7 @@
         <v>1000</v>
       </c>
       <c r="J41" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K41" t="n">
         <v>1000</v>
@@ -10787,22 +10787,22 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="O41" t="n">
         <v>1.01</v>
       </c>
       <c r="P41" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R41" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S41" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="T41" t="n">
         <v>1.01</v>
@@ -10871,52 +10871,52 @@
         <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF41" t="n">
         <v>1.01</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11029,7 @@
         <v>1000</v>
       </c>
       <c r="J42" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K42" t="n">
         <v>1000</v>
@@ -11041,22 +11041,22 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P42" t="n">
         <v>1.08</v>
       </c>
-      <c r="O42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Q42" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R42" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S42" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="T42" t="n">
         <v>1.01</v>
@@ -11125,52 +11125,52 @@
         <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF42" t="n">
         <v>1.01</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
         <v>1000</v>
       </c>
       <c r="J43" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K43" t="n">
         <v>1000</v>
@@ -11295,22 +11295,22 @@
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P43" t="n">
         <v>1.08</v>
       </c>
-      <c r="O43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P43" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Q43" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R43" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S43" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="T43" t="n">
         <v>1.01</v>
@@ -11379,52 +11379,52 @@
         <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF43" t="n">
         <v>1.01</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
         <v>1000</v>
       </c>
       <c r="J44" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K44" t="n">
         <v>1000</v>
@@ -11549,22 +11549,22 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P44" t="n">
         <v>1.08</v>
       </c>
-      <c r="O44" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P44" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Q44" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R44" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S44" t="n">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="T44" t="n">
         <v>1.01</v>
@@ -11633,52 +11633,52 @@
         <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF44" t="n">
         <v>1.01</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -11791,7 +11791,7 @@
         <v>1000</v>
       </c>
       <c r="J45" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K45" t="n">
         <v>1000</v>
@@ -11803,7 +11803,7 @@
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O45" t="n">
         <v>1.01</v>
@@ -11812,13 +11812,13 @@
         <v>1.07</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R45" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S45" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T45" t="n">
         <v>1.01</v>
@@ -11887,52 +11887,52 @@
         <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT45" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV45" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW45" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX45" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD45" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF45" t="n">
         <v>1.01</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -12311,7 +12311,7 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="O47" t="n">
         <v>1.01</v>
@@ -12323,10 +12323,10 @@
         <v>1.02</v>
       </c>
       <c r="R47" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="S47" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="T47" t="n">
         <v>1.01</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
         <v>2.62</v>
       </c>
       <c r="G48" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="H48" t="n">
         <v>2.76</v>
@@ -12559,16 +12559,16 @@
         <v>3.5</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P48" t="n">
         <v>1.63</v>
@@ -12577,184 +12577,184 @@
         <v>2.24</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH48" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BI48" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BJ48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ48" t="n">
         <v>0</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -12813,212 +12813,212 @@
         <v>4.1</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P49" t="n">
         <v>1.98</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -13049,19 +13049,19 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G50" t="n">
         <v>1000</v>
       </c>
       <c r="H50" t="n">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="I50" t="n">
         <v>1000</v>
       </c>
       <c r="J50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K50" t="n">
         <v>1000</v>
@@ -13070,7 +13070,7 @@
         <v>1.01</v>
       </c>
       <c r="M50" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N50" t="n">
         <v>1.36</v>
@@ -13082,13 +13082,13 @@
         <v>1.24</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.51</v>
+        <v>2.04</v>
       </c>
       <c r="R50" t="n">
         <v>1.18</v>
       </c>
       <c r="S50" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="T50" t="n">
         <v>1.01</v>
@@ -13097,7 +13097,7 @@
         <v>1.01</v>
       </c>
       <c r="V50" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W50" t="n">
         <v>1.01</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>
@@ -13575,16 +13575,16 @@
         <v>3.45</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P52" t="n">
         <v>1.67</v>
@@ -13593,194 +13593,194 @@
         <v>2.3</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-03 17:02:38</t>
+          <t>2026-07-03 19:21:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -1365,58 +1365,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="G4" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H4" t="n">
         <v>4.4</v>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R4" t="n">
         <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T4" t="n">
         <v>1.98</v>
       </c>
       <c r="U4" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W4" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="X4" t="n">
         <v>14</v>
@@ -1449,16 +1449,16 @@
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AK4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AL4" t="n">
         <v>170</v>
@@ -1485,7 +1485,7 @@
         <v>38</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU4" t="n">
         <v>7</v>
@@ -1521,7 +1521,7 @@
         <v>42</v>
       </c>
       <c r="BF4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BG4" t="n">
         <v>34</v>
@@ -1530,28 +1530,28 @@
         <v>3.15</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BN4" t="n">
         <v>4.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ4" t="n">
         <v>7.6</v>
@@ -1578,17 +1578,17 @@
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -1640,10 +1640,10 @@
         <v>1.46</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O5" t="n">
         <v>1.39</v>
@@ -1652,13 +1652,13 @@
         <v>1.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T5" t="n">
         <v>1.87</v>
@@ -1667,13 +1667,13 @@
         <v>2.04</v>
       </c>
       <c r="V5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
         <v>1.62</v>
       </c>
       <c r="X5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y5" t="n">
         <v>13</v>
@@ -1682,7 +1682,7 @@
         <v>24</v>
       </c>
       <c r="AA5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB5" t="n">
         <v>11.5</v>
@@ -1733,10 +1733,10 @@
         <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AT5" t="n">
         <v>8.6</v>
@@ -1748,46 +1748,46 @@
         <v>12</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="AY5" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.4</v>
+        <v>16.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BF5" t="n">
         <v>20</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BH5" t="n">
         <v>3.15</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK5" t="n">
         <v>6.2</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN5" t="n">
         <v>5.4</v>
@@ -1808,13 +1808,13 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT5" t="n">
         <v>6.2</v>
@@ -1826,13 +1826,13 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -1876,16 +1876,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>1.49</v>
       </c>
       <c r="I6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K6" t="n">
         <v>4.8</v>
@@ -1897,34 +1897,34 @@
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
         <v>1.34</v>
       </c>
       <c r="P6" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
         <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="n">
         <v>1.79</v>
       </c>
       <c r="V6" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
         <v>16</v>
@@ -1939,7 +1939,7 @@
         <v>13.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AC6" t="n">
         <v>10.5</v>
@@ -1948,19 +1948,19 @@
         <v>10.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AF6" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AH6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI6" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AJ6" t="n">
         <v>360</v>
@@ -1984,7 +1984,7 @@
         <v>13</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR6" t="n">
         <v>7.2</v>
@@ -2011,7 +2011,7 @@
         <v>20</v>
       </c>
       <c r="AZ6" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="BA6" t="n">
         <v>26</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -2130,22 +2130,22 @@
         <v>1.91</v>
       </c>
       <c r="G7" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H7" t="n">
         <v>4.4</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J7" t="n">
         <v>3.45</v>
       </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
@@ -2154,13 +2154,13 @@
         <v>3.55</v>
       </c>
       <c r="O7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P7" t="n">
         <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
         <v>1.33</v>
@@ -2178,13 +2178,13 @@
         <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X7" t="n">
         <v>15.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z7" t="n">
         <v>36</v>
@@ -2244,7 +2244,7 @@
         <v>23</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT7" t="n">
         <v>7.8</v>
@@ -2256,7 +2256,7 @@
         <v>14</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX7" t="n">
         <v>10</v>
@@ -2268,7 +2268,7 @@
         <v>14.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB7" t="n">
         <v>19</v>
@@ -2277,22 +2277,22 @@
         <v>18.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF7" t="n">
         <v>11</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH7" t="n">
         <v>3.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="BJ7" t="n">
         <v>10.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G8" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="H8" t="n">
         <v>2.12</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
         <v>3.95</v>
@@ -2405,7 +2405,7 @@
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O8" t="n">
         <v>1.27</v>
@@ -2420,25 +2420,25 @@
         <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T8" t="n">
         <v>1.66</v>
       </c>
       <c r="U8" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V8" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X8" t="n">
         <v>19.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z8" t="n">
         <v>17</v>
@@ -2450,7 +2450,7 @@
         <v>17.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD8" t="n">
         <v>13</v>
@@ -2468,13 +2468,13 @@
         <v>19.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ8" t="n">
         <v>75</v>
       </c>
       <c r="AK8" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AL8" t="n">
         <v>55</v>
@@ -2483,7 +2483,7 @@
         <v>95</v>
       </c>
       <c r="AN8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO8" t="n">
         <v>17</v>
@@ -2546,7 +2546,7 @@
         <v>3.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ8" t="n">
         <v>9.6</v>
@@ -2558,7 +2558,7 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN8" t="n">
         <v>7.2</v>
@@ -2576,7 +2576,7 @@
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT8" t="n">
         <v>5.3</v>
@@ -2594,7 +2594,7 @@
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
         <v>7.2</v>
       </c>
       <c r="H9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="I9" t="n">
         <v>1.69</v>
@@ -2650,7 +2650,7 @@
         <v>4.1</v>
       </c>
       <c r="K9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.31</v>
@@ -2662,7 +2662,7 @@
         <v>3.85</v>
       </c>
       <c r="O9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P9" t="n">
         <v>1.99</v>
@@ -2674,13 +2674,13 @@
         <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T9" t="n">
         <v>1.87</v>
       </c>
       <c r="U9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V9" t="n">
         <v>2.44</v>
@@ -2800,13 +2800,13 @@
         <v>3.7</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ9" t="n">
         <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2818,7 +2818,7 @@
         <v>10</v>
       </c>
       <c r="BO9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BP9" t="n">
         <v>60</v>
@@ -2836,13 +2836,13 @@
         <v>4.3</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="BV9" t="n">
         <v>11</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="BX9" t="n">
         <v>26</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G10" t="n">
         <v>3.05</v>
       </c>
       <c r="H10" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I10" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
@@ -2916,13 +2916,13 @@
         <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P10" t="n">
         <v>1.66</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R10" t="n">
         <v>1.25</v>
@@ -2937,7 +2937,7 @@
         <v>1.94</v>
       </c>
       <c r="V10" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W10" t="n">
         <v>1.48</v>
@@ -2991,7 +2991,7 @@
         <v>150</v>
       </c>
       <c r="AN10" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AO10" t="n">
         <v>46</v>
@@ -3003,13 +3003,13 @@
         <v>7.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS10" t="n">
         <v>4.7</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU10" t="n">
         <v>5.8</v>
@@ -3018,7 +3018,7 @@
         <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX10" t="n">
         <v>13.5</v>
@@ -3030,25 +3030,25 @@
         <v>14.5</v>
       </c>
       <c r="BA10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB10" t="n">
         <v>4.7</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BC10" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC10" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BD10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH10" t="n">
         <v>3.1</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
         <v>1.11</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="R12" t="n">
         <v>1.07</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -3654,19 +3654,19 @@
         <v>5.4</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="J13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K13" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -3675,31 +3675,31 @@
         <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O13" t="n">
         <v>1.22</v>
       </c>
       <c r="P13" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q13" t="n">
         <v>1.64</v>
       </c>
       <c r="R13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S13" t="n">
         <v>2.6</v>
       </c>
       <c r="T13" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U13" t="n">
         <v>2.32</v>
       </c>
       <c r="V13" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="W13" t="n">
         <v>1.2</v>
@@ -3711,7 +3711,7 @@
         <v>11</v>
       </c>
       <c r="Z13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA13" t="n">
         <v>16.5</v>
@@ -3720,13 +3720,13 @@
         <v>29</v>
       </c>
       <c r="AC13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD13" t="n">
         <v>10.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AF13" t="n">
         <v>55</v>
@@ -3747,7 +3747,7 @@
         <v>80</v>
       </c>
       <c r="AL13" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM13" t="n">
         <v>100</v>
@@ -3756,13 +3756,13 @@
         <v>75</v>
       </c>
       <c r="AO13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR13" t="n">
         <v>10</v>
@@ -3771,43 +3771,43 @@
         <v>14</v>
       </c>
       <c r="AT13" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU13" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AV13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW13" t="n">
         <v>14</v>
       </c>
       <c r="AX13" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ13" t="n">
         <v>16.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BC13" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BD13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BG13" t="n">
         <v>6.4</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -3929,16 +3929,16 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O14" t="n">
         <v>1.01</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5</v>
+        <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
         <v>1.07</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -4189,16 +4189,16 @@
         <v>1.02</v>
       </c>
       <c r="P15" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Q15" t="n">
         <v>1.43</v>
       </c>
       <c r="R15" t="n">
-        <v>1.07</v>
+        <v>2.04</v>
       </c>
       <c r="S15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -4431,13 +4431,13 @@
         <v>4.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M16" t="n">
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
         <v>1.37</v>
@@ -4467,103 +4467,103 @@
         <v>1.89</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
         <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
         <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
         <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
         <v>1.03</v>
@@ -4575,68 +4575,68 @@
         <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.38</v>
+        <v>5.4</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.38</v>
+        <v>3.25</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.38</v>
+        <v>6.2</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.38</v>
+        <v>4.6</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
         <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="T17" t="n">
         <v>1.59</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G19" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="H19" t="n">
         <v>4.2</v>
       </c>
       <c r="I19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J19" t="n">
         <v>4.5</v>
       </c>
       <c r="K19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L19" t="n">
         <v>1.19</v>
@@ -5202,31 +5202,31 @@
         <v>7.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P19" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="S19" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="T19" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="U19" t="n">
         <v>3</v>
       </c>
       <c r="V19" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W19" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X19" t="n">
         <v>40</v>
@@ -5274,7 +5274,7 @@
         <v>23</v>
       </c>
       <c r="AM19" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AN19" t="n">
         <v>6</v>
@@ -5286,7 +5286,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR19" t="n">
         <v>34</v>
@@ -5331,7 +5331,7 @@
         <v>28</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BG19" t="n">
         <v>17.5</v>
@@ -5340,65 +5340,65 @@
         <v>5.6</v>
       </c>
       <c r="BI19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BJ19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK19" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BL19" t="n">
         <v>60</v>
       </c>
       <c r="BM19" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BN19" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO19" t="n">
         <v>4.2</v>
       </c>
       <c r="BP19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BR19" t="n">
         <v>18</v>
       </c>
       <c r="BS19" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT19" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BV19" t="n">
         <v>28</v>
       </c>
       <c r="BW19" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX19" t="n">
         <v>29</v>
       </c>
       <c r="BY19" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -5432,13 +5432,13 @@
         <v>2.28</v>
       </c>
       <c r="G20" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H20" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I20" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J20" t="n">
         <v>3.65</v>
@@ -5447,67 +5447,67 @@
         <v>3.9</v>
       </c>
       <c r="L20" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O20" t="n">
         <v>1.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R20" t="n">
         <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T20" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U20" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V20" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W20" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X20" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z20" t="n">
         <v>25</v>
       </c>
       <c r="AA20" t="n">
-        <v>55</v>
+        <v>290</v>
       </c>
       <c r="AB20" t="n">
         <v>13</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD20" t="n">
         <v>14.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AF20" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG20" t="n">
         <v>12</v>
@@ -5516,7 +5516,7 @@
         <v>16</v>
       </c>
       <c r="AI20" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="AJ20" t="n">
         <v>32</v>
@@ -5525,28 +5525,28 @@
         <v>24</v>
       </c>
       <c r="AL20" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AM20" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
         <v>15</v>
       </c>
       <c r="AO20" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AP20" t="n">
         <v>16.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR20" t="n">
         <v>20</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="AT20" t="n">
         <v>11</v>
@@ -5555,7 +5555,7 @@
         <v>7.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW20" t="n">
         <v>27</v>
@@ -5567,28 +5567,28 @@
         <v>10</v>
       </c>
       <c r="AZ20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA20" t="n">
         <v>30</v>
       </c>
       <c r="BB20" t="n">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="BC20" t="n">
         <v>19.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="BE20" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="BF20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG20" t="n">
-        <v>7.4</v>
+        <v>18</v>
       </c>
       <c r="BH20" t="n">
         <v>4.1</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -5695,19 +5695,19 @@
         <v>7</v>
       </c>
       <c r="J21" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K21" t="n">
         <v>5.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M21" t="n">
         <v>1.04</v>
       </c>
       <c r="N21" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O21" t="n">
         <v>1.23</v>
@@ -5719,7 +5719,7 @@
         <v>1.68</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S21" t="n">
         <v>2.74</v>
@@ -5845,68 +5845,68 @@
         <v>10.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI21" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ21" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.76</v>
+        <v>6.6</v>
       </c>
       <c r="BL21" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM21" t="n">
-        <v>2</v>
+        <v>11.5</v>
       </c>
       <c r="BN21" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="BO21" t="n">
-        <v>2.96</v>
+        <v>3.8</v>
       </c>
       <c r="BP21" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.74</v>
+        <v>6.2</v>
       </c>
       <c r="BR21" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.88</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT21" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.76</v>
+        <v>6.6</v>
       </c>
       <c r="BV21" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.95</v>
+        <v>10.5</v>
       </c>
       <c r="BX21" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.95</v>
+        <v>10.5</v>
       </c>
       <c r="BZ21" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.83</v>
+        <v>7</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="G22" t="n">
         <v>1000</v>
@@ -5949,7 +5949,7 @@
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -5961,13 +5961,13 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.09</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
         <v>1.28</v>
       </c>
       <c r="P22" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Q22" t="n">
         <v>1.28</v>
@@ -5976,7 +5976,7 @@
         <v>1.07</v>
       </c>
       <c r="S22" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
         <v>1.07</v>
       </c>
       <c r="S23" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T23" t="n">
         <v>1.01</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -6541,7 +6541,7 @@
         <v>29</v>
       </c>
       <c r="AL24" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -6550,7 +6550,7 @@
         <v>22</v>
       </c>
       <c r="AO24" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP24" t="n">
         <v>5.3</v>
@@ -6580,16 +6580,16 @@
         <v>5.4</v>
       </c>
       <c r="AY24" t="n">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
         <v>5.6</v>
       </c>
       <c r="BA24" t="n">
-        <v>6.8</v>
+        <v>29</v>
       </c>
       <c r="BB24" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="BC24" t="n">
         <v>6.2</v>
@@ -6604,7 +6604,7 @@
         <v>17</v>
       </c>
       <c r="BG24" t="n">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="BH24" t="n">
         <v>4.5</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -6747,10 +6747,10 @@
         <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
         <v>4.9</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M26" t="n">
         <v>1.01</v>
@@ -7043,7 +7043,7 @@
         <v>27</v>
       </c>
       <c r="AJ26" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK26" t="n">
         <v>22</v>
@@ -7106,7 +7106,7 @@
         <v>19.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>27</v>
+        <v>7.4</v>
       </c>
       <c r="BF26" t="n">
         <v>6.4</v>
@@ -7115,68 +7115,68 @@
         <v>8.4</v>
       </c>
       <c r="BH26" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="BI26" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="BJ26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>20</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>19</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>22</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BZ26" t="n">
         <v>11.5</v>
       </c>
-      <c r="BK26" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM26" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BN26" t="n">
-        <v>9</v>
-      </c>
-      <c r="BO26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP26" t="n">
-        <v>21</v>
-      </c>
-      <c r="BQ26" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BR26" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS26" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BT26" t="n">
-        <v>10</v>
-      </c>
-      <c r="BU26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV26" t="n">
-        <v>26</v>
-      </c>
-      <c r="BW26" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BX26" t="n">
-        <v>30</v>
-      </c>
-      <c r="BY26" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BZ26" t="n">
-        <v>15.5</v>
-      </c>
       <c r="CA26" t="n">
-        <v>2.46</v>
+        <v>5.2</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -7225,7 +7225,7 @@
         <v>4.1</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M27" t="n">
         <v>1.05</v>
@@ -7369,13 +7369,13 @@
         <v>10</v>
       </c>
       <c r="BH27" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI27" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BJ27" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK27" t="n">
         <v>1.01</v>
@@ -7387,50 +7387,50 @@
         <v>1.01</v>
       </c>
       <c r="BN27" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO27" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BP27" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ27" t="n">
         <v>1.01</v>
       </c>
       <c r="BR27" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS27" t="n">
         <v>1.01</v>
       </c>
       <c r="BT27" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BV27" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BW27" t="n">
         <v>1.01</v>
       </c>
       <c r="BX27" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY27" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ27" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA27" t="n">
         <v>1.01</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -7497,7 +7497,7 @@
         <v>1.72</v>
       </c>
       <c r="R28" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S28" t="n">
         <v>1.72</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -7739,7 +7739,7 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="O29" t="n">
         <v>1.37</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G30" t="n">
         <v>3.9</v>
@@ -8008,7 +8008,7 @@
         <v>1.46</v>
       </c>
       <c r="S30" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T30" t="n">
         <v>1.61</v>
@@ -8077,58 +8077,58 @@
         <v>970</v>
       </c>
       <c r="AP30" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AQ30" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AR30" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AS30" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AU30" t="n">
         <v>3.5</v>
       </c>
       <c r="AV30" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AW30" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AX30" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AY30" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AZ30" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BA30" t="n">
         <v>4</v>
       </c>
       <c r="BB30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC30" t="n">
         <v>4.2</v>
       </c>
-      <c r="BC30" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BD30" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE30" t="n">
         <v>4.3</v>
       </c>
       <c r="BF30" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BG30" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BH30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -8250,19 +8250,19 @@
         <v>1.09</v>
       </c>
       <c r="O31" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P31" t="n">
         <v>1.09</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="R31" t="n">
         <v>1.08</v>
       </c>
       <c r="S31" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T31" t="n">
         <v>1.01</v>
@@ -8274,7 +8274,7 @@
         <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -8495,16 +8495,16 @@
         <v>4.4</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N32" t="n">
         <v>1.9</v>
       </c>
       <c r="O32" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P32" t="n">
         <v>1.9</v>
@@ -8513,16 +8513,16 @@
         <v>1.82</v>
       </c>
       <c r="R32" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S32" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="T32" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U32" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="V32" t="n">
         <v>2.04</v>
@@ -8531,58 +8531,58 @@
         <v>1.21</v>
       </c>
       <c r="X32" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y32" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z32" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA32" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AB32" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC32" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD32" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF32" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AG32" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH32" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI32" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL32" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM32" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO32" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AP32" t="n">
         <v>1.03</v>
@@ -8636,7 +8636,7 @@
         <v>1.01</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BH32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -8752,115 +8752,115 @@
         <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N33" t="n">
-        <v>2.52</v>
+        <v>2.94</v>
       </c>
       <c r="O33" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="P33" t="n">
         <v>1.65</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R33" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="S33" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V33" t="n">
         <v>1.46</v>
       </c>
       <c r="W33" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD33" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG33" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH33" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX33" t="n">
         <v>1.03</v>
@@ -8869,22 +8869,22 @@
         <v>1.03</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF33" t="n">
         <v>1.01</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -8985,22 +8985,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.04</v>
+        <v>1.9</v>
       </c>
       <c r="G34" t="n">
-        <v>1000</v>
+        <v>2.26</v>
       </c>
       <c r="H34" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="I34" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J34" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="K34" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -9009,22 +9009,22 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.06</v>
+        <v>3.1</v>
       </c>
       <c r="O34" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="P34" t="n">
-        <v>1.06</v>
+        <v>1.79</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.31</v>
+        <v>1.82</v>
       </c>
       <c r="R34" t="n">
-        <v>1.05</v>
+        <v>1.28</v>
       </c>
       <c r="S34" t="n">
-        <v>1.31</v>
+        <v>2.88</v>
       </c>
       <c r="T34" t="n">
         <v>1.01</v>
@@ -9033,10 +9033,10 @@
         <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -9251,7 +9251,7 @@
         <v>1000</v>
       </c>
       <c r="J35" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K35" t="n">
         <v>1000</v>
@@ -9263,13 +9263,13 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="O35" t="n">
         <v>1.01</v>
       </c>
       <c r="P35" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q35" t="n">
         <v>1.02</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -9505,7 +9505,7 @@
         <v>1000</v>
       </c>
       <c r="J36" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K36" t="n">
         <v>1000</v>
@@ -9520,13 +9520,13 @@
         <v>1.08</v>
       </c>
       <c r="O36" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P36" t="n">
         <v>1.08</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.65</v>
+        <v>1.02</v>
       </c>
       <c r="R36" t="n">
         <v>1.08</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -9762,10 +9762,10 @@
         <v>3.05</v>
       </c>
       <c r="K37" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M37" t="n">
         <v>1.08</v>
@@ -9864,7 +9864,7 @@
         <v>13</v>
       </c>
       <c r="AS37" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT37" t="n">
         <v>9</v>
@@ -9891,16 +9891,16 @@
         <v>4.4</v>
       </c>
       <c r="BB37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC37" t="n">
         <v>4.4</v>
       </c>
-      <c r="BC37" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BD37" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE37" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF37" t="n">
         <v>4.4</v>
@@ -9909,13 +9909,13 @@
         <v>4.2</v>
       </c>
       <c r="BH37" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="BI37" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BJ37" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BK37" t="n">
         <v>7.8</v>
@@ -9924,53 +9924,53 @@
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN37" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="BO37" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP37" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BQ37" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BR37" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS37" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT37" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="BU37" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="BV37" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BW37" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX37" t="n">
         <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ37" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10013,7 @@
         <v>1000</v>
       </c>
       <c r="J38" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K38" t="n">
         <v>1000</v>
@@ -10040,7 +10040,7 @@
         <v>1.08</v>
       </c>
       <c r="S38" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="T38" t="n">
         <v>1.01</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -10267,7 +10267,7 @@
         <v>1000</v>
       </c>
       <c r="J39" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K39" t="n">
         <v>1000</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -10521,7 +10521,7 @@
         <v>1000</v>
       </c>
       <c r="J40" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K40" t="n">
         <v>1000</v>
@@ -10548,7 +10548,7 @@
         <v>1.08</v>
       </c>
       <c r="S40" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="T40" t="n">
         <v>1.01</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -10775,7 +10775,7 @@
         <v>1000</v>
       </c>
       <c r="J41" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K41" t="n">
         <v>1000</v>
@@ -10793,7 +10793,7 @@
         <v>1.01</v>
       </c>
       <c r="P41" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q41" t="n">
         <v>1.02</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11029,7 @@
         <v>1000</v>
       </c>
       <c r="J42" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K42" t="n">
         <v>1000</v>
@@ -11056,7 +11056,7 @@
         <v>1.08</v>
       </c>
       <c r="S42" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="T42" t="n">
         <v>1.01</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
         <v>1000</v>
       </c>
       <c r="J43" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K43" t="n">
         <v>1000</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
         <v>1000</v>
       </c>
       <c r="J44" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K44" t="n">
         <v>1000</v>
@@ -11564,7 +11564,7 @@
         <v>1.08</v>
       </c>
       <c r="S44" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T44" t="n">
         <v>1.01</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -11791,7 +11791,7 @@
         <v>1000</v>
       </c>
       <c r="J45" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -12057,7 +12057,7 @@
         <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O46" t="n">
         <v>1.01</v>
@@ -12081,10 +12081,10 @@
         <v>1.01</v>
       </c>
       <c r="V46" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X46" t="n">
         <v>1000</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -12326,7 +12326,7 @@
         <v>1.08</v>
       </c>
       <c r="S47" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="T47" t="n">
         <v>1.01</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -12544,13 +12544,13 @@
         <v>2.62</v>
       </c>
       <c r="G48" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="H48" t="n">
         <v>2.76</v>
       </c>
       <c r="I48" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="J48" t="n">
         <v>2.98</v>
@@ -12559,16 +12559,16 @@
         <v>3.5</v>
       </c>
       <c r="L48" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M48" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N48" t="n">
-        <v>2.48</v>
+        <v>2.86</v>
       </c>
       <c r="O48" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="P48" t="n">
         <v>1.63</v>
@@ -12577,124 +12577,124 @@
         <v>2.24</v>
       </c>
       <c r="R48" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="S48" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="T48" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="U48" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V48" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W48" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X48" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y48" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z48" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA48" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB48" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC48" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD48" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE48" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF48" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG48" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH48" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI48" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK48" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL48" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM48" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN48" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO48" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT48" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AV48" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX48" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AY48" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AZ48" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA48" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC48" t="n">
         <v>1.03</v>
       </c>
       <c r="BD48" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF48" t="n">
         <v>1.01</v>
@@ -12703,58 +12703,58 @@
         <v>1.01</v>
       </c>
       <c r="BH48" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="BI48" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="BJ48" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK48" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL48" t="n">
         <v>1000</v>
       </c>
       <c r="BM48" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN48" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO48" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP48" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ48" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BR48" t="n">
         <v>1000</v>
       </c>
       <c r="BS48" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT48" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU48" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV48" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW48" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX48" t="n">
         <v>1000</v>
       </c>
       <c r="BY48" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ48" t="n">
         <v>0</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -12813,34 +12813,34 @@
         <v>4.1</v>
       </c>
       <c r="L49" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M49" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N49" t="n">
-        <v>1.98</v>
+        <v>3.75</v>
       </c>
       <c r="O49" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="P49" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="Q49" t="n">
         <v>1.68</v>
       </c>
       <c r="R49" t="n">
-        <v>1.07</v>
+        <v>1.46</v>
       </c>
       <c r="S49" t="n">
-        <v>1.68</v>
+        <v>2.46</v>
       </c>
       <c r="T49" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="U49" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V49" t="n">
         <v>1.56</v>
@@ -12849,112 +12849,112 @@
         <v>1.47</v>
       </c>
       <c r="X49" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y49" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z49" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA49" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB49" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AC49" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD49" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE49" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF49" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG49" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH49" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI49" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK49" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL49" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM49" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN49" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO49" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT49" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV49" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW49" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA49" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC49" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD49" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BG49" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BH49" t="n">
         <v>1000</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -13055,13 +13055,13 @@
         <v>1000</v>
       </c>
       <c r="H50" t="n">
-        <v>1.54</v>
+        <v>2.18</v>
       </c>
       <c r="I50" t="n">
         <v>1000</v>
       </c>
       <c r="J50" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K50" t="n">
         <v>1000</v>
@@ -13079,7 +13079,7 @@
         <v>1.45</v>
       </c>
       <c r="P50" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="Q50" t="n">
         <v>2.04</v>
@@ -13097,7 +13097,7 @@
         <v>1.01</v>
       </c>
       <c r="V50" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W50" t="n">
         <v>1.01</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -13309,7 +13309,7 @@
         <v>2.52</v>
       </c>
       <c r="H51" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="I51" t="n">
         <v>4.2</v>
@@ -13321,16 +13321,16 @@
         <v>3.5</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P51" t="n">
         <v>1.59</v>
@@ -13339,184 +13339,184 @@
         <v>2.34</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL51" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AN51" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AO51" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AP51" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AR51" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AS51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU51" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AV51" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX51" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY51" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB51" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC51" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH51" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BI51" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BJ51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ51" t="n">
         <v>0</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
@@ -13578,31 +13578,31 @@
         <v>1.01</v>
       </c>
       <c r="M52" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N52" t="n">
-        <v>1.67</v>
+        <v>2.96</v>
       </c>
       <c r="O52" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="P52" t="n">
         <v>1.67</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R52" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="S52" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="T52" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U52" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V52" t="n">
         <v>1.32</v>
@@ -13611,112 +13611,112 @@
         <v>1.75</v>
       </c>
       <c r="X52" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y52" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z52" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA52" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB52" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC52" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD52" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE52" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF52" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG52" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH52" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI52" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK52" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL52" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM52" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN52" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO52" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT52" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU52" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV52" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA52" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BD52" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BG52" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH52" t="n">
         <v>1000</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
@@ -896,7 +896,7 @@
         <v>1.07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q3" t="n">
         <v>1.38</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -1368,13 +1368,13 @@
         <v>1.99</v>
       </c>
       <c r="G4" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
@@ -1395,7 +1395,7 @@
         <v>1.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q4" t="n">
         <v>2.2</v>
@@ -1416,13 +1416,13 @@
         <v>1.27</v>
       </c>
       <c r="W4" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X4" t="n">
         <v>14</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z4" t="n">
         <v>50</v>
@@ -1437,10 +1437,10 @@
         <v>7.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AE4" t="n">
-        <v>970</v>
+        <v>760</v>
       </c>
       <c r="AF4" t="n">
         <v>11.5</v>
@@ -1458,7 +1458,7 @@
         <v>24</v>
       </c>
       <c r="AK4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL4" t="n">
         <v>170</v>
@@ -1467,7 +1467,7 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
@@ -1476,10 +1476,10 @@
         <v>10.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AS4" t="n">
         <v>38</v>
@@ -1500,7 +1500,7 @@
         <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
         <v>15.5</v>
@@ -1530,7 +1530,7 @@
         <v>3.15</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
@@ -1542,7 +1542,7 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BN4" t="n">
         <v>4.6</v>
@@ -1560,7 +1560,7 @@
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT4" t="n">
         <v>7.8</v>
@@ -1572,7 +1572,7 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
@@ -1581,14 +1581,14 @@
         <v>12</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA4" t="n">
         <v>10</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
         <v>2.62</v>
       </c>
       <c r="H5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I5" t="n">
         <v>3.3</v>
@@ -1637,34 +1637,34 @@
         <v>3.55</v>
       </c>
       <c r="L5" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O5" t="n">
         <v>1.39</v>
       </c>
       <c r="P5" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
         <v>2.18</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
         <v>1.87</v>
       </c>
       <c r="U5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V5" t="n">
         <v>1.44</v>
@@ -1673,10 +1673,10 @@
         <v>1.62</v>
       </c>
       <c r="X5" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z5" t="n">
         <v>24</v>
@@ -1691,19 +1691,19 @@
         <v>7.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
         <v>48</v>
       </c>
       <c r="AF5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG5" t="n">
         <v>14</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI5" t="n">
         <v>65</v>
@@ -1724,7 +1724,7 @@
         <v>32</v>
       </c>
       <c r="AO5" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AP5" t="n">
         <v>10.5</v>
@@ -1733,13 +1733,13 @@
         <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU5" t="n">
         <v>6.8</v>
@@ -1748,10 +1748,10 @@
         <v>12</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY5" t="n">
         <v>10.5</v>
@@ -1760,25 +1760,25 @@
         <v>16.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BF5" t="n">
         <v>20</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BH5" t="n">
         <v>3.15</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         <v>4.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1918,7 +1918,7 @@
         <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V6" t="n">
         <v>2.88</v>
@@ -1927,7 +1927,7 @@
         <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y6" t="n">
         <v>7.4</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
         <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
@@ -2298,13 +2298,13 @@
         <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN7" t="n">
         <v>4.6</v>
@@ -2322,35 +2322,35 @@
         <v>29</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT7" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU7" t="n">
         <v>5.1</v>
       </c>
       <c r="BV7" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ7" t="n">
         <v>25</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2662,7 @@
         <v>3.85</v>
       </c>
       <c r="O9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P9" t="n">
         <v>1.99</v>
@@ -2683,7 +2683,7 @@
         <v>1.95</v>
       </c>
       <c r="V9" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="W9" t="n">
         <v>1.17</v>
@@ -2749,7 +2749,7 @@
         <v>6.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AS9" t="n">
         <v>11.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="G10" t="n">
         <v>3.05</v>
@@ -2907,7 +2907,7 @@
         <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="M10" t="n">
         <v>1.1</v>
@@ -2916,31 +2916,31 @@
         <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P10" t="n">
         <v>1.66</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
         <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="T10" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U10" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V10" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W10" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X10" t="n">
         <v>12.5</v>
@@ -2976,7 +2976,7 @@
         <v>23</v>
       </c>
       <c r="AI10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ10" t="n">
         <v>55</v>
@@ -2991,7 +2991,7 @@
         <v>150</v>
       </c>
       <c r="AN10" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AO10" t="n">
         <v>46</v>
@@ -3030,7 +3030,7 @@
         <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BB10" t="n">
         <v>4.7</v>
@@ -3045,7 +3045,7 @@
         <v>5</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG10" t="n">
         <v>4.6</v>
@@ -3054,7 +3054,7 @@
         <v>3.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
@@ -3155,7 +3155,7 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3191,10 +3191,10 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -3421,22 +3421,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="O12" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="P12" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="R12" t="n">
         <v>1.07</v>
       </c>
       <c r="S12" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -3448,7 +3448,7 @@
         <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="G13" t="n">
         <v>6</v>
@@ -3663,19 +3663,19 @@
         <v>1.68</v>
       </c>
       <c r="J13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K13" t="n">
         <v>4.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M13" t="n">
         <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
         <v>1.22</v>
@@ -3720,7 +3720,7 @@
         <v>29</v>
       </c>
       <c r="AC13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD13" t="n">
         <v>10.5</v>
@@ -3783,7 +3783,7 @@
         <v>14</v>
       </c>
       <c r="AX13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY13" t="n">
         <v>8.199999999999999</v>
@@ -3795,86 +3795,86 @@
         <v>9.4</v>
       </c>
       <c r="BB13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE13" t="n">
         <v>11</v>
       </c>
-      <c r="BC13" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE13" t="n">
+      <c r="BF13" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>10</v>
       </c>
       <c r="BG13" t="n">
         <v>6.4</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BV13" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="O14" t="n">
         <v>1.01</v>
@@ -3953,10 +3953,10 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -4195,10 +4195,10 @@
         <v>1.43</v>
       </c>
       <c r="R15" t="n">
-        <v>2.04</v>
+        <v>1.07</v>
       </c>
       <c r="S15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -4416,55 +4416,55 @@
         <v>1.87</v>
       </c>
       <c r="G16" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
         <v>5.7</v>
       </c>
       <c r="J16" t="n">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="K16" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="L16" t="n">
         <v>1.41</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P16" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R16" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="S16" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="V16" t="n">
         <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X16" t="n">
         <v>970</v>
@@ -4521,58 +4521,58 @@
         <v>120</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH16" t="n">
         <v>3.2</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -4921,25 +4921,25 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G18" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="H18" t="n">
         <v>4.4</v>
       </c>
       <c r="I18" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K18" t="n">
         <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
@@ -4951,7 +4951,7 @@
         <v>1.35</v>
       </c>
       <c r="P18" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q18" t="n">
         <v>2.04</v>
@@ -4972,7 +4972,7 @@
         <v>1.27</v>
       </c>
       <c r="W18" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="X18" t="n">
         <v>15</v>
@@ -4984,7 +4984,7 @@
         <v>42</v>
       </c>
       <c r="AA18" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB18" t="n">
         <v>8.4</v>
@@ -4999,7 +4999,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG18" t="n">
         <v>12</v>
@@ -5014,16 +5014,16 @@
         <v>26</v>
       </c>
       <c r="AK18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL18" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM18" t="n">
         <v>150</v>
       </c>
       <c r="AN18" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO18" t="n">
         <v>100</v>
@@ -5035,10 +5035,10 @@
         <v>11.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AT18" t="n">
         <v>6.2</v>
@@ -5050,7 +5050,7 @@
         <v>14.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AX18" t="n">
         <v>8.800000000000001</v>
@@ -5062,7 +5062,7 @@
         <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BB18" t="n">
         <v>17</v>
@@ -5071,80 +5071,80 @@
         <v>16.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BF18" t="n">
         <v>12</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BH18" t="n">
         <v>3.3</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BJ18" t="n">
         <v>11</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN18" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP18" t="n">
         <v>14.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR18" t="n">
         <v>32</v>
       </c>
       <c r="BS18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT18" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV18" t="n">
         <v>44</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CA18" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="G19" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="H19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I19" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J19" t="n">
         <v>4.5</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L19" t="n">
         <v>1.19</v>
@@ -5199,7 +5199,7 @@
         <v>1.02</v>
       </c>
       <c r="N19" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="O19" t="n">
         <v>1.13</v>
@@ -5211,22 +5211,22 @@
         <v>1.4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="S19" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="T19" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="U19" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V19" t="n">
         <v>1.28</v>
       </c>
       <c r="W19" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="X19" t="n">
         <v>40</v>
@@ -5244,7 +5244,7 @@
         <v>18.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD19" t="n">
         <v>19.5</v>
@@ -5253,13 +5253,13 @@
         <v>42</v>
       </c>
       <c r="AF19" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG19" t="n">
         <v>12</v>
       </c>
       <c r="AH19" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI19" t="n">
         <v>38</v>
@@ -5268,7 +5268,7 @@
         <v>22</v>
       </c>
       <c r="AK19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL19" t="n">
         <v>23</v>
@@ -5277,25 +5277,25 @@
         <v>55</v>
       </c>
       <c r="AN19" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AO19" t="n">
         <v>24</v>
       </c>
       <c r="AP19" t="n">
-        <v>8.800000000000001</v>
+        <v>24</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="AR19" t="n">
         <v>34</v>
       </c>
       <c r="AS19" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="AT19" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU19" t="n">
         <v>10.5</v>
@@ -5304,7 +5304,7 @@
         <v>16</v>
       </c>
       <c r="AW19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX19" t="n">
         <v>14.5</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="BA19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB19" t="n">
         <v>18.5</v>
@@ -5328,13 +5328,13 @@
         <v>19</v>
       </c>
       <c r="BE19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BH19" t="n">
         <v>5.6</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="G20" t="n">
         <v>2.36</v>
@@ -5438,13 +5438,13 @@
         <v>3.2</v>
       </c>
       <c r="I20" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K20" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
         <v>1.3</v>
@@ -5453,19 +5453,19 @@
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O20" t="n">
         <v>1.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S20" t="n">
         <v>2.88</v>
@@ -5474,13 +5474,13 @@
         <v>1.64</v>
       </c>
       <c r="U20" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V20" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W20" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X20" t="n">
         <v>19.5</v>
@@ -5492,7 +5492,7 @@
         <v>25</v>
       </c>
       <c r="AA20" t="n">
-        <v>290</v>
+        <v>330</v>
       </c>
       <c r="AB20" t="n">
         <v>13</v>
@@ -5504,13 +5504,13 @@
         <v>14.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AF20" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH20" t="n">
         <v>16</v>
@@ -5522,10 +5522,10 @@
         <v>32</v>
       </c>
       <c r="AK20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL20" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
@@ -5534,7 +5534,7 @@
         <v>15</v>
       </c>
       <c r="AO20" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AP20" t="n">
         <v>16.5</v>
@@ -5570,10 +5570,10 @@
         <v>13.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BB20" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC20" t="n">
         <v>19.5</v>
@@ -5588,7 +5588,7 @@
         <v>13</v>
       </c>
       <c r="BG20" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BH20" t="n">
         <v>4.1</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -5686,13 +5686,13 @@
         <v>1.55</v>
       </c>
       <c r="G21" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H21" t="n">
         <v>6.2</v>
       </c>
       <c r="I21" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J21" t="n">
         <v>4.7</v>
@@ -5707,34 +5707,34 @@
         <v>1.04</v>
       </c>
       <c r="N21" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O21" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P21" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R21" t="n">
         <v>1.51</v>
       </c>
       <c r="S21" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T21" t="n">
         <v>1.83</v>
       </c>
       <c r="U21" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V21" t="n">
         <v>1.17</v>
       </c>
       <c r="W21" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X21" t="n">
         <v>22</v>
@@ -5785,7 +5785,7 @@
         <v>130</v>
       </c>
       <c r="AN21" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AO21" t="n">
         <v>110</v>
@@ -5839,7 +5839,7 @@
         <v>11</v>
       </c>
       <c r="BF21" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG21" t="n">
         <v>10.5</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="G22" t="n">
         <v>1000</v>
@@ -5949,7 +5949,7 @@
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -6454,7 +6454,7 @@
         <v>2.96</v>
       </c>
       <c r="I24" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J24" t="n">
         <v>3.2</v>
@@ -6493,7 +6493,7 @@
         <v>2.08</v>
       </c>
       <c r="V24" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
         <v>1.6</v>
@@ -6556,7 +6556,7 @@
         <v>5.3</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="AR24" t="n">
         <v>6</v>
@@ -6565,7 +6565,7 @@
         <v>7</v>
       </c>
       <c r="AT24" t="n">
-        <v>4.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU24" t="n">
         <v>6.6</v>
@@ -6577,7 +6577,7 @@
         <v>6.6</v>
       </c>
       <c r="AX24" t="n">
-        <v>5.4</v>
+        <v>13</v>
       </c>
       <c r="AY24" t="n">
         <v>9.800000000000001</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -6747,7 +6747,7 @@
         <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
         <v>1.01</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
         <v>7.8</v>
       </c>
       <c r="O26" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P26" t="n">
         <v>3.3</v>
@@ -7118,7 +7118,7 @@
         <v>5.8</v>
       </c>
       <c r="BI26" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BJ26" t="n">
         <v>8.4</v>
@@ -7136,7 +7136,7 @@
         <v>6.6</v>
       </c>
       <c r="BO26" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BP26" t="n">
         <v>15.5</v>
@@ -7154,7 +7154,7 @@
         <v>7.4</v>
       </c>
       <c r="BU26" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BV26" t="n">
         <v>19</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -7213,7 +7213,7 @@
         <v>4.2</v>
       </c>
       <c r="H27" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="I27" t="n">
         <v>2.06</v>
@@ -7225,7 +7225,7 @@
         <v>4.1</v>
       </c>
       <c r="L27" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M27" t="n">
         <v>1.05</v>
@@ -7300,7 +7300,7 @@
         <v>80</v>
       </c>
       <c r="AK27" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL27" t="n">
         <v>48</v>
@@ -7357,13 +7357,13 @@
         <v>9.6</v>
       </c>
       <c r="BD27" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE27" t="n">
         <v>10.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG27" t="n">
         <v>10</v>
@@ -7372,19 +7372,19 @@
         <v>3.85</v>
       </c>
       <c r="BI27" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ27" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BN27" t="n">
         <v>7.6</v>
@@ -7396,13 +7396,13 @@
         <v>32</v>
       </c>
       <c r="BQ27" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BR27" t="n">
         <v>38</v>
       </c>
       <c r="BS27" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BT27" t="n">
         <v>4.9</v>
@@ -7414,23 +7414,23 @@
         <v>13.5</v>
       </c>
       <c r="BW27" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX27" t="n">
         <v>25</v>
       </c>
       <c r="BY27" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BZ27" t="n">
         <v>19.5</v>
       </c>
       <c r="CA27" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -7485,22 +7485,22 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.12</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P28" t="n">
         <v>1.12</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.72</v>
+        <v>1.25</v>
       </c>
       <c r="R28" t="n">
-        <v>1.09</v>
+        <v>1.57</v>
       </c>
       <c r="S28" t="n">
-        <v>1.72</v>
+        <v>1.24</v>
       </c>
       <c r="T28" t="n">
         <v>1.01</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
         <v>1.07</v>
       </c>
       <c r="S29" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="T29" t="n">
         <v>1.01</v>
@@ -7763,7 +7763,7 @@
         <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
         <v>1.02</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -8080,16 +8080,16 @@
         <v>3.9</v>
       </c>
       <c r="AQ30" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AR30" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="AS30" t="n">
         <v>3.95</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AU30" t="n">
         <v>3.5</v>
@@ -8098,7 +8098,7 @@
         <v>3.75</v>
       </c>
       <c r="AW30" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AX30" t="n">
         <v>4.3</v>
@@ -8107,7 +8107,7 @@
         <v>3.8</v>
       </c>
       <c r="AZ30" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BA30" t="n">
         <v>4</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
         <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
         <v>4.9</v>
       </c>
       <c r="J34" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K34" t="n">
         <v>4.2</v>
@@ -9006,10 +9006,10 @@
         <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N34" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O34" t="n">
         <v>1.29</v>
@@ -9021,16 +9021,16 @@
         <v>1.82</v>
       </c>
       <c r="R34" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S34" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="T34" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U34" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="V34" t="n">
         <v>1.26</v>
@@ -9039,112 +9039,112 @@
         <v>1.79</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM34" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH34" t="n">
         <v>1000</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -9517,7 +9517,7 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O36" t="n">
         <v>1.01</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -9753,7 +9753,7 @@
         <v>3.7</v>
       </c>
       <c r="H37" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I37" t="n">
         <v>2.68</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -11056,7 +11056,7 @@
         <v>1.08</v>
       </c>
       <c r="S42" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="T42" t="n">
         <v>1.01</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -12658,7 +12658,7 @@
         <v>13.5</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT48" t="n">
         <v>7</v>
@@ -12670,7 +12670,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AX48" t="n">
         <v>13</v>
@@ -12682,25 +12682,25 @@
         <v>14</v>
       </c>
       <c r="BA48" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BD48" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BG48" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BH48" t="n">
         <v>3.05</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -12819,13 +12819,13 @@
         <v>1.05</v>
       </c>
       <c r="N49" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="O49" t="n">
         <v>1.24</v>
       </c>
       <c r="P49" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q49" t="n">
         <v>1.68</v>
@@ -12834,10 +12834,10 @@
         <v>1.46</v>
       </c>
       <c r="S49" t="n">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="T49" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="U49" t="n">
         <v>2.32</v>
@@ -12852,10 +12852,10 @@
         <v>24</v>
       </c>
       <c r="Y49" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Z49" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA49" t="n">
         <v>44</v>
@@ -12870,10 +12870,10 @@
         <v>15</v>
       </c>
       <c r="AE49" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AF49" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AG49" t="n">
         <v>16</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -13420,7 +13420,7 @@
         <v>19</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT51" t="n">
         <v>6.2</v>
@@ -13432,7 +13432,7 @@
         <v>12</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX51" t="n">
         <v>10.5</v>
@@ -13444,25 +13444,25 @@
         <v>16</v>
       </c>
       <c r="BA51" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD51" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG51" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH51" t="n">
         <v>3.45</v>
@@ -13474,49 +13474,49 @@
         <v>1000</v>
       </c>
       <c r="BK51" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BL51" t="n">
         <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BN51" t="n">
         <v>1000</v>
       </c>
       <c r="BO51" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BP51" t="n">
         <v>1000</v>
       </c>
       <c r="BQ51" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BR51" t="n">
         <v>1000</v>
       </c>
       <c r="BS51" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BT51" t="n">
         <v>1000</v>
       </c>
       <c r="BU51" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BV51" t="n">
         <v>1000</v>
       </c>
       <c r="BW51" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BX51" t="n">
         <v>1000</v>
       </c>
       <c r="BY51" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BZ51" t="n">
         <v>0</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
         <v>3.45</v>
       </c>
       <c r="L52" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M52" t="n">
         <v>1.08</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-03 21:39:56</t>
+          <t>2026-07-03 23:57:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB52"/>
+  <dimension ref="A1:CB58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
         <v>2.08</v>
@@ -1383,7 +1383,7 @@
         <v>3.65</v>
       </c>
       <c r="L4" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="G5" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J5" t="n">
         <v>3.35</v>
@@ -1637,25 +1637,25 @@
         <v>3.55</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P5" t="n">
         <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1667,10 +1667,10 @@
         <v>2.06</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W5" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X5" t="n">
         <v>12.5</v>
@@ -1679,7 +1679,7 @@
         <v>11.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA5" t="n">
         <v>65</v>
@@ -1694,25 +1694,25 @@
         <v>14</v>
       </c>
       <c r="AE5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF5" t="n">
         <v>16</v>
       </c>
       <c r="AG5" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ5" t="n">
         <v>44</v>
       </c>
       <c r="AK5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL5" t="n">
         <v>55</v>
@@ -1721,7 +1721,7 @@
         <v>130</v>
       </c>
       <c r="AN5" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AO5" t="n">
         <v>44</v>
@@ -1736,10 +1736,10 @@
         <v>18</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU5" t="n">
         <v>6.8</v>
@@ -1748,7 +1748,7 @@
         <v>12</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AX5" t="n">
         <v>13.5</v>
@@ -1760,89 +1760,89 @@
         <v>16.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB5" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE5" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BF5" t="n">
         <v>20</v>
       </c>
       <c r="BG5" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH5" t="n">
         <v>3.15</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BO5" t="n">
         <v>4.3</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ5" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT5" t="n">
         <v>6.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA5" t="n">
         <v>10.5</v>
       </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>11</v>
-      </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         <v>4.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G7" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H7" t="n">
         <v>4.4</v>
@@ -2145,13 +2145,13 @@
         <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O7" t="n">
         <v>1.34</v>
@@ -2166,7 +2166,7 @@
         <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T7" t="n">
         <v>1.84</v>
@@ -2178,7 +2178,7 @@
         <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X7" t="n">
         <v>15.5</v>
@@ -2202,7 +2202,7 @@
         <v>18.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF7" t="n">
         <v>12</v>
@@ -2286,10 +2286,10 @@
         <v>11</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI7" t="n">
         <v>3.05</v>
@@ -2298,37 +2298,37 @@
         <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN7" t="n">
         <v>4.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BP7" t="n">
         <v>13.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR7" t="n">
         <v>29</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT7" t="n">
         <v>8</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
@@ -2340,17 +2340,17 @@
         <v>55</v>
       </c>
       <c r="BY7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CA7" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
         <v>2.12</v>
       </c>
       <c r="I8" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J8" t="n">
         <v>3.6</v>
@@ -2423,13 +2423,13 @@
         <v>3.05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U8" t="n">
         <v>2.18</v>
       </c>
       <c r="V8" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="W8" t="n">
         <v>1.36</v>
@@ -2447,10 +2447,10 @@
         <v>32</v>
       </c>
       <c r="AB8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
         <v>13</v>
@@ -2459,10 +2459,10 @@
         <v>26</v>
       </c>
       <c r="AF8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH8" t="n">
         <v>19.5</v>
@@ -2546,65 +2546,65 @@
         <v>3.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ8" t="n">
         <v>9.6</v>
       </c>
       <c r="BK8" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BN8" t="n">
         <v>7.2</v>
       </c>
       <c r="BO8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT8" t="n">
         <v>5.4</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>5.3</v>
       </c>
       <c r="BU8" t="n">
         <v>4.1</v>
       </c>
       <c r="BV8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA8" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G9" t="n">
         <v>7.2</v>
@@ -2644,7 +2644,7 @@
         <v>1.58</v>
       </c>
       <c r="I9" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="J9" t="n">
         <v>4.1</v>
@@ -2662,7 +2662,7 @@
         <v>3.85</v>
       </c>
       <c r="O9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P9" t="n">
         <v>1.99</v>
@@ -2677,13 +2677,13 @@
         <v>3.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U9" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="V9" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="W9" t="n">
         <v>1.17</v>
@@ -2713,10 +2713,10 @@
         <v>21</v>
       </c>
       <c r="AF9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AG9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AH9" t="n">
         <v>27</v>
@@ -2725,7 +2725,7 @@
         <v>44</v>
       </c>
       <c r="AJ9" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AK9" t="n">
         <v>120</v>
@@ -2737,7 +2737,7 @@
         <v>150</v>
       </c>
       <c r="AN9" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AO9" t="n">
         <v>11</v>
@@ -2746,13 +2746,13 @@
         <v>12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT9" t="n">
         <v>15.5</v>
@@ -2770,16 +2770,16 @@
         <v>4</v>
       </c>
       <c r="AY9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BC9" t="n">
         <v>4.1</v>
@@ -2788,10 +2788,10 @@
         <v>4.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BG9" t="n">
         <v>6.8</v>
@@ -2800,19 +2800,19 @@
         <v>3.7</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BJ9" t="n">
         <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN9" t="n">
         <v>10</v>
@@ -2824,41 +2824,41 @@
         <v>60</v>
       </c>
       <c r="BQ9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BV9" t="n">
         <v>11</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BX9" t="n">
         <v>26</v>
       </c>
       <c r="BY9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
         <v>19.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -2892,13 +2892,13 @@
         <v>2.68</v>
       </c>
       <c r="G10" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H10" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I10" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
@@ -2907,43 +2907,43 @@
         <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="M10" t="n">
         <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
         <v>1.41</v>
       </c>
       <c r="P10" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R10" t="n">
         <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U10" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W10" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="n">
         <v>11.5</v>
@@ -2952,7 +2952,7 @@
         <v>22</v>
       </c>
       <c r="AA10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB10" t="n">
         <v>11.5</v>
@@ -2964,7 +2964,7 @@
         <v>15.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF10" t="n">
         <v>21</v>
@@ -2976,7 +2976,7 @@
         <v>23</v>
       </c>
       <c r="AI10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ10" t="n">
         <v>55</v>
@@ -2985,13 +2985,13 @@
         <v>42</v>
       </c>
       <c r="AL10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM10" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO10" t="n">
         <v>46</v>
@@ -3000,16 +3000,16 @@
         <v>8.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AR10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AS10" t="n">
         <v>4.7</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU10" t="n">
         <v>5.8</v>
@@ -3018,76 +3018,76 @@
         <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.6</v>
+        <v>29</v>
       </c>
       <c r="AX10" t="n">
         <v>13.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
         <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB10" t="n">
         <v>4.7</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.6</v>
+        <v>26</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BE10" t="n">
         <v>5</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.5</v>
+        <v>26</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.6</v>
+        <v>30</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BT10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BU10" t="n">
         <v>4.6</v>
@@ -3096,23 +3096,23 @@
         <v>26</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX10" t="n">
         <v>44</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BZ10" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
@@ -3167,7 +3167,7 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="O11" t="n">
         <v>1.02</v>
@@ -3191,10 +3191,10 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -3421,13 +3421,13 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="O12" t="n">
         <v>1.37</v>
       </c>
       <c r="P12" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Q12" t="n">
         <v>1.37</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
         <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O13" t="n">
         <v>1.22</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="O15" t="n">
         <v>1.02</v>
@@ -4198,7 +4198,7 @@
         <v>1.07</v>
       </c>
       <c r="S15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -4207,7 +4207,7 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
         <v>1.02</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -4404,239 +4404,239 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Foshan Nanshi FC</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.87</v>
+        <v>2.76</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1</v>
+        <v>3.15</v>
       </c>
       <c r="H16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N16" t="n">
         <v>4</v>
       </c>
-      <c r="I16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="O16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X16" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW16" t="n">
         <v>3.8</v>
       </c>
-      <c r="L16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="AX16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>3.55</v>
       </c>
-      <c r="T16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="X16" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC16" t="n">
+      <c r="BA16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BJ16" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AD16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP16" t="n">
+      <c r="BK16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>22</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU16" t="n">
         <v>3.7</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ16" t="n">
+      <c r="BV16" t="n">
+        <v>18</v>
+      </c>
+      <c r="BW16" t="n">
         <v>6.2</v>
       </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>1.5</v>
-      </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.51</v>
+        <v>7</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.48</v>
+        <v>6.4</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -4658,239 +4658,239 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Foshan Nanshi FC</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.76</v>
+        <v>1.87</v>
       </c>
       <c r="G17" t="n">
-        <v>3.15</v>
+        <v>2.1</v>
       </c>
       <c r="H17" t="n">
-        <v>2.38</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>2.68</v>
+        <v>5.7</v>
       </c>
       <c r="J17" t="n">
-        <v>3.55</v>
+        <v>2.86</v>
       </c>
       <c r="K17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X17" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV17" t="n">
         <v>4.1</v>
       </c>
-      <c r="L17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R17" t="n">
+      <c r="AW17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA17" t="n">
         <v>1.48</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X17" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>22</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>6</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>18</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>7</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>20</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>6.4</v>
-      </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
         <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>1.77</v>
       </c>
       <c r="G19" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H19" t="n">
         <v>4.3</v>
@@ -5187,7 +5187,7 @@
         <v>4.6</v>
       </c>
       <c r="J19" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K19" t="n">
         <v>4.9</v>
@@ -5202,7 +5202,7 @@
         <v>7.8</v>
       </c>
       <c r="O19" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P19" t="n">
         <v>3.25</v>
@@ -5211,7 +5211,7 @@
         <v>1.4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="S19" t="n">
         <v>1.98</v>
@@ -5226,7 +5226,7 @@
         <v>1.28</v>
       </c>
       <c r="W19" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X19" t="n">
         <v>40</v>
@@ -5235,7 +5235,7 @@
         <v>30</v>
       </c>
       <c r="Z19" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA19" t="n">
         <v>85</v>
@@ -5364,7 +5364,7 @@
         <v>11</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR19" t="n">
         <v>18</v>
@@ -5394,11 +5394,11 @@
         <v>10.5</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -5432,19 +5432,19 @@
         <v>2.24</v>
       </c>
       <c r="G20" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H20" t="n">
         <v>3.2</v>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J20" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K20" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L20" t="n">
         <v>1.3</v>
@@ -5456,7 +5456,7 @@
         <v>4.7</v>
       </c>
       <c r="O20" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P20" t="n">
         <v>2.22</v>
@@ -5486,13 +5486,13 @@
         <v>19.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z20" t="n">
         <v>25</v>
       </c>
       <c r="AA20" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AB20" t="n">
         <v>13</v>
@@ -5504,10 +5504,10 @@
         <v>14.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF20" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG20" t="n">
         <v>11.5</v>
@@ -5525,7 +5525,7 @@
         <v>23</v>
       </c>
       <c r="AL20" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
@@ -5534,13 +5534,13 @@
         <v>15</v>
       </c>
       <c r="AO20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP20" t="n">
         <v>16.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR20" t="n">
         <v>20</v>
@@ -5585,10 +5585,10 @@
         <v>32</v>
       </c>
       <c r="BF20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BH20" t="n">
         <v>4.1</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
         <v>1.17</v>
       </c>
       <c r="W21" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="X21" t="n">
         <v>22</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="G22" t="n">
         <v>1000</v>
@@ -5961,13 +5961,13 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>3.2</v>
+        <v>1.09</v>
       </c>
       <c r="O22" t="n">
         <v>1.28</v>
       </c>
       <c r="P22" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Q22" t="n">
         <v>1.28</v>
@@ -5985,7 +5985,7 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
         <v>1.02</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6182,246 +6182,246 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FK Atyrau</t>
+          <t>Ypiranga RS</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FK Kaspyi Aktau</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="H23" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="J23" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>1.12</v>
+        <v>3.4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1</v>
+        <v>1.81</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.45</v>
+        <v>1.93</v>
       </c>
       <c r="R23" t="n">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>1.45</v>
+        <v>3.35</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.6</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.03</v>
+        <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BH23" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BJ23" t="n">
         <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BN23" t="n">
         <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BP23" t="n">
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BT23" t="n">
         <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6436,239 +6436,239 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ypiranga RS</t>
+          <t>FK Aktobe</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>FC Zhetysu</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="G24" t="n">
-        <v>2.64</v>
+        <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>2.96</v>
+        <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="K24" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
       </c>
       <c r="M24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R24" t="n">
         <v>1.07</v>
       </c>
-      <c r="N24" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.33</v>
-      </c>
       <c r="S24" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="T24" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>1.6</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="AQ24" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR24" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AS24" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV24" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AW24" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX24" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ24" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="BA24" t="n">
-        <v>29</v>
+        <v>1.03</v>
       </c>
       <c r="BB24" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BC24" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BD24" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE24" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF24" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="BJ24" t="n">
         <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BN24" t="n">
         <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BT24" t="n">
         <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -6690,12 +6690,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FK Aktobe</t>
+          <t>FK Atyrau</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FC Zhetysu</t>
+          <t>FK Kaspyi Aktau</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -6723,22 +6723,22 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="O25" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="P25" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="R25" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="S25" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -6750,7 +6750,7 @@
         <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -6971,13 +6971,13 @@
         <v>4.9</v>
       </c>
       <c r="L26" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="M26" t="n">
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O26" t="n">
         <v>1.12</v>
@@ -6995,7 +6995,7 @@
         <v>1.89</v>
       </c>
       <c r="T26" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="U26" t="n">
         <v>3.05</v>
@@ -7109,7 +7109,7 @@
         <v>7.4</v>
       </c>
       <c r="BF26" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BG26" t="n">
         <v>8.4</v>
@@ -7130,7 +7130,7 @@
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BN26" t="n">
         <v>6.6</v>
@@ -7142,41 +7142,41 @@
         <v>15.5</v>
       </c>
       <c r="BQ26" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR26" t="n">
         <v>20</v>
       </c>
       <c r="BS26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BW26" t="n">
         <v>6.4</v>
-      </c>
-      <c r="BT26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV26" t="n">
-        <v>19</v>
-      </c>
-      <c r="BW26" t="n">
-        <v>6.2</v>
       </c>
       <c r="BX26" t="n">
         <v>22</v>
       </c>
       <c r="BY26" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BZ26" t="n">
         <v>11.5</v>
       </c>
       <c r="CA26" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -7210,13 +7210,13 @@
         <v>3.9</v>
       </c>
       <c r="G27" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H27" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="I27" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J27" t="n">
         <v>3.8</v>
@@ -7225,37 +7225,37 @@
         <v>4.1</v>
       </c>
       <c r="L27" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="M27" t="n">
         <v>1.05</v>
       </c>
       <c r="N27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O27" t="n">
         <v>1.26</v>
       </c>
       <c r="P27" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R27" t="n">
         <v>1.47</v>
       </c>
       <c r="S27" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T27" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U27" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V27" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="W27" t="n">
         <v>1.32</v>
@@ -7276,7 +7276,7 @@
         <v>17.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD27" t="n">
         <v>11</v>
@@ -7318,7 +7318,7 @@
         <v>16.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR27" t="n">
         <v>12</v>
@@ -7339,7 +7339,7 @@
         <v>17</v>
       </c>
       <c r="AX27" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY27" t="n">
         <v>14.5</v>
@@ -7348,25 +7348,25 @@
         <v>15</v>
       </c>
       <c r="BA27" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB27" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG27" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>10</v>
       </c>
       <c r="BH27" t="n">
         <v>3.85</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -7464,16 +7464,16 @@
         <v>1.09</v>
       </c>
       <c r="G28" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H28" t="n">
-        <v>5.9</v>
+        <v>3.7</v>
       </c>
       <c r="I28" t="n">
         <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="K28" t="n">
         <v>1000</v>
@@ -7485,7 +7485,7 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="O28" t="n">
         <v>1.25</v>
@@ -7497,7 +7497,7 @@
         <v>1.25</v>
       </c>
       <c r="R28" t="n">
-        <v>1.57</v>
+        <v>1.07</v>
       </c>
       <c r="S28" t="n">
         <v>1.24</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -7993,13 +7993,13 @@
         <v>1.04</v>
       </c>
       <c r="N30" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="O30" t="n">
         <v>1.22</v>
       </c>
       <c r="P30" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
         <v>1.64</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
         <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -8700,14 +8700,14 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8722,145 +8722,145 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="G33" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="H33" t="n">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="I33" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="J33" t="n">
-        <v>3.05</v>
+        <v>1.02</v>
       </c>
       <c r="K33" t="n">
-        <v>3.5</v>
+        <v>950</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>2.94</v>
+        <v>1.09</v>
       </c>
       <c r="O33" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="P33" t="n">
-        <v>1.65</v>
+        <v>1.08</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.26</v>
+        <v>1.49</v>
       </c>
       <c r="R33" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="S33" t="n">
-        <v>4.3</v>
+        <v>1.49</v>
       </c>
       <c r="T33" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="U33" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC33" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD33" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG33" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH33" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI33" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL33" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM33" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ33" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT33" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU33" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV33" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX33" t="n">
         <v>1.03</v>
@@ -8869,22 +8869,22 @@
         <v>1.03</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF33" t="n">
         <v>1.01</v>
@@ -8893,75 +8893,75 @@
         <v>1.01</v>
       </c>
       <c r="BH33" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="BI33" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BJ33" t="n">
         <v>1000</v>
       </c>
       <c r="BK33" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN33" t="n">
         <v>1000</v>
       </c>
       <c r="BO33" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP33" t="n">
         <v>1000</v>
       </c>
       <c r="BQ33" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR33" t="n">
         <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT33" t="n">
         <v>1000</v>
       </c>
       <c r="BU33" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV33" t="n">
         <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX33" t="n">
         <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8976,175 +8976,175 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Centro Atletico Fenix</t>
+          <t>HUSA Agadir</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Huracan del Paso</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.9</v>
+        <v>1.04</v>
       </c>
       <c r="G34" t="n">
-        <v>2.26</v>
+        <v>1000</v>
       </c>
       <c r="H34" t="n">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="J34" t="n">
-        <v>3.1</v>
+        <v>1.02</v>
       </c>
       <c r="K34" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>3.25</v>
+        <v>1.02</v>
       </c>
       <c r="O34" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="P34" t="n">
-        <v>1.79</v>
+        <v>1.08</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.82</v>
+        <v>1.49</v>
       </c>
       <c r="R34" t="n">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="S34" t="n">
-        <v>3.1</v>
+        <v>1.48</v>
       </c>
       <c r="T34" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="U34" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y34" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z34" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA34" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC34" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD34" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE34" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG34" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH34" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI34" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK34" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL34" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM34" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO34" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AQ34" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AR34" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS34" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="AV34" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AW34" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AX34" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY34" t="n">
-        <v>3.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB34" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BC34" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BF34" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BG34" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH34" t="n">
         <v>1000</v>
@@ -9201,21 +9201,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9225,17 +9225,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CA Germinal</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -9251,7 +9251,7 @@
         <v>1000</v>
       </c>
       <c r="J35" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K35" t="n">
         <v>1000</v>
@@ -9269,16 +9269,16 @@
         <v>1.01</v>
       </c>
       <c r="P35" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R35" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="S35" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="T35" t="n">
         <v>1.01</v>
@@ -9347,52 +9347,52 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF35" t="n">
         <v>1.01</v>
@@ -9455,21 +9455,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9479,17 +9479,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Olimpo</t>
+          <t>IRT Tanger</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Villa Mitre</t>
+          <t>CODM Meknes</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -9505,10 +9505,10 @@
         <v>1000</v>
       </c>
       <c r="J36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K36" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -9517,7 +9517,7 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="O36" t="n">
         <v>1.01</v>
@@ -9526,13 +9526,13 @@
         <v>1.08</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.02</v>
+        <v>1.52</v>
       </c>
       <c r="R36" t="n">
         <v>1.08</v>
       </c>
       <c r="S36" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="T36" t="n">
         <v>1.01</v>
@@ -9709,21 +9709,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -9733,251 +9733,251 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Union de Touarga</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="G37" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="H37" t="n">
-        <v>2.36</v>
+        <v>1.04</v>
       </c>
       <c r="I37" t="n">
-        <v>2.68</v>
+        <v>1000</v>
       </c>
       <c r="J37" t="n">
-        <v>3.05</v>
+        <v>1.02</v>
       </c>
       <c r="K37" t="n">
-        <v>3.5</v>
+        <v>950</v>
       </c>
       <c r="L37" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P37" t="n">
         <v>1.08</v>
       </c>
-      <c r="N37" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1.63</v>
-      </c>
       <c r="Q37" t="n">
-        <v>2.3</v>
+        <v>1.45</v>
       </c>
       <c r="R37" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="S37" t="n">
-        <v>4.3</v>
+        <v>1.45</v>
       </c>
       <c r="T37" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="U37" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="V37" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="X37" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y37" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z37" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA37" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC37" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD37" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE37" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AG37" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AH37" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI37" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ37" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AK37" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL37" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM37" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO37" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AQ37" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR37" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AS37" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AT37" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AU37" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV37" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW37" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AX37" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AY37" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ37" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA37" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB37" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC37" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE37" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF37" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG37" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH37" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI37" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="BJ37" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK37" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BN37" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO37" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP37" t="n">
         <v>1000</v>
       </c>
       <c r="BQ37" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BR37" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS37" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BT37" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU37" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV37" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW37" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX37" t="n">
         <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ37" t="n">
         <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9987,150 +9987,150 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sol De Mayo</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CA Kimberley</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="G38" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="H38" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="I38" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="J38" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="K38" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N38" t="n">
-        <v>1.09</v>
+        <v>2.94</v>
       </c>
       <c r="O38" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="P38" t="n">
-        <v>1.08</v>
+        <v>1.65</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.02</v>
+        <v>2.26</v>
       </c>
       <c r="R38" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="S38" t="n">
-        <v>1.52</v>
+        <v>4.3</v>
       </c>
       <c r="T38" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U38" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="W38" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="X38" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y38" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA38" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB38" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC38" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD38" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE38" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF38" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG38" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH38" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI38" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK38" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL38" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM38" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN38" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO38" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX38" t="n">
         <v>1.03</v>
@@ -10139,22 +10139,22 @@
         <v>1.03</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF38" t="n">
         <v>1.01</v>
@@ -10163,58 +10163,58 @@
         <v>1.01</v>
       </c>
       <c r="BH38" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI38" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BJ38" t="n">
         <v>1000</v>
       </c>
       <c r="BK38" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BN38" t="n">
         <v>1000</v>
       </c>
       <c r="BO38" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BP38" t="n">
         <v>1000</v>
       </c>
       <c r="BQ38" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BR38" t="n">
         <v>1000</v>
       </c>
       <c r="BS38" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BT38" t="n">
         <v>1000</v>
       </c>
       <c r="BU38" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BV38" t="n">
         <v>1000</v>
       </c>
       <c r="BW38" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BX38" t="n">
         <v>1000</v>
       </c>
       <c r="BY38" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BZ38" t="n">
         <v>0</v>
@@ -10224,14 +10224,14 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -10241,180 +10241,180 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CA Douglas Haig</t>
+          <t>Centro Atletico Fenix</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sportivo AC Las Parejas</t>
+          <t>Huracan del Paso</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.04</v>
+        <v>1.9</v>
       </c>
       <c r="G39" t="n">
-        <v>1000</v>
+        <v>2.32</v>
       </c>
       <c r="H39" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="I39" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J39" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="K39" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
       </c>
       <c r="M39" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N39" t="n">
-        <v>1.08</v>
+        <v>3.25</v>
       </c>
       <c r="O39" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="P39" t="n">
-        <v>1.08</v>
+        <v>1.79</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.02</v>
+        <v>1.82</v>
       </c>
       <c r="R39" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="S39" t="n">
-        <v>1.55</v>
+        <v>3.1</v>
       </c>
       <c r="T39" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U39" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="W39" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="X39" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z39" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA39" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB39" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC39" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF39" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG39" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI39" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK39" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL39" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM39" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN39" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO39" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AV39" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG39" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH39" t="n">
         <v>1000</v>
@@ -10478,14 +10478,14 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -10500,239 +10500,239 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Gimnasia Conc del Uruguay</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>9 de Julio Rafaela</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="G40" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="H40" t="n">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="I40" t="n">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="J40" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="K40" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="L40" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M40" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N40" t="n">
-        <v>1.09</v>
+        <v>2.84</v>
       </c>
       <c r="O40" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="P40" t="n">
-        <v>1.08</v>
+        <v>1.63</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.02</v>
+        <v>2.3</v>
       </c>
       <c r="R40" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="S40" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="T40" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="U40" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="V40" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="W40" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="X40" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA40" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB40" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC40" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF40" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG40" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH40" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI40" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK40" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL40" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM40" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN40" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO40" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG40" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH40" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI40" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BJ40" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK40" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BL40" t="n">
         <v>1000</v>
       </c>
       <c r="BM40" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN40" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO40" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BP40" t="n">
         <v>1000</v>
       </c>
       <c r="BQ40" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BR40" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS40" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT40" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU40" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV40" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW40" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX40" t="n">
         <v>1000</v>
       </c>
       <c r="BY40" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA40" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -10749,17 +10749,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Boca Unidos</t>
+          <t>Olimpo</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sarmiento de Resistencia</t>
+          <t>Villa Mitre</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -10793,7 +10793,7 @@
         <v>1.01</v>
       </c>
       <c r="P41" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q41" t="n">
         <v>1.02</v>
@@ -10802,7 +10802,7 @@
         <v>1.08</v>
       </c>
       <c r="S41" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="T41" t="n">
         <v>1.01</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -11003,21 +11003,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Def Belgrano VR</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Escobar FC</t>
+          <t>CA Germinal</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G42" t="n">
         <v>1000</v>
@@ -11029,7 +11029,7 @@
         <v>1000</v>
       </c>
       <c r="J42" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K42" t="n">
         <v>1000</v>
@@ -11041,7 +11041,7 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="O42" t="n">
         <v>1.01</v>
@@ -11056,7 +11056,7 @@
         <v>1.08</v>
       </c>
       <c r="S42" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="T42" t="n">
         <v>1.01</v>
@@ -11065,7 +11065,7 @@
         <v>1.01</v>
       </c>
       <c r="V42" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W42" t="n">
         <v>1.01</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -11257,17 +11257,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Sportivo Belgrano</t>
+          <t>Sol De Mayo</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Independiente Chivilcoy</t>
+          <t>CA Kimberley</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -11511,17 +11511,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Gimnasia y Chivilcoy</t>
+          <t>CA Douglas Haig</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Club Atletico el Linqueno</t>
+          <t>Sportivo AC Las Parejas</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -11549,7 +11549,7 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="O44" t="n">
         <v>1.01</v>
@@ -11564,7 +11564,7 @@
         <v>1.08</v>
       </c>
       <c r="S44" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="T44" t="n">
         <v>1.01</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -11765,17 +11765,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>San Martin de Mendoza</t>
+          <t>Gimnasia Conc del Uruguay</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportivo Rincon</t>
+          <t>9 de Julio Rafaela</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -11809,7 +11809,7 @@
         <v>1.01</v>
       </c>
       <c r="P45" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q45" t="n">
         <v>1.02</v>
@@ -11818,7 +11818,7 @@
         <v>1.08</v>
       </c>
       <c r="S45" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="T45" t="n">
         <v>1.01</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -12019,17 +12019,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>General SMF</t>
+          <t>Boca Unidos</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>C J Antoniana</t>
+          <t>Sarmiento de Resistencia</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -12045,7 +12045,7 @@
         <v>1000</v>
       </c>
       <c r="J46" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="K46" t="n">
         <v>1000</v>
@@ -12063,7 +12063,7 @@
         <v>1.01</v>
       </c>
       <c r="P46" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q46" t="n">
         <v>1.02</v>
@@ -12072,7 +12072,7 @@
         <v>1.08</v>
       </c>
       <c r="S46" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T46" t="n">
         <v>1.01</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
@@ -12273,17 +12273,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Tucuman Central</t>
+          <t>Def Belgrano VR</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sol de America de Formosa</t>
+          <t>Escobar FC</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -12299,7 +12299,7 @@
         <v>1000</v>
       </c>
       <c r="J47" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="K47" t="n">
         <v>1000</v>
@@ -12311,7 +12311,7 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="O47" t="n">
         <v>1.01</v>
@@ -12326,7 +12326,7 @@
         <v>1.08</v>
       </c>
       <c r="S47" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="T47" t="n">
         <v>1.01</v>
@@ -12335,10 +12335,10 @@
         <v>1.01</v>
       </c>
       <c r="V47" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W47" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X47" t="n">
         <v>1000</v>
@@ -12503,21 +12503,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ47" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA47" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12527,234 +12527,234 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Tacuarembo</t>
+          <t>Sportivo Belgrano</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cerrito</t>
+          <t>Independiente Chivilcoy</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="G48" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="H48" t="n">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="I48" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="J48" t="n">
-        <v>2.98</v>
+        <v>1.03</v>
       </c>
       <c r="K48" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="L48" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M48" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>2.86</v>
+        <v>1.09</v>
       </c>
       <c r="O48" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="P48" t="n">
-        <v>1.63</v>
+        <v>1.08</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.24</v>
+        <v>1.02</v>
       </c>
       <c r="R48" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="S48" t="n">
-        <v>4.3</v>
+        <v>1.52</v>
       </c>
       <c r="T48" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="U48" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="V48" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="W48" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="X48" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y48" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z48" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA48" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB48" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC48" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD48" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE48" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF48" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG48" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH48" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI48" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ48" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK48" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AL48" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM48" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN48" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AO48" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ48" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AR48" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS48" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AT48" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AU48" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV48" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AW48" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX48" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AY48" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ48" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BA48" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BB48" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BC48" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BD48" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BE48" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF48" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG48" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BH48" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI48" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BJ48" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK48" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL48" t="n">
         <v>1000</v>
       </c>
       <c r="BM48" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN48" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO48" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP48" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ48" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BR48" t="n">
         <v>1000</v>
       </c>
       <c r="BS48" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BT48" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU48" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV48" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW48" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX48" t="n">
         <v>1000</v>
       </c>
       <c r="BY48" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ48" t="n">
         <v>0</v>
@@ -12764,14 +12764,14 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -12781,126 +12781,126 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Gimnasia y Chivilcoy</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>Club Atletico el Linqueno</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="G49" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="H49" t="n">
-        <v>2.42</v>
+        <v>1.04</v>
       </c>
       <c r="I49" t="n">
-        <v>2.76</v>
+        <v>1000</v>
       </c>
       <c r="J49" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="K49" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L49" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M49" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="O49" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="P49" t="n">
-        <v>2.14</v>
+        <v>1.08</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.68</v>
+        <v>1.02</v>
       </c>
       <c r="R49" t="n">
-        <v>1.46</v>
+        <v>1.08</v>
       </c>
       <c r="S49" t="n">
-        <v>2.74</v>
+        <v>1.49</v>
       </c>
       <c r="T49" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="U49" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="V49" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="W49" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="X49" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y49" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z49" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA49" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AB49" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AC49" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD49" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE49" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF49" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG49" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH49" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI49" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ49" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK49" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL49" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM49" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN49" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO49" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AP49" t="n">
         <v>1.03</v>
@@ -12951,10 +12951,10 @@
         <v>1.03</v>
       </c>
       <c r="BF49" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BG49" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH49" t="n">
         <v>1000</v>
@@ -13011,21 +13011,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ49" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -13035,60 +13035,60 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Delfin</t>
+          <t>San Martin de Mendoza</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Deportivo Rincon</t>
         </is>
       </c>
       <c r="F50" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N50" t="n">
         <v>1.09</v>
       </c>
-      <c r="G50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H50" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="K50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N50" t="n">
-        <v>1.36</v>
-      </c>
       <c r="O50" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="P50" t="n">
-        <v>1.36</v>
+        <v>1.07</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.04</v>
+        <v>1.02</v>
       </c>
       <c r="R50" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="S50" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="T50" t="n">
         <v>1.01</v>
@@ -13157,52 +13157,52 @@
         <v>1000</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF50" t="n">
         <v>1.01</v>
@@ -13265,21 +13265,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ50" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA50" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -13289,234 +13289,234 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Colon FC</t>
+          <t>General SMF</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Uruguay Montevideo FC</t>
+          <t>C J Antoniana</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.22</v>
+        <v>1.04</v>
       </c>
       <c r="G51" t="n">
-        <v>2.52</v>
+        <v>1000</v>
       </c>
       <c r="H51" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="I51" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="J51" t="n">
-        <v>2.98</v>
+        <v>1.06</v>
       </c>
       <c r="K51" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="L51" t="n">
         <v>1.01</v>
       </c>
       <c r="M51" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N51" t="n">
-        <v>2.74</v>
+        <v>1.09</v>
       </c>
       <c r="O51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S51" t="n">
         <v>1.45</v>
       </c>
-      <c r="P51" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S51" t="n">
-        <v>4.3</v>
-      </c>
       <c r="T51" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="U51" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="V51" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="W51" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="X51" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y51" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z51" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA51" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB51" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC51" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD51" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE51" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF51" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG51" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH51" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI51" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ51" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK51" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL51" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM51" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN51" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO51" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP51" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ51" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR51" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AS51" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AT51" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU51" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="AV51" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AW51" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AX51" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY51" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ51" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BA51" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB51" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC51" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD51" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BE51" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BF51" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG51" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH51" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI51" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="BJ51" t="n">
         <v>1000</v>
       </c>
       <c r="BK51" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="BL51" t="n">
         <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="BN51" t="n">
         <v>1000</v>
       </c>
       <c r="BO51" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="BP51" t="n">
         <v>1000</v>
       </c>
       <c r="BQ51" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="BR51" t="n">
         <v>1000</v>
       </c>
       <c r="BS51" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="BT51" t="n">
         <v>1000</v>
       </c>
       <c r="BU51" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="BV51" t="n">
         <v>1000</v>
       </c>
       <c r="BW51" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="BX51" t="n">
         <v>1000</v>
       </c>
       <c r="BY51" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="BZ51" t="n">
         <v>0</v>
@@ -13526,261 +13526,1785 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-03 23:57:36</t>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>Argentinian Torneo A</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Tucuman Central</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Sol de America de Formosa</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB52" t="inlineStr">
+        <is>
+          <t>2026-07-04 02:16:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Tacuarembo</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Cerrito</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I53" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N53" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S53" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X53" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG53" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BH53" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI53" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ53" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK53" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM53" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN53" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO53" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP53" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ53" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS53" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT53" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU53" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV53" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW53" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY53" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB53" t="inlineStr">
+        <is>
+          <t>2026-07-04 02:16:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>HFX Wanderers</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G54" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J54" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K54" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S54" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X54" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF54" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG54" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BH54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB54" t="inlineStr">
+        <is>
+          <t>2026-07-04 02:16:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Delfin</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Emelec</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB55" t="inlineStr">
+        <is>
+          <t>2026-07-04 02:16:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Colon FC</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Uruguay Montevideo FC</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I56" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N56" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O56" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S56" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X56" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG56" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH56" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI56" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BJ56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK56" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BL56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ56" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BR56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS56" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BT56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU56" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BV56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW56" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BX56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY56" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BZ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB56" t="inlineStr">
+        <is>
+          <t>2026-07-04 02:16:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Nautico PE</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Juventude</t>
         </is>
       </c>
-      <c r="F52" t="n">
+      <c r="F57" t="n">
         <v>2.18</v>
       </c>
-      <c r="G52" t="n">
+      <c r="G57" t="n">
         <v>2.32</v>
       </c>
-      <c r="H52" t="n">
+      <c r="H57" t="n">
         <v>3.8</v>
       </c>
-      <c r="I52" t="n">
+      <c r="I57" t="n">
         <v>4.2</v>
       </c>
-      <c r="J52" t="n">
+      <c r="J57" t="n">
         <v>3.2</v>
       </c>
-      <c r="K52" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L52" t="n">
+      <c r="K57" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L57" t="n">
         <v>1.42</v>
       </c>
-      <c r="M52" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N52" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="O52" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="P52" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R52" t="n">
+      <c r="M57" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N57" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R57" t="n">
         <v>1.24</v>
       </c>
-      <c r="S52" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U52" t="n">
+      <c r="S57" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
         <v>1.9</v>
       </c>
-      <c r="V52" t="n">
+      <c r="V57" t="n">
         <v>1.32</v>
       </c>
-      <c r="W52" t="n">
+      <c r="W57" t="n">
         <v>1.75</v>
       </c>
-      <c r="X52" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y52" t="n">
+      <c r="X57" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y57" t="n">
         <v>12</v>
       </c>
-      <c r="Z52" t="n">
+      <c r="Z57" t="n">
         <v>34</v>
       </c>
-      <c r="AA52" t="n">
+      <c r="AA57" t="n">
         <v>110</v>
       </c>
-      <c r="AB52" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC52" t="n">
+      <c r="AB57" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC57" t="n">
         <v>7.4</v>
       </c>
-      <c r="AD52" t="n">
+      <c r="AD57" t="n">
         <v>21</v>
       </c>
-      <c r="AE52" t="n">
+      <c r="AE57" t="n">
         <v>70</v>
       </c>
-      <c r="AF52" t="n">
+      <c r="AF57" t="n">
         <v>13.5</v>
       </c>
-      <c r="AG52" t="n">
+      <c r="AG57" t="n">
         <v>14</v>
       </c>
-      <c r="AH52" t="n">
+      <c r="AH57" t="n">
         <v>25</v>
       </c>
-      <c r="AI52" t="n">
+      <c r="AI57" t="n">
         <v>90</v>
       </c>
-      <c r="AJ52" t="n">
+      <c r="AJ57" t="n">
         <v>38</v>
       </c>
-      <c r="AK52" t="n">
+      <c r="AK57" t="n">
         <v>28</v>
       </c>
-      <c r="AL52" t="n">
+      <c r="AL57" t="n">
         <v>60</v>
       </c>
-      <c r="AM52" t="n">
+      <c r="AM57" t="n">
         <v>180</v>
       </c>
-      <c r="AN52" t="n">
+      <c r="AN57" t="n">
         <v>32</v>
       </c>
-      <c r="AO52" t="n">
+      <c r="AO57" t="n">
         <v>90</v>
       </c>
-      <c r="AP52" t="n">
+      <c r="AP57" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AQ52" t="n">
+      <c r="AQ57" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR52" t="n">
+      <c r="AR57" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC57" t="n">
         <v>4.8</v>
       </c>
-      <c r="AS52" t="n">
+      <c r="BD57" t="n">
         <v>5.3</v>
       </c>
-      <c r="AT52" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV52" t="n">
+      <c r="BE57" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG57" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BH57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI57" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK57" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM57" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO57" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ57" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS57" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU57" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW57" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY57" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA57" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB57" t="inlineStr">
+        <is>
+          <t>2026-07-04 02:16:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Anapolis GO</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Botafogo PB</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H58" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I58" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J58" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S58" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X58" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR58" t="n">
         <v>14.5</v>
       </c>
-      <c r="AW52" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY52" t="n">
+      <c r="AS58" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV58" t="n">
         <v>10</v>
       </c>
-      <c r="AZ52" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB52" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD52" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE52" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF52" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG52" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BH52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB52" t="inlineStr">
-        <is>
-          <t>2026-07-03 23:57:36</t>
+      <c r="AW58" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF58" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG58" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH58" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI58" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BJ58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK58" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BL58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM58" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BN58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO58" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BP58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ58" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BR58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS58" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BT58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU58" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BV58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW58" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BX58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY58" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BZ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB58" t="inlineStr">
+        <is>
+          <t>2026-07-04 02:16:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G4" t="n">
         <v>2.08</v>
@@ -1374,7 +1374,7 @@
         <v>4.3</v>
       </c>
       <c r="I4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
@@ -1392,7 +1392,7 @@
         <v>3.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P4" t="n">
         <v>1.76</v>
@@ -1431,7 +1431,7 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC4" t="n">
         <v>7.8</v>
@@ -1440,7 +1440,7 @@
         <v>19</v>
       </c>
       <c r="AE4" t="n">
-        <v>760</v>
+        <v>770</v>
       </c>
       <c r="AF4" t="n">
         <v>11.5</v>
@@ -1491,7 +1491,7 @@
         <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW4" t="n">
         <v>30</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J5" t="n">
         <v>3.35</v>
@@ -1637,7 +1637,7 @@
         <v>3.55</v>
       </c>
       <c r="L5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
@@ -1646,10 +1646,10 @@
         <v>3.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q5" t="n">
         <v>2.16</v>
@@ -1658,10 +1658,10 @@
         <v>1.31</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T5" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="U5" t="n">
         <v>2.06</v>
@@ -1670,19 +1670,19 @@
         <v>1.46</v>
       </c>
       <c r="W5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X5" t="n">
         <v>12.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
         <v>21</v>
       </c>
       <c r="AA5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB5" t="n">
         <v>11.5</v>
@@ -1691,13 +1691,13 @@
         <v>7.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF5" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AG5" t="n">
         <v>12.5</v>
@@ -1721,7 +1721,7 @@
         <v>130</v>
       </c>
       <c r="AN5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO5" t="n">
         <v>44</v>
@@ -1736,7 +1736,7 @@
         <v>18</v>
       </c>
       <c r="AS5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT5" t="n">
         <v>9</v>
@@ -1748,37 +1748,37 @@
         <v>12</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AX5" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ5" t="n">
         <v>16.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF5" t="n">
         <v>20</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH5" t="n">
         <v>3.15</v>
@@ -1790,7 +1790,7 @@
         <v>10</v>
       </c>
       <c r="BK5" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1802,19 +1802,19 @@
         <v>5.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BP5" t="n">
         <v>21</v>
       </c>
       <c r="BQ5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT5" t="n">
         <v>6.2</v>
@@ -1823,10 +1823,10 @@
         <v>5.4</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1835,14 +1835,14 @@
         <v>11</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA5" t="n">
         <v>10.5</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -1879,10 +1879,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="I6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="J6" t="n">
         <v>4.4</v>
@@ -1891,7 +1891,7 @@
         <v>4.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1918,13 +1918,13 @@
         <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V6" t="n">
         <v>2.88</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
         <v>15</v>
@@ -1936,7 +1936,7 @@
         <v>8</v>
       </c>
       <c r="AA6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AB6" t="n">
         <v>24</v>
@@ -1987,7 +1987,7 @@
         <v>6.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS6" t="n">
         <v>11.5</v>
@@ -2038,37 +2038,37 @@
         <v>3.55</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BJ6" t="n">
         <v>12.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN6" t="n">
         <v>12</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BP6" t="n">
         <v>85</v>
       </c>
       <c r="BQ6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT6" t="n">
         <v>3.95</v>
@@ -2080,23 +2080,23 @@
         <v>10</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BX6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BY6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>2.04</v>
       </c>
       <c r="H7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I7" t="n">
         <v>4.9</v>
@@ -2160,7 +2160,7 @@
         <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R7" t="n">
         <v>1.33</v>
@@ -2184,19 +2184,19 @@
         <v>15.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA7" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB7" t="n">
         <v>9</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
         <v>18.5</v>
@@ -2217,7 +2217,7 @@
         <v>75</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK7" t="n">
         <v>22</v>
@@ -2238,25 +2238,25 @@
         <v>10</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AR7" t="n">
         <v>23</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT7" t="n">
         <v>7.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.800000000000001</v>
+        <v>44</v>
       </c>
       <c r="AX7" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BB7" t="n">
         <v>19</v>
@@ -2277,16 +2277,16 @@
         <v>18.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF7" t="n">
         <v>11</v>
       </c>
       <c r="BG7" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BH7" t="n">
         <v>3.35</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
         <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N8" t="n">
         <v>4.1</v>
@@ -2435,7 +2435,7 @@
         <v>1.36</v>
       </c>
       <c r="X8" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y8" t="n">
         <v>12.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
         <v>1.58</v>
       </c>
       <c r="I9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="J9" t="n">
         <v>4.1</v>
@@ -2665,7 +2665,7 @@
         <v>1.28</v>
       </c>
       <c r="P9" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q9" t="n">
         <v>1.83</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="G10" t="n">
         <v>2.98</v>
@@ -2919,40 +2919,40 @@
         <v>1.41</v>
       </c>
       <c r="P10" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R10" t="n">
         <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U10" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V10" t="n">
         <v>1.44</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="X10" t="n">
         <v>13</v>
       </c>
       <c r="Y10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB10" t="n">
         <v>11.5</v>
@@ -2979,10 +2979,10 @@
         <v>65</v>
       </c>
       <c r="AJ10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK10" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL10" t="n">
         <v>60</v>
@@ -2991,22 +2991,22 @@
         <v>140</v>
       </c>
       <c r="AN10" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AO10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP10" t="n">
         <v>8.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.7</v>
+        <v>38</v>
       </c>
       <c r="AT10" t="n">
         <v>8.199999999999999</v>
@@ -3018,37 +3018,37 @@
         <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>29</v>
+        <v>4.8</v>
       </c>
       <c r="AX10" t="n">
         <v>13.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
         <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC10" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC10" t="n">
-        <v>26</v>
-      </c>
       <c r="BD10" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF10" t="n">
         <v>4.7</v>
       </c>
-      <c r="BE10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>26</v>
-      </c>
       <c r="BG10" t="n">
-        <v>30</v>
+        <v>4.9</v>
       </c>
       <c r="BH10" t="n">
         <v>3.15</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -3176,13 +3176,13 @@
         <v>1.07</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="R11" t="n">
         <v>1.07</v>
       </c>
       <c r="S11" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
@@ -3448,7 +3448,7 @@
         <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="I13" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="J13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L13" t="n">
         <v>1.28</v>
@@ -3681,7 +3681,7 @@
         <v>1.22</v>
       </c>
       <c r="P13" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q13" t="n">
         <v>1.64</v>
@@ -3693,31 +3693,31 @@
         <v>2.6</v>
       </c>
       <c r="T13" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U13" t="n">
         <v>2.32</v>
       </c>
       <c r="V13" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y13" t="n">
         <v>11</v>
       </c>
       <c r="Z13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA13" t="n">
         <v>16.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AC13" t="n">
         <v>10.5</v>
@@ -3726,43 +3726,43 @@
         <v>10.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI13" t="n">
         <v>34</v>
       </c>
       <c r="AJ13" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR13" t="n">
         <v>10</v>
@@ -3771,10 +3771,10 @@
         <v>14</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.4</v>
+        <v>17</v>
       </c>
       <c r="AU13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV13" t="n">
         <v>9.199999999999999</v>
@@ -3783,31 +3783,31 @@
         <v>14</v>
       </c>
       <c r="AX13" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.4</v>
+        <v>19.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>11.5</v>
+        <v>42</v>
       </c>
       <c r="BC13" t="n">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="BD13" t="n">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="BE13" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="BF13" t="n">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="BG13" t="n">
         <v>6.4</v>
@@ -3852,7 +3852,7 @@
         <v>4.5</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="BV13" t="n">
         <v>10</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="G14" t="n">
         <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="I14" t="n">
         <v>1000</v>
@@ -3929,13 +3929,13 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O14" t="n">
         <v>1.01</v>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>1.1</v>
       </c>
       <c r="Q14" t="n">
         <v>1.01</v>
@@ -3956,7 +3956,7 @@
         <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -4159,13 +4159,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
@@ -4183,7 +4183,7 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="O15" t="n">
         <v>1.02</v>
@@ -4207,7 +4207,7 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
         <v>1.02</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -4422,10 +4422,10 @@
         <v>2.38</v>
       </c>
       <c r="I16" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K16" t="n">
         <v>4.1</v>
@@ -4449,7 +4449,7 @@
         <v>1.67</v>
       </c>
       <c r="R16" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S16" t="n">
         <v>2.56</v>
@@ -4461,7 +4461,7 @@
         <v>2.38</v>
       </c>
       <c r="V16" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W16" t="n">
         <v>1.46</v>
@@ -4497,7 +4497,7 @@
         <v>16</v>
       </c>
       <c r="AH16" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI16" t="n">
         <v>40</v>
@@ -4518,58 +4518,58 @@
         <v>25</v>
       </c>
       <c r="AO16" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AQ16" t="n">
         <v>3.45</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AT16" t="n">
         <v>3.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AV16" t="n">
         <v>3.35</v>
       </c>
       <c r="AW16" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AX16" t="n">
         <v>3.75</v>
       </c>
       <c r="AY16" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AZ16" t="n">
         <v>3.55</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BB16" t="n">
         <v>4</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE16" t="n">
         <v>4.1</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BG16" t="n">
         <v>3.55</v>
@@ -4578,40 +4578,40 @@
         <v>4.2</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="BJ16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK16" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>8.6</v>
+        <v>2.88</v>
       </c>
       <c r="BN16" t="n">
         <v>6.6</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BP16" t="n">
         <v>22</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT16" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU16" t="n">
         <v>3.7</v>
@@ -4620,23 +4620,23 @@
         <v>18</v>
       </c>
       <c r="BW16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ16" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
         <v>3.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="M17" t="n">
         <v>1.09</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -4921,19 +4921,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="G18" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H18" t="n">
         <v>4.4</v>
       </c>
       <c r="I18" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K18" t="n">
         <v>3.95</v>
@@ -4951,10 +4951,10 @@
         <v>1.35</v>
       </c>
       <c r="P18" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R18" t="n">
         <v>1.29</v>
@@ -4969,10 +4969,10 @@
         <v>1.93</v>
       </c>
       <c r="V18" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="W18" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X18" t="n">
         <v>15</v>
@@ -5011,7 +5011,7 @@
         <v>85</v>
       </c>
       <c r="AJ18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK18" t="n">
         <v>25</v>
@@ -5029,7 +5029,7 @@
         <v>100</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ18" t="n">
         <v>11.5</v>
@@ -5041,19 +5041,19 @@
         <v>5.8</v>
       </c>
       <c r="AT18" t="n">
-        <v>6.2</v>
+        <v>3.55</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.4</v>
+        <v>3.55</v>
       </c>
       <c r="AV18" t="n">
         <v>14.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX18" t="n">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="AY18" t="n">
         <v>8</v>
@@ -5062,25 +5062,25 @@
         <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB18" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>16.5</v>
+        <v>4.9</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BE18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG18" t="n">
         <v>5.8</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>5.7</v>
       </c>
       <c r="BH18" t="n">
         <v>3.3</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G19" t="n">
         <v>1.82</v>
@@ -5223,7 +5223,7 @@
         <v>3.05</v>
       </c>
       <c r="V19" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W19" t="n">
         <v>2.2</v>
@@ -5394,11 +5394,11 @@
         <v>10.5</v>
       </c>
       <c r="CA19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -5438,10 +5438,10 @@
         <v>3.2</v>
       </c>
       <c r="I20" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K20" t="n">
         <v>3.9</v>
@@ -5456,7 +5456,7 @@
         <v>4.7</v>
       </c>
       <c r="O20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P20" t="n">
         <v>2.22</v>
@@ -5465,7 +5465,7 @@
         <v>1.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S20" t="n">
         <v>2.88</v>
@@ -5483,7 +5483,7 @@
         <v>1.74</v>
       </c>
       <c r="X20" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y20" t="n">
         <v>16.5</v>
@@ -5492,7 +5492,7 @@
         <v>25</v>
       </c>
       <c r="AA20" t="n">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="AB20" t="n">
         <v>13</v>
@@ -5516,7 +5516,7 @@
         <v>16</v>
       </c>
       <c r="AI20" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AJ20" t="n">
         <v>32</v>
@@ -5552,7 +5552,7 @@
         <v>11</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV20" t="n">
         <v>12.5</v>
@@ -5585,7 +5585,7 @@
         <v>32</v>
       </c>
       <c r="BF20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG20" t="n">
         <v>18</v>
@@ -5639,7 +5639,7 @@
         <v>7</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY20" t="n">
         <v>7.6</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
         <v>1.58</v>
       </c>
       <c r="H21" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="I21" t="n">
         <v>6.8</v>
@@ -5698,7 +5698,7 @@
         <v>4.7</v>
       </c>
       <c r="K21" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
         <v>1.28</v>
@@ -5707,37 +5707,37 @@
         <v>1.04</v>
       </c>
       <c r="N21" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O21" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P21" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q21" t="n">
         <v>1.69</v>
       </c>
       <c r="R21" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S21" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="T21" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U21" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V21" t="n">
         <v>1.17</v>
       </c>
       <c r="W21" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y21" t="n">
         <v>25</v>
@@ -5746,13 +5746,13 @@
         <v>60</v>
       </c>
       <c r="AA21" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD21" t="n">
         <v>25</v>
@@ -5761,7 +5761,7 @@
         <v>100</v>
       </c>
       <c r="AF21" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG21" t="n">
         <v>10</v>
@@ -5770,19 +5770,19 @@
         <v>22</v>
       </c>
       <c r="AI21" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
         <v>14.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL21" t="n">
         <v>32</v>
       </c>
       <c r="AM21" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
         <v>7</v>
@@ -5791,7 +5791,7 @@
         <v>110</v>
       </c>
       <c r="AP21" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ21" t="n">
         <v>21</v>
@@ -5800,10 +5800,10 @@
         <v>40</v>
       </c>
       <c r="AS21" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="AT21" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU21" t="n">
         <v>9.800000000000001</v>
@@ -5812,19 +5812,19 @@
         <v>21</v>
       </c>
       <c r="AW21" t="n">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="AX21" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY21" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ21" t="n">
         <v>19</v>
       </c>
       <c r="BA21" t="n">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="BB21" t="n">
         <v>12.5</v>
@@ -5833,52 +5833,52 @@
         <v>13.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE21" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="BF21" t="n">
         <v>6.4</v>
       </c>
       <c r="BG21" t="n">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="BH21" t="n">
         <v>4.1</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ21" t="n">
         <v>10.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BL21" t="n">
         <v>120</v>
       </c>
       <c r="BM21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN21" t="n">
         <v>4.3</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="BP21" t="n">
         <v>9.6</v>
       </c>
       <c r="BQ21" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BR21" t="n">
         <v>23</v>
       </c>
       <c r="BS21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT21" t="n">
         <v>10.5</v>
@@ -5899,14 +5899,14 @@
         <v>10.5</v>
       </c>
       <c r="BZ21" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA21" t="n">
         <v>7</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -5943,7 +5943,7 @@
         <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>1.51</v>
       </c>
       <c r="I22" t="n">
         <v>1000</v>
@@ -5985,7 +5985,7 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
         <v>1.02</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
         <v>1.93</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S23" t="n">
         <v>3.35</v>
@@ -6239,7 +6239,7 @@
         <v>2.08</v>
       </c>
       <c r="V23" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W23" t="n">
         <v>1.6</v>
@@ -6299,10 +6299,10 @@
         <v>46</v>
       </c>
       <c r="AP23" t="n">
-        <v>11</v>
+        <v>5.2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="AR23" t="n">
         <v>6</v>
@@ -6311,7 +6311,7 @@
         <v>7</v>
       </c>
       <c r="AT23" t="n">
-        <v>8.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="AU23" t="n">
         <v>6.6</v>
@@ -6323,16 +6323,16 @@
         <v>6.6</v>
       </c>
       <c r="AX23" t="n">
-        <v>13</v>
+        <v>5.4</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ23" t="n">
         <v>5.6</v>
       </c>
       <c r="BA23" t="n">
-        <v>29</v>
+        <v>6.8</v>
       </c>
       <c r="BB23" t="n">
         <v>21</v>
@@ -6347,10 +6347,10 @@
         <v>7.4</v>
       </c>
       <c r="BF23" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BH23" t="n">
         <v>4.5</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -6953,13 +6953,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G26" t="n">
         <v>2.5</v>
       </c>
       <c r="H26" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="I26" t="n">
         <v>3.05</v>
@@ -6968,7 +6968,7 @@
         <v>4.1</v>
       </c>
       <c r="K26" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L26" t="n">
         <v>1.17</v>
@@ -7001,7 +7001,7 @@
         <v>3.05</v>
       </c>
       <c r="V26" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W26" t="n">
         <v>1.66</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="G27" t="n">
         <v>4.1</v>
@@ -7216,7 +7216,7 @@
         <v>1.98</v>
       </c>
       <c r="I27" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J27" t="n">
         <v>3.8</v>
@@ -7243,10 +7243,10 @@
         <v>1.77</v>
       </c>
       <c r="R27" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S27" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T27" t="n">
         <v>1.7</v>
@@ -7255,7 +7255,7 @@
         <v>2.32</v>
       </c>
       <c r="V27" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="W27" t="n">
         <v>1.32</v>
@@ -7288,7 +7288,7 @@
         <v>32</v>
       </c>
       <c r="AG27" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH27" t="n">
         <v>17</v>
@@ -7297,7 +7297,7 @@
         <v>32</v>
       </c>
       <c r="AJ27" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK27" t="n">
         <v>44</v>
@@ -7306,7 +7306,7 @@
         <v>48</v>
       </c>
       <c r="AM27" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN27" t="n">
         <v>40</v>
@@ -7339,7 +7339,7 @@
         <v>17</v>
       </c>
       <c r="AX27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY27" t="n">
         <v>14.5</v>
@@ -7348,22 +7348,22 @@
         <v>15</v>
       </c>
       <c r="BA27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC27" t="n">
         <v>10</v>
       </c>
       <c r="BD27" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF27" t="n">
         <v>10</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="BG27" t="n">
         <v>10.5</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
         <v>1.09</v>
       </c>
       <c r="G28" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="H28" t="n">
         <v>3.7</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
         <v>1.07</v>
       </c>
       <c r="S29" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T29" t="n">
         <v>1.01</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -7969,22 +7969,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="G30" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="H30" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="I30" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K30" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -7993,37 +7993,37 @@
         <v>1.04</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="O30" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P30" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="R30" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S30" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T30" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="U30" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="V30" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="W30" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="X30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y30" t="n">
         <v>970</v>
@@ -8032,7 +8032,7 @@
         <v>970</v>
       </c>
       <c r="AA30" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AB30" t="n">
         <v>970</v>
@@ -8044,91 +8044,91 @@
         <v>970</v>
       </c>
       <c r="AE30" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AF30" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AG30" t="n">
         <v>970</v>
       </c>
       <c r="AH30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI30" t="n">
         <v>36</v>
       </c>
       <c r="AJ30" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AL30" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM30" t="n">
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AO30" t="n">
         <v>970</v>
       </c>
       <c r="AP30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW30" t="n">
         <v>3.9</v>
       </c>
-      <c r="AQ30" t="n">
+      <c r="AX30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY30" t="n">
         <v>3.85</v>
       </c>
-      <c r="AR30" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AZ30" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BA30" t="n">
         <v>4</v>
       </c>
       <c r="BB30" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BC30" t="n">
         <v>4.2</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF30" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG30" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="BH30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -8734,16 +8734,16 @@
         <v>1.04</v>
       </c>
       <c r="G33" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H33" t="n">
         <v>1.04</v>
       </c>
       <c r="I33" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J33" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K33" t="n">
         <v>950</v>
@@ -8758,7 +8758,7 @@
         <v>1.09</v>
       </c>
       <c r="O33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P33" t="n">
         <v>1.08</v>
@@ -8779,10 +8779,10 @@
         <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -8988,16 +8988,16 @@
         <v>1.04</v>
       </c>
       <c r="G34" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H34" t="n">
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J34" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K34" t="n">
         <v>950</v>
@@ -9009,10 +9009,10 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O34" t="n">
         <v>1.02</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.01</v>
       </c>
       <c r="P34" t="n">
         <v>1.08</v>
@@ -9033,10 +9033,10 @@
         <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -9251,10 +9251,10 @@
         <v>1000</v>
       </c>
       <c r="J35" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K35" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -9266,19 +9266,19 @@
         <v>1.08</v>
       </c>
       <c r="O35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P35" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="R35" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S35" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="T35" t="n">
         <v>1.01</v>
@@ -9287,10 +9287,10 @@
         <v>1.01</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -9347,52 +9347,52 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF35" t="n">
         <v>1.01</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -9496,16 +9496,16 @@
         <v>1.04</v>
       </c>
       <c r="G36" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H36" t="n">
         <v>1.04</v>
       </c>
       <c r="I36" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J36" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K36" t="n">
         <v>950</v>
@@ -9517,7 +9517,7 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O36" t="n">
         <v>1.01</v>
@@ -9541,10 +9541,10 @@
         <v>1.01</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -9750,16 +9750,16 @@
         <v>1.04</v>
       </c>
       <c r="G37" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H37" t="n">
         <v>1.04</v>
       </c>
       <c r="I37" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J37" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K37" t="n">
         <v>950</v>
@@ -9771,22 +9771,22 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P37" t="n">
         <v>1.09</v>
       </c>
-      <c r="O37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Q37" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="R37" t="n">
         <v>1.08</v>
       </c>
       <c r="S37" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="T37" t="n">
         <v>1.01</v>
@@ -9795,10 +9795,10 @@
         <v>1.01</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W37" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G38" t="n">
         <v>3</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -10267,7 +10267,7 @@
         <v>4.9</v>
       </c>
       <c r="J39" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K39" t="n">
         <v>4.2</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -10518,7 +10518,7 @@
         <v>2.36</v>
       </c>
       <c r="I40" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J40" t="n">
         <v>3.05</v>
@@ -10527,13 +10527,13 @@
         <v>3.5</v>
       </c>
       <c r="L40" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="M40" t="n">
         <v>1.08</v>
       </c>
       <c r="N40" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O40" t="n">
         <v>1.46</v>
@@ -10551,10 +10551,10 @@
         <v>4.3</v>
       </c>
       <c r="T40" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U40" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V40" t="n">
         <v>1.6</v>
@@ -10674,7 +10674,7 @@
         <v>3.05</v>
       </c>
       <c r="BI40" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BJ40" t="n">
         <v>11</v>
@@ -10686,25 +10686,25 @@
         <v>1000</v>
       </c>
       <c r="BM40" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN40" t="n">
         <v>6.6</v>
       </c>
       <c r="BO40" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP40" t="n">
         <v>1000</v>
       </c>
       <c r="BQ40" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR40" t="n">
         <v>65</v>
       </c>
       <c r="BS40" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT40" t="n">
         <v>5.4</v>
@@ -10713,7 +10713,7 @@
         <v>4.5</v>
       </c>
       <c r="BV40" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW40" t="n">
         <v>7.2</v>
@@ -10722,17 +10722,17 @@
         <v>1000</v>
       </c>
       <c r="BY40" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ40" t="n">
         <v>1000</v>
       </c>
       <c r="CA40" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -11017,7 +11017,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="G42" t="n">
         <v>1000</v>
@@ -11029,7 +11029,7 @@
         <v>1000</v>
       </c>
       <c r="J42" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="K42" t="n">
         <v>1000</v>
@@ -11065,7 +11065,7 @@
         <v>1.01</v>
       </c>
       <c r="V42" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W42" t="n">
         <v>1.01</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -12290,7 +12290,7 @@
         <v>1.04</v>
       </c>
       <c r="G47" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="H47" t="n">
         <v>1.04</v>
@@ -12338,7 +12338,7 @@
         <v>1.01</v>
       </c>
       <c r="W47" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X47" t="n">
         <v>1000</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -13351,7 +13351,7 @@
         <v>1.01</v>
       </c>
       <c r="V51" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W51" t="n">
         <v>1.01</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -13823,7 +13823,7 @@
         <v>3.25</v>
       </c>
       <c r="J53" t="n">
-        <v>2.98</v>
+        <v>2.74</v>
       </c>
       <c r="K53" t="n">
         <v>3.5</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -14089,7 +14089,7 @@
         <v>1.05</v>
       </c>
       <c r="N54" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="O54" t="n">
         <v>1.24</v>
@@ -14107,7 +14107,7 @@
         <v>2.74</v>
       </c>
       <c r="T54" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="U54" t="n">
         <v>2.32</v>
@@ -14140,7 +14140,7 @@
         <v>15</v>
       </c>
       <c r="AE54" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AF54" t="n">
         <v>26</v>
@@ -14155,10 +14155,10 @@
         <v>42</v>
       </c>
       <c r="AJ54" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AK54" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AL54" t="n">
         <v>44</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -14830,10 +14830,10 @@
         <v>2.18</v>
       </c>
       <c r="G57" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H57" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I57" t="n">
         <v>4.2</v>
@@ -14845,7 +14845,7 @@
         <v>3.4</v>
       </c>
       <c r="L57" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="M57" t="n">
         <v>1.1</v>
@@ -14878,7 +14878,7 @@
         <v>1.32</v>
       </c>
       <c r="W57" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X57" t="n">
         <v>12.5</v>
@@ -14908,7 +14908,7 @@
         <v>13.5</v>
       </c>
       <c r="AG57" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH57" t="n">
         <v>25</v>
@@ -14917,7 +14917,7 @@
         <v>90</v>
       </c>
       <c r="AJ57" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK57" t="n">
         <v>28</v>
@@ -14929,7 +14929,7 @@
         <v>180</v>
       </c>
       <c r="AN57" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO57" t="n">
         <v>90</v>
@@ -14941,10 +14941,10 @@
         <v>10.5</v>
       </c>
       <c r="AR57" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AS57" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AT57" t="n">
         <v>7</v>
@@ -14956,7 +14956,7 @@
         <v>14.5</v>
       </c>
       <c r="AW57" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AX57" t="n">
         <v>11.5</v>
@@ -14965,28 +14965,28 @@
         <v>10</v>
       </c>
       <c r="AZ57" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BA57" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD57" t="n">
         <v>5.4</v>
       </c>
-      <c r="BB57" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC57" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD57" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BE57" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF57" t="n">
         <v>18</v>
       </c>
       <c r="BG57" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BH57" t="n">
         <v>1000</v>
@@ -14995,62 +14995,62 @@
         <v>1.01</v>
       </c>
       <c r="BJ57" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BK57" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL57" t="n">
         <v>1000</v>
       </c>
       <c r="BM57" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN57" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO57" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP57" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ57" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BR57" t="n">
         <v>1000</v>
       </c>
       <c r="BS57" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT57" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU57" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV57" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW57" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX57" t="n">
         <v>1000</v>
       </c>
       <c r="BY57" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ57" t="n">
         <v>1000</v>
       </c>
       <c r="CA57" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>
@@ -15168,16 +15168,16 @@
         <v>24</v>
       </c>
       <c r="AI58" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AJ58" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AK58" t="n">
         <v>32</v>
       </c>
       <c r="AL58" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -15192,16 +15192,16 @@
         <v>11.5</v>
       </c>
       <c r="AQ58" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR58" t="n">
         <v>14.5</v>
       </c>
       <c r="AS58" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AT58" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AU58" t="n">
         <v>5.9</v>
@@ -15210,19 +15210,19 @@
         <v>10</v>
       </c>
       <c r="AW58" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX58" t="n">
         <v>12.5</v>
       </c>
       <c r="AY58" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ58" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA58" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BB58" t="n">
         <v>1.01</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-07-04 02:16:57</t>
+          <t>2026-07-04 04:35:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.14</v>
+        <v>2.52</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="H2" t="n">
-        <v>1.14</v>
+        <v>2.86</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="J2" t="n">
-        <v>1.09</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>1.08</v>
+        <v>2.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.08</v>
+        <v>1.64</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.32</v>
+        <v>2.08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>1.31</v>
+        <v>3.45</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.51</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -1111,172 +1111,172 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.14</v>
+        <v>2.12</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>2.56</v>
       </c>
       <c r="H3" t="n">
-        <v>1.14</v>
+        <v>3.5</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="n">
-        <v>1.09</v>
+        <v>2.84</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>1.08</v>
+        <v>2.58</v>
       </c>
       <c r="O3" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="P3" t="n">
-        <v>1.08</v>
+        <v>1.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.38</v>
+        <v>2.18</v>
       </c>
       <c r="R3" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="S3" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.64</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
@@ -1291,7 +1291,7 @@
         <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         <v>3.65</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1407,7 +1407,7 @@
         <v>4.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U4" t="n">
         <v>1.95</v>
@@ -1425,13 +1425,13 @@
         <v>14</v>
       </c>
       <c r="Z4" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC4" t="n">
         <v>7.8</v>
@@ -1503,7 +1503,7 @@
         <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BA4" t="n">
         <v>34</v>
@@ -1530,7 +1530,7 @@
         <v>3.15</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
@@ -1560,13 +1560,13 @@
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT4" t="n">
         <v>7.8</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
@@ -1584,11 +1584,11 @@
         <v>32</v>
       </c>
       <c r="CA4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
         <v>130</v>
       </c>
       <c r="AN5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO5" t="n">
         <v>44</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="J6" t="n">
         <v>4.4</v>
@@ -1891,7 +1891,7 @@
         <v>4.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1903,7 +1903,7 @@
         <v>1.34</v>
       </c>
       <c r="P6" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q6" t="n">
         <v>2</v>
@@ -1951,10 +1951,10 @@
         <v>18</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AG6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AH6" t="n">
         <v>29</v>
@@ -2011,7 +2011,7 @@
         <v>20</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BA6" t="n">
         <v>26</v>
@@ -2026,7 +2026,7 @@
         <v>42</v>
       </c>
       <c r="BE6" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF6" t="n">
         <v>48</v>
@@ -2038,13 +2038,13 @@
         <v>3.55</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BJ6" t="n">
         <v>12.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2056,7 +2056,7 @@
         <v>12</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BP6" t="n">
         <v>85</v>
@@ -2065,7 +2065,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BS6" t="n">
         <v>9.800000000000001</v>
@@ -2080,10 +2080,10 @@
         <v>10</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BX6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BY6" t="n">
         <v>8</v>
@@ -2092,11 +2092,11 @@
         <v>20</v>
       </c>
       <c r="CA6" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="G7" t="n">
         <v>2.04</v>
@@ -2145,7 +2145,7 @@
         <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="M7" t="n">
         <v>1.08</v>
@@ -2160,13 +2160,13 @@
         <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
         <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T7" t="n">
         <v>1.84</v>
@@ -2184,43 +2184,43 @@
         <v>15.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AA7" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB7" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AE7" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AK7" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL7" t="n">
         <v>46</v>
@@ -2229,76 +2229,76 @@
         <v>130</v>
       </c>
       <c r="AN7" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO7" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AP7" t="n">
         <v>10</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>23</v>
+        <v>4.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AV7" t="n">
         <v>13.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>44</v>
+        <v>4.7</v>
       </c>
       <c r="AX7" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.4</v>
+        <v>4.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BC7" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.6</v>
+        <v>4.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="BF7" t="n">
         <v>11</v>
       </c>
       <c r="BG7" t="n">
-        <v>9.4</v>
+        <v>4.8</v>
       </c>
       <c r="BH7" t="n">
         <v>3.35</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.05</v>
+        <v>2.76</v>
       </c>
       <c r="BJ7" t="n">
         <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2310,34 +2310,34 @@
         <v>4.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="BP7" t="n">
         <v>13.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR7" t="n">
         <v>29</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT7" t="n">
         <v>8</v>
       </c>
       <c r="BU7" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
         <v>11.5</v>
@@ -2346,11 +2346,11 @@
         <v>26</v>
       </c>
       <c r="CA7" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="G8" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="H8" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K8" t="n">
         <v>3.95</v>
@@ -2405,7 +2405,7 @@
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
         <v>1.27</v>
@@ -2414,7 +2414,7 @@
         <v>2.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R8" t="n">
         <v>1.4</v>
@@ -2429,34 +2429,34 @@
         <v>2.18</v>
       </c>
       <c r="V8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="W8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X8" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z8" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AB8" t="n">
         <v>17</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD8" t="n">
         <v>13</v>
       </c>
       <c r="AE8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF8" t="n">
         <v>30</v>
@@ -2468,13 +2468,13 @@
         <v>19.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AJ8" t="n">
         <v>75</v>
       </c>
       <c r="AK8" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AL8" t="n">
         <v>55</v>
@@ -2483,25 +2483,25 @@
         <v>95</v>
       </c>
       <c r="AN8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>8.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS8" t="n">
         <v>21</v>
       </c>
       <c r="AT8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU8" t="n">
         <v>6.6</v>
@@ -2513,10 +2513,10 @@
         <v>17</v>
       </c>
       <c r="AX8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ8" t="n">
         <v>12.5</v>
@@ -2540,13 +2540,13 @@
         <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH8" t="n">
         <v>3.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ8" t="n">
         <v>9.6</v>
@@ -2597,14 +2597,14 @@
         <v>7.2</v>
       </c>
       <c r="BZ8" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
         <v>7</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -2638,13 +2638,13 @@
         <v>6.2</v>
       </c>
       <c r="G9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="H9" t="n">
         <v>1.58</v>
       </c>
       <c r="I9" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="J9" t="n">
         <v>4.1</v>
@@ -2662,7 +2662,7 @@
         <v>3.85</v>
       </c>
       <c r="O9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P9" t="n">
         <v>1.98</v>
@@ -2746,7 +2746,7 @@
         <v>12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AR9" t="n">
         <v>7.2</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G10" t="n">
         <v>2.98</v>
@@ -2907,7 +2907,7 @@
         <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="M10" t="n">
         <v>1.1</v>
@@ -2916,7 +2916,7 @@
         <v>3.05</v>
       </c>
       <c r="O10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P10" t="n">
         <v>1.69</v>
@@ -2931,7 +2931,7 @@
         <v>4.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U10" t="n">
         <v>1.96</v>
@@ -2940,7 +2940,7 @@
         <v>1.44</v>
       </c>
       <c r="W10" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
         <v>13</v>
@@ -2976,10 +2976,10 @@
         <v>23</v>
       </c>
       <c r="AI10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ10" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK10" t="n">
         <v>38</v>
@@ -3006,7 +3006,7 @@
         <v>14.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="AT10" t="n">
         <v>8.199999999999999</v>
@@ -3033,13 +3033,13 @@
         <v>5</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.9</v>
+        <v>36</v>
       </c>
       <c r="BC10" t="n">
         <v>4.7</v>
       </c>
       <c r="BD10" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="BE10" t="n">
         <v>5.2</v>
@@ -3054,7 +3054,7 @@
         <v>3.15</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3445,7 +3445,7 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="W12" t="n">
         <v>1.02</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
         <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
         <v>1.22</v>
@@ -3684,13 +3684,13 @@
         <v>2.42</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R13" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
         <v>1.73</v>
@@ -3699,7 +3699,7 @@
         <v>2.32</v>
       </c>
       <c r="V13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="W13" t="n">
         <v>1.19</v>
@@ -3711,7 +3711,7 @@
         <v>11</v>
       </c>
       <c r="Z13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA13" t="n">
         <v>16.5</v>
@@ -3759,7 +3759,7 @@
         <v>7</v>
       </c>
       <c r="AP13" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AQ13" t="n">
         <v>10</v>
@@ -3789,7 +3789,7 @@
         <v>15.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA13" t="n">
         <v>19.5</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="G14" t="n">
         <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="I14" t="n">
         <v>1000</v>
@@ -3929,16 +3929,16 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="O14" t="n">
         <v>1.01</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1</v>
+        <v>1.49</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="R14" t="n">
         <v>1.07</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -4159,13 +4159,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
@@ -4186,7 +4186,7 @@
         <v>1.01</v>
       </c>
       <c r="O15" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="P15" t="n">
         <v>1.07</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O16" t="n">
         <v>1.23</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -4685,13 +4685,13 @@
         <v>3.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
         <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="O17" t="n">
         <v>1.39</v>
@@ -4706,7 +4706,7 @@
         <v>1.26</v>
       </c>
       <c r="S17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T17" t="n">
         <v>1.94</v>
@@ -4832,7 +4832,7 @@
         <v>3.2</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -4921,82 +4921,82 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="G18" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="H18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I18" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="J18" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="O18" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P18" t="n">
         <v>1.79</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U18" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V18" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W18" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X18" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA18" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF18" t="n">
         <v>13</v>
@@ -5008,7 +5008,7 @@
         <v>24</v>
       </c>
       <c r="AI18" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ18" t="n">
         <v>25</v>
@@ -5023,128 +5023,128 @@
         <v>150</v>
       </c>
       <c r="AN18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO18" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP18" t="n">
-        <v>10</v>
+        <v>3.8</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11.5</v>
+        <v>3.95</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY18" t="n">
         <v>3.55</v>
       </c>
-      <c r="AU18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX18" t="n">
+      <c r="AZ18" t="n">
         <v>4.1</v>
       </c>
-      <c r="AY18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BA18" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB18" t="n">
-        <v>16.5</v>
+        <v>4.2</v>
       </c>
       <c r="BC18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE18" t="n">
         <v>4.9</v>
       </c>
-      <c r="BD18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BF18" t="n">
-        <v>11.5</v>
+        <v>3.9</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="BJ18" t="n">
         <v>11</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>11</v>
+        <v>2.54</v>
       </c>
       <c r="BN18" t="n">
         <v>4.6</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="BP18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR18" t="n">
         <v>32</v>
       </c>
       <c r="BS18" t="n">
-        <v>8.6</v>
+        <v>2.38</v>
       </c>
       <c r="BT18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU18" t="n">
         <v>4.8</v>
       </c>
       <c r="BV18" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>9.4</v>
+        <v>2.44</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>9.800000000000001</v>
+        <v>2.46</v>
       </c>
       <c r="BZ18" t="n">
         <v>28</v>
       </c>
       <c r="CA18" t="n">
-        <v>8.4</v>
+        <v>2.36</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>1.76</v>
       </c>
       <c r="G19" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H19" t="n">
         <v>4.3</v>
@@ -5226,7 +5226,7 @@
         <v>1.27</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X19" t="n">
         <v>40</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -5429,16 +5429,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G20" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="H20" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
         <v>3.7</v>
@@ -5447,7 +5447,7 @@
         <v>3.9</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
@@ -5459,16 +5459,16 @@
         <v>1.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R20" t="n">
         <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T20" t="n">
         <v>1.64</v>
@@ -5477,37 +5477,37 @@
         <v>2.46</v>
       </c>
       <c r="V20" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="X20" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y20" t="n">
         <v>16.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA20" t="n">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="AB20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC20" t="n">
         <v>8.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE20" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AF20" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG20" t="n">
         <v>11.5</v>
@@ -5516,7 +5516,7 @@
         <v>16</v>
       </c>
       <c r="AI20" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AJ20" t="n">
         <v>32</v>
@@ -5531,10 +5531,10 @@
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO20" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AP20" t="n">
         <v>16.5</v>
@@ -5546,10 +5546,10 @@
         <v>20</v>
       </c>
       <c r="AS20" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AT20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU20" t="n">
         <v>7.6</v>
@@ -5558,10 +5558,10 @@
         <v>12.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AX20" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY20" t="n">
         <v>10</v>
@@ -5570,25 +5570,25 @@
         <v>13.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BC20" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD20" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BE20" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="BF20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BH20" t="n">
         <v>4.1</v>
@@ -5606,40 +5606,40 @@
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN20" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO20" t="n">
         <v>4.3</v>
       </c>
       <c r="BP20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BQ20" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BR20" t="n">
         <v>27</v>
       </c>
       <c r="BS20" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT20" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV20" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY20" t="n">
         <v>7.6</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -5683,16 +5683,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="G21" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="H21" t="n">
         <v>6.6</v>
       </c>
       <c r="I21" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J21" t="n">
         <v>4.7</v>
@@ -5716,28 +5716,28 @@
         <v>2.36</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R21" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S21" t="n">
         <v>2.72</v>
       </c>
       <c r="T21" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="U21" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V21" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W21" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="X21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y21" t="n">
         <v>25</v>
@@ -5785,10 +5785,10 @@
         <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO21" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP21" t="n">
         <v>19.5</v>
@@ -5803,7 +5803,7 @@
         <v>46</v>
       </c>
       <c r="AT21" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU21" t="n">
         <v>9.800000000000001</v>
@@ -5839,7 +5839,7 @@
         <v>38</v>
       </c>
       <c r="BF21" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG21" t="n">
         <v>36</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="G22" t="n">
         <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
         <v>3.4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P23" t="n">
         <v>1.81</v>
@@ -6299,7 +6299,7 @@
         <v>46</v>
       </c>
       <c r="AP23" t="n">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="AQ23" t="n">
         <v>5</v>
@@ -6323,7 +6323,7 @@
         <v>6.6</v>
       </c>
       <c r="AX23" t="n">
-        <v>5.4</v>
+        <v>13</v>
       </c>
       <c r="AY23" t="n">
         <v>9.6</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -6469,16 +6469,16 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="O24" t="n">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="P24" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="R24" t="n">
         <v>1.07</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -6726,19 +6726,19 @@
         <v>1.12</v>
       </c>
       <c r="O25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P25" t="n">
         <v>1.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.45</v>
+        <v>2.88</v>
       </c>
       <c r="R25" t="n">
         <v>1.07</v>
       </c>
       <c r="S25" t="n">
-        <v>1.45</v>
+        <v>2.88</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -6953,19 +6953,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G26" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="H26" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="I26" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="J26" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="K26" t="n">
         <v>4.8</v>
@@ -6989,7 +6989,7 @@
         <v>1.37</v>
       </c>
       <c r="R26" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="S26" t="n">
         <v>1.89</v>
@@ -7001,118 +7001,118 @@
         <v>3.05</v>
       </c>
       <c r="V26" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="W26" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="X26" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>42</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AK26" t="n">
         <v>26</v>
       </c>
-      <c r="Z26" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA26" t="n">
+      <c r="AL26" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM26" t="n">
         <v>46</v>
       </c>
-      <c r="AB26" t="n">
-        <v>24</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD26" t="n">
+      <c r="AN26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC26" t="n">
         <v>15.5</v>
       </c>
-      <c r="AE26" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>27</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>40</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BD26" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="BE26" t="n">
-        <v>7.4</v>
+        <v>3.9</v>
       </c>
       <c r="BF26" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG26" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH26" t="n">
         <v>5.8</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -7255,13 +7255,13 @@
         <v>2.32</v>
       </c>
       <c r="V27" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="W27" t="n">
         <v>1.32</v>
       </c>
       <c r="X27" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Y27" t="n">
         <v>11</v>
@@ -7333,13 +7333,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV27" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW27" t="n">
         <v>17</v>
       </c>
       <c r="AX27" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AY27" t="n">
         <v>14.5</v>
@@ -7348,22 +7348,22 @@
         <v>15</v>
       </c>
       <c r="BA27" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BB27" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD27" t="n">
         <v>36</v>
       </c>
       <c r="BE27" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BG27" t="n">
         <v>10.5</v>
@@ -7390,7 +7390,7 @@
         <v>7.6</v>
       </c>
       <c r="BO27" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BP27" t="n">
         <v>32</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
         <v>1.4</v>
       </c>
       <c r="H28" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -7969,61 +7969,61 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.85</v>
+        <v>2.86</v>
       </c>
       <c r="G30" t="n">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="H30" t="n">
-        <v>1.79</v>
+        <v>2.22</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>2.54</v>
       </c>
       <c r="J30" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="K30" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N30" t="n">
         <v>3.45</v>
       </c>
       <c r="O30" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P30" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="R30" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S30" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="T30" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U30" t="n">
         <v>2.2</v>
       </c>
       <c r="V30" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="W30" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="X30" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y30" t="n">
         <v>970</v>
@@ -8032,7 +8032,7 @@
         <v>970</v>
       </c>
       <c r="AA30" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AB30" t="n">
         <v>970</v>
@@ -8047,88 +8047,88 @@
         <v>970</v>
       </c>
       <c r="AF30" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AG30" t="n">
         <v>970</v>
       </c>
       <c r="AH30" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AI30" t="n">
         <v>36</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK30" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AL30" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM30" t="n">
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AO30" t="n">
         <v>970</v>
       </c>
       <c r="AP30" t="n">
-        <v>3.85</v>
+        <v>2.92</v>
       </c>
       <c r="AQ30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU30" t="n">
         <v>3.45</v>
       </c>
-      <c r="AR30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU30" t="n">
+      <c r="AV30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BE30" t="n">
         <v>3.25</v>
       </c>
-      <c r="AV30" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BF30" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="BG30" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="BH30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
         <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="G32" t="n">
         <v>5.7</v>
@@ -8486,10 +8486,10 @@
         <v>1.71</v>
       </c>
       <c r="I32" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="J32" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="K32" t="n">
         <v>4.4</v>
@@ -8501,7 +8501,7 @@
         <v>1.06</v>
       </c>
       <c r="N32" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="O32" t="n">
         <v>1.28</v>
@@ -8510,13 +8510,13 @@
         <v>1.9</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R32" t="n">
         <v>1.35</v>
       </c>
       <c r="S32" t="n">
-        <v>3.05</v>
+        <v>2.56</v>
       </c>
       <c r="T32" t="n">
         <v>1.76</v>
@@ -8534,7 +8534,7 @@
         <v>19</v>
       </c>
       <c r="Y32" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="Z32" t="n">
         <v>14</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -8734,19 +8734,19 @@
         <v>1.04</v>
       </c>
       <c r="G33" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H33" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="I33" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J33" t="n">
         <v>1.04</v>
       </c>
       <c r="K33" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -8988,19 +8988,19 @@
         <v>1.04</v>
       </c>
       <c r="G34" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H34" t="n">
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J34" t="n">
         <v>1.04</v>
       </c>
       <c r="K34" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -9024,7 +9024,7 @@
         <v>1.08</v>
       </c>
       <c r="S34" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T34" t="n">
         <v>1.01</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -9245,16 +9245,16 @@
         <v>1000</v>
       </c>
       <c r="H35" t="n">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="I35" t="n">
-        <v>1000</v>
+        <v>1.82</v>
       </c>
       <c r="J35" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K35" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -9263,34 +9263,34 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O35" t="n">
         <v>1.02</v>
       </c>
       <c r="P35" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="R35" t="n">
         <v>1.08</v>
       </c>
       <c r="S35" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="T35" t="n">
         <v>1.01</v>
       </c>
       <c r="U35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="V35" t="n">
-        <v>1.02</v>
+        <v>2.2</v>
       </c>
       <c r="W35" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -9496,19 +9496,19 @@
         <v>1.04</v>
       </c>
       <c r="G36" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H36" t="n">
         <v>1.04</v>
       </c>
       <c r="I36" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J36" t="n">
         <v>1.04</v>
       </c>
       <c r="K36" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -9750,19 +9750,19 @@
         <v>1.04</v>
       </c>
       <c r="G37" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H37" t="n">
         <v>1.04</v>
       </c>
       <c r="I37" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J37" t="n">
         <v>1.04</v>
       </c>
       <c r="K37" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -10070,7 +10070,7 @@
         <v>970</v>
       </c>
       <c r="AC38" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AD38" t="n">
         <v>970</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -10255,16 +10255,16 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G39" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="H39" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I39" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J39" t="n">
         <v>3.15</v>
@@ -10303,10 +10303,10 @@
         <v>1.99</v>
       </c>
       <c r="V39" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W39" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="X39" t="n">
         <v>16.5</v>
@@ -10327,7 +10327,7 @@
         <v>9.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE39" t="n">
         <v>60</v>
@@ -10387,10 +10387,10 @@
         <v>4.7</v>
       </c>
       <c r="AX39" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AY39" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AZ39" t="n">
         <v>4.1</v>
@@ -10399,7 +10399,7 @@
         <v>4.8</v>
       </c>
       <c r="BB39" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BC39" t="n">
         <v>4.3</v>
@@ -10414,7 +10414,7 @@
         <v>4</v>
       </c>
       <c r="BG39" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH39" t="n">
         <v>1000</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -10512,22 +10512,22 @@
         <v>3.15</v>
       </c>
       <c r="G40" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="H40" t="n">
         <v>2.36</v>
       </c>
       <c r="I40" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="J40" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K40" t="n">
         <v>3.5</v>
       </c>
       <c r="L40" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M40" t="n">
         <v>1.08</v>
@@ -10542,13 +10542,13 @@
         <v>1.63</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="R40" t="n">
         <v>1.23</v>
       </c>
       <c r="S40" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T40" t="n">
         <v>1.9</v>
@@ -10560,7 +10560,7 @@
         <v>1.6</v>
       </c>
       <c r="W40" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="X40" t="n">
         <v>12.5</v>
@@ -10578,7 +10578,7 @@
         <v>13</v>
       </c>
       <c r="AC40" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD40" t="n">
         <v>14.5</v>
@@ -10626,10 +10626,10 @@
         <v>13</v>
       </c>
       <c r="AS40" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="AT40" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU40" t="n">
         <v>6.2</v>
@@ -10638,7 +10638,7 @@
         <v>10</v>
       </c>
       <c r="AW40" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AX40" t="n">
         <v>19</v>
@@ -10650,25 +10650,25 @@
         <v>17</v>
       </c>
       <c r="BA40" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BB40" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BC40" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BF40" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BG40" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="BH40" t="n">
         <v>3.05</v>
@@ -10680,7 +10680,7 @@
         <v>11</v>
       </c>
       <c r="BK40" t="n">
-        <v>7.8</v>
+        <v>5.5</v>
       </c>
       <c r="BL40" t="n">
         <v>1000</v>
@@ -10692,7 +10692,7 @@
         <v>6.6</v>
       </c>
       <c r="BO40" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BP40" t="n">
         <v>1000</v>
@@ -10701,7 +10701,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BR40" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS40" t="n">
         <v>9</v>
@@ -10710,7 +10710,7 @@
         <v>5.4</v>
       </c>
       <c r="BU40" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BV40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -10790,13 +10790,13 @@
         <v>1.09</v>
       </c>
       <c r="O41" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P41" t="n">
         <v>1.08</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="R41" t="n">
         <v>1.08</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
         <v>1.08</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R42" t="n">
         <v>1.08</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -11304,13 +11304,13 @@
         <v>1.08</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.02</v>
+        <v>1.54</v>
       </c>
       <c r="R43" t="n">
         <v>1.08</v>
       </c>
       <c r="S43" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="T43" t="n">
         <v>1.01</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -11558,7 +11558,7 @@
         <v>1.08</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R44" t="n">
         <v>1.08</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -11803,22 +11803,22 @@
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O45" t="n">
         <v>1.01</v>
       </c>
       <c r="P45" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R45" t="n">
         <v>1.08</v>
       </c>
       <c r="S45" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="T45" t="n">
         <v>1.01</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -12063,10 +12063,10 @@
         <v>1.01</v>
       </c>
       <c r="P46" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R46" t="n">
         <v>1.08</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -12287,10 +12287,10 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G47" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="H47" t="n">
         <v>1.04</v>
@@ -12320,7 +12320,7 @@
         <v>1.08</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R47" t="n">
         <v>1.08</v>
@@ -12338,7 +12338,7 @@
         <v>1.01</v>
       </c>
       <c r="W47" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X47" t="n">
         <v>1000</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -12574,7 +12574,7 @@
         <v>1.08</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R48" t="n">
         <v>1.08</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G49" t="n">
         <v>1000</v>
@@ -12828,7 +12828,7 @@
         <v>1.08</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R49" t="n">
         <v>1.08</v>
@@ -12843,7 +12843,7 @@
         <v>1.01</v>
       </c>
       <c r="V49" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W49" t="n">
         <v>1.01</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -13073,7 +13073,7 @@
         <v>1.01</v>
       </c>
       <c r="N50" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="O50" t="n">
         <v>1.01</v>
@@ -13082,13 +13082,13 @@
         <v>1.07</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R50" t="n">
         <v>1.08</v>
       </c>
       <c r="S50" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="T50" t="n">
         <v>1.01</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -13330,7 +13330,7 @@
         <v>1.09</v>
       </c>
       <c r="O51" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P51" t="n">
         <v>1.08</v>
@@ -13351,7 +13351,7 @@
         <v>1.01</v>
       </c>
       <c r="V51" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W51" t="n">
         <v>1.01</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -13590,7 +13590,7 @@
         <v>1.08</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R52" t="n">
         <v>1.08</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -13823,7 +13823,7 @@
         <v>3.25</v>
       </c>
       <c r="J53" t="n">
-        <v>2.74</v>
+        <v>2.98</v>
       </c>
       <c r="K53" t="n">
         <v>3.5</v>
@@ -13838,7 +13838,7 @@
         <v>2.86</v>
       </c>
       <c r="O53" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P53" t="n">
         <v>1.63</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -14089,16 +14089,16 @@
         <v>1.05</v>
       </c>
       <c r="N54" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="O54" t="n">
         <v>1.24</v>
       </c>
       <c r="P54" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R54" t="n">
         <v>1.46</v>
@@ -14107,7 +14107,7 @@
         <v>2.74</v>
       </c>
       <c r="T54" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="U54" t="n">
         <v>2.32</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -14322,16 +14322,16 @@
         <v>1.09</v>
       </c>
       <c r="G55" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="H55" t="n">
-        <v>1.09</v>
+        <v>2.2</v>
       </c>
       <c r="I55" t="n">
         <v>1000</v>
       </c>
       <c r="J55" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="K55" t="n">
         <v>1000</v>
@@ -14343,13 +14343,13 @@
         <v>1.01</v>
       </c>
       <c r="N55" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="O55" t="n">
         <v>1.45</v>
       </c>
       <c r="P55" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Q55" t="n">
         <v>1.52</v>
@@ -14361,16 +14361,16 @@
         <v>1.52</v>
       </c>
       <c r="T55" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="U55" t="n">
         <v>1.01</v>
       </c>
       <c r="V55" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W55" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X55" t="n">
         <v>1000</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -14579,7 +14579,7 @@
         <v>2.52</v>
       </c>
       <c r="H56" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="I56" t="n">
         <v>4.2</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -14827,46 +14827,46 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="G57" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="H57" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="I57" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J57" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K57" t="n">
         <v>3.4</v>
       </c>
       <c r="L57" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="M57" t="n">
         <v>1.1</v>
       </c>
       <c r="N57" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O57" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P57" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R57" t="n">
         <v>1.24</v>
       </c>
       <c r="S57" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="T57" t="n">
         <v>2</v>
@@ -14878,13 +14878,13 @@
         <v>1.32</v>
       </c>
       <c r="W57" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="X57" t="n">
         <v>12.5</v>
       </c>
       <c r="Y57" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="Z57" t="n">
         <v>34</v>
@@ -14893,22 +14893,22 @@
         <v>110</v>
       </c>
       <c r="AB57" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC57" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AD57" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE57" t="n">
         <v>70</v>
       </c>
       <c r="AF57" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AG57" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH57" t="n">
         <v>25</v>
@@ -14917,19 +14917,19 @@
         <v>90</v>
       </c>
       <c r="AJ57" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK57" t="n">
         <v>36</v>
       </c>
-      <c r="AK57" t="n">
-        <v>28</v>
-      </c>
       <c r="AL57" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM57" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN57" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO57" t="n">
         <v>90</v>
@@ -14938,25 +14938,25 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ57" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR57" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="AS57" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="AT57" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU57" t="n">
         <v>6.6</v>
       </c>
       <c r="AV57" t="n">
-        <v>14.5</v>
+        <v>3.55</v>
       </c>
       <c r="AW57" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AX57" t="n">
         <v>11.5</v>
@@ -14965,92 +14965,92 @@
         <v>10</v>
       </c>
       <c r="AZ57" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="BA57" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="BB57" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="BC57" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BG57" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH57" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BI57" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ57" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK57" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM57" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BN57" t="n">
         <v>4.9</v>
       </c>
-      <c r="BD57" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE57" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF57" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG57" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BH57" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI57" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ57" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BK57" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL57" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM57" t="n">
-        <v>21</v>
-      </c>
-      <c r="BN57" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BO57" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="BP57" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ57" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR57" t="n">
         <v>1000</v>
       </c>
       <c r="BS57" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="BT57" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BU57" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BV57" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW57" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="BX57" t="n">
         <v>1000</v>
       </c>
       <c r="BY57" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="BZ57" t="n">
         <v>1000</v>
       </c>
       <c r="CA57" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
         <v>1.07</v>
       </c>
       <c r="N58" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O58" t="n">
         <v>1.34</v>
@@ -15192,16 +15192,16 @@
         <v>11.5</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AR58" t="n">
         <v>14.5</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AT58" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AU58" t="n">
         <v>5.9</v>
@@ -15210,31 +15210,31 @@
         <v>10</v>
       </c>
       <c r="AW58" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX58" t="n">
         <v>12.5</v>
       </c>
       <c r="AY58" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AZ58" t="n">
         <v>12.5</v>
       </c>
       <c r="BA58" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BB58" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC58" t="n">
         <v>21</v>
       </c>
       <c r="BD58" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BE58" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF58" t="n">
         <v>17.5</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-07-04 04:35:46</t>
+          <t>2026-07-04 06:54:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB58"/>
+  <dimension ref="A1:CB61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -881,28 +881,28 @@
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
         <v>1.4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R2" t="n">
         <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="T2" t="n">
         <v>1.89</v>
       </c>
       <c r="U2" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V2" t="n">
         <v>1.37</v>
@@ -926,7 +926,7 @@
         <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AD2" t="n">
         <v>16.5</v>
@@ -965,64 +965,64 @@
         <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="AU2" t="n">
         <v>3.15</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BH2" t="n">
         <v>3.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.44</v>
+        <v>2.68</v>
       </c>
       <c r="BJ2" t="n">
         <v>10.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -1114,28 +1114,28 @@
         <v>2.12</v>
       </c>
       <c r="G3" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J3" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L3" t="n">
         <v>1.44</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O3" t="n">
         <v>1.45</v>
@@ -1144,13 +1144,13 @@
         <v>1.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="R3" t="n">
         <v>1.21</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="T3" t="n">
         <v>1.99</v>
@@ -1162,10 +1162,10 @@
         <v>1.28</v>
       </c>
       <c r="W3" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y3" t="n">
         <v>970</v>
@@ -1180,7 +1180,7 @@
         <v>8.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD3" t="n">
         <v>20</v>
@@ -1222,61 +1222,61 @@
         <v>3.65</v>
       </c>
       <c r="AQ3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY3" t="n">
         <v>3.8</v>
       </c>
-      <c r="AR3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS3" t="n">
+      <c r="AZ3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD3" t="n">
         <v>5</v>
       </c>
-      <c r="AT3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BE3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG3" t="n">
         <v>5.1</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>5</v>
       </c>
       <c r="BH3" t="n">
         <v>2.96</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G4" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H4" t="n">
         <v>4.3</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
@@ -1383,19 +1383,19 @@
         <v>3.65</v>
       </c>
       <c r="L4" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O4" t="n">
         <v>1.39</v>
       </c>
       <c r="P4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q4" t="n">
         <v>2.2</v>
@@ -1407,7 +1407,7 @@
         <v>4.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
         <v>1.95</v>
@@ -1416,16 +1416,16 @@
         <v>1.27</v>
       </c>
       <c r="W4" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X4" t="n">
         <v>14</v>
       </c>
       <c r="Y4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
@@ -1440,7 +1440,7 @@
         <v>19</v>
       </c>
       <c r="AE4" t="n">
-        <v>770</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
         <v>11.5</v>
@@ -1479,7 +1479,7 @@
         <v>12</v>
       </c>
       <c r="AR4" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS4" t="n">
         <v>38</v>
@@ -1491,7 +1491,7 @@
         <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW4" t="n">
         <v>30</v>
@@ -1503,7 +1503,7 @@
         <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BA4" t="n">
         <v>34</v>
@@ -1530,40 +1530,40 @@
         <v>3.15</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BN4" t="n">
         <v>4.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP4" t="n">
         <v>15</v>
       </c>
       <c r="BQ4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT4" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>7.8</v>
       </c>
       <c r="BU4" t="n">
         <v>5.7</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ4" t="n">
         <v>32</v>
       </c>
       <c r="CA4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G5" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -1634,7 +1634,7 @@
         <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
         <v>1.46</v>
@@ -1646,13 +1646,13 @@
         <v>3.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P5" t="n">
         <v>1.81</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R5" t="n">
         <v>1.31</v>
@@ -1709,7 +1709,7 @@
         <v>60</v>
       </c>
       <c r="AJ5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK5" t="n">
         <v>34</v>
@@ -1748,7 +1748,7 @@
         <v>12</v>
       </c>
       <c r="AW5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX5" t="n">
         <v>14.5</v>
@@ -1757,28 +1757,28 @@
         <v>11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16.5</v>
+        <v>7.4</v>
       </c>
       <c r="BA5" t="n">
         <v>10</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC5" t="n">
         <v>8.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF5" t="n">
         <v>20</v>
       </c>
       <c r="BG5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH5" t="n">
         <v>3.15</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="I6" t="n">
         <v>1.53</v>
@@ -1888,7 +1888,7 @@
         <v>4.4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L6" t="n">
         <v>1.39</v>
@@ -1897,7 +1897,7 @@
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O6" t="n">
         <v>1.34</v>
@@ -1915,7 +1915,7 @@
         <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U6" t="n">
         <v>1.79</v>
@@ -1924,7 +1924,7 @@
         <v>2.88</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
         <v>15</v>
@@ -1963,7 +1963,7 @@
         <v>46</v>
       </c>
       <c r="AJ6" t="n">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="AK6" t="n">
         <v>1000</v>
@@ -1993,7 +1993,7 @@
         <v>11.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU6" t="n">
         <v>9.199999999999999</v>
@@ -2032,7 +2032,7 @@
         <v>48</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH6" t="n">
         <v>3.55</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="G7" t="n">
         <v>2.04</v>
@@ -2136,22 +2136,22 @@
         <v>4.3</v>
       </c>
       <c r="I7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="M7" t="n">
         <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O7" t="n">
         <v>1.34</v>
@@ -2160,22 +2160,22 @@
         <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R7" t="n">
         <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U7" t="n">
         <v>2.02</v>
       </c>
       <c r="V7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W7" t="n">
         <v>1.96</v>
@@ -2184,7 +2184,7 @@
         <v>15.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z7" t="n">
         <v>40</v>
@@ -2193,34 +2193,34 @@
         <v>130</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC7" t="n">
         <v>9.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE7" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG7" t="n">
         <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI7" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL7" t="n">
         <v>46</v>
@@ -2229,7 +2229,7 @@
         <v>130</v>
       </c>
       <c r="AN7" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO7" t="n">
         <v>85</v>
@@ -2241,22 +2241,22 @@
         <v>11.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.5</v>
+        <v>27</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AT7" t="n">
         <v>6.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV7" t="n">
         <v>13.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AX7" t="n">
         <v>9.199999999999999</v>
@@ -2268,31 +2268,31 @@
         <v>14.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BF7" t="n">
         <v>11</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BH7" t="n">
         <v>3.35</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="BJ7" t="n">
         <v>10.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="G8" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H8" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="I8" t="n">
         <v>2.32</v>
@@ -2396,7 +2396,7 @@
         <v>3.55</v>
       </c>
       <c r="K8" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L8" t="n">
         <v>1.32</v>
@@ -2408,37 +2408,37 @@
         <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P8" t="n">
         <v>2.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="R8" t="n">
         <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U8" t="n">
         <v>2.18</v>
       </c>
       <c r="V8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W8" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X8" t="n">
         <v>19.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z8" t="n">
         <v>17.5</v>
@@ -2450,7 +2450,7 @@
         <v>17</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD8" t="n">
         <v>13</v>
@@ -2465,7 +2465,7 @@
         <v>17</v>
       </c>
       <c r="AH8" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI8" t="n">
         <v>40</v>
@@ -2543,7 +2543,7 @@
         <v>11.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI8" t="n">
         <v>3</v>
@@ -2552,13 +2552,13 @@
         <v>9.6</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN8" t="n">
         <v>7.2</v>
@@ -2570,13 +2570,13 @@
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT8" t="n">
         <v>5.4</v>
@@ -2588,23 +2588,23 @@
         <v>16.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
         <v>7.2</v>
       </c>
-      <c r="BZ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>7</v>
-      </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="I9" t="n">
         <v>1.67</v>
@@ -2665,7 +2665,7 @@
         <v>1.29</v>
       </c>
       <c r="P9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q9" t="n">
         <v>1.83</v>
@@ -2674,13 +2674,13 @@
         <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T9" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U9" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V9" t="n">
         <v>2.48</v>
@@ -2692,13 +2692,13 @@
         <v>20</v>
       </c>
       <c r="Y9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z9" t="n">
         <v>12</v>
       </c>
       <c r="AA9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AB9" t="n">
         <v>26</v>
@@ -2734,7 +2734,7 @@
         <v>110</v>
       </c>
       <c r="AM9" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN9" t="n">
         <v>150</v>
@@ -2749,7 +2749,7 @@
         <v>6.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AS9" t="n">
         <v>11</v>
@@ -2767,7 +2767,7 @@
         <v>12.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AY9" t="n">
         <v>18</v>
@@ -2776,61 +2776,61 @@
         <v>16</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG9" t="n">
         <v>6.8</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ9" t="n">
         <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BN9" t="n">
         <v>10</v>
       </c>
       <c r="BO9" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="BP9" t="n">
         <v>60</v>
       </c>
       <c r="BQ9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BR9" t="n">
         <v>65</v>
       </c>
       <c r="BS9" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BT9" t="n">
         <v>4.2</v>
@@ -2839,26 +2839,26 @@
         <v>3.2</v>
       </c>
       <c r="BV9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BX9" t="n">
         <v>26</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="CA9" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
         <v>2.98</v>
       </c>
       <c r="H10" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="I10" t="n">
         <v>3.25</v>
@@ -2907,7 +2907,7 @@
         <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M10" t="n">
         <v>1.1</v>
@@ -2919,10 +2919,10 @@
         <v>1.42</v>
       </c>
       <c r="P10" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="R10" t="n">
         <v>1.25</v>
@@ -2931,7 +2931,7 @@
         <v>4.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U10" t="n">
         <v>1.96</v>
@@ -2943,7 +2943,7 @@
         <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y10" t="n">
         <v>11</v>
@@ -2994,7 +2994,7 @@
         <v>38</v>
       </c>
       <c r="AO10" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AP10" t="n">
         <v>8.4</v>
@@ -3006,7 +3006,7 @@
         <v>14.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT10" t="n">
         <v>8.199999999999999</v>
@@ -3018,7 +3018,7 @@
         <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX10" t="n">
         <v>13.5</v>
@@ -3030,22 +3030,22 @@
         <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB10" t="n">
         <v>36</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG10" t="n">
         <v>4.9</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -3143,145 +3143,145 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1.03</v>
+        <v>2.74</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="O11" t="n">
-        <v>1.02</v>
+        <v>1.61</v>
       </c>
       <c r="P11" t="n">
-        <v>1.07</v>
+        <v>1.49</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.57</v>
+        <v>2.78</v>
       </c>
       <c r="R11" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="S11" t="n">
-        <v>1.57</v>
+        <v>3.95</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
         <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
         <v>1.03</v>
@@ -3290,7 +3290,7 @@
         <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
         <v>1.03</v>
@@ -3305,13 +3305,13 @@
         <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>2.6</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK11" t="n">
         <v>1.01</v>
@@ -3323,13 +3323,13 @@
         <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO11" t="n">
         <v>1.01</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ11" t="n">
         <v>1.01</v>
@@ -3341,13 +3341,13 @@
         <v>1.01</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU11" t="n">
         <v>1.01</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -3397,118 +3397,118 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.13</v>
+        <v>1.52</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>1.68</v>
       </c>
       <c r="H12" t="n">
-        <v>1.13</v>
+        <v>6.6</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="J12" t="n">
-        <v>1.13</v>
+        <v>3.2</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>1.11</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="P12" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.37</v>
+        <v>2.28</v>
       </c>
       <c r="R12" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="S12" t="n">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="V12" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>2.46</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
         <v>1.03</v>
@@ -3517,34 +3517,34 @@
         <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
         <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
         <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
         <v>1.03</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="I13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="J13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K13" t="n">
         <v>4.8</v>
@@ -3675,13 +3675,13 @@
         <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O13" t="n">
         <v>1.22</v>
       </c>
       <c r="P13" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q13" t="n">
         <v>1.66</v>
@@ -3690,19 +3690,19 @@
         <v>1.57</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U13" t="n">
         <v>2.32</v>
       </c>
       <c r="V13" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="W13" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="X13" t="n">
         <v>26</v>
@@ -3714,7 +3714,7 @@
         <v>11.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AB13" t="n">
         <v>28</v>
@@ -3729,7 +3729,7 @@
         <v>15.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AG13" t="n">
         <v>26</v>
@@ -3738,7 +3738,7 @@
         <v>22</v>
       </c>
       <c r="AI13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ13" t="n">
         <v>1000</v>
@@ -3747,7 +3747,7 @@
         <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>790</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
@@ -3756,7 +3756,7 @@
         <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AP13" t="n">
         <v>16.5</v>
@@ -3786,10 +3786,10 @@
         <v>26</v>
       </c>
       <c r="AY13" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA13" t="n">
         <v>19.5</v>
@@ -3798,7 +3798,7 @@
         <v>42</v>
       </c>
       <c r="BC13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD13" t="n">
         <v>30</v>
@@ -3807,16 +3807,16 @@
         <v>36</v>
       </c>
       <c r="BF13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH13" t="n">
         <v>4.2</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BJ13" t="n">
         <v>9.800000000000001</v>
@@ -3831,10 +3831,10 @@
         <v>13.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BO13" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
@@ -3849,16 +3849,16 @@
         <v>11.5</v>
       </c>
       <c r="BT13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BV13" t="n">
         <v>10</v>
       </c>
       <c r="BW13" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BX13" t="n">
         <v>22</v>
@@ -3867,14 +3867,14 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BZ13" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="CA13" t="n">
         <v>7.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -3905,109 +3905,109 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
         <v>1.13</v>
       </c>
-      <c r="G14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N14" t="n">
-        <v>1.09</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="P14" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.52</v>
+        <v>2.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="S14" t="n">
-        <v>1.66</v>
+        <v>2.02</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.57</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -4159,109 +4159,109 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.13</v>
+        <v>1.8</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>1.13</v>
+        <v>4.4</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="J15" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="O15" t="n">
-        <v>1.05</v>
+        <v>1.42</v>
       </c>
       <c r="P15" t="n">
-        <v>1.07</v>
+        <v>1.65</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.43</v>
+        <v>2.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="S15" t="n">
-        <v>1.42</v>
+        <v>3.9</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>2</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE15" t="n">
         <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI15" t="n">
         <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM15" t="n">
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
@@ -4315,7 +4315,7 @@
         <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG15" t="n">
         <v>1.01</v>
@@ -4324,13 +4324,13 @@
         <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
@@ -4342,25 +4342,25 @@
         <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BT15" t="n">
         <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
@@ -4378,11 +4378,11 @@
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -4404,239 +4404,239 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Dalian Kun City FC</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.76</v>
+        <v>1.8</v>
       </c>
       <c r="G16" t="n">
-        <v>3.15</v>
+        <v>1.95</v>
       </c>
       <c r="H16" t="n">
-        <v>2.38</v>
+        <v>4.5</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6</v>
+        <v>5.4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L16" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="P16" t="n">
-        <v>2.24</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.49</v>
+        <v>1.31</v>
       </c>
       <c r="S16" t="n">
-        <v>2.56</v>
+        <v>3.4</v>
       </c>
       <c r="T16" t="n">
-        <v>1.59</v>
+        <v>1.86</v>
       </c>
       <c r="U16" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="V16" t="n">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="W16" t="n">
-        <v>1.46</v>
+        <v>2.04</v>
       </c>
       <c r="X16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH16" t="n">
         <v>24</v>
       </c>
-      <c r="Y16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG16" t="n">
+      <c r="AI16" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN16" t="n">
         <v>16</v>
       </c>
-      <c r="AH16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>25</v>
-      </c>
       <c r="AO16" t="n">
-        <v>18.5</v>
+        <v>100</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3.45</v>
+        <v>13.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="AS16" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="AT16" t="n">
         <v>3.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.15</v>
+        <v>6.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.35</v>
+        <v>16.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="AX16" t="n">
-        <v>3.75</v>
+        <v>9.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>3.45</v>
+        <v>7.8</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.55</v>
+        <v>17.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.95</v>
+        <v>5.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="BD16" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.75</v>
+        <v>11.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.55</v>
+        <v>5.7</v>
       </c>
       <c r="BH16" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="BJ16" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="BN16" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="BO16" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="BP16" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BR16" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS16" t="n">
-        <v>7.4</v>
+        <v>2.42</v>
       </c>
       <c r="BT16" t="n">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="BU16" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="BV16" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>6.4</v>
+        <v>2.48</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>7.2</v>
+        <v>2.52</v>
       </c>
       <c r="BZ16" t="n">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="CA16" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -4658,239 +4658,239 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Foshan Nanshi FC</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.87</v>
+        <v>2.76</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="H17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X17" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AS17" t="n">
         <v>4</v>
       </c>
-      <c r="I17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="AT17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX17" t="n">
         <v>3.8</v>
       </c>
-      <c r="L17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="X17" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC17" t="n">
+      <c r="AY17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ17" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AD17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>1000</v>
-      </c>
       <c r="BK17" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.53</v>
+        <v>8.6</v>
       </c>
       <c r="BN17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO17" t="n">
         <v>4.7</v>
       </c>
-      <c r="BO17" t="n">
-        <v>3.25</v>
-      </c>
       <c r="BP17" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>18</v>
+      </c>
+      <c r="BW17" t="n">
         <v>6.2</v>
       </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>1.5</v>
-      </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.51</v>
+        <v>7</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.48</v>
+        <v>6.4</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -4912,85 +4912,85 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dalian Kun City FC</t>
+          <t>Foshan Nanshi FC</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="G18" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="H18" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5</v>
+        <v>2.86</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L18" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="M18" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="O18" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="P18" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="S18" t="n">
         <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="U18" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="V18" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W18" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="X18" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Y18" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="Z18" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA18" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC18" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AD18" t="n">
         <v>23</v>
@@ -4999,40 +4999,40 @@
         <v>85</v>
       </c>
       <c r="AF18" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AG18" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI18" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AK18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL18" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM18" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AN18" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AO18" t="n">
         <v>110</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AR18" t="n">
         <v>4.5</v>
@@ -5041,110 +5041,110 @@
         <v>4.9</v>
       </c>
       <c r="AT18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU18" t="n">
         <v>3.25</v>
       </c>
-      <c r="AU18" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AV18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX18" t="n">
         <v>3.65</v>
       </c>
       <c r="AY18" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA18" t="n">
         <v>4.8</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BE18" t="n">
         <v>4.9</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="BJ18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="BN18" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BP18" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ18" t="n">
         <v>6.2</v>
       </c>
       <c r="BR18" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>2.38</v>
+        <v>4.1</v>
       </c>
       <c r="BT18" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>2.44</v>
+        <v>4.2</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.46</v>
+        <v>4.2</v>
       </c>
       <c r="BZ18" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>2.36</v>
+        <v>4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G19" t="n">
         <v>1.81</v>
@@ -5226,7 +5226,7 @@
         <v>1.27</v>
       </c>
       <c r="W19" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X19" t="n">
         <v>40</v>
@@ -5256,7 +5256,7 @@
         <v>17</v>
       </c>
       <c r="AG19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH19" t="n">
         <v>15</v>
@@ -5277,7 +5277,7 @@
         <v>55</v>
       </c>
       <c r="AN19" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AO19" t="n">
         <v>24</v>
@@ -5337,16 +5337,16 @@
         <v>21</v>
       </c>
       <c r="BH19" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BI19" t="n">
         <v>4.8</v>
       </c>
       <c r="BJ19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL19" t="n">
         <v>60</v>
@@ -5367,28 +5367,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BR19" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BS19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT19" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU19" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV19" t="n">
         <v>28</v>
       </c>
       <c r="BW19" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY19" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ19" t="n">
         <v>10.5</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
         <v>3.3</v>
       </c>
       <c r="I20" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J20" t="n">
         <v>3.7</v>
@@ -5459,7 +5459,7 @@
         <v>1.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
         <v>1.76</v>
@@ -5468,13 +5468,13 @@
         <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="T20" t="n">
         <v>1.64</v>
       </c>
       <c r="U20" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V20" t="n">
         <v>1.4</v>
@@ -5504,7 +5504,7 @@
         <v>15</v>
       </c>
       <c r="AE20" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AF20" t="n">
         <v>16</v>
@@ -5516,7 +5516,7 @@
         <v>16</v>
       </c>
       <c r="AI20" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="AJ20" t="n">
         <v>32</v>
@@ -5546,10 +5546,10 @@
         <v>20</v>
       </c>
       <c r="AS20" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AT20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU20" t="n">
         <v>7.6</v>
@@ -5558,34 +5558,34 @@
         <v>12.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AX20" t="n">
         <v>13.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
         <v>13.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BB20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC20" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BE20" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="BF20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG20" t="n">
         <v>18.5</v>
@@ -5594,7 +5594,7 @@
         <v>4.1</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="BJ20" t="n">
         <v>9.199999999999999</v>
@@ -5603,7 +5603,7 @@
         <v>4.8</v>
       </c>
       <c r="BL20" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM20" t="n">
         <v>9</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
         <v>6.6</v>
       </c>
       <c r="I21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J21" t="n">
         <v>4.7</v>
@@ -5719,7 +5719,7 @@
         <v>1.67</v>
       </c>
       <c r="R21" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S21" t="n">
         <v>2.72</v>
@@ -5734,13 +5734,13 @@
         <v>1.16</v>
       </c>
       <c r="W21" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="X21" t="n">
         <v>22</v>
       </c>
       <c r="Y21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z21" t="n">
         <v>60</v>
@@ -5758,7 +5758,7 @@
         <v>25</v>
       </c>
       <c r="AE21" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF21" t="n">
         <v>10</v>
@@ -5770,13 +5770,13 @@
         <v>22</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ21" t="n">
         <v>14.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL21" t="n">
         <v>32</v>
@@ -5791,7 +5791,7 @@
         <v>100</v>
       </c>
       <c r="AP21" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AQ21" t="n">
         <v>21</v>
@@ -5821,7 +5821,7 @@
         <v>9</v>
       </c>
       <c r="AZ21" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA21" t="n">
         <v>34</v>
@@ -5857,7 +5857,7 @@
         <v>8</v>
       </c>
       <c r="BL21" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BM21" t="n">
         <v>12</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="G22" t="n">
         <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>1.52</v>
+        <v>1.09</v>
       </c>
       <c r="I22" t="n">
         <v>1000</v>
@@ -5961,13 +5961,13 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="O22" t="n">
         <v>1.28</v>
       </c>
       <c r="P22" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Q22" t="n">
         <v>1.28</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G23" t="n">
         <v>2.64</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -6445,19 +6445,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="G24" t="n">
         <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="I24" t="n">
         <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="K24" t="n">
         <v>1000</v>
@@ -6469,19 +6469,19 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="O24" t="n">
         <v>1.34</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Q24" t="n">
         <v>1.34</v>
       </c>
       <c r="R24" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S24" t="n">
         <v>1.01</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -6699,19 +6699,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="G25" t="n">
         <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="I25" t="n">
         <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="K25" t="n">
         <v>1000</v>
@@ -6723,7 +6723,7 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="O25" t="n">
         <v>1.02</v>
@@ -6747,7 +6747,7 @@
         <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W25" t="n">
         <v>1.02</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -6953,19 +6953,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G26" t="n">
-        <v>2.84</v>
+        <v>2.56</v>
       </c>
       <c r="H26" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="I26" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="J26" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K26" t="n">
         <v>4.8</v>
@@ -6974,7 +6974,7 @@
         <v>1.17</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N26" t="n">
         <v>8</v>
@@ -6992,7 +6992,7 @@
         <v>1.94</v>
       </c>
       <c r="S26" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="T26" t="n">
         <v>1.39</v>
@@ -7001,10 +7001,10 @@
         <v>3.05</v>
       </c>
       <c r="V26" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="W26" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="X26" t="n">
         <v>50</v>
@@ -7022,22 +7022,22 @@
         <v>28</v>
       </c>
       <c r="AC26" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AD26" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE26" t="n">
         <v>30</v>
       </c>
       <c r="AF26" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AG26" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH26" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI26" t="n">
         <v>32</v>
@@ -7046,22 +7046,22 @@
         <v>42</v>
       </c>
       <c r="AK26" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL26" t="n">
         <v>29</v>
       </c>
       <c r="AM26" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AN26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO26" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AP26" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="AQ26" t="n">
         <v>18</v>
@@ -7070,7 +7070,7 @@
         <v>20</v>
       </c>
       <c r="AS26" t="n">
-        <v>3.95</v>
+        <v>30</v>
       </c>
       <c r="AT26" t="n">
         <v>16.5</v>
@@ -7088,31 +7088,31 @@
         <v>17.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ26" t="n">
         <v>10</v>
       </c>
       <c r="BA26" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BB26" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="BC26" t="n">
         <v>15.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BE26" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="BF26" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH26" t="n">
         <v>5.8</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="H27" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="I27" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L27" t="n">
         <v>1.35</v>
@@ -7237,28 +7237,28 @@
         <v>1.26</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R27" t="n">
         <v>1.48</v>
       </c>
       <c r="S27" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="T27" t="n">
         <v>1.7</v>
       </c>
       <c r="U27" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V27" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="W27" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X27" t="n">
         <v>23</v>
@@ -7267,58 +7267,58 @@
         <v>11</v>
       </c>
       <c r="Z27" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB27" t="n">
         <v>17.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD27" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF27" t="n">
         <v>32</v>
       </c>
       <c r="AG27" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH27" t="n">
         <v>17</v>
       </c>
       <c r="AI27" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ27" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AK27" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AL27" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AM27" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AN27" t="n">
         <v>40</v>
       </c>
       <c r="AO27" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP27" t="n">
         <v>16.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AR27" t="n">
         <v>12</v>
@@ -7327,19 +7327,19 @@
         <v>20</v>
       </c>
       <c r="AT27" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW27" t="n">
         <v>17</v>
       </c>
       <c r="AX27" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AY27" t="n">
         <v>14.5</v>
@@ -7348,31 +7348,31 @@
         <v>15</v>
       </c>
       <c r="BA27" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC27" t="n">
         <v>10.5</v>
       </c>
-      <c r="BC27" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BD27" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BE27" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BG27" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH27" t="n">
         <v>3.85</v>
       </c>
       <c r="BI27" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="BJ27" t="n">
         <v>9.199999999999999</v>
@@ -7390,7 +7390,7 @@
         <v>7.6</v>
       </c>
       <c r="BO27" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BP27" t="n">
         <v>32</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -7715,19 +7715,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="G29" t="n">
         <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="I29" t="n">
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="K29" t="n">
         <v>1000</v>
@@ -7739,19 +7739,19 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="O29" t="n">
         <v>1.37</v>
       </c>
       <c r="P29" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Q29" t="n">
         <v>1.37</v>
       </c>
       <c r="R29" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S29" t="n">
         <v>1.37</v>
@@ -7766,7 +7766,7 @@
         <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -7969,19 +7969,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="G30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J30" t="n">
         <v>3.55</v>
-      </c>
-      <c r="H30" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J30" t="n">
-        <v>3.4</v>
       </c>
       <c r="K30" t="n">
         <v>4.4</v>
@@ -7993,34 +7993,34 @@
         <v>1.05</v>
       </c>
       <c r="N30" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="O30" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P30" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="Q30" t="n">
         <v>1.73</v>
       </c>
       <c r="R30" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
         <v>2.88</v>
       </c>
       <c r="T30" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U30" t="n">
         <v>2.2</v>
       </c>
       <c r="V30" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W30" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="X30" t="n">
         <v>22</v>
@@ -8059,7 +8059,7 @@
         <v>36</v>
       </c>
       <c r="AJ30" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AK30" t="n">
         <v>42</v>
@@ -8071,61 +8071,61 @@
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AO30" t="n">
         <v>970</v>
       </c>
       <c r="AP30" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="AQ30" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV30" t="n">
         <v>3.8</v>
       </c>
-      <c r="AR30" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AS30" t="n">
+      <c r="AW30" t="n">
         <v>3.05</v>
       </c>
-      <c r="AT30" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AW30" t="n">
+      <c r="AX30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ30" t="n">
         <v>2.98</v>
       </c>
-      <c r="AX30" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>2.92</v>
-      </c>
       <c r="BA30" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BB30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BD30" t="n">
         <v>3.2</v>
       </c>
-      <c r="BC30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BD30" t="n">
+      <c r="BE30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BF30" t="n">
         <v>3.15</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>3.05</v>
       </c>
       <c r="BG30" t="n">
         <v>2.88</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -8223,13 +8223,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="G31" t="n">
         <v>1000</v>
       </c>
       <c r="H31" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="I31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -8477,13 +8477,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="G32" t="n">
         <v>5.7</v>
       </c>
       <c r="H32" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="I32" t="n">
         <v>1.96</v>
@@ -8501,7 +8501,7 @@
         <v>1.06</v>
       </c>
       <c r="N32" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O32" t="n">
         <v>1.28</v>
@@ -8516,7 +8516,7 @@
         <v>1.35</v>
       </c>
       <c r="S32" t="n">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="T32" t="n">
         <v>1.76</v>
@@ -8534,7 +8534,7 @@
         <v>19</v>
       </c>
       <c r="Y32" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z32" t="n">
         <v>14</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -9230,31 +9230,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Club R Zemamra</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>1.04</v>
       </c>
       <c r="G35" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H35" t="n">
-        <v>1.78</v>
+        <v>1.04</v>
       </c>
       <c r="I35" t="n">
-        <v>1.82</v>
+        <v>110</v>
       </c>
       <c r="J35" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="K35" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -9266,31 +9266,31 @@
         <v>1.09</v>
       </c>
       <c r="O35" t="n">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="P35" t="n">
         <v>1.09</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="R35" t="n">
         <v>1.08</v>
       </c>
       <c r="S35" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="T35" t="n">
         <v>1.01</v>
       </c>
       <c r="U35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="V35" t="n">
-        <v>2.2</v>
+        <v>1.02</v>
       </c>
       <c r="W35" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -9484,31 +9484,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>IRT Tanger</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CODM Meknes</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="G36" t="n">
         <v>1000</v>
       </c>
       <c r="H36" t="n">
-        <v>1.04</v>
+        <v>1.74</v>
       </c>
       <c r="I36" t="n">
-        <v>1000</v>
+        <v>1.76</v>
       </c>
       <c r="J36" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="K36" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -9520,31 +9520,31 @@
         <v>1.09</v>
       </c>
       <c r="O36" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="P36" t="n">
         <v>1.08</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="R36" t="n">
         <v>1.08</v>
       </c>
       <c r="S36" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="T36" t="n">
         <v>1.01</v>
       </c>
       <c r="U36" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="V36" t="n">
-        <v>1.02</v>
+        <v>2.3</v>
       </c>
       <c r="W36" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -9738,12 +9738,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>IRT Tanger</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Union de Touarga</t>
+          <t>CODM Meknes</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -9771,22 +9771,22 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="O37" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="P37" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="R37" t="n">
         <v>1.08</v>
       </c>
       <c r="S37" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="T37" t="n">
         <v>1.01</v>
@@ -9970,14 +9970,14 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9992,145 +9992,145 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>DHJ El Jadida</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.68</v>
+        <v>1.04</v>
       </c>
       <c r="G38" t="n">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="H38" t="n">
-        <v>2.78</v>
+        <v>1.04</v>
       </c>
       <c r="I38" t="n">
-        <v>3.15</v>
+        <v>110</v>
       </c>
       <c r="J38" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="K38" t="n">
-        <v>3.5</v>
+        <v>950</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>2.94</v>
+        <v>1.09</v>
       </c>
       <c r="O38" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P38" t="n">
-        <v>1.65</v>
+        <v>1.09</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.26</v>
+        <v>1.42</v>
       </c>
       <c r="R38" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="S38" t="n">
-        <v>4.3</v>
+        <v>1.42</v>
       </c>
       <c r="T38" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="U38" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="V38" t="n">
-        <v>1.46</v>
+        <v>1.02</v>
       </c>
       <c r="W38" t="n">
-        <v>1.5</v>
+        <v>1.02</v>
       </c>
       <c r="X38" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y38" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z38" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA38" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB38" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC38" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD38" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE38" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF38" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG38" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH38" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI38" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ38" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK38" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL38" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM38" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN38" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO38" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ38" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT38" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU38" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV38" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX38" t="n">
         <v>1.03</v>
@@ -10139,22 +10139,22 @@
         <v>1.03</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF38" t="n">
         <v>1.01</v>
@@ -10163,75 +10163,75 @@
         <v>1.01</v>
       </c>
       <c r="BH38" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="BI38" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BJ38" t="n">
         <v>1000</v>
       </c>
       <c r="BK38" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN38" t="n">
         <v>1000</v>
       </c>
       <c r="BO38" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP38" t="n">
         <v>1000</v>
       </c>
       <c r="BQ38" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR38" t="n">
         <v>1000</v>
       </c>
       <c r="BS38" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT38" t="n">
         <v>1000</v>
       </c>
       <c r="BU38" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV38" t="n">
         <v>1000</v>
       </c>
       <c r="BW38" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX38" t="n">
         <v>1000</v>
       </c>
       <c r="BY38" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -10246,175 +10246,175 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Centro Atletico Fenix</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Huracan del Paso</t>
+          <t>Union de Touarga</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.91</v>
+        <v>1.04</v>
       </c>
       <c r="G39" t="n">
-        <v>2.28</v>
+        <v>1000</v>
       </c>
       <c r="H39" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="I39" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="J39" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="K39" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
       </c>
       <c r="M39" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>3.25</v>
+        <v>1.1</v>
       </c>
       <c r="O39" t="n">
-        <v>1.29</v>
+        <v>1.02</v>
       </c>
       <c r="P39" t="n">
-        <v>1.79</v>
+        <v>1.09</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.82</v>
+        <v>1.46</v>
       </c>
       <c r="R39" t="n">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="S39" t="n">
-        <v>3.1</v>
+        <v>1.46</v>
       </c>
       <c r="T39" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="U39" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="V39" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="W39" t="n">
-        <v>1.78</v>
+        <v>1.02</v>
       </c>
       <c r="X39" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y39" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z39" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA39" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB39" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC39" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD39" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE39" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF39" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG39" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH39" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI39" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ39" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK39" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL39" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM39" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO39" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AQ39" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AR39" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS39" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AT39" t="n">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="AV39" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AX39" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="AY39" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AZ39" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BA39" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB39" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC39" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE39" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BF39" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BG39" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH39" t="n">
         <v>1000</v>
@@ -10471,21 +10471,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -10495,251 +10495,251 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>MAS Maghrib A Fes</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Olympique Dcheira</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="G40" t="n">
-        <v>4.2</v>
+        <v>110</v>
       </c>
       <c r="H40" t="n">
-        <v>2.36</v>
+        <v>1.04</v>
       </c>
       <c r="I40" t="n">
-        <v>2.68</v>
+        <v>110</v>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="K40" t="n">
-        <v>3.5</v>
+        <v>950</v>
       </c>
       <c r="L40" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P40" t="n">
         <v>1.08</v>
       </c>
-      <c r="N40" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P40" t="n">
-        <v>1.63</v>
-      </c>
       <c r="Q40" t="n">
-        <v>2.26</v>
+        <v>1.39</v>
       </c>
       <c r="R40" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="S40" t="n">
-        <v>4.4</v>
+        <v>1.39</v>
       </c>
       <c r="T40" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U40" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="V40" t="n">
-        <v>1.6</v>
+        <v>1.02</v>
       </c>
       <c r="W40" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="X40" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y40" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z40" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA40" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC40" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD40" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE40" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF40" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AG40" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AH40" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI40" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ40" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AK40" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL40" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM40" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO40" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AQ40" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR40" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AS40" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AT40" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AU40" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV40" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW40" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX40" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AY40" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ40" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA40" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BB40" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BC40" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF40" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BG40" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH40" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI40" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BJ40" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK40" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BL40" t="n">
         <v>1000</v>
       </c>
       <c r="BM40" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN40" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO40" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP40" t="n">
         <v>1000</v>
       </c>
       <c r="BQ40" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BR40" t="n">
         <v>1000</v>
       </c>
       <c r="BS40" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BT40" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU40" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BV40" t="n">
         <v>1000</v>
       </c>
       <c r="BW40" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX40" t="n">
         <v>1000</v>
       </c>
       <c r="BY40" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ40" t="n">
         <v>1000</v>
       </c>
       <c r="CA40" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -10749,150 +10749,150 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Olimpo</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Villa Mitre</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.04</v>
+        <v>2.68</v>
       </c>
       <c r="G41" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="H41" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="I41" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="J41" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="K41" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="L41" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M41" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N41" t="n">
-        <v>1.09</v>
+        <v>2.94</v>
       </c>
       <c r="O41" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="P41" t="n">
-        <v>1.08</v>
+        <v>1.65</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.05</v>
+        <v>2.26</v>
       </c>
       <c r="R41" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="S41" t="n">
-        <v>1.65</v>
+        <v>4.3</v>
       </c>
       <c r="T41" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U41" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V41" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="W41" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="X41" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y41" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA41" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB41" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC41" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD41" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE41" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF41" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG41" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH41" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI41" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK41" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL41" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM41" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN41" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO41" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV41" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX41" t="n">
         <v>1.03</v>
@@ -10901,22 +10901,22 @@
         <v>1.03</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF41" t="n">
         <v>1.01</v>
@@ -10925,58 +10925,58 @@
         <v>1.01</v>
       </c>
       <c r="BH41" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI41" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BJ41" t="n">
         <v>1000</v>
       </c>
       <c r="BK41" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL41" t="n">
         <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BN41" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO41" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP41" t="n">
         <v>1000</v>
       </c>
       <c r="BQ41" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BR41" t="n">
         <v>1000</v>
       </c>
       <c r="BS41" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BT41" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BU41" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV41" t="n">
         <v>1000</v>
       </c>
       <c r="BW41" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BX41" t="n">
         <v>1000</v>
       </c>
       <c r="BY41" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BZ41" t="n">
         <v>0</v>
@@ -10986,14 +10986,14 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -11003,180 +11003,180 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Centro Atletico Fenix</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CA Germinal</t>
+          <t>Huracan del Paso</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.07</v>
+        <v>1.91</v>
       </c>
       <c r="G42" t="n">
-        <v>1000</v>
+        <v>2.28</v>
       </c>
       <c r="H42" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="I42" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="J42" t="n">
-        <v>1.07</v>
+        <v>3.15</v>
       </c>
       <c r="K42" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
       </c>
       <c r="M42" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N42" t="n">
-        <v>1.08</v>
+        <v>3.25</v>
       </c>
       <c r="O42" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="P42" t="n">
-        <v>1.08</v>
+        <v>1.79</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="R42" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="S42" t="n">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="T42" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U42" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="V42" t="n">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="W42" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="X42" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z42" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA42" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB42" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC42" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD42" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE42" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF42" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG42" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI42" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK42" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL42" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM42" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN42" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO42" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG42" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH42" t="n">
         <v>1000</v>
@@ -11240,14 +11240,14 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -11262,239 +11262,239 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Sol De Mayo</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CA Kimberley</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="G43" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="H43" t="n">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="I43" t="n">
-        <v>1000</v>
+        <v>2.46</v>
       </c>
       <c r="J43" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="K43" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="L43" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M43" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N43" t="n">
-        <v>1.09</v>
+        <v>2.94</v>
       </c>
       <c r="O43" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="P43" t="n">
-        <v>1.08</v>
+        <v>1.66</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.54</v>
+        <v>2.24</v>
       </c>
       <c r="R43" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="S43" t="n">
-        <v>1.53</v>
+        <v>4.3</v>
       </c>
       <c r="T43" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U43" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V43" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="W43" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="X43" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z43" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA43" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB43" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC43" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD43" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE43" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF43" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG43" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH43" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI43" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK43" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL43" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM43" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN43" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO43" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT43" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG43" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH43" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI43" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BJ43" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK43" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BL43" t="n">
         <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN43" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO43" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BP43" t="n">
         <v>1000</v>
       </c>
       <c r="BQ43" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR43" t="n">
         <v>1000</v>
       </c>
       <c r="BS43" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BT43" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BU43" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV43" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW43" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX43" t="n">
         <v>1000</v>
       </c>
       <c r="BY43" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA43" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -11516,16 +11516,16 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CA Douglas Haig</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sportivo AC Las Parejas</t>
+          <t>CA Germinal</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="G44" t="n">
         <v>1000</v>
@@ -11537,7 +11537,7 @@
         <v>1000</v>
       </c>
       <c r="J44" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="K44" t="n">
         <v>1000</v>
@@ -11564,7 +11564,7 @@
         <v>1.08</v>
       </c>
       <c r="S44" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="T44" t="n">
         <v>1.01</v>
@@ -11573,7 +11573,7 @@
         <v>1.01</v>
       </c>
       <c r="V44" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W44" t="n">
         <v>1.01</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -11770,12 +11770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Gimnasia Conc del Uruguay</t>
+          <t>Olimpo</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>9 de Julio Rafaela</t>
+          <t>Villa Mitre</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -11803,22 +11803,22 @@
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="O45" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P45" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="R45" t="n">
         <v>1.08</v>
       </c>
       <c r="S45" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="T45" t="n">
         <v>1.01</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -12019,17 +12019,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Boca Unidos</t>
+          <t>Sol De Mayo</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sarmiento de Resistencia</t>
+          <t>CA Kimberley</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -12072,7 +12072,7 @@
         <v>1.08</v>
       </c>
       <c r="S46" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="T46" t="n">
         <v>1.01</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -12273,21 +12273,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Def Belgrano VR</t>
+          <t>CA Douglas Haig</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Escobar FC</t>
+          <t>Sportivo AC Las Parejas</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G47" t="n">
         <v>1000</v>
@@ -12311,7 +12311,7 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="O47" t="n">
         <v>1.01</v>
@@ -12326,7 +12326,7 @@
         <v>1.08</v>
       </c>
       <c r="S47" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="T47" t="n">
         <v>1.01</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -12527,21 +12527,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Sportivo Belgrano</t>
+          <t>Gimnasia Conc del Uruguay</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Independiente Chivilcoy</t>
+          <t>9 de Julio Rafaela</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.04</v>
+        <v>1.7</v>
       </c>
       <c r="G48" t="n">
         <v>1000</v>
@@ -12565,13 +12565,13 @@
         <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="O48" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P48" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Q48" t="n">
         <v>1.01</v>
@@ -12580,7 +12580,7 @@
         <v>1.08</v>
       </c>
       <c r="S48" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="T48" t="n">
         <v>1.01</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -12781,21 +12781,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Gimnasia y Chivilcoy</t>
+          <t>Boca Unidos</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Club Atletico el Linqueno</t>
+          <t>Sarmiento de Resistencia</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="G49" t="n">
         <v>1000</v>
@@ -12834,7 +12834,7 @@
         <v>1.08</v>
       </c>
       <c r="S49" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="T49" t="n">
         <v>1.01</v>
@@ -12843,7 +12843,7 @@
         <v>1.01</v>
       </c>
       <c r="V49" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W49" t="n">
         <v>1.01</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -13035,17 +13035,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>San Martin de Mendoza</t>
+          <t>Def Belgrano VR</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Deportivo Rincon</t>
+          <t>Escobar FC</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -13073,13 +13073,13 @@
         <v>1.01</v>
       </c>
       <c r="N50" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P50" t="n">
         <v>1.08</v>
-      </c>
-      <c r="O50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P50" t="n">
-        <v>1.07</v>
       </c>
       <c r="Q50" t="n">
         <v>1.01</v>
@@ -13088,7 +13088,7 @@
         <v>1.08</v>
       </c>
       <c r="S50" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="T50" t="n">
         <v>1.01</v>
@@ -13097,7 +13097,7 @@
         <v>1.01</v>
       </c>
       <c r="V50" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W50" t="n">
         <v>1.01</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -13294,12 +13294,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>General SMF</t>
+          <t>Sportivo Belgrano</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>C J Antoniana</t>
+          <t>Independiente Chivilcoy</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -13315,7 +13315,7 @@
         <v>1000</v>
       </c>
       <c r="J51" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="K51" t="n">
         <v>1000</v>
@@ -13330,19 +13330,19 @@
         <v>1.09</v>
       </c>
       <c r="O51" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P51" t="n">
         <v>1.08</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R51" t="n">
         <v>1.08</v>
       </c>
       <c r="S51" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="T51" t="n">
         <v>1.01</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -13548,28 +13548,28 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Tucuman Central</t>
+          <t>Gimnasia y Chivilcoy</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sol de America de Formosa</t>
+          <t>Club Atletico el Linqueno</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G52" t="n">
         <v>1000</v>
       </c>
       <c r="H52" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I52" t="n">
         <v>1000</v>
       </c>
       <c r="J52" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="K52" t="n">
         <v>1000</v>
@@ -13581,7 +13581,7 @@
         <v>1.01</v>
       </c>
       <c r="N52" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="O52" t="n">
         <v>1.01</v>
@@ -13596,7 +13596,7 @@
         <v>1.08</v>
       </c>
       <c r="S52" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="T52" t="n">
         <v>1.01</v>
@@ -13605,10 +13605,10 @@
         <v>1.01</v>
       </c>
       <c r="V52" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W52" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X52" t="n">
         <v>1000</v>
@@ -13773,21 +13773,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ52" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA52" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -13797,234 +13797,234 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Tacuarembo</t>
+          <t>San Martin de Mendoza</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Cerrito</t>
+          <t>Deportivo Rincon</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="G53" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="H53" t="n">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="I53" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="J53" t="n">
-        <v>2.98</v>
+        <v>1.03</v>
       </c>
       <c r="K53" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="L53" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M53" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N53" t="n">
-        <v>2.86</v>
+        <v>1.08</v>
       </c>
       <c r="O53" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="P53" t="n">
-        <v>1.63</v>
+        <v>1.07</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="R53" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="S53" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="T53" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="U53" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="V53" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="W53" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="X53" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y53" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z53" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA53" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB53" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC53" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD53" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE53" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF53" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG53" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH53" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI53" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ53" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK53" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AL53" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM53" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN53" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AO53" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP53" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ53" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AR53" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS53" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AT53" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AU53" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV53" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AW53" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX53" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AY53" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ53" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BA53" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BB53" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BC53" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BD53" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BE53" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF53" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG53" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BH53" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI53" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BJ53" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK53" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL53" t="n">
         <v>1000</v>
       </c>
       <c r="BM53" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN53" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO53" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP53" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ53" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BR53" t="n">
         <v>1000</v>
       </c>
       <c r="BS53" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BT53" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU53" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV53" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW53" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX53" t="n">
         <v>1000</v>
       </c>
       <c r="BY53" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ53" t="n">
         <v>0</v>
@@ -14034,14 +14034,14 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -14051,126 +14051,126 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>General SMF</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>C J Antoniana</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="G54" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="H54" t="n">
-        <v>2.42</v>
+        <v>1.04</v>
       </c>
       <c r="I54" t="n">
-        <v>2.76</v>
+        <v>1000</v>
       </c>
       <c r="J54" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="K54" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L54" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M54" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N54" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="O54" t="n">
-        <v>1.24</v>
+        <v>1.02</v>
       </c>
       <c r="P54" t="n">
-        <v>2.16</v>
+        <v>1.08</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.69</v>
+        <v>1.02</v>
       </c>
       <c r="R54" t="n">
-        <v>1.46</v>
+        <v>1.08</v>
       </c>
       <c r="S54" t="n">
-        <v>2.74</v>
+        <v>1.45</v>
       </c>
       <c r="T54" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="U54" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="V54" t="n">
-        <v>1.56</v>
+        <v>1.02</v>
       </c>
       <c r="W54" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="X54" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y54" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z54" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA54" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AB54" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AC54" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD54" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE54" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF54" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG54" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH54" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI54" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ54" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK54" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL54" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM54" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN54" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO54" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AP54" t="n">
         <v>1.03</v>
@@ -14221,10 +14221,10 @@
         <v>1.03</v>
       </c>
       <c r="BF54" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BG54" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH54" t="n">
         <v>1000</v>
@@ -14281,21 +14281,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ54" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA54" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -14305,33 +14305,33 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Delfin</t>
+          <t>Tucuman Central</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Sol de America de Formosa</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G55" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H55" t="n">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="I55" t="n">
         <v>1000</v>
       </c>
       <c r="J55" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="K55" t="n">
         <v>1000</v>
@@ -14343,25 +14343,25 @@
         <v>1.01</v>
       </c>
       <c r="N55" t="n">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="O55" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="P55" t="n">
-        <v>1.38</v>
+        <v>1.08</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="R55" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="S55" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="T55" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="U55" t="n">
         <v>1.01</v>
@@ -14370,7 +14370,7 @@
         <v>1.02</v>
       </c>
       <c r="W55" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X55" t="n">
         <v>1000</v>
@@ -14427,52 +14427,52 @@
         <v>1000</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS55" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT55" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU55" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV55" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX55" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA55" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC55" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD55" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF55" t="n">
         <v>1.01</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
@@ -14559,30 +14559,30 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Colon FC</t>
+          <t>Tacuarembo</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Uruguay Montevideo FC</t>
+          <t>Cerrito</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2.22</v>
+        <v>2.62</v>
       </c>
       <c r="G56" t="n">
-        <v>2.52</v>
+        <v>3.05</v>
       </c>
       <c r="H56" t="n">
-        <v>3.45</v>
+        <v>2.76</v>
       </c>
       <c r="I56" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="J56" t="n">
         <v>2.98</v>
@@ -14591,202 +14591,202 @@
         <v>3.5</v>
       </c>
       <c r="L56" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M56" t="n">
         <v>1.1</v>
       </c>
       <c r="N56" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="O56" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="P56" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="R56" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S56" t="n">
         <v>4.3</v>
       </c>
       <c r="T56" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="U56" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="V56" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="W56" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="X56" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB56" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y56" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AC56" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD56" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AE56" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AF56" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG56" t="n">
         <v>16</v>
       </c>
-      <c r="AG56" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AH56" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI56" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AJ56" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AK56" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AL56" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM56" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AN56" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AO56" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AP56" t="n">
         <v>7.6</v>
       </c>
       <c r="AQ56" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="AR56" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="AS56" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AT56" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG56" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BH56" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ56" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK56" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ56" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS56" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT56" t="n">
         <v>6.2</v>
       </c>
-      <c r="AU56" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA56" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB56" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC56" t="n">
+      <c r="BU56" t="n">
         <v>4.4</v>
       </c>
-      <c r="BD56" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF56" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG56" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BH56" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI56" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BJ56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK56" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BL56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM56" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BN56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO56" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BP56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ56" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BR56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS56" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BT56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU56" t="n">
-        <v>1.42</v>
-      </c>
       <c r="BV56" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW56" t="n">
-        <v>1.42</v>
+        <v>7.2</v>
       </c>
       <c r="BX56" t="n">
         <v>1000</v>
       </c>
       <c r="BY56" t="n">
-        <v>1.42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ56" t="n">
         <v>0</v>
@@ -14796,14 +14796,14 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -14813,498 +14813,1260 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>HFX Wanderers</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2.26</v>
+        <v>2.66</v>
       </c>
       <c r="G57" t="n">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="H57" t="n">
-        <v>3.7</v>
+        <v>2.42</v>
       </c>
       <c r="I57" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K57" t="n">
         <v>4.1</v>
       </c>
-      <c r="J57" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K57" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L57" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="M57" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="N57" t="n">
-        <v>2.96</v>
+        <v>4.1</v>
       </c>
       <c r="O57" t="n">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="P57" t="n">
-        <v>1.66</v>
+        <v>1.98</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.34</v>
+        <v>1.68</v>
       </c>
       <c r="R57" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="S57" t="n">
-        <v>4.5</v>
+        <v>2.74</v>
       </c>
       <c r="T57" t="n">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="U57" t="n">
-        <v>1.9</v>
+        <v>2.32</v>
       </c>
       <c r="V57" t="n">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="W57" t="n">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="X57" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG57" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y57" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN57" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO57" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR57" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA57" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB57" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC57" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD57" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE57" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF57" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BG57" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BH57" t="n">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="BI57" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BJ57" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK57" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL57" t="n">
         <v>1000</v>
       </c>
       <c r="BM57" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="BN57" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO57" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP57" t="n">
         <v>1000</v>
       </c>
       <c r="BQ57" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BR57" t="n">
         <v>1000</v>
       </c>
       <c r="BS57" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT57" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU57" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV57" t="n">
         <v>1000</v>
       </c>
       <c r="BW57" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX57" t="n">
         <v>1000</v>
       </c>
       <c r="BY57" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BZ57" t="n">
         <v>1000</v>
       </c>
       <c r="CA57" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-04 06:54:33</t>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Delfin</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Emelec</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G58" t="n">
+        <v>100</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N58" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB58" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Colon FC</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Uruguay Montevideo FC</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H59" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I59" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K59" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N59" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S59" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X59" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT59" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB59" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC59" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD59" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE59" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF59" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG59" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH59" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI59" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BJ59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK59" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BL59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM59" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BN59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO59" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BP59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ59" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BR59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS59" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BT59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU59" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BV59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW59" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BX59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY59" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BZ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB59" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Nautico PE</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H60" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I60" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N60" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P60" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S60" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X60" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ60" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT60" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU60" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY60" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB60" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC60" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD60" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE60" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF60" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BG60" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH60" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BI60" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ60" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK60" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM60" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN60" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO60" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ60" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS60" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT60" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU60" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW60" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY60" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BZ60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA60" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="CB60" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>Brazilian Serie C</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>21:00:00</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Anapolis GO</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Botafogo PB</t>
         </is>
       </c>
-      <c r="F58" t="n">
+      <c r="F61" t="n">
         <v>2.5</v>
       </c>
-      <c r="G58" t="n">
+      <c r="G61" t="n">
         <v>2.88</v>
       </c>
-      <c r="H58" t="n">
+      <c r="H61" t="n">
         <v>2.8</v>
       </c>
-      <c r="I58" t="n">
+      <c r="I61" t="n">
         <v>3.25</v>
       </c>
-      <c r="J58" t="n">
+      <c r="J61" t="n">
         <v>3.15</v>
       </c>
-      <c r="K58" t="n">
+      <c r="K61" t="n">
         <v>3.75</v>
       </c>
-      <c r="L58" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M58" t="n">
+      <c r="L61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M61" t="n">
         <v>1.07</v>
       </c>
-      <c r="N58" t="n">
+      <c r="N61" t="n">
         <v>3.35</v>
       </c>
-      <c r="O58" t="n">
+      <c r="O61" t="n">
         <v>1.34</v>
       </c>
-      <c r="P58" t="n">
+      <c r="P61" t="n">
         <v>1.81</v>
       </c>
-      <c r="Q58" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R58" t="n">
+      <c r="Q61" t="n">
+        <v>2</v>
+      </c>
+      <c r="R61" t="n">
         <v>1.34</v>
       </c>
-      <c r="S58" t="n">
+      <c r="S61" t="n">
         <v>3.4</v>
       </c>
-      <c r="T58" t="n">
+      <c r="T61" t="n">
         <v>1.75</v>
       </c>
-      <c r="U58" t="n">
+      <c r="U61" t="n">
         <v>2.04</v>
       </c>
-      <c r="V58" t="n">
+      <c r="V61" t="n">
         <v>1.44</v>
       </c>
-      <c r="W58" t="n">
+      <c r="W61" t="n">
         <v>1.53</v>
       </c>
-      <c r="X58" t="n">
+      <c r="X61" t="n">
         <v>19.5</v>
       </c>
-      <c r="Y58" t="n">
+      <c r="Y61" t="n">
         <v>12.5</v>
       </c>
-      <c r="Z58" t="n">
+      <c r="Z61" t="n">
         <v>28</v>
       </c>
-      <c r="AA58" t="n">
+      <c r="AA61" t="n">
         <v>55</v>
       </c>
-      <c r="AB58" t="n">
+      <c r="AB61" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD61" t="n">
         <v>970</v>
       </c>
-      <c r="AC58" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD58" t="n">
+      <c r="AE61" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF61" t="n">
         <v>970</v>
       </c>
-      <c r="AE58" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF58" t="n">
+      <c r="AG61" t="n">
         <v>970</v>
       </c>
-      <c r="AG58" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH58" t="n">
+      <c r="AH61" t="n">
         <v>24</v>
       </c>
-      <c r="AI58" t="n">
+      <c r="AI61" t="n">
         <v>46</v>
       </c>
-      <c r="AJ58" t="n">
+      <c r="AJ61" t="n">
         <v>44</v>
       </c>
-      <c r="AK58" t="n">
+      <c r="AK61" t="n">
         <v>32</v>
       </c>
-      <c r="AL58" t="n">
+      <c r="AL61" t="n">
         <v>44</v>
       </c>
-      <c r="AM58" t="n">
+      <c r="AM61" t="n">
         <v>110</v>
       </c>
-      <c r="AN58" t="n">
+      <c r="AN61" t="n">
         <v>26</v>
       </c>
-      <c r="AO58" t="n">
+      <c r="AO61" t="n">
         <v>32</v>
       </c>
-      <c r="AP58" t="n">
+      <c r="AP61" t="n">
         <v>11.5</v>
       </c>
-      <c r="AQ58" t="n">
+      <c r="AQ61" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT61" t="n">
         <v>5</v>
       </c>
-      <c r="AR58" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS58" t="n">
+      <c r="AU61" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV61" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW61" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY61" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA61" t="n">
         <v>7.6</v>
       </c>
-      <c r="AT58" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU58" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV58" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW58" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX58" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY58" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AZ58" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA58" t="n">
+      <c r="BB61" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB58" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC58" t="n">
+      <c r="BC61" t="n">
         <v>21</v>
       </c>
-      <c r="BD58" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE58" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF58" t="n">
+      <c r="BD61" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE61" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF61" t="n">
         <v>17.5</v>
       </c>
-      <c r="BG58" t="n">
+      <c r="BG61" t="n">
         <v>21</v>
       </c>
-      <c r="BH58" t="n">
+      <c r="BH61" t="n">
         <v>4</v>
       </c>
-      <c r="BI58" t="n">
+      <c r="BI61" t="n">
         <v>2.7</v>
       </c>
-      <c r="BJ58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK58" t="n">
+      <c r="BJ61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK61" t="n">
         <v>1.34</v>
       </c>
-      <c r="BL58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM58" t="n">
+      <c r="BL61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM61" t="n">
         <v>1.34</v>
       </c>
-      <c r="BN58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO58" t="n">
+      <c r="BN61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO61" t="n">
         <v>1.34</v>
       </c>
-      <c r="BP58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ58" t="n">
+      <c r="BP61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ61" t="n">
         <v>1.34</v>
       </c>
-      <c r="BR58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS58" t="n">
+      <c r="BR61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS61" t="n">
         <v>1.34</v>
       </c>
-      <c r="BT58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU58" t="n">
+      <c r="BT61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU61" t="n">
         <v>1.34</v>
       </c>
-      <c r="BV58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW58" t="n">
+      <c r="BV61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW61" t="n">
         <v>1.34</v>
       </c>
-      <c r="BX58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY58" t="n">
+      <c r="BX61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY61" t="n">
         <v>1.34</v>
       </c>
-      <c r="BZ58" t="n">
+      <c r="BZ61" t="n">
         <v>0</v>
       </c>
-      <c r="CA58" t="n">
+      <c r="CA61" t="n">
         <v>0</v>
       </c>
-      <c r="CB58" t="inlineStr">
-        <is>
-          <t>2026-07-04 06:54:33</t>
+      <c r="CB61" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:13:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
@@ -896,7 +896,7 @@
         <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="T2" t="n">
         <v>1.89</v>
@@ -953,7 +953,7 @@
         <v>38</v>
       </c>
       <c r="AL2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
         <v>150</v>
@@ -974,13 +974,13 @@
         <v>4.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT2" t="n">
         <v>3.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AV2" t="n">
         <v>4.1</v>
@@ -992,13 +992,13 @@
         <v>4.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB2" t="n">
         <v>4.9</v>
@@ -1013,10 +1013,10 @@
         <v>5.3</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH2" t="n">
         <v>3.1</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>2.44</v>
       </c>
       <c r="H3" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="I3" t="n">
         <v>4.6</v>
@@ -1276,65 +1276,65 @@
         <v>2.96</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BN3" t="n">
         <v>5.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
         <v>1.39</v>
@@ -1407,7 +1407,7 @@
         <v>4.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="U4" t="n">
         <v>1.95</v>
@@ -1416,7 +1416,7 @@
         <v>1.27</v>
       </c>
       <c r="W4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="X4" t="n">
         <v>14</v>
@@ -1449,7 +1449,7 @@
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
         <v>1.38</v>
       </c>
       <c r="P5" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q5" t="n">
         <v>2.14</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="H6" t="n">
         <v>1.49</v>
@@ -1888,7 +1888,7 @@
         <v>4.4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.39</v>
@@ -1984,7 +1984,7 @@
         <v>13</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR6" t="n">
         <v>7.4</v>
@@ -2011,7 +2011,7 @@
         <v>20</v>
       </c>
       <c r="AZ6" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="BA6" t="n">
         <v>26</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2157,7 @@
         <v>1.34</v>
       </c>
       <c r="P7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q7" t="n">
         <v>2.02</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
         <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P8" t="n">
         <v>2.04</v>
@@ -2546,7 +2546,7 @@
         <v>3.75</v>
       </c>
       <c r="BI8" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ8" t="n">
         <v>9.6</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="I9" t="n">
         <v>1.67</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
         <v>2.98</v>
       </c>
       <c r="H10" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="I10" t="n">
         <v>3.25</v>
@@ -3081,7 +3081,7 @@
         <v>7.2</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS10" t="n">
         <v>8.4</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>2.8</v>
       </c>
       <c r="G11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H11" t="n">
         <v>2.86</v>
@@ -3155,28 +3155,28 @@
         <v>3.3</v>
       </c>
       <c r="J11" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="K11" t="n">
         <v>3.15</v>
       </c>
       <c r="L11" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="M11" t="n">
         <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="O11" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="P11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="R11" t="n">
         <v>1.17</v>
@@ -3185,22 +3185,22 @@
         <v>3.95</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="V11" t="n">
         <v>1.43</v>
       </c>
       <c r="W11" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X11" t="n">
         <v>8.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z11" t="n">
         <v>22</v>
@@ -3215,158 +3215,158 @@
         <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF11" t="n">
         <v>21</v>
       </c>
       <c r="AG11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AI11" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN11" t="n">
         <v>70</v>
       </c>
-      <c r="AK11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>80</v>
-      </c>
       <c r="AO11" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="BJ11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BN11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BP11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BT11" t="n">
         <v>6</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BV11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -3409,13 +3409,13 @@
         <v>11.5</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K12" t="n">
         <v>4.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M12" t="n">
         <v>1.1</v>
@@ -3436,7 +3436,7 @@
         <v>1.19</v>
       </c>
       <c r="S12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T12" t="n">
         <v>2.38</v>
@@ -3445,7 +3445,7 @@
         <v>1.55</v>
       </c>
       <c r="V12" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W12" t="n">
         <v>2.46</v>
@@ -3454,7 +3454,7 @@
         <v>12</v>
       </c>
       <c r="Y12" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Z12" t="n">
         <v>95</v>
@@ -3475,10 +3475,10 @@
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AG12" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH12" t="n">
         <v>44</v>
@@ -3487,7 +3487,7 @@
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AK12" t="n">
         <v>28</v>
@@ -3499,128 +3499,128 @@
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -3654,13 +3654,13 @@
         <v>5.5</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="H13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="I13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="J13" t="n">
         <v>4.5</v>
@@ -3681,7 +3681,7 @@
         <v>1.22</v>
       </c>
       <c r="P13" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q13" t="n">
         <v>1.66</v>
@@ -3690,19 +3690,19 @@
         <v>1.57</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="T13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U13" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V13" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X13" t="n">
         <v>26</v>
@@ -3729,7 +3729,7 @@
         <v>15.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AG13" t="n">
         <v>26</v>
@@ -3747,7 +3747,7 @@
         <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>790</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
@@ -3759,7 +3759,7 @@
         <v>7.2</v>
       </c>
       <c r="AP13" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ13" t="n">
         <v>10</v>
@@ -3771,10 +3771,10 @@
         <v>14</v>
       </c>
       <c r="AT13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV13" t="n">
         <v>9.199999999999999</v>
@@ -3798,7 +3798,7 @@
         <v>42</v>
       </c>
       <c r="BC13" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD13" t="n">
         <v>30</v>
@@ -3807,10 +3807,10 @@
         <v>36</v>
       </c>
       <c r="BF13" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH13" t="n">
         <v>4.2</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="G14" t="n">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="I14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J14" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="K14" t="n">
         <v>3.75</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M14" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="O14" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="P14" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="R14" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.02</v>
       </c>
-      <c r="T14" t="n">
-        <v>1.95</v>
-      </c>
       <c r="U14" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="V14" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="W14" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="X14" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="Y14" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
         <v>29</v>
@@ -3971,10 +3971,10 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AD14" t="n">
         <v>20</v>
@@ -3983,94 +3983,94 @@
         <v>75</v>
       </c>
       <c r="AF14" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AG14" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AK14" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AL14" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
         <v>3.1</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
         <v>1.43</v>
@@ -4201,10 +4201,10 @@
         <v>3.9</v>
       </c>
       <c r="T15" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="U15" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="V15" t="n">
         <v>1.18</v>
@@ -4213,10 +4213,10 @@
         <v>2</v>
       </c>
       <c r="X15" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Y15" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="Z15" t="n">
         <v>46</v>
@@ -4228,7 +4228,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD15" t="n">
         <v>25</v>
@@ -4237,10 +4237,10 @@
         <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH15" t="n">
         <v>27</v>
@@ -4267,58 +4267,58 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF15" t="n">
-        <v>13.5</v>
+        <v>4.1</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
@@ -4330,7 +4330,7 @@
         <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
@@ -4342,25 +4342,25 @@
         <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BT15" t="n">
         <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
@@ -4378,11 +4378,11 @@
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4419,7 @@
         <v>1.95</v>
       </c>
       <c r="H16" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I16" t="n">
         <v>5.4</v>
@@ -4428,7 +4428,7 @@
         <v>3.5</v>
       </c>
       <c r="K16" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
         <v>1.37</v>
@@ -4536,7 +4536,7 @@
         <v>3.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV16" t="n">
         <v>16.5</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
         <v>1.62</v>
       </c>
       <c r="W17" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X17" t="n">
         <v>24</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -4921,46 +4921,46 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I18" t="n">
         <v>5.7</v>
       </c>
       <c r="J18" t="n">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="K18" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L18" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P18" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="R18" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
         <v>1.94</v>
@@ -4969,34 +4969,34 @@
         <v>1.88</v>
       </c>
       <c r="V18" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="X18" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Y18" t="n">
         <v>970</v>
       </c>
       <c r="Z18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA18" t="n">
         <v>140</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF18" t="n">
         <v>970</v>
@@ -5029,97 +5029,97 @@
         <v>110</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AR18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV18" t="n">
         <v>4.5</v>
       </c>
-      <c r="AS18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT18" t="n">
+      <c r="AW18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BH18" t="n">
         <v>3.2</v>
       </c>
-      <c r="AU18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>3.15</v>
-      </c>
       <c r="BI18" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="BJ18" t="n">
         <v>11.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>2.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN18" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BP18" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU18" t="n">
         <v>4.6</v>
@@ -5128,23 +5128,23 @@
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G19" t="n">
         <v>1.81</v>
@@ -5184,7 +5184,7 @@
         <v>4.3</v>
       </c>
       <c r="I19" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J19" t="n">
         <v>4.4</v>
@@ -5193,43 +5193,43 @@
         <v>4.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="M19" t="n">
         <v>1.02</v>
       </c>
       <c r="N19" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P19" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="R19" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="S19" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="T19" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="U19" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="V19" t="n">
         <v>1.27</v>
       </c>
       <c r="W19" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X19" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Y19" t="n">
         <v>30</v>
@@ -5241,52 +5241,52 @@
         <v>85</v>
       </c>
       <c r="AB19" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AC19" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD19" t="n">
         <v>19.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG19" t="n">
         <v>11.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK19" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AL19" t="n">
         <v>23</v>
       </c>
       <c r="AM19" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AN19" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AO19" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AP19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR19" t="n">
         <v>34</v>
@@ -5295,7 +5295,7 @@
         <v>38</v>
       </c>
       <c r="AT19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU19" t="n">
         <v>10.5</v>
@@ -5307,58 +5307,58 @@
         <v>30</v>
       </c>
       <c r="AX19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY19" t="n">
         <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA19" t="n">
         <v>27</v>
       </c>
       <c r="BB19" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BC19" t="n">
         <v>14</v>
       </c>
       <c r="BD19" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BE19" t="n">
         <v>29</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BG19" t="n">
         <v>21</v>
       </c>
       <c r="BH19" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BI19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BJ19" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BL19" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BM19" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN19" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BO19" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BP19" t="n">
         <v>11</v>
@@ -5367,38 +5367,38 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BR19" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BS19" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BU19" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BV19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BW19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BX19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BZ19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CA19" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -5429,16 +5429,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="G20" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I20" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
         <v>3.7</v>
@@ -5456,19 +5456,19 @@
         <v>4.7</v>
       </c>
       <c r="O20" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R20" t="n">
         <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T20" t="n">
         <v>1.64</v>
@@ -5477,10 +5477,10 @@
         <v>2.44</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W20" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="X20" t="n">
         <v>19.5</v>
@@ -5492,7 +5492,7 @@
         <v>26</v>
       </c>
       <c r="AA20" t="n">
-        <v>350</v>
+        <v>310</v>
       </c>
       <c r="AB20" t="n">
         <v>12.5</v>
@@ -5501,13 +5501,13 @@
         <v>8.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE20" t="n">
         <v>38</v>
       </c>
       <c r="AF20" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG20" t="n">
         <v>11.5</v>
@@ -5531,7 +5531,7 @@
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AO20" t="n">
         <v>28</v>
@@ -5564,7 +5564,7 @@
         <v>13.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ20" t="n">
         <v>13.5</v>
@@ -5573,7 +5573,7 @@
         <v>34</v>
       </c>
       <c r="BB20" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BC20" t="n">
         <v>18.5</v>
@@ -5585,10 +5585,10 @@
         <v>32</v>
       </c>
       <c r="BF20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BH20" t="n">
         <v>4.1</v>
@@ -5612,7 +5612,7 @@
         <v>5.6</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BP20" t="n">
         <v>16</v>
@@ -5630,7 +5630,7 @@
         <v>7</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BV20" t="n">
         <v>25</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -5683,13 +5683,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G21" t="n">
         <v>1.56</v>
       </c>
       <c r="H21" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I21" t="n">
         <v>7.2</v>
@@ -5722,7 +5722,7 @@
         <v>1.55</v>
       </c>
       <c r="S21" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T21" t="n">
         <v>1.82</v>
@@ -5752,10 +5752,10 @@
         <v>10</v>
       </c>
       <c r="AC21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE21" t="n">
         <v>95</v>
@@ -5866,13 +5866,13 @@
         <v>4.3</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="BP21" t="n">
         <v>9.6</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BR21" t="n">
         <v>23</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -5937,230 +5937,230 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.13</v>
+        <v>2.16</v>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>2.42</v>
       </c>
       <c r="H22" t="n">
-        <v>1.09</v>
+        <v>3.25</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="J22" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="K22" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P22" t="n">
-        <v>1.07</v>
+        <v>1.96</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="R22" t="n">
-        <v>1.07</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>1.28</v>
+        <v>3.25</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>1.7</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AS22" t="n">
         <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
         <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG22" t="n">
         <v>1.01</v>
       </c>
       <c r="BH22" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN22" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP22" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BR22" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT22" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV22" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BX22" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -6191,13 +6191,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G23" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I23" t="n">
         <v>3.6</v>
@@ -6206,10 +6206,10 @@
         <v>3.2</v>
       </c>
       <c r="K23" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M23" t="n">
         <v>1.07</v>
@@ -6224,16 +6224,16 @@
         <v>1.81</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R23" t="n">
         <v>1.31</v>
       </c>
       <c r="S23" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="T23" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U23" t="n">
         <v>2.08</v>
@@ -6242,10 +6242,10 @@
         <v>1.38</v>
       </c>
       <c r="W23" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y23" t="n">
         <v>13.5</v>
@@ -6266,10 +6266,10 @@
         <v>15</v>
       </c>
       <c r="AE23" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AF23" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG23" t="n">
         <v>12.5</v>
@@ -6278,7 +6278,7 @@
         <v>18.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AJ23" t="n">
         <v>36</v>
@@ -6320,7 +6320,7 @@
         <v>5.2</v>
       </c>
       <c r="AW23" t="n">
-        <v>6.6</v>
+        <v>24</v>
       </c>
       <c r="AX23" t="n">
         <v>13</v>
@@ -6329,7 +6329,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ23" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BA23" t="n">
         <v>6.8</v>
@@ -6353,58 +6353,58 @@
         <v>24</v>
       </c>
       <c r="BH23" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="BJ23" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.29</v>
+        <v>4.8</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.29</v>
+        <v>8.4</v>
       </c>
       <c r="BN23" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.29</v>
+        <v>4</v>
       </c>
       <c r="BP23" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.29</v>
+        <v>6</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.29</v>
+        <v>7</v>
       </c>
       <c r="BT23" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.29</v>
+        <v>4.9</v>
       </c>
       <c r="BV23" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.29</v>
+        <v>6.8</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.29</v>
+        <v>7.4</v>
       </c>
       <c r="BZ23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -6445,43 +6445,43 @@
         </is>
       </c>
       <c r="F24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N24" t="n">
         <v>1.12</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1.01</v>
       </c>
       <c r="O24" t="n">
         <v>1.34</v>
       </c>
       <c r="P24" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Q24" t="n">
         <v>1.34</v>
       </c>
       <c r="R24" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="S24" t="n">
         <v>1.01</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="G25" t="n">
         <v>1000</v>
@@ -6732,22 +6732,22 @@
         <v>1.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="R25" t="n">
         <v>1.07</v>
       </c>
       <c r="S25" t="n">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="U25" t="n">
         <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W25" t="n">
         <v>1.02</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G26" t="n">
         <v>2.56</v>
@@ -6962,7 +6962,7 @@
         <v>2.66</v>
       </c>
       <c r="I26" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J26" t="n">
         <v>4</v>
@@ -6971,13 +6971,13 @@
         <v>4.8</v>
       </c>
       <c r="L26" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="M26" t="n">
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O26" t="n">
         <v>1.12</v>
@@ -6998,10 +6998,10 @@
         <v>1.39</v>
       </c>
       <c r="U26" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="V26" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W26" t="n">
         <v>1.64</v>
@@ -7010,28 +7010,28 @@
         <v>50</v>
       </c>
       <c r="Y26" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="Z26" t="n">
         <v>36</v>
       </c>
       <c r="AA26" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AB26" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AC26" t="n">
         <v>13</v>
       </c>
       <c r="AD26" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AF26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG26" t="n">
         <v>16</v>
@@ -7043,10 +7043,10 @@
         <v>32</v>
       </c>
       <c r="AJ26" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL26" t="n">
         <v>29</v>
@@ -7061,10 +7061,10 @@
         <v>12</v>
       </c>
       <c r="AP26" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR26" t="n">
         <v>20</v>
@@ -7097,7 +7097,7 @@
         <v>21</v>
       </c>
       <c r="BB26" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BC26" t="n">
         <v>15.5</v>
@@ -7106,7 +7106,7 @@
         <v>20</v>
       </c>
       <c r="BE26" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BF26" t="n">
         <v>7.4</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -7207,16 +7207,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G27" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H27" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="J27" t="n">
         <v>3.95</v>
@@ -7231,7 +7231,7 @@
         <v>1.05</v>
       </c>
       <c r="N27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O27" t="n">
         <v>1.26</v>
@@ -7240,7 +7240,7 @@
         <v>2.22</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R27" t="n">
         <v>1.48</v>
@@ -7249,25 +7249,25 @@
         <v>2.92</v>
       </c>
       <c r="T27" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U27" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V27" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W27" t="n">
         <v>1.3</v>
       </c>
       <c r="X27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y27" t="n">
         <v>11</v>
       </c>
       <c r="Z27" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA27" t="n">
         <v>23</v>
@@ -7276,7 +7276,7 @@
         <v>17.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD27" t="n">
         <v>10.5</v>
@@ -7288,7 +7288,7 @@
         <v>32</v>
       </c>
       <c r="AG27" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AH27" t="n">
         <v>17</v>
@@ -7300,25 +7300,25 @@
         <v>95</v>
       </c>
       <c r="AK27" t="n">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="AL27" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM27" t="n">
         <v>95</v>
       </c>
       <c r="AN27" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AO27" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AP27" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ27" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR27" t="n">
         <v>12</v>
@@ -7333,37 +7333,37 @@
         <v>8.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW27" t="n">
         <v>17</v>
       </c>
       <c r="AX27" t="n">
-        <v>9.4</v>
+        <v>20</v>
       </c>
       <c r="AY27" t="n">
         <v>14.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>9.4</v>
+        <v>21</v>
       </c>
       <c r="BB27" t="n">
-        <v>11.5</v>
+        <v>34</v>
       </c>
       <c r="BC27" t="n">
-        <v>10.5</v>
+        <v>25</v>
       </c>
       <c r="BD27" t="n">
         <v>40</v>
       </c>
       <c r="BE27" t="n">
-        <v>11.5</v>
+        <v>34</v>
       </c>
       <c r="BF27" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="BG27" t="n">
         <v>10</v>
@@ -7378,19 +7378,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK27" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN27" t="n">
         <v>7.6</v>
       </c>
       <c r="BO27" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BP27" t="n">
         <v>32</v>
@@ -7402,16 +7402,16 @@
         <v>38</v>
       </c>
       <c r="BS27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT27" t="n">
         <v>4.9</v>
       </c>
       <c r="BU27" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BV27" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BW27" t="n">
         <v>7.2</v>
@@ -7420,17 +7420,17 @@
         <v>25</v>
       </c>
       <c r="BY27" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ27" t="n">
         <v>19.5</v>
       </c>
       <c r="CA27" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="G28" t="n">
         <v>1.4</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -7715,19 +7715,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="G29" t="n">
         <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="I29" t="n">
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="K29" t="n">
         <v>1000</v>
@@ -7739,7 +7739,7 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="O29" t="n">
         <v>1.37</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -7969,16 +7969,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="G30" t="n">
         <v>3.85</v>
       </c>
       <c r="H30" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="I30" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="J30" t="n">
         <v>3.55</v>
@@ -7987,16 +7987,16 @@
         <v>4.4</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M30" t="n">
         <v>1.05</v>
       </c>
       <c r="N30" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O30" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P30" t="n">
         <v>1.97</v>
@@ -8017,10 +8017,10 @@
         <v>2.2</v>
       </c>
       <c r="V30" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W30" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X30" t="n">
         <v>22</v>
@@ -8071,7 +8071,7 @@
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO30" t="n">
         <v>970</v>
@@ -8080,13 +8080,13 @@
         <v>2.98</v>
       </c>
       <c r="AQ30" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AS30" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AT30" t="n">
         <v>2.84</v>
@@ -8095,7 +8095,7 @@
         <v>3.55</v>
       </c>
       <c r="AV30" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AW30" t="n">
         <v>3.05</v>
@@ -8104,7 +8104,7 @@
         <v>3.05</v>
       </c>
       <c r="AY30" t="n">
-        <v>3.9</v>
+        <v>2.82</v>
       </c>
       <c r="AZ30" t="n">
         <v>2.98</v>
@@ -8113,16 +8113,16 @@
         <v>3.15</v>
       </c>
       <c r="BB30" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BC30" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BD30" t="n">
         <v>3.2</v>
       </c>
       <c r="BE30" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BF30" t="n">
         <v>3.15</v>
@@ -8131,58 +8131,58 @@
         <v>2.88</v>
       </c>
       <c r="BH30" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BI30" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BJ30" t="n">
         <v>1000</v>
       </c>
       <c r="BK30" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BN30" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BO30" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BP30" t="n">
         <v>1000</v>
       </c>
       <c r="BQ30" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BR30" t="n">
         <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BT30" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU30" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BV30" t="n">
         <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BZ30" t="n">
         <v>0</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -8223,13 +8223,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="G31" t="n">
         <v>1000</v>
       </c>
       <c r="H31" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="I31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -8510,13 +8510,13 @@
         <v>1.9</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R32" t="n">
         <v>1.35</v>
       </c>
       <c r="S32" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T32" t="n">
         <v>1.76</v>
@@ -8573,7 +8573,7 @@
         <v>80</v>
       </c>
       <c r="AL32" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AM32" t="n">
         <v>130</v>
@@ -8585,37 +8585,37 @@
         <v>14.5</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AX32" t="n">
         <v>1.03</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA32" t="n">
         <v>1.03</v>
@@ -8633,7 +8633,7 @@
         <v>1.03</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BG32" t="n">
         <v>8.6</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -8731,7 +8731,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G33" t="n">
         <v>1000</v>
@@ -8740,10 +8740,10 @@
         <v>2.26</v>
       </c>
       <c r="I33" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K33" t="n">
         <v>1000</v>
@@ -8779,10 +8779,10 @@
         <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W33" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -9493,22 +9493,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>5.7</v>
+        <v>3.65</v>
       </c>
       <c r="G36" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="H36" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="I36" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="J36" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="K36" t="n">
-        <v>3.9</v>
+        <v>6.8</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -9520,7 +9520,7 @@
         <v>1.09</v>
       </c>
       <c r="O36" t="n">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="P36" t="n">
         <v>1.08</v>
@@ -9538,13 +9538,13 @@
         <v>1.01</v>
       </c>
       <c r="U36" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="V36" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="W36" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -9601,52 +9601,52 @@
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF36" t="n">
         <v>1.01</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -10028,7 +10028,7 @@
         <v>1.09</v>
       </c>
       <c r="O38" t="n">
-        <v>1.42</v>
+        <v>1.02</v>
       </c>
       <c r="P38" t="n">
         <v>1.09</v>
@@ -10040,7 +10040,7 @@
         <v>1.08</v>
       </c>
       <c r="S38" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T38" t="n">
         <v>1.01</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -10279,13 +10279,13 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="O39" t="n">
         <v>1.02</v>
       </c>
       <c r="P39" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q39" t="n">
         <v>1.46</v>
@@ -10294,7 +10294,7 @@
         <v>1.08</v>
       </c>
       <c r="S39" t="n">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="T39" t="n">
         <v>1.01</v>
@@ -10303,7 +10303,7 @@
         <v>1.01</v>
       </c>
       <c r="V39" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W39" t="n">
         <v>1.02</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -10533,16 +10533,16 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>1.07</v>
+        <v>1.4</v>
       </c>
       <c r="O40" t="n">
         <v>1.4</v>
       </c>
       <c r="P40" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R40" t="n">
         <v>1.08</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -10778,10 +10778,10 @@
         <v>3.05</v>
       </c>
       <c r="K41" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L41" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="M41" t="n">
         <v>1.1</v>
@@ -10832,7 +10832,7 @@
         <v>970</v>
       </c>
       <c r="AC41" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AD41" t="n">
         <v>970</v>
@@ -10856,7 +10856,7 @@
         <v>65</v>
       </c>
       <c r="AK41" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AL41" t="n">
         <v>75</v>
@@ -10901,13 +10901,13 @@
         <v>1.03</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA41" t="n">
         <v>1.01</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC41" t="n">
         <v>1.01</v>
@@ -10922,7 +10922,7 @@
         <v>1.01</v>
       </c>
       <c r="BG41" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BH41" t="n">
         <v>3.05</v>
@@ -10940,7 +10940,7 @@
         <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>1.64</v>
+        <v>2.14</v>
       </c>
       <c r="BN41" t="n">
         <v>5.8</v>
@@ -10961,7 +10961,7 @@
         <v>2.06</v>
       </c>
       <c r="BT41" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BU41" t="n">
         <v>4.6</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -11023,7 +11023,7 @@
         <v>2.28</v>
       </c>
       <c r="H42" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I42" t="n">
         <v>4.7</v>
@@ -11035,7 +11035,7 @@
         <v>4.2</v>
       </c>
       <c r="L42" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M42" t="n">
         <v>1.06</v>
@@ -11044,7 +11044,7 @@
         <v>3.25</v>
       </c>
       <c r="O42" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P42" t="n">
         <v>1.79</v>
@@ -11179,58 +11179,58 @@
         <v>4.8</v>
       </c>
       <c r="BH42" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI42" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BJ42" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK42" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BL42" t="n">
         <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BN42" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO42" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BP42" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ42" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BR42" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS42" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BT42" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU42" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BV42" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW42" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BX42" t="n">
         <v>1000</v>
       </c>
       <c r="BY42" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BZ42" t="n">
         <v>0</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -11271,43 +11271,43 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="G43" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="H43" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="I43" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="J43" t="n">
         <v>3.1</v>
       </c>
       <c r="K43" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L43" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M43" t="n">
         <v>1.09</v>
       </c>
       <c r="N43" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O43" t="n">
         <v>1.43</v>
       </c>
       <c r="P43" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q43" t="n">
         <v>2.24</v>
       </c>
       <c r="R43" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S43" t="n">
         <v>4.3</v>
@@ -11319,7 +11319,7 @@
         <v>1.9</v>
       </c>
       <c r="V43" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="W43" t="n">
         <v>1.35</v>
@@ -11361,7 +11361,7 @@
         <v>50</v>
       </c>
       <c r="AJ43" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK43" t="n">
         <v>60</v>
@@ -11424,19 +11424,19 @@
         <v>4.7</v>
       </c>
       <c r="BE43" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BF43" t="n">
         <v>4.7</v>
       </c>
       <c r="BG43" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH43" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI43" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ43" t="n">
         <v>11</v>
@@ -11454,13 +11454,13 @@
         <v>6.8</v>
       </c>
       <c r="BO43" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BP43" t="n">
         <v>1000</v>
       </c>
       <c r="BQ43" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR43" t="n">
         <v>1000</v>
@@ -11472,29 +11472,29 @@
         <v>5.3</v>
       </c>
       <c r="BU43" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV43" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BW43" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX43" t="n">
         <v>1000</v>
       </c>
       <c r="BY43" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ43" t="n">
         <v>1000</v>
       </c>
       <c r="CA43" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -11791,7 +11791,7 @@
         <v>1000</v>
       </c>
       <c r="J45" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -12066,13 +12066,13 @@
         <v>1.08</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="R46" t="n">
         <v>1.08</v>
       </c>
       <c r="S46" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="T46" t="n">
         <v>1.01</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -12541,7 +12541,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.7</v>
+        <v>1.04</v>
       </c>
       <c r="G48" t="n">
         <v>1000</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="G49" t="n">
         <v>1000</v>
       </c>
       <c r="H49" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="I49" t="n">
         <v>1000</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -13315,7 +13315,7 @@
         <v>1000</v>
       </c>
       <c r="J51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="K51" t="n">
         <v>1000</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
         <v>1000</v>
       </c>
       <c r="H52" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I52" t="n">
         <v>1000</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -13859,7 +13859,7 @@
         <v>1.01</v>
       </c>
       <c r="V53" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W53" t="n">
         <v>1.01</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -14065,13 +14065,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="G54" t="n">
         <v>1000</v>
       </c>
       <c r="H54" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="I54" t="n">
         <v>1000</v>
@@ -14116,7 +14116,7 @@
         <v>1.02</v>
       </c>
       <c r="W54" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X54" t="n">
         <v>1000</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -14319,13 +14319,13 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="G55" t="n">
         <v>1000</v>
       </c>
       <c r="H55" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="I55" t="n">
         <v>1000</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -14827,22 +14827,22 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G57" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H57" t="n">
         <v>2.42</v>
       </c>
       <c r="I57" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J57" t="n">
         <v>3.55</v>
       </c>
       <c r="K57" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L57" t="n">
         <v>1.28</v>
@@ -14851,34 +14851,34 @@
         <v>1.05</v>
       </c>
       <c r="N57" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="O57" t="n">
         <v>1.24</v>
       </c>
       <c r="P57" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R57" t="n">
         <v>1.46</v>
       </c>
       <c r="S57" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T57" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="U57" t="n">
         <v>2.32</v>
       </c>
       <c r="V57" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W57" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X57" t="n">
         <v>24</v>
@@ -14914,13 +14914,13 @@
         <v>19</v>
       </c>
       <c r="AI57" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AJ57" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AK57" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AL57" t="n">
         <v>44</v>
@@ -14935,49 +14935,49 @@
         <v>21</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AT57" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AU57" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV57" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AW57" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AX57" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AY57" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AZ57" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BA57" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BB57" t="n">
         <v>1.03</v>
       </c>
       <c r="BC57" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BD57" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BE57" t="n">
         <v>1.03</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -15087,13 +15087,13 @@
         <v>100</v>
       </c>
       <c r="H58" t="n">
-        <v>1.08</v>
+        <v>2.02</v>
       </c>
       <c r="I58" t="n">
         <v>1000</v>
       </c>
       <c r="J58" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="K58" t="n">
         <v>1000</v>
@@ -15105,13 +15105,13 @@
         <v>1.01</v>
       </c>
       <c r="N58" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="O58" t="n">
         <v>1.45</v>
       </c>
       <c r="P58" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Q58" t="n">
         <v>1.52</v>
@@ -15120,7 +15120,7 @@
         <v>1.18</v>
       </c>
       <c r="S58" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="T58" t="n">
         <v>1.04</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -15341,7 +15341,7 @@
         <v>2.52</v>
       </c>
       <c r="H59" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="I59" t="n">
         <v>4.2</v>
@@ -15353,7 +15353,7 @@
         <v>3.5</v>
       </c>
       <c r="L59" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M59" t="n">
         <v>1.1</v>
@@ -15497,58 +15497,58 @@
         <v>4.8</v>
       </c>
       <c r="BH59" t="n">
-        <v>3.45</v>
+        <v>2.96</v>
       </c>
       <c r="BI59" t="n">
-        <v>2.24</v>
+        <v>2.56</v>
       </c>
       <c r="BJ59" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK59" t="n">
-        <v>1.42</v>
+        <v>5.5</v>
       </c>
       <c r="BL59" t="n">
         <v>1000</v>
       </c>
       <c r="BM59" t="n">
-        <v>1.42</v>
+        <v>10</v>
       </c>
       <c r="BN59" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO59" t="n">
-        <v>1.42</v>
+        <v>4</v>
       </c>
       <c r="BP59" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ59" t="n">
-        <v>1.42</v>
+        <v>7</v>
       </c>
       <c r="BR59" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS59" t="n">
-        <v>1.42</v>
+        <v>8.6</v>
       </c>
       <c r="BT59" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU59" t="n">
-        <v>1.42</v>
+        <v>5.3</v>
       </c>
       <c r="BV59" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW59" t="n">
-        <v>1.42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX59" t="n">
         <v>1000</v>
       </c>
       <c r="BY59" t="n">
-        <v>1.42</v>
+        <v>9</v>
       </c>
       <c r="BZ59" t="n">
         <v>0</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -15592,7 +15592,7 @@
         <v>2.28</v>
       </c>
       <c r="G60" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H60" t="n">
         <v>3.8</v>
@@ -15604,7 +15604,7 @@
         <v>3.1</v>
       </c>
       <c r="K60" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L60" t="n">
         <v>1.42</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>
@@ -15843,22 +15843,22 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="G61" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="H61" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="I61" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="J61" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K61" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L61" t="n">
         <v>1.01</v>
@@ -15867,196 +15867,196 @@
         <v>1.07</v>
       </c>
       <c r="N61" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O61" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P61" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q61" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="R61" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S61" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T61" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U61" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V61" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W61" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X61" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="Y61" t="n">
         <v>12.5</v>
       </c>
       <c r="Z61" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA61" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB61" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AC61" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD61" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AE61" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AF61" t="n">
         <v>970</v>
       </c>
       <c r="AG61" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AH61" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AI61" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AJ61" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AK61" t="n">
         <v>32</v>
       </c>
       <c r="AL61" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AM61" t="n">
         <v>110</v>
       </c>
       <c r="AN61" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO61" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AP61" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AQ61" t="n">
-        <v>5.2</v>
+        <v>8.6</v>
       </c>
       <c r="AR61" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AS61" t="n">
-        <v>7.8</v>
+        <v>5.3</v>
       </c>
       <c r="AT61" t="n">
-        <v>5</v>
+        <v>9.4</v>
       </c>
       <c r="AU61" t="n">
         <v>5.9</v>
       </c>
       <c r="AV61" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW61" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="AX61" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AY61" t="n">
-        <v>5.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ61" t="n">
         <v>12.5</v>
       </c>
       <c r="BA61" t="n">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BB61" t="n">
-        <v>7.4</v>
+        <v>22</v>
       </c>
       <c r="BC61" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BD61" t="n">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="BE61" t="n">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF61" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG61" t="n">
-        <v>21</v>
+        <v>4.9</v>
       </c>
       <c r="BH61" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BI61" t="n">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="BJ61" t="n">
         <v>1000</v>
       </c>
       <c r="BK61" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="BL61" t="n">
         <v>1000</v>
       </c>
       <c r="BM61" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="BN61" t="n">
         <v>1000</v>
       </c>
       <c r="BO61" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="BP61" t="n">
         <v>1000</v>
       </c>
       <c r="BQ61" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="BR61" t="n">
         <v>1000</v>
       </c>
       <c r="BS61" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="BT61" t="n">
         <v>1000</v>
       </c>
       <c r="BU61" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="BV61" t="n">
         <v>1000</v>
       </c>
       <c r="BW61" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="BX61" t="n">
         <v>1000</v>
       </c>
       <c r="BY61" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="BZ61" t="n">
         <v>0</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-07-04 09:13:30</t>
+          <t>2026-07-04 11:30:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
@@ -875,7 +875,7 @@
         <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
@@ -887,7 +887,7 @@
         <v>1.4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="Q2" t="n">
         <v>2.16</v>
@@ -896,7 +896,7 @@
         <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="T2" t="n">
         <v>1.84</v>
@@ -908,7 +908,7 @@
         <v>1.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X2" t="n">
         <v>13.5</v>
@@ -917,7 +917,7 @@
         <v>11.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AA2" t="n">
         <v>55</v>
@@ -929,7 +929,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE2" t="n">
         <v>42</v>
@@ -938,7 +938,7 @@
         <v>24</v>
       </c>
       <c r="AG2" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH2" t="n">
         <v>23</v>
@@ -947,7 +947,7 @@
         <v>65</v>
       </c>
       <c r="AJ2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK2" t="n">
         <v>48</v>
@@ -959,70 +959,70 @@
         <v>150</v>
       </c>
       <c r="AN2" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AO2" t="n">
         <v>42</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="AR2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT2" t="n">
         <v>3.55</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AU2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>4</v>
       </c>
-      <c r="AT2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BA2" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BH2" t="n">
         <v>3.15</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="BJ2" t="n">
         <v>11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J3" t="n">
         <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
         <v>1.41</v>
@@ -1135,40 +1135,40 @@
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>2.68</v>
+        <v>2.96</v>
       </c>
       <c r="O3" t="n">
         <v>1.42</v>
       </c>
       <c r="P3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R3" t="n">
         <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U3" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="V3" t="n">
         <v>1.22</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
       </c>
       <c r="Y3" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="Z3" t="n">
         <v>46</v>
@@ -1219,122 +1219,122 @@
         <v>140</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AQ3" t="n">
         <v>3.45</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AW3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD3" t="n">
         <v>4.1</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="BE3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO3" t="n">
         <v>3.25</v>
       </c>
-      <c r="AY3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>3.15</v>
-      </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.95</v>
+        <v>1.69</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.39</v>
+        <v>1.13</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.39</v>
+        <v>1.09</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>1.98</v>
       </c>
       <c r="G4" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H4" t="n">
         <v>4.3</v>
@@ -1377,16 +1377,16 @@
         <v>4.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K4" t="n">
         <v>3.65</v>
       </c>
       <c r="L4" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="M4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
         <v>3.35</v>
@@ -1437,10 +1437,10 @@
         <v>7.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>910</v>
+        <v>940</v>
       </c>
       <c r="AF4" t="n">
         <v>11.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G5" t="n">
         <v>2.66</v>
@@ -1634,7 +1634,7 @@
         <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
         <v>1.46</v>
@@ -1655,7 +1655,7 @@
         <v>2.14</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S5" t="n">
         <v>3.95</v>
@@ -1685,7 +1685,7 @@
         <v>60</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AC5" t="n">
         <v>7.6</v>
@@ -1736,7 +1736,7 @@
         <v>18</v>
       </c>
       <c r="AS5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT5" t="n">
         <v>9</v>
@@ -1748,7 +1748,7 @@
         <v>12</v>
       </c>
       <c r="AW5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX5" t="n">
         <v>14.5</v>
@@ -1760,25 +1760,25 @@
         <v>16.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC5" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BC5" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BD5" t="n">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BE5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF5" t="n">
         <v>20</v>
       </c>
       <c r="BG5" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="BH5" t="n">
         <v>3.15</v>
@@ -1790,7 +1790,7 @@
         <v>10</v>
       </c>
       <c r="BK5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1802,7 +1802,7 @@
         <v>5.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BP5" t="n">
         <v>21</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -1879,10 +1879,10 @@
         <v>8.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="I6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="J6" t="n">
         <v>4.4</v>
@@ -1903,16 +1903,16 @@
         <v>1.34</v>
       </c>
       <c r="P6" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T6" t="n">
         <v>2.18</v>
@@ -1921,7 +1921,7 @@
         <v>1.79</v>
       </c>
       <c r="V6" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="W6" t="n">
         <v>1.13</v>
@@ -1942,19 +1942,19 @@
         <v>23</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD6" t="n">
         <v>10.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AF6" t="n">
         <v>75</v>
       </c>
       <c r="AG6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AH6" t="n">
         <v>29</v>
@@ -1963,7 +1963,7 @@
         <v>46</v>
       </c>
       <c r="AJ6" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
         <v>1000</v>
@@ -1978,7 +1978,7 @@
         <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP6" t="n">
         <v>13</v>
@@ -1993,7 +1993,7 @@
         <v>11.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AU6" t="n">
         <v>9.199999999999999</v>
@@ -2011,7 +2011,7 @@
         <v>20</v>
       </c>
       <c r="AZ6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA6" t="n">
         <v>26</v>
@@ -2032,7 +2032,7 @@
         <v>48</v>
       </c>
       <c r="BG6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH6" t="n">
         <v>3.45</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
         <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L7" t="n">
         <v>1.37</v>
@@ -2157,7 +2157,7 @@
         <v>1.34</v>
       </c>
       <c r="P7" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q7" t="n">
         <v>2</v>
@@ -2169,7 +2169,7 @@
         <v>3.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
         <v>2.02</v>
@@ -2187,7 +2187,7 @@
         <v>17.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AA7" t="n">
         <v>130</v>
@@ -2202,10 +2202,10 @@
         <v>21</v>
       </c>
       <c r="AE7" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG7" t="n">
         <v>12.5</v>
@@ -2226,7 +2226,7 @@
         <v>46</v>
       </c>
       <c r="AM7" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN7" t="n">
         <v>17</v>
@@ -2244,7 +2244,7 @@
         <v>27</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AT7" t="n">
         <v>6.8</v>
@@ -2280,13 +2280,13 @@
         <v>30</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF7" t="n">
         <v>11</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BH7" t="n">
         <v>3.35</v>
@@ -2310,7 +2310,7 @@
         <v>4.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BP7" t="n">
         <v>13.5</v>
@@ -2328,7 +2328,7 @@
         <v>8</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -2387,16 +2387,16 @@
         <v>3.7</v>
       </c>
       <c r="H8" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="I8" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J8" t="n">
         <v>3.55</v>
       </c>
       <c r="K8" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L8" t="n">
         <v>1.32</v>
@@ -2405,31 +2405,31 @@
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P8" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R8" t="n">
         <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T8" t="n">
         <v>1.66</v>
       </c>
       <c r="U8" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="W8" t="n">
         <v>1.37</v>
@@ -2468,7 +2468,7 @@
         <v>19</v>
       </c>
       <c r="AI8" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ8" t="n">
         <v>75</v>
@@ -2480,7 +2480,7 @@
         <v>48</v>
       </c>
       <c r="AM8" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN8" t="n">
         <v>40</v>
@@ -2504,7 +2504,7 @@
         <v>11</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AV8" t="n">
         <v>8.6</v>
@@ -2513,7 +2513,7 @@
         <v>17</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AY8" t="n">
         <v>11</v>
@@ -2522,22 +2522,22 @@
         <v>12.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG8" t="n">
         <v>11.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
         <v>3.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M10" t="n">
         <v>1.1</v>
@@ -2919,7 +2919,7 @@
         <v>1.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q10" t="n">
         <v>2.18</v>
@@ -2934,7 +2934,7 @@
         <v>1.84</v>
       </c>
       <c r="U10" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
         <v>1.46</v>
@@ -2955,7 +2955,7 @@
         <v>60</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
         <v>8.4</v>
@@ -2976,7 +2976,7 @@
         <v>19.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ10" t="n">
         <v>48</v>
@@ -2985,10 +2985,10 @@
         <v>38</v>
       </c>
       <c r="AL10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM10" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AN10" t="n">
         <v>38</v>
@@ -3006,7 +3006,7 @@
         <v>14.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AT10" t="n">
         <v>8.199999999999999</v>
@@ -3018,7 +3018,7 @@
         <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX10" t="n">
         <v>13.5</v>
@@ -3030,31 +3030,31 @@
         <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BB10" t="n">
         <v>36</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BD10" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF10" t="n">
         <v>5.4</v>
       </c>
-      <c r="BE10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BG10" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BH10" t="n">
         <v>3.15</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3562,7 @@
         <v>2.96</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -3657,10 +3657,10 @@
         <v>5.9</v>
       </c>
       <c r="H13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="I13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="J13" t="n">
         <v>4.5</v>
@@ -3690,7 +3690,7 @@
         <v>1.57</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T13" t="n">
         <v>1.73</v>
@@ -3852,7 +3852,7 @@
         <v>4.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BV13" t="n">
         <v>10</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         <v>3.6</v>
       </c>
       <c r="I14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J14" t="n">
         <v>2.86</v>
@@ -3929,7 +3929,7 @@
         <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.44</v>
+        <v>2.68</v>
       </c>
       <c r="O14" t="n">
         <v>1.5</v>
@@ -3944,7 +3944,7 @@
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="T14" t="n">
         <v>2.04</v>
@@ -3953,7 +3953,7 @@
         <v>1.73</v>
       </c>
       <c r="V14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W14" t="n">
         <v>1.66</v>
@@ -4070,7 +4070,7 @@
         <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -4159,13 +4159,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I15" t="n">
         <v>6.4</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -4413,58 +4413,58 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="G16" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I16" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J16" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K16" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L16" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M16" t="n">
         <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O16" t="n">
         <v>1.39</v>
       </c>
       <c r="P16" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="T16" t="n">
         <v>1.92</v>
       </c>
       <c r="U16" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V16" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W16" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X16" t="n">
         <v>13.5</v>
@@ -4509,16 +4509,16 @@
         <v>27</v>
       </c>
       <c r="AL16" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AM16" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN16" t="n">
         <v>21</v>
       </c>
       <c r="AO16" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP16" t="n">
         <v>8.800000000000001</v>
@@ -4527,10 +4527,10 @@
         <v>11</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT16" t="n">
         <v>6</v>
@@ -4542,7 +4542,7 @@
         <v>14.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AX16" t="n">
         <v>8.6</v>
@@ -4554,7 +4554,7 @@
         <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB16" t="n">
         <v>17.5</v>
@@ -4566,19 +4566,19 @@
         <v>4.9</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF16" t="n">
         <v>13.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BH16" t="n">
         <v>3.2</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ16" t="n">
         <v>11</v>
@@ -4593,7 +4593,7 @@
         <v>10</v>
       </c>
       <c r="BN16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO16" t="n">
         <v>3.6</v>
@@ -4611,7 +4611,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU16" t="n">
         <v>4.7</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="G17" t="n">
         <v>3.1</v>
       </c>
       <c r="H17" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I17" t="n">
         <v>2.6</v>
       </c>
       <c r="J17" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.27</v>
@@ -4697,13 +4697,13 @@
         <v>1.23</v>
       </c>
       <c r="P17" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="R17" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S17" t="n">
         <v>2.66</v>
@@ -4712,13 +4712,13 @@
         <v>1.59</v>
       </c>
       <c r="U17" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V17" t="n">
         <v>1.62</v>
       </c>
       <c r="W17" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X17" t="n">
         <v>25</v>
@@ -4751,10 +4751,10 @@
         <v>16</v>
       </c>
       <c r="AH17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ17" t="n">
         <v>55</v>
@@ -4763,16 +4763,16 @@
         <v>36</v>
       </c>
       <c r="AL17" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM17" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN17" t="n">
         <v>25</v>
       </c>
       <c r="AO17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AP17" t="n">
         <v>14.5</v>
@@ -4784,7 +4784,7 @@
         <v>13.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AT17" t="n">
         <v>11</v>
@@ -4793,7 +4793,7 @@
         <v>7.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW17" t="n">
         <v>17.5</v>
@@ -4808,19 +4808,19 @@
         <v>11</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BB17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BC17" t="n">
         <v>21</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF17" t="n">
         <v>15</v>
@@ -4835,7 +4835,7 @@
         <v>3.15</v>
       </c>
       <c r="BJ17" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK17" t="n">
         <v>4.7</v>
@@ -4862,13 +4862,13 @@
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT17" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BU17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV17" t="n">
         <v>18</v>
@@ -4883,14 +4883,14 @@
         <v>7.2</v>
       </c>
       <c r="BZ17" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="CA17" t="n">
         <v>6.6</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
         <v>5.4</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
         <v>3.95</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="G19" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="H19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J19" t="n">
         <v>4.3</v>
       </c>
-      <c r="I19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>4.4</v>
-      </c>
       <c r="K19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L19" t="n">
         <v>1.23</v>
@@ -5202,10 +5202,10 @@
         <v>7.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P19" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q19" t="n">
         <v>1.43</v>
@@ -5214,19 +5214,19 @@
         <v>1.88</v>
       </c>
       <c r="S19" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T19" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U19" t="n">
         <v>2.94</v>
       </c>
       <c r="V19" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W19" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="X19" t="n">
         <v>36</v>
@@ -5241,10 +5241,10 @@
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AC19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD19" t="n">
         <v>19</v>
@@ -5256,7 +5256,7 @@
         <v>17</v>
       </c>
       <c r="AG19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH19" t="n">
         <v>15</v>
@@ -5271,7 +5271,7 @@
         <v>16</v>
       </c>
       <c r="AL19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM19" t="n">
         <v>60</v>
@@ -5283,7 +5283,7 @@
         <v>27</v>
       </c>
       <c r="AP19" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AQ19" t="n">
         <v>25</v>
@@ -5313,7 +5313,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA19" t="n">
         <v>27</v>
@@ -5325,13 +5325,13 @@
         <v>13.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BE19" t="n">
         <v>29</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG19" t="n">
         <v>21</v>
@@ -5346,13 +5346,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL19" t="n">
         <v>65</v>
       </c>
       <c r="BM19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN19" t="n">
         <v>5.2</v>
@@ -5370,35 +5370,35 @@
         <v>18</v>
       </c>
       <c r="BS19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT19" t="n">
         <v>8.6</v>
       </c>
       <c r="BU19" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV19" t="n">
         <v>29</v>
       </c>
       <c r="BW19" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX19" t="n">
         <v>30</v>
       </c>
       <c r="BY19" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA19" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -5429,25 +5429,25 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G20" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="H20" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J20" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K20" t="n">
         <v>3.9</v>
       </c>
       <c r="L20" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
@@ -5459,16 +5459,16 @@
         <v>1.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R20" t="n">
         <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T20" t="n">
         <v>1.65</v>
@@ -5477,22 +5477,22 @@
         <v>2.44</v>
       </c>
       <c r="V20" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="X20" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y20" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA20" t="n">
-        <v>310</v>
+        <v>60</v>
       </c>
       <c r="AB20" t="n">
         <v>12.5</v>
@@ -5504,82 +5504,82 @@
         <v>14.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF20" t="n">
         <v>16</v>
       </c>
       <c r="AG20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH20" t="n">
         <v>16</v>
       </c>
       <c r="AI20" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ20" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN20" t="n">
         <v>14.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP20" t="n">
         <v>16.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS20" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AT20" t="n">
         <v>11</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW20" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AX20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY20" t="n">
         <v>10</v>
       </c>
       <c r="AZ20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA20" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BB20" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC20" t="n">
         <v>19.5</v>
       </c>
-      <c r="BC20" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BD20" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BE20" t="n">
         <v>32</v>
@@ -5588,37 +5588,37 @@
         <v>12.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BH20" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BK20" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN20" t="n">
         <v>5.6</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP20" t="n">
         <v>16.5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR20" t="n">
         <v>27</v>
@@ -5645,14 +5645,14 @@
         <v>7.6</v>
       </c>
       <c r="BZ20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CA20" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -5686,10 +5686,10 @@
         <v>1.54</v>
       </c>
       <c r="G21" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="H21" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I21" t="n">
         <v>7.2</v>
@@ -5698,7 +5698,7 @@
         <v>4.7</v>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L21" t="n">
         <v>1.28</v>
@@ -5713,16 +5713,16 @@
         <v>1.23</v>
       </c>
       <c r="P21" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R21" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S21" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="T21" t="n">
         <v>1.82</v>
@@ -5737,7 +5737,7 @@
         <v>2.78</v>
       </c>
       <c r="X21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y21" t="n">
         <v>26</v>
@@ -5758,19 +5758,19 @@
         <v>26</v>
       </c>
       <c r="AE21" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF21" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG21" t="n">
         <v>10</v>
       </c>
       <c r="AH21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI21" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AJ21" t="n">
         <v>14.5</v>
@@ -5782,58 +5782,58 @@
         <v>32</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN21" t="n">
         <v>6.8</v>
       </c>
       <c r="AO21" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AP21" t="n">
         <v>19</v>
       </c>
       <c r="AQ21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR21" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AS21" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AT21" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW21" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="AX21" t="n">
         <v>9</v>
       </c>
       <c r="AY21" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ21" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA21" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BB21" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC21" t="n">
         <v>13.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BE21" t="n">
         <v>38</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -5943,13 +5943,13 @@
         <v>2.36</v>
       </c>
       <c r="H22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J22" t="n">
         <v>3.35</v>
-      </c>
-      <c r="I22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.4</v>
       </c>
       <c r="K22" t="n">
         <v>3.9</v>
@@ -5961,37 +5961,37 @@
         <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O22" t="n">
         <v>1.29</v>
       </c>
       <c r="P22" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Q22" t="n">
         <v>1.88</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S22" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U22" t="n">
         <v>2.16</v>
       </c>
       <c r="V22" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W22" t="n">
         <v>1.73</v>
       </c>
       <c r="X22" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y22" t="n">
         <v>15</v>
@@ -6003,10 +6003,10 @@
         <v>80</v>
       </c>
       <c r="AB22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD22" t="n">
         <v>16</v>
@@ -6015,7 +6015,7 @@
         <v>44</v>
       </c>
       <c r="AF22" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG22" t="n">
         <v>13</v>
@@ -6027,10 +6027,10 @@
         <v>60</v>
       </c>
       <c r="AJ22" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL22" t="n">
         <v>42</v>
@@ -6039,7 +6039,7 @@
         <v>110</v>
       </c>
       <c r="AN22" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO22" t="n">
         <v>42</v>
@@ -6048,22 +6048,22 @@
         <v>11.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR22" t="n">
-        <v>21</v>
+        <v>5.1</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AT22" t="n">
         <v>8</v>
       </c>
       <c r="AU22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW22" t="n">
         <v>32</v>
@@ -6072,7 +6072,7 @@
         <v>11.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ22" t="n">
         <v>13.5</v>
@@ -6084,25 +6084,25 @@
         <v>21</v>
       </c>
       <c r="BC22" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD22" t="n">
-        <v>27</v>
+        <v>5.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BF22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BG22" t="n">
-        <v>30</v>
+        <v>5.4</v>
       </c>
       <c r="BH22" t="n">
         <v>3.65</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BJ22" t="n">
         <v>9.800000000000001</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -6194,22 +6194,22 @@
         <v>2.32</v>
       </c>
       <c r="G23" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="H23" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="I23" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K23" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M23" t="n">
         <v>1.02</v>
@@ -6236,13 +6236,13 @@
         <v>1.37</v>
       </c>
       <c r="U23" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="V23" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W23" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X23" t="n">
         <v>50</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G24" t="n">
         <v>2.6</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="G25" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="H25" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="I25" t="n">
         <v>6.2</v>
       </c>
       <c r="J25" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K25" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L25" t="n">
         <v>1.4</v>
@@ -6723,34 +6723,34 @@
         <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P25" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S25" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U25" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V25" t="n">
         <v>1.21</v>
       </c>
       <c r="W25" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="X25" t="n">
         <v>970</v>
@@ -6789,10 +6789,10 @@
         <v>95</v>
       </c>
       <c r="AJ25" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL25" t="n">
         <v>48</v>
@@ -6807,65 +6807,65 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>2.64</v>
+        <v>4</v>
       </c>
       <c r="AQ25" t="n">
-        <v>2.76</v>
+        <v>4.3</v>
       </c>
       <c r="AR25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AZ25" t="n">
         <v>3</v>
       </c>
-      <c r="AS25" t="n">
+      <c r="BA25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BD25" t="n">
         <v>3.15</v>
       </c>
-      <c r="AT25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>3</v>
-      </c>
       <c r="BE25" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BF25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI25" t="n">
         <v>2.7</v>
       </c>
-      <c r="BG25" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>2.64</v>
-      </c>
       <c r="BJ25" t="n">
         <v>1000</v>
       </c>
@@ -6882,7 +6882,7 @@
         <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G26" t="n">
         <v>2.3</v>
@@ -6983,7 +6983,7 @@
         <v>1.47</v>
       </c>
       <c r="P26" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q26" t="n">
         <v>2.42</v>
@@ -7004,7 +7004,7 @@
         <v>1.27</v>
       </c>
       <c r="W26" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="X26" t="n">
         <v>10</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
         <v>4.3</v>
       </c>
       <c r="H27" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="I27" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="J27" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K27" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L27" t="n">
         <v>1.35</v>
@@ -7240,7 +7240,7 @@
         <v>2.22</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R27" t="n">
         <v>1.48</v>
@@ -7273,10 +7273,10 @@
         <v>23</v>
       </c>
       <c r="AB27" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AC27" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD27" t="n">
         <v>10.5</v>
@@ -7303,7 +7303,7 @@
         <v>130</v>
       </c>
       <c r="AL27" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM27" t="n">
         <v>95</v>
@@ -7318,7 +7318,7 @@
         <v>17</v>
       </c>
       <c r="AQ27" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR27" t="n">
         <v>12</v>
@@ -7330,10 +7330,10 @@
         <v>15.5</v>
       </c>
       <c r="AU27" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AV27" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW27" t="n">
         <v>17</v>
@@ -7345,13 +7345,13 @@
         <v>14.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA27" t="n">
         <v>21</v>
       </c>
       <c r="BB27" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BC27" t="n">
         <v>38</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -7464,13 +7464,13 @@
         <v>2.44</v>
       </c>
       <c r="G28" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="H28" t="n">
         <v>2.92</v>
       </c>
       <c r="I28" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J28" t="n">
         <v>3.25</v>
@@ -7512,7 +7512,7 @@
         <v>1.45</v>
       </c>
       <c r="W28" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X28" t="n">
         <v>14.5</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -7715,22 +7715,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="G29" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="H29" t="n">
         <v>10</v>
       </c>
       <c r="I29" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="J29" t="n">
         <v>5.7</v>
       </c>
       <c r="K29" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L29" t="n">
         <v>1.3</v>
@@ -7766,7 +7766,7 @@
         <v>1.07</v>
       </c>
       <c r="W29" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="X29" t="n">
         <v>21</v>
@@ -7775,7 +7775,7 @@
         <v>42</v>
       </c>
       <c r="Z29" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AA29" t="n">
         <v>850</v>
@@ -7817,7 +7817,7 @@
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>6.4</v>
+        <v>970</v>
       </c>
       <c r="AO29" t="n">
         <v>660</v>
@@ -7829,10 +7829,10 @@
         <v>30</v>
       </c>
       <c r="AR29" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS29" t="n">
-        <v>6.8</v>
+        <v>3.35</v>
       </c>
       <c r="AT29" t="n">
         <v>6.8</v>
@@ -7847,7 +7847,7 @@
         <v>3.3</v>
       </c>
       <c r="AX29" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY29" t="n">
         <v>9.199999999999999</v>
@@ -7874,7 +7874,7 @@
         <v>5</v>
       </c>
       <c r="BG29" t="n">
-        <v>6.8</v>
+        <v>3.3</v>
       </c>
       <c r="BH29" t="n">
         <v>4.1</v>
@@ -7886,16 +7886,16 @@
         <v>1000</v>
       </c>
       <c r="BK29" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BN29" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BO29" t="n">
         <v>2.98</v>
@@ -7910,35 +7910,35 @@
         <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BT29" t="n">
         <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BV29" t="n">
         <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BX29" t="n">
         <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BZ29" t="n">
         <v>1000</v>
       </c>
       <c r="CA29" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -7969,13 +7969,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="G30" t="n">
         <v>3.65</v>
       </c>
       <c r="H30" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I30" t="n">
         <v>2.4</v>
@@ -8002,7 +8002,7 @@
         <v>2.02</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R30" t="n">
         <v>1.4</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -8226,13 +8226,13 @@
         <v>2.2</v>
       </c>
       <c r="G31" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="H31" t="n">
         <v>3.1</v>
       </c>
       <c r="I31" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="J31" t="n">
         <v>2.26</v>
@@ -8271,10 +8271,10 @@
         <v>1.03</v>
       </c>
       <c r="V31" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W31" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -8489,7 +8489,7 @@
         <v>4.3</v>
       </c>
       <c r="J32" t="n">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="K32" t="n">
         <v>4.7</v>
@@ -8507,10 +8507,10 @@
         <v>1.19</v>
       </c>
       <c r="P32" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="R32" t="n">
         <v>1.49</v>
@@ -8642,65 +8642,65 @@
         <v>4.6</v>
       </c>
       <c r="BI32" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BJ32" t="n">
         <v>9.6</v>
       </c>
       <c r="BK32" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BN32" t="n">
         <v>5.8</v>
       </c>
       <c r="BO32" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BP32" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ32" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BR32" t="n">
         <v>26</v>
       </c>
       <c r="BS32" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BT32" t="n">
         <v>7.8</v>
       </c>
       <c r="BU32" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BV32" t="n">
         <v>27</v>
       </c>
       <c r="BW32" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BX32" t="n">
         <v>34</v>
       </c>
       <c r="BY32" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BZ32" t="n">
         <v>19</v>
       </c>
       <c r="CA32" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -8848,10 +8848,10 @@
         <v>14.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AU33" t="n">
         <v>5.7</v>
@@ -8860,7 +8860,7 @@
         <v>10</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AX33" t="n">
         <v>13.5</v>
@@ -8872,25 +8872,25 @@
         <v>14.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH33" t="n">
         <v>3</v>
@@ -8914,13 +8914,13 @@
         <v>5.7</v>
       </c>
       <c r="BO33" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BP33" t="n">
         <v>1000</v>
       </c>
       <c r="BQ33" t="n">
-        <v>3.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR33" t="n">
         <v>1000</v>
@@ -8929,16 +8929,16 @@
         <v>3.3</v>
       </c>
       <c r="BT33" t="n">
-        <v>16.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU33" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BV33" t="n">
         <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>3.15</v>
+        <v>9.4</v>
       </c>
       <c r="BX33" t="n">
         <v>1000</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
         <v>4.7</v>
       </c>
       <c r="J34" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K34" t="n">
         <v>4.2</v>
@@ -9018,7 +9018,7 @@
         <v>1.79</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="R34" t="n">
         <v>1.32</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -9245,13 +9245,13 @@
         <v>1000</v>
       </c>
       <c r="H35" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="I35" t="n">
-        <v>36</v>
+        <v>3.8</v>
       </c>
       <c r="J35" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="K35" t="n">
         <v>1000</v>
@@ -9263,19 +9263,19 @@
         <v>1.05</v>
       </c>
       <c r="N35" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="O35" t="n">
         <v>1.31</v>
       </c>
       <c r="P35" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="Q35" t="n">
         <v>1.35</v>
       </c>
       <c r="R35" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="S35" t="n">
         <v>3.15</v>
@@ -9287,7 +9287,7 @@
         <v>1.04</v>
       </c>
       <c r="V35" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W35" t="n">
         <v>1.02</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -9514,25 +9514,25 @@
         <v>1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="O36" t="n">
         <v>1.4</v>
       </c>
       <c r="P36" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="Q36" t="n">
         <v>1.39</v>
       </c>
       <c r="R36" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="S36" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T36" t="n">
         <v>1.01</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -9753,7 +9753,7 @@
         <v>2.46</v>
       </c>
       <c r="H37" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I37" t="n">
         <v>4.5</v>
@@ -9786,7 +9786,7 @@
         <v>1.2</v>
       </c>
       <c r="S37" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="T37" t="n">
         <v>2.06</v>
@@ -9930,7 +9930,7 @@
         <v>5</v>
       </c>
       <c r="BO37" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BP37" t="n">
         <v>1000</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -10001,230 +10001,230 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="G38" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="H38" t="n">
         <v>5.1</v>
       </c>
       <c r="I38" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="J38" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K38" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L38" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N38" t="n">
         <v>1.09</v>
       </c>
-      <c r="N38" t="n">
-        <v>2.72</v>
-      </c>
       <c r="O38" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="P38" t="n">
-        <v>1.66</v>
+        <v>1.09</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.2</v>
+        <v>1.39</v>
       </c>
       <c r="R38" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="S38" t="n">
-        <v>3.15</v>
+        <v>1.39</v>
       </c>
       <c r="T38" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="U38" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="V38" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="W38" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="X38" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y38" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z38" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA38" t="n">
         <v>1000</v>
       </c>
       <c r="AB38" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC38" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD38" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE38" t="n">
         <v>1000</v>
       </c>
       <c r="AF38" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AG38" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH38" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI38" t="n">
         <v>1000</v>
       </c>
       <c r="AJ38" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK38" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL38" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM38" t="n">
         <v>1000</v>
       </c>
       <c r="AN38" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO38" t="n">
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AQ38" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AR38" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS38" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV38" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AW38" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AX38" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY38" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AZ38" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BA38" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB38" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC38" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD38" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BE38" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF38" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG38" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH38" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="BI38" t="n">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="BJ38" t="n">
         <v>1000</v>
       </c>
       <c r="BK38" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="BN38" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO38" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="BP38" t="n">
         <v>1000</v>
       </c>
       <c r="BQ38" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR38" t="n">
         <v>1000</v>
       </c>
       <c r="BS38" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="BT38" t="n">
         <v>1000</v>
       </c>
       <c r="BU38" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV38" t="n">
         <v>1000</v>
       </c>
       <c r="BW38" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="BX38" t="n">
         <v>1000</v>
       </c>
       <c r="BY38" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="BZ38" t="n">
         <v>1000</v>
       </c>
       <c r="CA38" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -10255,19 +10255,19 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="G39" t="n">
         <v>1.47</v>
       </c>
       <c r="H39" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I39" t="n">
         <v>13</v>
       </c>
       <c r="J39" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K39" t="n">
         <v>4.9</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -10763,19 +10763,19 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="G41" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H41" t="n">
         <v>2.4</v>
       </c>
       <c r="I41" t="n">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="J41" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="K41" t="n">
         <v>3.4</v>
@@ -10811,10 +10811,10 @@
         <v>1.78</v>
       </c>
       <c r="V41" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="W41" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X41" t="n">
         <v>11</v>
@@ -10940,7 +10940,7 @@
         <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>2.24</v>
+        <v>8</v>
       </c>
       <c r="BN41" t="n">
         <v>6.6</v>
@@ -10952,13 +10952,13 @@
         <v>34</v>
       </c>
       <c r="BQ41" t="n">
-        <v>2.14</v>
+        <v>6.6</v>
       </c>
       <c r="BR41" t="n">
         <v>1000</v>
       </c>
       <c r="BS41" t="n">
-        <v>2.18</v>
+        <v>7.4</v>
       </c>
       <c r="BT41" t="n">
         <v>5.4</v>
@@ -10976,17 +10976,17 @@
         <v>46</v>
       </c>
       <c r="BY41" t="n">
-        <v>2.16</v>
+        <v>7.2</v>
       </c>
       <c r="BZ41" t="n">
         <v>50</v>
       </c>
       <c r="CA41" t="n">
-        <v>2.18</v>
+        <v>7.2</v>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -11017,13 +11017,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="G42" t="n">
         <v>5.8</v>
       </c>
       <c r="H42" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="I42" t="n">
         <v>1.91</v>
@@ -11035,7 +11035,7 @@
         <v>4.3</v>
       </c>
       <c r="L42" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M42" t="n">
         <v>1.06</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -11277,13 +11277,13 @@
         <v>7.4</v>
       </c>
       <c r="H43" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="I43" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="J43" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K43" t="n">
         <v>3.8</v>
@@ -11301,7 +11301,7 @@
         <v>1.51</v>
       </c>
       <c r="P43" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="Q43" t="n">
         <v>2.5</v>
@@ -11319,7 +11319,7 @@
         <v>1.63</v>
       </c>
       <c r="V43" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="W43" t="n">
         <v>1.16</v>
@@ -11364,7 +11364,7 @@
         <v>260</v>
       </c>
       <c r="AK43" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AL43" t="n">
         <v>310</v>
@@ -11379,7 +11379,7 @@
         <v>19.5</v>
       </c>
       <c r="AP43" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="AQ43" t="n">
         <v>5.3</v>
@@ -11406,7 +11406,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AY43" t="n">
-        <v>23</v>
+        <v>7.6</v>
       </c>
       <c r="AZ43" t="n">
         <v>26</v>
@@ -11448,7 +11448,7 @@
         <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>2.3</v>
+        <v>8.4</v>
       </c>
       <c r="BN43" t="n">
         <v>10</v>
@@ -11460,13 +11460,13 @@
         <v>1000</v>
       </c>
       <c r="BQ43" t="n">
-        <v>2.26</v>
+        <v>8</v>
       </c>
       <c r="BR43" t="n">
         <v>1000</v>
       </c>
       <c r="BS43" t="n">
-        <v>2.26</v>
+        <v>8</v>
       </c>
       <c r="BT43" t="n">
         <v>4.1</v>
@@ -11484,17 +11484,17 @@
         <v>40</v>
       </c>
       <c r="BY43" t="n">
-        <v>2.2</v>
+        <v>7.2</v>
       </c>
       <c r="BZ43" t="n">
         <v>38</v>
       </c>
       <c r="CA43" t="n">
-        <v>2.18</v>
+        <v>7.2</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
         <v>4.5</v>
       </c>
       <c r="J44" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="K44" t="n">
         <v>3.2</v>
@@ -11576,7 +11576,7 @@
         <v>1.28</v>
       </c>
       <c r="W44" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X44" t="n">
         <v>7.4</v>
@@ -11648,7 +11648,7 @@
         <v>5.5</v>
       </c>
       <c r="AU44" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AV44" t="n">
         <v>15.5</v>
@@ -11660,7 +11660,7 @@
         <v>5</v>
       </c>
       <c r="AY44" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AZ44" t="n">
         <v>9.199999999999999</v>
@@ -11684,7 +11684,7 @@
         <v>6.8</v>
       </c>
       <c r="BG44" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH44" t="n">
         <v>2.56</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -11791,10 +11791,10 @@
         <v>3.3</v>
       </c>
       <c r="J45" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="K45" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="L45" t="n">
         <v>1.58</v>
@@ -11893,7 +11893,7 @@
         <v>3.65</v>
       </c>
       <c r="AR45" t="n">
-        <v>2.26</v>
+        <v>1.46</v>
       </c>
       <c r="AS45" t="n">
         <v>1.53</v>
@@ -11905,7 +11905,7 @@
         <v>3.45</v>
       </c>
       <c r="AV45" t="n">
-        <v>2.5</v>
+        <v>1.56</v>
       </c>
       <c r="AW45" t="n">
         <v>1.53</v>
@@ -11914,7 +11914,7 @@
         <v>1.46</v>
       </c>
       <c r="AY45" t="n">
-        <v>2.22</v>
+        <v>1.56</v>
       </c>
       <c r="AZ45" t="n">
         <v>1.49</v>
@@ -11944,37 +11944,37 @@
         <v>2.58</v>
       </c>
       <c r="BI45" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="BJ45" t="n">
         <v>1000</v>
       </c>
       <c r="BK45" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BL45" t="n">
         <v>1000</v>
       </c>
       <c r="BM45" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BN45" t="n">
         <v>1000</v>
       </c>
       <c r="BO45" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BP45" t="n">
         <v>1000</v>
       </c>
       <c r="BQ45" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BR45" t="n">
         <v>1000</v>
       </c>
       <c r="BS45" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BT45" t="n">
         <v>1000</v>
@@ -11986,23 +11986,23 @@
         <v>1000</v>
       </c>
       <c r="BW45" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BX45" t="n">
         <v>1000</v>
       </c>
       <c r="BY45" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BZ45" t="n">
         <v>1000</v>
       </c>
       <c r="CA45" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -12033,13 +12033,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.45</v>
+        <v>1.04</v>
       </c>
       <c r="G46" t="n">
         <v>1000</v>
       </c>
       <c r="H46" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="I46" t="n">
         <v>1000</v>
@@ -12081,10 +12081,10 @@
         <v>1.01</v>
       </c>
       <c r="V46" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W46" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X46" t="n">
         <v>1000</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -12287,13 +12287,13 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="G47" t="n">
         <v>1000</v>
       </c>
       <c r="H47" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="I47" t="n">
         <v>1000</v>
@@ -12335,7 +12335,7 @@
         <v>1.01</v>
       </c>
       <c r="V47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W47" t="n">
         <v>1.01</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -12553,7 +12553,7 @@
         <v>2.42</v>
       </c>
       <c r="J48" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K48" t="n">
         <v>3.45</v>
@@ -12592,7 +12592,7 @@
         <v>1.7</v>
       </c>
       <c r="W48" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X48" t="n">
         <v>13.5</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="G49" t="n">
         <v>1000</v>
       </c>
       <c r="H49" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="I49" t="n">
         <v>1000</v>
@@ -12843,7 +12843,7 @@
         <v>1.01</v>
       </c>
       <c r="V49" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W49" t="n">
         <v>1.01</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -13049,13 +13049,13 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G50" t="n">
         <v>3.1</v>
       </c>
       <c r="H50" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I50" t="n">
         <v>3.25</v>
@@ -13088,7 +13088,7 @@
         <v>1.23</v>
       </c>
       <c r="S50" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="T50" t="n">
         <v>1.88</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -13303,19 +13303,19 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G51" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="H51" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="I51" t="n">
         <v>2.74</v>
       </c>
       <c r="J51" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K51" t="n">
         <v>4</v>
@@ -13333,28 +13333,28 @@
         <v>1.24</v>
       </c>
       <c r="P51" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R51" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S51" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T51" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="U51" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V51" t="n">
         <v>1.57</v>
       </c>
       <c r="W51" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="X51" t="n">
         <v>24</v>
@@ -13381,31 +13381,31 @@
         <v>32</v>
       </c>
       <c r="AF51" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AG51" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH51" t="n">
         <v>19</v>
       </c>
       <c r="AI51" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AJ51" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AK51" t="n">
         <v>36</v>
       </c>
       <c r="AL51" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM51" t="n">
         <v>85</v>
       </c>
       <c r="AN51" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO51" t="n">
         <v>21</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -13560,16 +13560,16 @@
         <v>2.8</v>
       </c>
       <c r="G52" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H52" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="I52" t="n">
         <v>3.25</v>
       </c>
       <c r="J52" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K52" t="n">
         <v>3.15</v>
@@ -13587,13 +13587,13 @@
         <v>1.56</v>
       </c>
       <c r="P52" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="Q52" t="n">
         <v>2.66</v>
       </c>
       <c r="R52" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S52" t="n">
         <v>5.1</v>
@@ -13605,10 +13605,10 @@
         <v>1.76</v>
       </c>
       <c r="V52" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W52" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X52" t="n">
         <v>8.4</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -13811,64 +13811,64 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G53" t="n">
         <v>2.72</v>
       </c>
       <c r="H53" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I53" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J53" t="n">
         <v>3.55</v>
       </c>
       <c r="K53" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="L53" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M53" t="n">
         <v>1.05</v>
       </c>
       <c r="N53" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O53" t="n">
         <v>1.25</v>
       </c>
       <c r="P53" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="R53" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S53" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="T53" t="n">
         <v>1.57</v>
       </c>
       <c r="U53" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V53" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W53" t="n">
         <v>1.58</v>
       </c>
       <c r="X53" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y53" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z53" t="n">
         <v>26</v>
@@ -13877,19 +13877,19 @@
         <v>55</v>
       </c>
       <c r="AB53" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC53" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD53" t="n">
         <v>16</v>
       </c>
       <c r="AE53" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF53" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG53" t="n">
         <v>14.5</v>
@@ -13898,7 +13898,7 @@
         <v>19</v>
       </c>
       <c r="AI53" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ53" t="n">
         <v>44</v>
@@ -13910,19 +13910,19 @@
         <v>42</v>
       </c>
       <c r="AM53" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN53" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO53" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AP53" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ53" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR53" t="n">
         <v>15.5</v>
@@ -13931,10 +13931,10 @@
         <v>1.03</v>
       </c>
       <c r="AT53" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU53" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV53" t="n">
         <v>9.6</v>
@@ -13943,7 +13943,7 @@
         <v>21</v>
       </c>
       <c r="AX53" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY53" t="n">
         <v>8.800000000000001</v>
@@ -13967,16 +13967,16 @@
         <v>1.03</v>
       </c>
       <c r="BF53" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG53" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH53" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BI53" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ53" t="n">
         <v>9.199999999999999</v>
@@ -13988,13 +13988,13 @@
         <v>1000</v>
       </c>
       <c r="BM53" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BN53" t="n">
         <v>5.9</v>
       </c>
       <c r="BO53" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP53" t="n">
         <v>18.5</v>
@@ -14006,7 +14006,7 @@
         <v>1000</v>
       </c>
       <c r="BS53" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BT53" t="n">
         <v>6.4</v>
@@ -14027,14 +14027,14 @@
         <v>21</v>
       </c>
       <c r="BZ53" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA53" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -14071,13 +14071,13 @@
         <v>2.6</v>
       </c>
       <c r="H54" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I54" t="n">
         <v>4.1</v>
       </c>
       <c r="J54" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="K54" t="n">
         <v>3.4</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -14319,7 +14319,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="G55" t="n">
         <v>2.42</v>
@@ -14328,7 +14328,7 @@
         <v>3.55</v>
       </c>
       <c r="I55" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J55" t="n">
         <v>3.15</v>
@@ -14337,13 +14337,13 @@
         <v>3.35</v>
       </c>
       <c r="L55" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="M55" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N55" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O55" t="n">
         <v>1.46</v>
@@ -14355,7 +14355,7 @@
         <v>2.36</v>
       </c>
       <c r="R55" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S55" t="n">
         <v>4.7</v>
@@ -14367,7 +14367,7 @@
         <v>1.91</v>
       </c>
       <c r="V55" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W55" t="n">
         <v>1.7</v>
@@ -14490,19 +14490,19 @@
         <v>10.5</v>
       </c>
       <c r="BK55" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL55" t="n">
         <v>1000</v>
       </c>
       <c r="BM55" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN55" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO55" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="BP55" t="n">
         <v>1000</v>
@@ -14517,7 +14517,7 @@
         <v>11.5</v>
       </c>
       <c r="BT55" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU55" t="n">
         <v>5</v>
@@ -14538,11 +14538,11 @@
         <v>1000</v>
       </c>
       <c r="CA55" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>
@@ -14588,7 +14588,7 @@
         <v>3.2</v>
       </c>
       <c r="K56" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="L56" t="n">
         <v>1.38</v>
@@ -14600,7 +14600,7 @@
         <v>3.5</v>
       </c>
       <c r="O56" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P56" t="n">
         <v>1.85</v>
@@ -14624,10 +14624,10 @@
         <v>1.42</v>
       </c>
       <c r="W56" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X56" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y56" t="n">
         <v>12.5</v>
@@ -14639,7 +14639,7 @@
         <v>60</v>
       </c>
       <c r="AB56" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC56" t="n">
         <v>8.4</v>
@@ -14651,10 +14651,10 @@
         <v>38</v>
       </c>
       <c r="AF56" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AG56" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH56" t="n">
         <v>970</v>
@@ -14666,31 +14666,31 @@
         <v>38</v>
       </c>
       <c r="AK56" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AL56" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
       </c>
       <c r="AN56" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AO56" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AP56" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ56" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR56" t="n">
-        <v>5.9</v>
+        <v>15.5</v>
       </c>
       <c r="AS56" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AT56" t="n">
         <v>9.199999999999999</v>
@@ -14702,7 +14702,7 @@
         <v>10</v>
       </c>
       <c r="AW56" t="n">
-        <v>6.6</v>
+        <v>25</v>
       </c>
       <c r="AX56" t="n">
         <v>11.5</v>
@@ -14726,13 +14726,13 @@
         <v>30</v>
       </c>
       <c r="BE56" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF56" t="n">
         <v>15</v>
       </c>
       <c r="BG56" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH56" t="n">
         <v>3.65</v>
@@ -14756,16 +14756,16 @@
         <v>5.8</v>
       </c>
       <c r="BO56" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BP56" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ56" t="n">
         <v>6</v>
       </c>
       <c r="BR56" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS56" t="n">
         <v>7</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-04 16:01:15</t>
+          <t>2026-07-04 18:15:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
@@ -887,7 +887,7 @@
         <v>1.4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q2" t="n">
         <v>2.16</v>
@@ -896,7 +896,7 @@
         <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T2" t="n">
         <v>1.84</v>
@@ -971,7 +971,7 @@
         <v>5.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AS2" t="n">
         <v>6.6</v>
@@ -983,19 +983,19 @@
         <v>4.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AW2" t="n">
         <v>6.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AY2" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BA2" t="n">
         <v>6.8</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="G3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J3" t="n">
         <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>1.42</v>
       </c>
       <c r="P3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q3" t="n">
         <v>2.22</v>
@@ -1150,10 +1150,10 @@
         <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U3" t="n">
         <v>1.84</v>
@@ -1162,13 +1162,13 @@
         <v>1.23</v>
       </c>
       <c r="W3" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X3" t="n">
         <v>18</v>
       </c>
       <c r="Y3" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
         <v>100</v>
@@ -1177,7 +1177,7 @@
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AC3" t="n">
         <v>9.199999999999999</v>
@@ -1189,10 +1189,10 @@
         <v>700</v>
       </c>
       <c r="AF3" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AG3" t="n">
-        <v>36</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
         <v>85</v>
@@ -1213,22 +1213,22 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AO3" t="n">
         <v>700</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AQ3" t="n">
         <v>6.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="AT3" t="n">
         <v>4.4</v>
@@ -1237,104 +1237,104 @@
         <v>4.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="AX3" t="n">
         <v>6.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BF3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK3" t="n">
         <v>5.4</v>
       </c>
-      <c r="BG3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
       <c r="BN3" t="n">
         <v>4.6</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.69</v>
+        <v>4</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.13</v>
+        <v>2.56</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.13</v>
+        <v>2.56</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.09</v>
+        <v>2.56</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H4" t="n">
         <v>4.3</v>
@@ -1380,10 +1380,10 @@
         <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
@@ -1395,19 +1395,19 @@
         <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U4" t="n">
         <v>2</v>
@@ -1419,13 +1419,13 @@
         <v>1.98</v>
       </c>
       <c r="X4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z4" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AA4" t="n">
         <v>490</v>
@@ -1434,7 +1434,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="n">
         <v>18.5</v>
@@ -1455,10 +1455,10 @@
         <v>150</v>
       </c>
       <c r="AJ4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK4" t="n">
         <v>24</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>29</v>
       </c>
       <c r="AL4" t="n">
         <v>90</v>
@@ -1473,13 +1473,13 @@
         <v>170</v>
       </c>
       <c r="AP4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ4" t="n">
         <v>12.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AS4" t="n">
         <v>38</v>
@@ -1500,22 +1500,22 @@
         <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA4" t="n">
         <v>48</v>
       </c>
       <c r="BB4" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BC4" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BE4" t="n">
         <v>75</v>
@@ -1536,7 +1536,7 @@
         <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1548,13 +1548,13 @@
         <v>4.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BP4" t="n">
         <v>15</v>
       </c>
       <c r="BQ4" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
@@ -1566,7 +1566,7 @@
         <v>7.8</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1655,7 @@
         <v>2.14</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S5" t="n">
         <v>3.95</v>
@@ -1679,7 +1679,7 @@
         <v>11</v>
       </c>
       <c r="Z5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA5" t="n">
         <v>120</v>
@@ -1697,19 +1697,19 @@
         <v>40</v>
       </c>
       <c r="AF5" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG5" t="n">
         <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI5" t="n">
         <v>110</v>
       </c>
       <c r="AJ5" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="AK5" t="n">
         <v>32</v>
@@ -1721,7 +1721,7 @@
         <v>440</v>
       </c>
       <c r="AN5" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AO5" t="n">
         <v>42</v>
@@ -1766,7 +1766,7 @@
         <v>29</v>
       </c>
       <c r="BC5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BD5" t="n">
         <v>34</v>
@@ -1778,7 +1778,7 @@
         <v>22</v>
       </c>
       <c r="BG5" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BH5" t="n">
         <v>3.15</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>7.4</v>
       </c>
       <c r="G6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="H6" t="n">
         <v>1.51</v>
@@ -1888,37 +1888,37 @@
         <v>4.5</v>
       </c>
       <c r="K6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
         <v>1.34</v>
       </c>
       <c r="P6" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
         <v>1.34</v>
       </c>
       <c r="S6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T6" t="n">
         <v>2.18</v>
       </c>
       <c r="U6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V6" t="n">
         <v>2.84</v>
@@ -1939,13 +1939,13 @@
         <v>13</v>
       </c>
       <c r="AB6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC6" t="n">
         <v>10</v>
       </c>
       <c r="AD6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE6" t="n">
         <v>18.5</v>
@@ -1954,7 +1954,7 @@
         <v>75</v>
       </c>
       <c r="AG6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AH6" t="n">
         <v>29</v>
@@ -1987,37 +1987,37 @@
         <v>6.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS6" t="n">
         <v>11.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AU6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW6" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="AY6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ6" t="n">
         <v>23</v>
       </c>
       <c r="BA6" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BB6" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BC6" t="n">
         <v>42</v>
@@ -2029,10 +2029,10 @@
         <v>70</v>
       </c>
       <c r="BF6" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH6" t="n">
         <v>3.45</v>
@@ -2074,7 +2074,7 @@
         <v>3.9</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="BV6" t="n">
         <v>10.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -2133,16 +2133,16 @@
         <v>2.02</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J7" t="n">
         <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
         <v>1.43</v>
@@ -2193,10 +2193,10 @@
         <v>500</v>
       </c>
       <c r="AB7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD7" t="n">
         <v>19</v>
@@ -2214,7 +2214,7 @@
         <v>20</v>
       </c>
       <c r="AI7" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ7" t="n">
         <v>25</v>
@@ -2238,7 +2238,7 @@
         <v>12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR7" t="n">
         <v>27</v>
@@ -2250,7 +2250,7 @@
         <v>7.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV7" t="n">
         <v>16</v>
@@ -2292,28 +2292,28 @@
         <v>3.35</v>
       </c>
       <c r="BI7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ7" t="n">
         <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ7" t="n">
         <v>9.6</v>
@@ -2322,7 +2322,7 @@
         <v>29</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT7" t="n">
         <v>8</v>
@@ -2334,23 +2334,23 @@
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BZ7" t="n">
         <v>26</v>
       </c>
       <c r="CA7" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G8" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H8" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L8" t="n">
         <v>1.32</v>
@@ -2414,7 +2414,7 @@
         <v>2.06</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="R8" t="n">
         <v>1.42</v>
@@ -2429,61 +2429,61 @@
         <v>2.18</v>
       </c>
       <c r="V8" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W8" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X8" t="n">
-        <v>19.5</v>
+        <v>29</v>
       </c>
       <c r="Y8" t="n">
         <v>11.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="AB8" t="n">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="AC8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AF8" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AG8" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AH8" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AJ8" t="n">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="AK8" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AL8" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AM8" t="n">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="AO8" t="n">
         <v>17.5</v>
@@ -2495,10 +2495,10 @@
         <v>9.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AT8" t="n">
         <v>12.5</v>
@@ -2510,10 +2510,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW8" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AX8" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="AY8" t="n">
         <v>12.5</v>
@@ -2522,22 +2522,22 @@
         <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>24</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB8" t="n">
-        <v>40</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="BD8" t="n">
-        <v>29</v>
+        <v>8.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="BF8" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BG8" t="n">
         <v>13</v>
@@ -2546,7 +2546,7 @@
         <v>3.75</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BJ8" t="n">
         <v>9.6</v>
@@ -2561,16 +2561,16 @@
         <v>9.6</v>
       </c>
       <c r="BN8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
@@ -2579,13 +2579,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BU8" t="n">
         <v>4.1</v>
       </c>
       <c r="BV8" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BW8" t="n">
         <v>6.4</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>6.2</v>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="H9" t="n">
         <v>1.59</v>
@@ -2653,13 +2653,13 @@
         <v>4.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
         <v>1.29</v>
@@ -2668,19 +2668,19 @@
         <v>2.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.93</v>
+        <v>1.69</v>
       </c>
       <c r="U9" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V9" t="n">
         <v>2.52</v>
@@ -2689,10 +2689,10 @@
         <v>1.17</v>
       </c>
       <c r="X9" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="Z9" t="n">
         <v>10</v>
@@ -2707,7 +2707,7 @@
         <v>12</v>
       </c>
       <c r="AD9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
@@ -2716,7 +2716,7 @@
         <v>70</v>
       </c>
       <c r="AG9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AH9" t="n">
         <v>24</v>
@@ -2734,7 +2734,7 @@
         <v>110</v>
       </c>
       <c r="AM9" t="n">
-        <v>160</v>
+        <v>390</v>
       </c>
       <c r="AN9" t="n">
         <v>700</v>
@@ -2746,7 +2746,7 @@
         <v>14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR9" t="n">
         <v>8.4</v>
@@ -2767,98 +2767,98 @@
         <v>15</v>
       </c>
       <c r="AX9" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="AY9" t="n">
         <v>18.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA9" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="BD9" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="BE9" t="n">
-        <v>29</v>
+        <v>6.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="BG9" t="n">
         <v>8</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ9" t="n">
         <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BN9" t="n">
         <v>10</v>
       </c>
       <c r="BO9" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BP9" t="n">
         <v>60</v>
       </c>
       <c r="BQ9" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BR9" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BT9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BV9" t="n">
         <v>10.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BX9" t="n">
         <v>26</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G10" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="H10" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
@@ -2904,10 +2904,10 @@
         <v>3.2</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L10" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M10" t="n">
         <v>1.1</v>
@@ -2919,13 +2919,13 @@
         <v>1.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="R10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S10" t="n">
         <v>4.1</v>
@@ -2934,13 +2934,13 @@
         <v>1.88</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V10" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W10" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X10" t="n">
         <v>11.5</v>
@@ -2949,7 +2949,7 @@
         <v>11</v>
       </c>
       <c r="Z10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA10" t="n">
         <v>55</v>
@@ -2961,13 +2961,13 @@
         <v>7.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AF10" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AG10" t="n">
         <v>13.5</v>
@@ -2976,7 +2976,7 @@
         <v>19.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AJ10" t="n">
         <v>50</v>
@@ -2994,19 +2994,19 @@
         <v>38</v>
       </c>
       <c r="AO10" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AP10" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR10" t="n">
         <v>16.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AT10" t="n">
         <v>8.800000000000001</v>
@@ -3024,13 +3024,13 @@
         <v>15</v>
       </c>
       <c r="AY10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ10" t="n">
         <v>16.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB10" t="n">
         <v>36</v>
@@ -3039,13 +3039,13 @@
         <v>24</v>
       </c>
       <c r="BD10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE10" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BF10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BG10" t="n">
         <v>23</v>
@@ -3054,31 +3054,31 @@
         <v>3.15</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN10" t="n">
         <v>5.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP10" t="n">
         <v>24</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR10" t="n">
         <v>42</v>
@@ -3096,10 +3096,10 @@
         <v>26</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX10" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
         <v>8.4</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -3161,10 +3161,10 @@
         <v>3.25</v>
       </c>
       <c r="L11" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="M11" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N11" t="n">
         <v>2.36</v>
@@ -3176,13 +3176,13 @@
         <v>1.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="R11" t="n">
         <v>1.17</v>
       </c>
       <c r="S11" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="T11" t="n">
         <v>2.1</v>
@@ -3275,10 +3275,10 @@
         <v>8</v>
       </c>
       <c r="AX11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY11" t="n">
         <v>6</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>5.6</v>
       </c>
       <c r="AZ11" t="n">
         <v>6.6</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G12" t="n">
         <v>1.67</v>
@@ -3406,10 +3406,10 @@
         <v>6.6</v>
       </c>
       <c r="I12" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K12" t="n">
         <v>4.3</v>
@@ -3421,16 +3421,16 @@
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.74</v>
+        <v>2.54</v>
       </c>
       <c r="O12" t="n">
         <v>1.47</v>
       </c>
       <c r="P12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="R12" t="n">
         <v>1.2</v>
@@ -3445,7 +3445,7 @@
         <v>1.55</v>
       </c>
       <c r="V12" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W12" t="n">
         <v>2.48</v>
@@ -3466,7 +3466,7 @@
         <v>6.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AD12" t="n">
         <v>110</v>
@@ -3478,7 +3478,7 @@
         <v>8.4</v>
       </c>
       <c r="AG12" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AH12" t="n">
         <v>500</v>
@@ -3508,13 +3508,13 @@
         <v>4.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AR12" t="n">
         <v>6</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="AT12" t="n">
         <v>3.5</v>
@@ -3526,7 +3526,7 @@
         <v>5.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="AX12" t="n">
         <v>4.2</v>
@@ -3538,10 +3538,10 @@
         <v>5.6</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
         <v>5.1</v>
@@ -3556,7 +3556,7 @@
         <v>4.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH12" t="n">
         <v>2.96</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="G13" t="n">
         <v>5.9</v>
       </c>
       <c r="H13" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="I13" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="J13" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L13" t="n">
         <v>1.32</v>
@@ -3681,52 +3681,52 @@
         <v>1.21</v>
       </c>
       <c r="P13" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R13" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U13" t="n">
         <v>2.3</v>
       </c>
       <c r="V13" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="W13" t="n">
         <v>1.2</v>
       </c>
       <c r="X13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y13" t="n">
         <v>11.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA13" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AC13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD13" t="n">
         <v>10.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AF13" t="n">
         <v>46</v>
@@ -3735,7 +3735,7 @@
         <v>21</v>
       </c>
       <c r="AH13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI13" t="n">
         <v>34</v>
@@ -3756,13 +3756,13 @@
         <v>590</v>
       </c>
       <c r="AO13" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AP13" t="n">
         <v>20</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR13" t="n">
         <v>10</v>
@@ -3771,25 +3771,25 @@
         <v>14.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AU13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV13" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AX13" t="n">
         <v>26</v>
       </c>
       <c r="AY13" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA13" t="n">
         <v>24</v>
@@ -3798,7 +3798,7 @@
         <v>42</v>
       </c>
       <c r="BC13" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="BD13" t="n">
         <v>44</v>
@@ -3807,10 +3807,10 @@
         <v>50</v>
       </c>
       <c r="BF13" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH13" t="n">
         <v>4.2</v>
@@ -3828,7 +3828,7 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN13" t="n">
         <v>9.4</v>
@@ -3864,7 +3864,7 @@
         <v>22</v>
       </c>
       <c r="BY13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ13" t="n">
         <v>14.5</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G14" t="n">
         <v>2.5</v>
@@ -3914,22 +3914,22 @@
         <v>3.6</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="J14" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K14" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L14" t="n">
         <v>1.47</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="O14" t="n">
         <v>1.5</v>
@@ -3938,22 +3938,22 @@
         <v>1.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="R14" t="n">
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U14" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W14" t="n">
         <v>1.66</v>
@@ -3974,10 +3974,10 @@
         <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD14" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AE14" t="n">
         <v>500</v>
@@ -4007,82 +4007,82 @@
         <v>500</v>
       </c>
       <c r="AN14" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="AR14" t="n">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="AS14" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.6</v>
+        <v>2.26</v>
       </c>
       <c r="AW14" t="n">
-        <v>3.15</v>
+        <v>2.54</v>
       </c>
       <c r="AX14" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.98</v>
+        <v>2.56</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.1</v>
+        <v>2.54</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.25</v>
+        <v>2.54</v>
       </c>
       <c r="BE14" t="n">
-        <v>3</v>
+        <v>2.44</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.92</v>
+        <v>2.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.98</v>
+        <v>2.4</v>
       </c>
       <c r="BH14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
@@ -4094,41 +4094,41 @@
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -4159,40 +4159,40 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="G15" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="H15" t="n">
         <v>4.6</v>
       </c>
       <c r="I15" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M15" t="n">
         <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="O15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P15" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R15" t="n">
         <v>1.24</v>
@@ -4207,13 +4207,13 @@
         <v>1.79</v>
       </c>
       <c r="V15" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="X15" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Y15" t="n">
         <v>970</v>
@@ -4252,7 +4252,7 @@
         <v>900</v>
       </c>
       <c r="AK15" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AL15" t="n">
         <v>500</v>
@@ -4264,19 +4264,19 @@
         <v>60</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP15" t="n">
         <v>5.1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.72</v>
+        <v>3.15</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="AT15" t="n">
         <v>4.2</v>
@@ -4285,40 +4285,40 @@
         <v>4.9</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="AX15" t="n">
         <v>5.1</v>
       </c>
       <c r="AY15" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2.76</v>
+        <v>4</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.54</v>
+        <v>2.74</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="BF15" t="n">
         <v>4</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="BH15" t="n">
         <v>4.8</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -4416,13 +4416,13 @@
         <v>1.88</v>
       </c>
       <c r="G16" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H16" t="n">
         <v>4.5</v>
       </c>
       <c r="I16" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J16" t="n">
         <v>3.35</v>
@@ -4443,19 +4443,19 @@
         <v>1.39</v>
       </c>
       <c r="P16" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R16" t="n">
         <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U16" t="n">
         <v>1.87</v>
@@ -4464,10 +4464,10 @@
         <v>1.23</v>
       </c>
       <c r="W16" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X16" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="Y16" t="n">
         <v>970</v>
@@ -4479,10 +4479,10 @@
         <v>500</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD16" t="n">
         <v>38</v>
@@ -4494,10 +4494,10 @@
         <v>970</v>
       </c>
       <c r="AG16" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH16" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AI16" t="n">
         <v>500</v>
@@ -4518,61 +4518,61 @@
         <v>55</v>
       </c>
       <c r="AO16" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE16" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BF16" t="n">
-        <v>13.5</v>
+        <v>6.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="BH16" t="n">
         <v>3.2</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
         <v>2.38</v>
       </c>
       <c r="I17" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="J17" t="n">
         <v>3.7</v>
@@ -4700,10 +4700,10 @@
         <v>2.28</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S17" t="n">
         <v>2.66</v>
@@ -4715,7 +4715,7 @@
         <v>2.4</v>
       </c>
       <c r="V17" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W17" t="n">
         <v>1.48</v>
@@ -4736,7 +4736,7 @@
         <v>16</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD17" t="n">
         <v>13</v>
@@ -4751,82 +4751,82 @@
         <v>14</v>
       </c>
       <c r="AH17" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI17" t="n">
         <v>38</v>
       </c>
       <c r="AJ17" t="n">
-        <v>280</v>
+        <v>55</v>
       </c>
       <c r="AK17" t="n">
         <v>32</v>
       </c>
       <c r="AL17" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AM17" t="n">
-        <v>320</v>
+        <v>90</v>
       </c>
       <c r="AN17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA17" t="n">
         <v>25</v>
       </c>
-      <c r="AO17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AP17" t="n">
+      <c r="BB17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF17" t="n">
         <v>14.5</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>15</v>
-      </c>
       <c r="BG17" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BH17" t="n">
         <v>4.2</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
         <v>1.8</v>
       </c>
       <c r="G18" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H18" t="n">
         <v>4.6</v>
@@ -4936,7 +4936,7 @@
         <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
         <v>1.41</v>
@@ -4954,16 +4954,16 @@
         <v>1.82</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S18" t="n">
         <v>3.55</v>
       </c>
       <c r="T18" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U18" t="n">
         <v>1.94</v>
@@ -4972,10 +4972,10 @@
         <v>1.22</v>
       </c>
       <c r="W18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X18" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Y18" t="n">
         <v>17</v>
@@ -4996,10 +4996,10 @@
         <v>21</v>
       </c>
       <c r="AE18" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="AF18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG18" t="n">
         <v>12</v>
@@ -5008,7 +5008,7 @@
         <v>22</v>
       </c>
       <c r="AI18" t="n">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="AJ18" t="n">
         <v>22</v>
@@ -5023,10 +5023,10 @@
         <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="AP18" t="n">
         <v>10.5</v>
@@ -5035,10 +5035,10 @@
         <v>12</v>
       </c>
       <c r="AR18" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AT18" t="n">
         <v>7</v>
@@ -5050,7 +5050,7 @@
         <v>15</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.6</v>
+        <v>38</v>
       </c>
       <c r="AX18" t="n">
         <v>9.4</v>
@@ -5059,10 +5059,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.6</v>
+        <v>40</v>
       </c>
       <c r="BB18" t="n">
         <v>16</v>
@@ -5071,16 +5071,16 @@
         <v>15.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.8</v>
+        <v>29</v>
       </c>
       <c r="BF18" t="n">
         <v>10.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.6</v>
+        <v>42</v>
       </c>
       <c r="BH18" t="n">
         <v>3.4</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -5175,46 +5175,46 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="H19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J19" t="n">
         <v>4.4</v>
       </c>
-      <c r="I19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J19" t="n">
-        <v>4.3</v>
-      </c>
       <c r="K19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L19" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M19" t="n">
         <v>1.02</v>
       </c>
       <c r="N19" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="O19" t="n">
         <v>1.13</v>
       </c>
       <c r="P19" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R19" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="S19" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T19" t="n">
         <v>1.47</v>
@@ -5223,13 +5223,13 @@
         <v>2.94</v>
       </c>
       <c r="V19" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="X19" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y19" t="n">
         <v>32</v>
@@ -5241,16 +5241,16 @@
         <v>490</v>
       </c>
       <c r="AB19" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AE19" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF19" t="n">
         <v>17</v>
@@ -5265,10 +5265,10 @@
         <v>38</v>
       </c>
       <c r="AJ19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL19" t="n">
         <v>22</v>
@@ -5277,61 +5277,61 @@
         <v>60</v>
       </c>
       <c r="AN19" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AO19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>26</v>
       </c>
-      <c r="AP19" t="n">
-        <v>25</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>25</v>
-      </c>
       <c r="AR19" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS19" t="n">
         <v>50</v>
       </c>
       <c r="AT19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX19" t="n">
         <v>15</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="AY19" t="n">
         <v>10</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
         <v>13</v>
       </c>
       <c r="BA19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BB19" t="n">
         <v>18</v>
       </c>
       <c r="BC19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD19" t="n">
         <v>19</v>
       </c>
       <c r="BE19" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG19" t="n">
         <v>21</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -5441,10 +5441,10 @@
         <v>3.45</v>
       </c>
       <c r="J20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K20" t="n">
         <v>3.8</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.85</v>
       </c>
       <c r="L20" t="n">
         <v>1.35</v>
@@ -5459,7 +5459,7 @@
         <v>1.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q20" t="n">
         <v>1.74</v>
@@ -5474,7 +5474,7 @@
         <v>1.64</v>
       </c>
       <c r="U20" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="V20" t="n">
         <v>1.4</v>
@@ -5531,7 +5531,7 @@
         <v>75</v>
       </c>
       <c r="AN20" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AO20" t="n">
         <v>29</v>
@@ -5570,10 +5570,10 @@
         <v>14</v>
       </c>
       <c r="BA20" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BB20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC20" t="n">
         <v>19.5</v>
@@ -5582,13 +5582,13 @@
         <v>28</v>
       </c>
       <c r="BE20" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BF20" t="n">
         <v>12.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH20" t="n">
         <v>4</v>
@@ -5600,31 +5600,31 @@
         <v>9.4</v>
       </c>
       <c r="BK20" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN20" t="n">
         <v>5.6</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP20" t="n">
         <v>16.5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="BR20" t="n">
         <v>27</v>
       </c>
       <c r="BS20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT20" t="n">
         <v>7</v>
@@ -5636,23 +5636,23 @@
         <v>25</v>
       </c>
       <c r="BW20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX20" t="n">
         <v>34</v>
       </c>
       <c r="BY20" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA20" t="n">
         <v>6.8</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G21" t="n">
         <v>1.55</v>
@@ -5695,13 +5695,13 @@
         <v>7</v>
       </c>
       <c r="J21" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K21" t="n">
         <v>4.9</v>
       </c>
       <c r="L21" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="M21" t="n">
         <v>1.04</v>
@@ -5716,7 +5716,7 @@
         <v>2.36</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R21" t="n">
         <v>1.54</v>
@@ -5725,7 +5725,7 @@
         <v>2.72</v>
       </c>
       <c r="T21" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U21" t="n">
         <v>2.14</v>
@@ -5734,7 +5734,7 @@
         <v>1.16</v>
       </c>
       <c r="W21" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="X21" t="n">
         <v>21</v>
@@ -5746,7 +5746,7 @@
         <v>60</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB21" t="n">
         <v>10</v>
@@ -5755,25 +5755,25 @@
         <v>11</v>
       </c>
       <c r="AD21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE21" t="n">
         <v>90</v>
       </c>
       <c r="AF21" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG21" t="n">
         <v>10</v>
       </c>
       <c r="AH21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI21" t="n">
         <v>80</v>
       </c>
       <c r="AJ21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK21" t="n">
         <v>15</v>
@@ -5806,7 +5806,7 @@
         <v>9.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV21" t="n">
         <v>22</v>
@@ -5836,13 +5836,13 @@
         <v>26</v>
       </c>
       <c r="BE21" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="BF21" t="n">
         <v>6.2</v>
       </c>
       <c r="BG21" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BH21" t="n">
         <v>4.1</v>
@@ -5860,25 +5860,25 @@
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BN21" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO21" t="n">
         <v>3.8</v>
       </c>
       <c r="BP21" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BQ21" t="n">
         <v>7.6</v>
       </c>
       <c r="BR21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS21" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT21" t="n">
         <v>10.5</v>
@@ -5890,23 +5890,23 @@
         <v>55</v>
       </c>
       <c r="BW21" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX21" t="n">
         <v>55</v>
       </c>
       <c r="BY21" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ21" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA21" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G22" t="n">
         <v>2.36</v>
@@ -5946,16 +5946,16 @@
         <v>3.4</v>
       </c>
       <c r="I22" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J22" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K22" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L22" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="M22" t="n">
         <v>1.06</v>
@@ -5967,28 +5967,28 @@
         <v>1.29</v>
       </c>
       <c r="P22" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S22" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U22" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V22" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W22" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X22" t="n">
         <v>16</v>
@@ -5997,16 +5997,16 @@
         <v>15</v>
       </c>
       <c r="Z22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA22" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AB22" t="n">
         <v>11</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD22" t="n">
         <v>16</v>
@@ -6015,7 +6015,7 @@
         <v>44</v>
       </c>
       <c r="AF22" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG22" t="n">
         <v>13</v>
@@ -6051,10 +6051,10 @@
         <v>12</v>
       </c>
       <c r="AR22" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AS22" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT22" t="n">
         <v>8.6</v>
@@ -6087,10 +6087,10 @@
         <v>19.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BE22" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF22" t="n">
         <v>14</v>
@@ -6099,7 +6099,7 @@
         <v>7.2</v>
       </c>
       <c r="BH22" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BI22" t="n">
         <v>2.88</v>
@@ -6108,13 +6108,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK22" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN22" t="n">
         <v>5.3</v>
@@ -6126,13 +6126,13 @@
         <v>16.5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR22" t="n">
         <v>30</v>
       </c>
       <c r="BS22" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT22" t="n">
         <v>7.2</v>
@@ -6144,23 +6144,23 @@
         <v>30</v>
       </c>
       <c r="BW22" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX22" t="n">
         <v>40</v>
       </c>
       <c r="BY22" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ22" t="n">
         <v>26</v>
       </c>
       <c r="CA22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -6191,22 +6191,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="G23" t="n">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="H23" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="I23" t="n">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K23" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L23" t="n">
         <v>1.21</v>
@@ -6215,7 +6215,7 @@
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="O23" t="n">
         <v>1.12</v>
@@ -6224,25 +6224,25 @@
         <v>3.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R23" t="n">
         <v>1.94</v>
       </c>
       <c r="S23" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="T23" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="U23" t="n">
         <v>3.2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="W23" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="X23" t="n">
         <v>120</v>
@@ -6257,7 +6257,7 @@
         <v>55</v>
       </c>
       <c r="AB23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC23" t="n">
         <v>12</v>
@@ -6293,37 +6293,37 @@
         <v>580</v>
       </c>
       <c r="AN23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO23" t="n">
         <v>12</v>
       </c>
       <c r="AP23" t="n">
-        <v>5.9</v>
+        <v>11.5</v>
       </c>
       <c r="AQ23" t="n">
         <v>18.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>20</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS23" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AT23" t="n">
         <v>17</v>
       </c>
       <c r="AU23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV23" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW23" t="n">
         <v>21</v>
       </c>
       <c r="AX23" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AY23" t="n">
         <v>11</v>
@@ -6335,25 +6335,25 @@
         <v>18.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>5.8</v>
+        <v>14.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BD23" t="n">
         <v>17</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG23" t="n">
         <v>9.6</v>
       </c>
       <c r="BH23" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BI23" t="n">
         <v>4.2</v>
@@ -6368,40 +6368,40 @@
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN23" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP23" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BS23" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT23" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV23" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BW23" t="n">
         <v>6.4</v>
       </c>
       <c r="BX23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BY23" t="n">
         <v>6.8</v>
@@ -6410,11 +6410,11 @@
         <v>11.5</v>
       </c>
       <c r="CA23" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G24" t="n">
         <v>2.6</v>
@@ -6481,7 +6481,7 @@
         <v>1.97</v>
       </c>
       <c r="R24" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
         <v>3.45</v>
@@ -6496,7 +6496,7 @@
         <v>1.38</v>
       </c>
       <c r="W24" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X24" t="n">
         <v>14.5</v>
@@ -6559,10 +6559,10 @@
         <v>10</v>
       </c>
       <c r="AR24" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AS24" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT24" t="n">
         <v>8.4</v>
@@ -6586,19 +6586,19 @@
         <v>12.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BB24" t="n">
         <v>21</v>
       </c>
       <c r="BC24" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD24" t="n">
         <v>25</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF24" t="n">
         <v>18</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -6708,13 +6708,13 @@
         <v>5</v>
       </c>
       <c r="I25" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J25" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L25" t="n">
         <v>1.4</v>
@@ -6741,7 +6741,7 @@
         <v>3.15</v>
       </c>
       <c r="T25" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="U25" t="n">
         <v>1.87</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G26" t="n">
         <v>2.3</v>
@@ -6965,10 +6965,10 @@
         <v>4.6</v>
       </c>
       <c r="J26" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K26" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L26" t="n">
         <v>1.52</v>
@@ -6977,7 +6977,7 @@
         <v>1.11</v>
       </c>
       <c r="N26" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O26" t="n">
         <v>1.48</v>
@@ -6989,13 +6989,13 @@
         <v>2.4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S26" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U26" t="n">
         <v>1.73</v>
@@ -7004,7 +7004,7 @@
         <v>1.28</v>
       </c>
       <c r="W26" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="X26" t="n">
         <v>9.4</v>
@@ -7064,7 +7064,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR26" t="n">
         <v>23</v>
@@ -7073,19 +7073,19 @@
         <v>9</v>
       </c>
       <c r="AT26" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU26" t="n">
         <v>6.4</v>
       </c>
       <c r="AV26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW26" t="n">
         <v>50</v>
       </c>
       <c r="AX26" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY26" t="n">
         <v>9.800000000000001</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -7213,7 +7213,7 @@
         <v>4.3</v>
       </c>
       <c r="H27" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="I27" t="n">
         <v>2</v>
@@ -7243,7 +7243,7 @@
         <v>1.76</v>
       </c>
       <c r="R27" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S27" t="n">
         <v>2.92</v>
@@ -7261,7 +7261,7 @@
         <v>1.31</v>
       </c>
       <c r="X27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y27" t="n">
         <v>11.5</v>
@@ -7330,7 +7330,7 @@
         <v>15.5</v>
       </c>
       <c r="AU27" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV27" t="n">
         <v>9.4</v>
@@ -7372,13 +7372,13 @@
         <v>3.85</v>
       </c>
       <c r="BI27" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ27" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK27" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -7476,16 +7476,16 @@
         <v>3.2</v>
       </c>
       <c r="K28" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L28" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M28" t="n">
         <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O28" t="n">
         <v>1.33</v>
@@ -7494,28 +7494,28 @@
         <v>1.83</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
         <v>1.32</v>
       </c>
       <c r="S28" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="T28" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U28" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="V28" t="n">
         <v>1.43</v>
       </c>
       <c r="W28" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X28" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y28" t="n">
         <v>12.5</v>
@@ -7530,7 +7530,7 @@
         <v>11</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD28" t="n">
         <v>14</v>
@@ -7563,7 +7563,7 @@
         <v>500</v>
       </c>
       <c r="AN28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO28" t="n">
         <v>36</v>
@@ -7578,31 +7578,31 @@
         <v>17.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT28" t="n">
         <v>5.8</v>
       </c>
       <c r="AU28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AV28" t="n">
         <v>8.4</v>
       </c>
       <c r="AW28" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX28" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AY28" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ28" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA28" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BB28" t="n">
         <v>23</v>
@@ -7614,77 +7614,77 @@
         <v>23</v>
       </c>
       <c r="BE28" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF28" t="n">
         <v>16</v>
       </c>
       <c r="BG28" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH28" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI28" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="BJ28" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK28" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN28" t="n">
         <v>5.7</v>
       </c>
       <c r="BO28" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP28" t="n">
         <v>20</v>
       </c>
       <c r="BQ28" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BR28" t="n">
         <v>34</v>
       </c>
       <c r="BS28" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BT28" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU28" t="n">
         <v>4.7</v>
       </c>
       <c r="BV28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BW28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>8</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA28" t="n">
         <v>7.4</v>
       </c>
-      <c r="BX28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BZ28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA28" t="n">
-        <v>7.8</v>
-      </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -7718,19 +7718,19 @@
         <v>1.3</v>
       </c>
       <c r="G29" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="H29" t="n">
         <v>10</v>
       </c>
       <c r="I29" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="J29" t="n">
         <v>5.7</v>
       </c>
       <c r="K29" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="L29" t="n">
         <v>1.3</v>
@@ -7760,13 +7760,13 @@
         <v>2.18</v>
       </c>
       <c r="U29" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V29" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W29" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="X29" t="n">
         <v>21</v>
@@ -7778,31 +7778,31 @@
         <v>130</v>
       </c>
       <c r="AA29" t="n">
-        <v>640</v>
+        <v>810</v>
       </c>
       <c r="AB29" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="AC29" t="n">
         <v>14</v>
       </c>
       <c r="AD29" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AE29" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG29" t="n">
         <v>500</v>
       </c>
       <c r="AH29" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AI29" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
         <v>11</v>
@@ -7814,13 +7814,13 @@
         <v>500</v>
       </c>
       <c r="AM29" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
         <v>14.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>390</v>
+        <v>430</v>
       </c>
       <c r="AP29" t="n">
         <v>14.5</v>
@@ -7829,10 +7829,10 @@
         <v>30</v>
       </c>
       <c r="AR29" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AT29" t="n">
         <v>6.8</v>
@@ -7841,10 +7841,10 @@
         <v>5.5</v>
       </c>
       <c r="AV29" t="n">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AX29" t="n">
         <v>6.2</v>
@@ -7853,10 +7853,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ29" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BB29" t="n">
         <v>8.6</v>
@@ -7868,7 +7868,7 @@
         <v>32</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BF29" t="n">
         <v>5</v>
@@ -7880,7 +7880,7 @@
         <v>4.1</v>
       </c>
       <c r="BI29" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ29" t="n">
         <v>1000</v>
@@ -7895,7 +7895,7 @@
         <v>1.78</v>
       </c>
       <c r="BN29" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO29" t="n">
         <v>2.98</v>
@@ -7904,13 +7904,13 @@
         <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="BR29" t="n">
         <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="BT29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -7969,25 +7969,25 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G30" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H30" t="n">
         <v>2.16</v>
       </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="J30" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K30" t="n">
         <v>4.1</v>
       </c>
       <c r="L30" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M30" t="n">
         <v>1.05</v>
@@ -8002,7 +8002,7 @@
         <v>2.04</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="R30" t="n">
         <v>1.41</v>
@@ -8017,7 +8017,7 @@
         <v>2.2</v>
       </c>
       <c r="V30" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="W30" t="n">
         <v>1.37</v>
@@ -8029,7 +8029,7 @@
         <v>970</v>
       </c>
       <c r="Z30" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AA30" t="n">
         <v>900</v>
@@ -8053,7 +8053,7 @@
         <v>970</v>
       </c>
       <c r="AH30" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI30" t="n">
         <v>500</v>
@@ -8068,67 +8068,67 @@
         <v>500</v>
       </c>
       <c r="AM30" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN30" t="n">
         <v>500</v>
       </c>
       <c r="AO30" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AP30" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AQ30" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AR30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV30" t="n">
         <v>4.1</v>
       </c>
-      <c r="AS30" t="n">
+      <c r="AW30" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG30" t="n">
         <v>4.5</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>4</v>
       </c>
       <c r="BH30" t="n">
         <v>3.95</v>
@@ -8158,7 +8158,7 @@
         <v>1000</v>
       </c>
       <c r="BQ30" t="n">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="BR30" t="n">
         <v>1000</v>
@@ -8176,7 +8176,7 @@
         <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -8223,230 +8223,230 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="G31" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="H31" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="I31" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="J31" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="K31" t="n">
-        <v>950</v>
+        <v>3.05</v>
       </c>
       <c r="L31" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="N31" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="O31" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="P31" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="R31" t="n">
         <v>1.11</v>
       </c>
       <c r="S31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>200</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>540</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>540</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>410</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>180</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA31" t="n">
         <v>7.2</v>
       </c>
-      <c r="T31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BB31" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH31" t="n">
-        <v>1000</v>
+        <v>2.4</v>
       </c>
       <c r="BI31" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="BJ31" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK31" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN31" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO31" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP31" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ31" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT31" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU31" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BZ31" t="n">
         <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -8731,19 +8731,19 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="G33" t="n">
         <v>2.36</v>
       </c>
       <c r="H33" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="I33" t="n">
         <v>3.95</v>
       </c>
       <c r="J33" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K33" t="n">
         <v>4.7</v>
@@ -8755,7 +8755,7 @@
         <v>1.04</v>
       </c>
       <c r="N33" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="O33" t="n">
         <v>1.19</v>
@@ -8776,7 +8776,7 @@
         <v>1.54</v>
       </c>
       <c r="U33" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V33" t="n">
         <v>1.33</v>
@@ -8791,7 +8791,7 @@
         <v>22</v>
       </c>
       <c r="Z33" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA33" t="n">
         <v>65</v>
@@ -8800,13 +8800,13 @@
         <v>16</v>
       </c>
       <c r="AC33" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD33" t="n">
         <v>18.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF33" t="n">
         <v>19.5</v>
@@ -8815,10 +8815,10 @@
         <v>13.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AJ33" t="n">
         <v>29</v>
@@ -8827,70 +8827,70 @@
         <v>23</v>
       </c>
       <c r="AL33" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM33" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AN33" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AO33" t="n">
         <v>32</v>
       </c>
       <c r="AP33" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AQ33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY33" t="n">
         <v>3.65</v>
       </c>
-      <c r="AR33" t="n">
+      <c r="AZ33" t="n">
         <v>3.9</v>
       </c>
-      <c r="AS33" t="n">
+      <c r="BA33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC33" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT33" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX33" t="n">
+      <c r="BD33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF33" t="n">
         <v>3.6</v>
       </c>
-      <c r="AY33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>3.35</v>
-      </c>
       <c r="BG33" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BH33" t="n">
         <v>4.6</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -8991,7 +8991,7 @@
         <v>2.96</v>
       </c>
       <c r="H34" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I34" t="n">
         <v>3.15</v>
@@ -9003,7 +9003,7 @@
         <v>3.45</v>
       </c>
       <c r="L34" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="M34" t="n">
         <v>1.1</v>
@@ -9048,7 +9048,7 @@
         <v>970</v>
       </c>
       <c r="AA34" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB34" t="n">
         <v>11</v>
@@ -9069,7 +9069,7 @@
         <v>14.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AI34" t="n">
         <v>500</v>
@@ -9084,7 +9084,7 @@
         <v>500</v>
       </c>
       <c r="AM34" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN34" t="n">
         <v>500</v>
@@ -9105,7 +9105,7 @@
         <v>7.8</v>
       </c>
       <c r="AT34" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AU34" t="n">
         <v>5.7</v>
@@ -9123,7 +9123,7 @@
         <v>10</v>
       </c>
       <c r="AZ34" t="n">
-        <v>14.5</v>
+        <v>6.2</v>
       </c>
       <c r="BA34" t="n">
         <v>8</v>
@@ -9135,10 +9135,10 @@
         <v>7.6</v>
       </c>
       <c r="BD34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BE34" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="BF34" t="n">
         <v>7.4</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -9293,13 +9293,13 @@
         <v>1.78</v>
       </c>
       <c r="X35" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y35" t="n">
         <v>17</v>
       </c>
       <c r="Z35" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA35" t="n">
         <v>900</v>
@@ -9308,25 +9308,25 @@
         <v>11</v>
       </c>
       <c r="AC35" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD35" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AF35" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG35" t="n">
         <v>12</v>
       </c>
       <c r="AH35" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI35" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AJ35" t="n">
         <v>28</v>
@@ -9335,70 +9335,70 @@
         <v>25</v>
       </c>
       <c r="AL35" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AM35" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN35" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO35" t="n">
         <v>65</v>
       </c>
       <c r="AP35" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AQ35" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AR35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ35" t="n">
         <v>4.6</v>
       </c>
-      <c r="AS35" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW35" t="n">
+      <c r="BA35" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB35" t="n">
         <v>4.9</v>
       </c>
-      <c r="AX35" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BC35" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF35" t="n">
         <v>4.4</v>
       </c>
-      <c r="BD35" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BG35" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BH35" t="n">
         <v>3.7</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -9493,19 +9493,19 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.58</v>
+        <v>1.65</v>
       </c>
       <c r="G36" t="n">
         <v>1000</v>
       </c>
       <c r="H36" t="n">
-        <v>1.14</v>
+        <v>1.42</v>
       </c>
       <c r="I36" t="n">
-        <v>3.7</v>
+        <v>110</v>
       </c>
       <c r="J36" t="n">
-        <v>1.1</v>
+        <v>1.65</v>
       </c>
       <c r="K36" t="n">
         <v>1000</v>
@@ -9517,22 +9517,22 @@
         <v>1.05</v>
       </c>
       <c r="N36" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="O36" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P36" t="n">
-        <v>1.4</v>
+        <v>1.08</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="R36" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="S36" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="T36" t="n">
         <v>1.01</v>
@@ -9541,118 +9541,118 @@
         <v>1.04</v>
       </c>
       <c r="V36" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="W36" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA36" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE36" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH36" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI36" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK36" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL36" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM36" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN36" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO36" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH36" t="n">
         <v>1000</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -9747,91 +9747,91 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="G37" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="H37" t="n">
-        <v>1.51</v>
+        <v>1.21</v>
       </c>
       <c r="I37" t="n">
-        <v>1.62</v>
+        <v>2.14</v>
       </c>
       <c r="J37" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="K37" t="n">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="L37" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M37" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="N37" t="n">
-        <v>2.62</v>
+        <v>1.19</v>
       </c>
       <c r="O37" t="n">
-        <v>1.45</v>
+        <v>1.04</v>
       </c>
       <c r="P37" t="n">
-        <v>1.63</v>
+        <v>1.19</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.22</v>
+        <v>1.04</v>
       </c>
       <c r="R37" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="S37" t="n">
-        <v>4.5</v>
+        <v>1.06</v>
       </c>
       <c r="T37" t="n">
-        <v>2.36</v>
+        <v>1.11</v>
       </c>
       <c r="U37" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="V37" t="n">
-        <v>2.6</v>
+        <v>1.88</v>
       </c>
       <c r="W37" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X37" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y37" t="n">
-        <v>6.4</v>
+        <v>970</v>
       </c>
       <c r="Z37" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AA37" t="n">
+        <v>970</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE37" t="n">
         <v>500</v>
       </c>
-      <c r="AB37" t="n">
-        <v>24</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>65</v>
-      </c>
       <c r="AF37" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AG37" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AH37" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AI37" t="n">
         <v>500</v>
@@ -9840,10 +9840,10 @@
         <v>1000</v>
       </c>
       <c r="AK37" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AL37" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AM37" t="n">
         <v>1000</v>
@@ -9852,125 +9852,125 @@
         <v>1000</v>
       </c>
       <c r="AO37" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AP37" t="n">
-        <v>4.4</v>
+        <v>1.13</v>
       </c>
       <c r="AQ37" t="n">
-        <v>3.35</v>
+        <v>1.08</v>
       </c>
       <c r="AR37" t="n">
-        <v>3.75</v>
+        <v>1.1</v>
       </c>
       <c r="AS37" t="n">
-        <v>4.7</v>
+        <v>1.12</v>
       </c>
       <c r="AT37" t="n">
-        <v>5.5</v>
+        <v>1.13</v>
       </c>
       <c r="AU37" t="n">
-        <v>4.1</v>
+        <v>1.13</v>
       </c>
       <c r="AV37" t="n">
-        <v>4.4</v>
+        <v>1.09</v>
       </c>
       <c r="AW37" t="n">
-        <v>5.5</v>
+        <v>1.11</v>
       </c>
       <c r="AX37" t="n">
-        <v>6.4</v>
+        <v>1.13</v>
       </c>
       <c r="AY37" t="n">
-        <v>6</v>
+        <v>1.13</v>
       </c>
       <c r="AZ37" t="n">
-        <v>6</v>
+        <v>1.13</v>
       </c>
       <c r="BA37" t="n">
-        <v>6.4</v>
+        <v>1.12</v>
       </c>
       <c r="BB37" t="n">
-        <v>7</v>
+        <v>1.13</v>
       </c>
       <c r="BC37" t="n">
-        <v>6.8</v>
+        <v>1.13</v>
       </c>
       <c r="BD37" t="n">
-        <v>6.8</v>
+        <v>1.13</v>
       </c>
       <c r="BE37" t="n">
-        <v>6.8</v>
+        <v>1.13</v>
       </c>
       <c r="BF37" t="n">
-        <v>7</v>
+        <v>1.55</v>
       </c>
       <c r="BG37" t="n">
-        <v>4.7</v>
+        <v>1.12</v>
       </c>
       <c r="BH37" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="BI37" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BJ37" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK37" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN37" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BO37" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BP37" t="n">
         <v>1000</v>
       </c>
       <c r="BQ37" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="BR37" t="n">
         <v>1000</v>
       </c>
       <c r="BS37" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="BT37" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BU37" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="BV37" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BW37" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX37" t="n">
         <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ37" t="n">
         <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -10001,64 +10001,64 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.26</v>
+        <v>1.88</v>
       </c>
       <c r="G38" t="n">
-        <v>2.46</v>
+        <v>6.2</v>
       </c>
       <c r="H38" t="n">
-        <v>3.5</v>
+        <v>2.48</v>
       </c>
       <c r="I38" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="J38" t="n">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="K38" t="n">
-        <v>3.35</v>
+        <v>7</v>
       </c>
       <c r="L38" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>2.62</v>
+        <v>1.08</v>
       </c>
       <c r="O38" t="n">
-        <v>1.51</v>
+        <v>1.02</v>
       </c>
       <c r="P38" t="n">
-        <v>1.56</v>
+        <v>1.07</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="R38" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="S38" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="T38" t="n">
-        <v>2.06</v>
+        <v>1.61</v>
       </c>
       <c r="U38" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="V38" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="W38" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="X38" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Y38" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Z38" t="n">
         <v>500</v>
@@ -10067,10 +10067,10 @@
         <v>900</v>
       </c>
       <c r="AB38" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AC38" t="n">
-        <v>8.4</v>
+        <v>42</v>
       </c>
       <c r="AD38" t="n">
         <v>970</v>
@@ -10079,10 +10079,10 @@
         <v>500</v>
       </c>
       <c r="AF38" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AG38" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AH38" t="n">
         <v>500</v>
@@ -10109,122 +10109,122 @@
         <v>500</v>
       </c>
       <c r="AP38" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ38" t="n">
-        <v>3.7</v>
+        <v>1.53</v>
       </c>
       <c r="AR38" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="AS38" t="n">
-        <v>5</v>
+        <v>1.61</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AV38" t="n">
-        <v>4.1</v>
+        <v>1.56</v>
       </c>
       <c r="AW38" t="n">
-        <v>4.9</v>
+        <v>1.61</v>
       </c>
       <c r="AX38" t="n">
-        <v>3.9</v>
+        <v>1.55</v>
       </c>
       <c r="AY38" t="n">
-        <v>3.8</v>
+        <v>1.54</v>
       </c>
       <c r="AZ38" t="n">
-        <v>4.3</v>
+        <v>1.59</v>
       </c>
       <c r="BA38" t="n">
-        <v>5</v>
+        <v>1.62</v>
       </c>
       <c r="BB38" t="n">
-        <v>4.6</v>
+        <v>1.61</v>
       </c>
       <c r="BC38" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.9</v>
+        <v>1.62</v>
       </c>
       <c r="BE38" t="n">
-        <v>5.1</v>
+        <v>1.62</v>
       </c>
       <c r="BF38" t="n">
         <v>4.6</v>
       </c>
       <c r="BG38" t="n">
-        <v>5</v>
+        <v>1.62</v>
       </c>
       <c r="BH38" t="n">
-        <v>2.78</v>
+        <v>1000</v>
       </c>
       <c r="BI38" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="BJ38" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK38" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BN38" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO38" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP38" t="n">
         <v>1000</v>
       </c>
       <c r="BQ38" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="BR38" t="n">
         <v>1000</v>
       </c>
       <c r="BS38" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="BT38" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU38" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV38" t="n">
         <v>1000</v>
       </c>
       <c r="BW38" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX38" t="n">
         <v>1000</v>
       </c>
       <c r="BY38" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="BZ38" t="n">
         <v>1000</v>
       </c>
       <c r="CA38" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -10255,58 +10255,58 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.59</v>
+        <v>1.36</v>
       </c>
       <c r="G39" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="H39" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="I39" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="J39" t="n">
-        <v>3.45</v>
+        <v>2.52</v>
       </c>
       <c r="K39" t="n">
-        <v>4.2</v>
+        <v>100</v>
       </c>
       <c r="L39" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M39" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="N39" t="n">
-        <v>2.72</v>
+        <v>1.08</v>
       </c>
       <c r="O39" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="P39" t="n">
-        <v>1.66</v>
+        <v>1.08</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.2</v>
+        <v>1.39</v>
       </c>
       <c r="R39" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>1.39</v>
       </c>
       <c r="T39" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="U39" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="V39" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="W39" t="n">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="X39" t="n">
         <v>970</v>
@@ -10321,10 +10321,10 @@
         <v>700</v>
       </c>
       <c r="AB39" t="n">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="AC39" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AD39" t="n">
         <v>500</v>
@@ -10333,7 +10333,7 @@
         <v>700</v>
       </c>
       <c r="AF39" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AG39" t="n">
         <v>970</v>
@@ -10354,7 +10354,7 @@
         <v>500</v>
       </c>
       <c r="AM39" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN39" t="n">
         <v>970</v>
@@ -10366,119 +10366,119 @@
         <v>4.5</v>
       </c>
       <c r="AQ39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU39" t="n">
         <v>5.1</v>
       </c>
-      <c r="AR39" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AV39" t="n">
-        <v>3.6</v>
+        <v>1.78</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.5</v>
+        <v>1.82</v>
       </c>
       <c r="AX39" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AY39" t="n">
-        <v>4.2</v>
+        <v>1.66</v>
       </c>
       <c r="AZ39" t="n">
-        <v>4.2</v>
+        <v>1.78</v>
       </c>
       <c r="BA39" t="n">
-        <v>4.5</v>
+        <v>1.82</v>
       </c>
       <c r="BB39" t="n">
-        <v>4.9</v>
+        <v>1.76</v>
       </c>
       <c r="BC39" t="n">
-        <v>5.2</v>
+        <v>1.77</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="BE39" t="n">
-        <v>4.5</v>
+        <v>1.82</v>
       </c>
       <c r="BF39" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="BG39" t="n">
-        <v>4.5</v>
+        <v>1.82</v>
       </c>
       <c r="BH39" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="BI39" t="n">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="BJ39" t="n">
         <v>1000</v>
       </c>
       <c r="BK39" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="BN39" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO39" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="BP39" t="n">
         <v>1000</v>
       </c>
       <c r="BQ39" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR39" t="n">
         <v>1000</v>
       </c>
       <c r="BS39" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="BT39" t="n">
         <v>1000</v>
       </c>
       <c r="BU39" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV39" t="n">
         <v>1000</v>
       </c>
       <c r="BW39" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="BX39" t="n">
         <v>1000</v>
       </c>
       <c r="BY39" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="BZ39" t="n">
         <v>1000</v>
       </c>
       <c r="CA39" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -10509,166 +10509,166 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="G40" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="H40" t="n">
-        <v>9</v>
+        <v>5.9</v>
       </c>
       <c r="I40" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="J40" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="K40" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="L40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O40" t="n">
         <v>1.34</v>
       </c>
-      <c r="M40" t="n">
+      <c r="P40" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="R40" t="n">
         <v>1.07</v>
       </c>
-      <c r="N40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P40" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.3</v>
-      </c>
       <c r="S40" t="n">
-        <v>3.55</v>
+        <v>1.34</v>
       </c>
       <c r="T40" t="n">
-        <v>2.38</v>
+        <v>1.11</v>
       </c>
       <c r="U40" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="V40" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W40" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="X40" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y40" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z40" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AA40" t="n">
         <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="AC40" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AD40" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AE40" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AF40" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AG40" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AH40" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AI40" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AJ40" t="n">
-        <v>12</v>
+        <v>900</v>
       </c>
       <c r="AK40" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AL40" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AM40" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>9.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="AO40" t="n">
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>3.65</v>
+        <v>1.56</v>
       </c>
       <c r="AQ40" t="n">
-        <v>4.1</v>
+        <v>1.57</v>
       </c>
       <c r="AR40" t="n">
-        <v>4.5</v>
+        <v>1.57</v>
       </c>
       <c r="AS40" t="n">
-        <v>4.7</v>
+        <v>1.57</v>
       </c>
       <c r="AT40" t="n">
-        <v>2.94</v>
+        <v>3.85</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.5</v>
+        <v>1.51</v>
       </c>
       <c r="AV40" t="n">
-        <v>4.3</v>
+        <v>1.57</v>
       </c>
       <c r="AW40" t="n">
-        <v>4.6</v>
+        <v>1.57</v>
       </c>
       <c r="AX40" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="AY40" t="n">
-        <v>3.45</v>
+        <v>1.44</v>
       </c>
       <c r="AZ40" t="n">
-        <v>4.2</v>
+        <v>1.57</v>
       </c>
       <c r="BA40" t="n">
-        <v>4.6</v>
+        <v>1.57</v>
       </c>
       <c r="BB40" t="n">
-        <v>3.4</v>
+        <v>1.48</v>
       </c>
       <c r="BC40" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.4</v>
+        <v>1.55</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.6</v>
+        <v>1.57</v>
       </c>
       <c r="BF40" t="n">
-        <v>3.2</v>
+        <v>2.48</v>
       </c>
       <c r="BG40" t="n">
-        <v>4.7</v>
+        <v>1.57</v>
       </c>
       <c r="BH40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -10763,230 +10763,230 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.82</v>
+        <v>1.52</v>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="H41" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="I41" t="n">
-        <v>5.8</v>
+        <v>17.5</v>
       </c>
       <c r="J41" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="K41" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="L41" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V41" t="n">
         <v>1.11</v>
       </c>
-      <c r="N41" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O41" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P41" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.21</v>
-      </c>
       <c r="W41" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="X41" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Y41" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Z41" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AA41" t="n">
         <v>900</v>
       </c>
       <c r="AB41" t="n">
-        <v>7</v>
+        <v>970</v>
       </c>
       <c r="AC41" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD41" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AE41" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AF41" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AG41" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH41" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AI41" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AJ41" t="n">
-        <v>23</v>
+        <v>900</v>
       </c>
       <c r="AK41" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AL41" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AM41" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN41" t="n">
         <v>500</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>21</v>
       </c>
       <c r="AO41" t="n">
         <v>700</v>
       </c>
       <c r="AP41" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AQ41" t="n">
-        <v>5.1</v>
+        <v>1.75</v>
       </c>
       <c r="AR41" t="n">
-        <v>6.8</v>
+        <v>1.84</v>
       </c>
       <c r="AS41" t="n">
-        <v>7.4</v>
+        <v>1.86</v>
       </c>
       <c r="AT41" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AU41" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AV41" t="n">
-        <v>5.9</v>
+        <v>1.81</v>
       </c>
       <c r="AW41" t="n">
-        <v>7.2</v>
+        <v>1.86</v>
       </c>
       <c r="AX41" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BF41" t="n">
         <v>4.4</v>
       </c>
-      <c r="AY41" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE41" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF41" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BG41" t="n">
-        <v>7.4</v>
+        <v>1.86</v>
       </c>
       <c r="BH41" t="n">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="BI41" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="BJ41" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK41" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BL41" t="n">
         <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="BN41" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO41" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP41" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ41" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR41" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS41" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="BT41" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU41" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV41" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW41" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BX41" t="n">
         <v>1000</v>
       </c>
       <c r="BY41" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="BZ41" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA41" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -11017,178 +11017,178 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="G42" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="H42" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="I42" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="J42" t="n">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="K42" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="L42" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M42" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>2.6</v>
+        <v>1.08</v>
       </c>
       <c r="O42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U42" t="n">
         <v>1.51</v>
       </c>
-      <c r="P42" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.78</v>
-      </c>
       <c r="V42" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="W42" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="X42" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Y42" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="Z42" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AA42" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC42" t="n">
         <v>42</v>
       </c>
-      <c r="AB42" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AD42" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AE42" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AF42" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AG42" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AH42" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AI42" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AJ42" t="n">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AK42" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AL42" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AM42" t="n">
         <v>500</v>
       </c>
       <c r="AN42" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AO42" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AP42" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AQ42" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AR42" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS42" t="n">
-        <v>6.6</v>
+        <v>1.63</v>
       </c>
       <c r="AT42" t="n">
-        <v>4.5</v>
+        <v>1.55</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AV42" t="n">
-        <v>4.9</v>
+        <v>1.56</v>
       </c>
       <c r="AW42" t="n">
-        <v>6.6</v>
+        <v>1.62</v>
       </c>
       <c r="AX42" t="n">
-        <v>6</v>
+        <v>1.62</v>
       </c>
       <c r="AY42" t="n">
-        <v>5.4</v>
+        <v>1.6</v>
       </c>
       <c r="AZ42" t="n">
-        <v>6</v>
+        <v>1.61</v>
       </c>
       <c r="BA42" t="n">
-        <v>7.2</v>
+        <v>1.64</v>
       </c>
       <c r="BB42" t="n">
-        <v>7.4</v>
+        <v>1.64</v>
       </c>
       <c r="BC42" t="n">
-        <v>7</v>
+        <v>1.64</v>
       </c>
       <c r="BD42" t="n">
-        <v>7.2</v>
+        <v>1.61</v>
       </c>
       <c r="BE42" t="n">
-        <v>7.8</v>
+        <v>1.64</v>
       </c>
       <c r="BF42" t="n">
-        <v>7.4</v>
+        <v>1.64</v>
       </c>
       <c r="BG42" t="n">
-        <v>6.6</v>
+        <v>1.62</v>
       </c>
       <c r="BH42" t="n">
-        <v>2.8</v>
+        <v>1000</v>
       </c>
       <c r="BI42" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BJ42" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK42" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL42" t="n">
         <v>1000</v>
@@ -11197,50 +11197,50 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN42" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO42" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP42" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ42" t="n">
-        <v>2.14</v>
+        <v>7.6</v>
       </c>
       <c r="BR42" t="n">
         <v>1000</v>
       </c>
       <c r="BS42" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BT42" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU42" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BV42" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW42" t="n">
-        <v>2.06</v>
+        <v>6.8</v>
       </c>
       <c r="BX42" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY42" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BZ42" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="CA42" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -11277,7 +11277,7 @@
         <v>5.8</v>
       </c>
       <c r="H43" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="I43" t="n">
         <v>1.91</v>
@@ -11301,10 +11301,10 @@
         <v>1.28</v>
       </c>
       <c r="P43" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="R43" t="n">
         <v>1.36</v>
@@ -11316,16 +11316,16 @@
         <v>1.78</v>
       </c>
       <c r="U43" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V43" t="n">
         <v>2.08</v>
       </c>
       <c r="W43" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="X43" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y43" t="n">
         <v>9.800000000000001</v>
@@ -11349,7 +11349,7 @@
         <v>23</v>
       </c>
       <c r="AF43" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AG43" t="n">
         <v>22</v>
@@ -11358,7 +11358,7 @@
         <v>24</v>
       </c>
       <c r="AI43" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AJ43" t="n">
         <v>900</v>
@@ -11367,10 +11367,10 @@
         <v>700</v>
       </c>
       <c r="AL43" t="n">
-        <v>700</v>
+        <v>320</v>
       </c>
       <c r="AM43" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN43" t="n">
         <v>700</v>
@@ -11403,7 +11403,7 @@
         <v>13.5</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AY43" t="n">
         <v>14.5</v>
@@ -11412,7 +11412,7 @@
         <v>14</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BB43" t="n">
         <v>1.03</v>
@@ -11427,7 +11427,7 @@
         <v>1.03</v>
       </c>
       <c r="BF43" t="n">
-        <v>50</v>
+        <v>1.55</v>
       </c>
       <c r="BG43" t="n">
         <v>8.4</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -11525,19 +11525,19 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="G44" t="n">
         <v>12.5</v>
       </c>
       <c r="H44" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="I44" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="J44" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K44" t="n">
         <v>4.1</v>
@@ -11549,142 +11549,142 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="O44" t="n">
         <v>1.03</v>
       </c>
       <c r="P44" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="Q44" t="n">
         <v>1.48</v>
       </c>
       <c r="R44" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="S44" t="n">
         <v>5.1</v>
       </c>
       <c r="T44" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="U44" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V44" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="W44" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X44" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y44" t="n">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="Z44" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AB44" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC44" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD44" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AE44" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AF44" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AG44" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AH44" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AI44" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AJ44" t="n">
-        <v>900</v>
+        <v>520</v>
       </c>
       <c r="AK44" t="n">
+        <v>370</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>510</v>
+      </c>
+      <c r="AM44" t="n">
         <v>700</v>
       </c>
-      <c r="AL44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>1000</v>
-      </c>
       <c r="AN44" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AO44" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.13</v>
+        <v>4.4</v>
       </c>
       <c r="AQ44" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.1</v>
+        <v>6.4</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.13</v>
+        <v>13</v>
       </c>
       <c r="AT44" t="n">
-        <v>1.13</v>
+        <v>11.5</v>
       </c>
       <c r="AU44" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="AV44" t="n">
-        <v>1.1</v>
+        <v>8.4</v>
       </c>
       <c r="AW44" t="n">
-        <v>1.11</v>
+        <v>16.5</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.13</v>
+        <v>32</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.13</v>
+        <v>18</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1.13</v>
+        <v>20</v>
       </c>
       <c r="BA44" t="n">
-        <v>1.13</v>
+        <v>38</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.13</v>
+        <v>2.84</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.13</v>
+        <v>2.82</v>
       </c>
       <c r="BD44" t="n">
-        <v>1.13</v>
+        <v>2.84</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.13</v>
+        <v>2.84</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.13</v>
+        <v>2.84</v>
       </c>
       <c r="BG44" t="n">
-        <v>1.13</v>
+        <v>12.5</v>
       </c>
       <c r="BH44" t="n">
         <v>1000</v>
@@ -11696,7 +11696,7 @@
         <v>1000</v>
       </c>
       <c r="BK44" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL44" t="n">
         <v>1000</v>
@@ -11708,47 +11708,47 @@
         <v>1000</v>
       </c>
       <c r="BO44" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="BP44" t="n">
         <v>1000</v>
       </c>
       <c r="BQ44" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BR44" t="n">
         <v>1000</v>
       </c>
       <c r="BS44" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT44" t="n">
         <v>1000</v>
       </c>
       <c r="BU44" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BV44" t="n">
         <v>1000</v>
       </c>
       <c r="BW44" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BX44" t="n">
         <v>1000</v>
       </c>
       <c r="BY44" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ44" t="n">
         <v>1000</v>
       </c>
       <c r="CA44" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -11791,7 +11791,7 @@
         <v>4.5</v>
       </c>
       <c r="J45" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="K45" t="n">
         <v>3.2</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -12198,7 +12198,7 @@
         <v>2.58</v>
       </c>
       <c r="BI46" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="BJ46" t="n">
         <v>1000</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -12287,19 +12287,19 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="G47" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="H47" t="n">
-        <v>2.64</v>
+        <v>3.05</v>
       </c>
       <c r="I47" t="n">
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>2.52</v>
+        <v>2.84</v>
       </c>
       <c r="K47" t="n">
         <v>7</v>
@@ -12308,16 +12308,16 @@
         <v>1.01</v>
       </c>
       <c r="M47" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="O47" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="P47" t="n">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="Q47" t="n">
         <v>1.04</v>
@@ -12326,7 +12326,7 @@
         <v>1.08</v>
       </c>
       <c r="S47" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="T47" t="n">
         <v>1.01</v>
@@ -12338,7 +12338,7 @@
         <v>1.15</v>
       </c>
       <c r="W47" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="X47" t="n">
         <v>500</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -12541,13 +12541,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="G48" t="n">
         <v>1000</v>
       </c>
       <c r="H48" t="n">
-        <v>1.66</v>
+        <v>3.3</v>
       </c>
       <c r="I48" t="n">
         <v>1000</v>
@@ -12574,7 +12574,7 @@
         <v>1.08</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="R48" t="n">
         <v>1.08</v>
@@ -12589,34 +12589,34 @@
         <v>1.01</v>
       </c>
       <c r="V48" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W48" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X48" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y48" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z48" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA48" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB48" t="n">
         <v>500</v>
       </c>
       <c r="AC48" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD48" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE48" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF48" t="n">
         <v>500</v>
@@ -12625,10 +12625,10 @@
         <v>500</v>
       </c>
       <c r="AH48" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI48" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ48" t="n">
         <v>500</v>
@@ -12640,13 +12640,13 @@
         <v>500</v>
       </c>
       <c r="AM48" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN48" t="n">
         <v>500</v>
       </c>
       <c r="AO48" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP48" t="n">
         <v>1.01</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -12819,13 +12819,13 @@
         <v>1.09</v>
       </c>
       <c r="N49" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O49" t="n">
         <v>1.43</v>
       </c>
       <c r="P49" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q49" t="n">
         <v>2.26</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -13049,13 +13049,13 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="G50" t="n">
         <v>1000</v>
       </c>
       <c r="H50" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="I50" t="n">
         <v>1000</v>
@@ -13076,13 +13076,13 @@
         <v>1.09</v>
       </c>
       <c r="O50" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P50" t="n">
         <v>1.08</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R50" t="n">
         <v>1.08</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -13330,10 +13330,10 @@
         <v>2.86</v>
       </c>
       <c r="O51" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P51" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q51" t="n">
         <v>2.24</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -13572,7 +13572,7 @@
         <v>3.55</v>
       </c>
       <c r="K52" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L52" t="n">
         <v>1.27</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -13811,73 +13811,73 @@
         </is>
       </c>
       <c r="F53" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H53" t="n">
         <v>2.8</v>
       </c>
-      <c r="G53" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="H53" t="n">
-        <v>2.88</v>
-      </c>
       <c r="I53" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J53" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="K53" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L53" t="n">
         <v>1.53</v>
       </c>
       <c r="M53" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N53" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="O53" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P53" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="R53" t="n">
         <v>1.18</v>
       </c>
       <c r="S53" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="T53" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U53" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V53" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W53" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="X53" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y53" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z53" t="n">
         <v>19</v>
       </c>
       <c r="AA53" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AB53" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC53" t="n">
         <v>7.4</v>
@@ -13886,7 +13886,7 @@
         <v>15</v>
       </c>
       <c r="AE53" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AF53" t="n">
         <v>19.5</v>
@@ -13895,7 +13895,7 @@
         <v>15</v>
       </c>
       <c r="AH53" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AI53" t="n">
         <v>500</v>
@@ -13904,7 +13904,7 @@
         <v>900</v>
       </c>
       <c r="AK53" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AL53" t="n">
         <v>500</v>
@@ -13913,64 +13913,64 @@
         <v>500</v>
       </c>
       <c r="AN53" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AO53" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AP53" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AQ53" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AR53" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS53" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT53" t="n">
         <v>4.5</v>
       </c>
       <c r="AU53" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AV53" t="n">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="AW53" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX53" t="n">
-        <v>6.2</v>
+        <v>15.5</v>
       </c>
       <c r="AY53" t="n">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="AZ53" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="BA53" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB53" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BC53" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD53" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE53" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF53" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BG53" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH53" t="n">
         <v>2.7</v>
@@ -13982,34 +13982,34 @@
         <v>12</v>
       </c>
       <c r="BK53" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL53" t="n">
         <v>1000</v>
       </c>
       <c r="BM53" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BN53" t="n">
         <v>6</v>
       </c>
       <c r="BO53" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP53" t="n">
         <v>1000</v>
       </c>
       <c r="BQ53" t="n">
-        <v>2.02</v>
+        <v>8.4</v>
       </c>
       <c r="BR53" t="n">
         <v>1000</v>
       </c>
       <c r="BS53" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="BT53" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU53" t="n">
         <v>4.6</v>
@@ -14018,23 +14018,23 @@
         <v>1000</v>
       </c>
       <c r="BW53" t="n">
-        <v>2.02</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX53" t="n">
         <v>1000</v>
       </c>
       <c r="BY53" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="BZ53" t="n">
         <v>1000</v>
       </c>
       <c r="CA53" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -14092,7 +14092,7 @@
         <v>4.4</v>
       </c>
       <c r="O54" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P54" t="n">
         <v>2.16</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -14364,7 +14364,7 @@
         <v>2.04</v>
       </c>
       <c r="U55" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V55" t="n">
         <v>1.33</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -14573,28 +14573,28 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G56" t="n">
         <v>2.44</v>
       </c>
       <c r="H56" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I56" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J56" t="n">
         <v>3.1</v>
       </c>
       <c r="K56" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L56" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="M56" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N56" t="n">
         <v>2.88</v>
@@ -14603,7 +14603,7 @@
         <v>1.51</v>
       </c>
       <c r="P56" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q56" t="n">
         <v>2.52</v>
@@ -14615,7 +14615,7 @@
         <v>5</v>
       </c>
       <c r="T56" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U56" t="n">
         <v>1.84</v>
@@ -14681,7 +14681,7 @@
         <v>80</v>
       </c>
       <c r="AP56" t="n">
-        <v>8.6</v>
+        <v>3.9</v>
       </c>
       <c r="AQ56" t="n">
         <v>9.4</v>
@@ -14708,7 +14708,7 @@
         <v>10</v>
       </c>
       <c r="AY56" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ56" t="n">
         <v>18</v>
@@ -14729,7 +14729,7 @@
         <v>5.8</v>
       </c>
       <c r="BF56" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="BG56" t="n">
         <v>5.5</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>
@@ -14830,7 +14830,7 @@
         <v>2.36</v>
       </c>
       <c r="G57" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H57" t="n">
         <v>2.84</v>
@@ -14839,10 +14839,10 @@
         <v>3.4</v>
       </c>
       <c r="J57" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K57" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="L57" t="n">
         <v>1.38</v>
@@ -14857,7 +14857,7 @@
         <v>1.31</v>
       </c>
       <c r="P57" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q57" t="n">
         <v>1.92</v>
@@ -14872,7 +14872,7 @@
         <v>1.72</v>
       </c>
       <c r="U57" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V57" t="n">
         <v>1.42</v>
@@ -14899,7 +14899,7 @@
         <v>8.4</v>
       </c>
       <c r="AD57" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AE57" t="n">
         <v>38</v>
@@ -14980,13 +14980,13 @@
         <v>30</v>
       </c>
       <c r="BE57" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF57" t="n">
         <v>15</v>
       </c>
       <c r="BG57" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH57" t="n">
         <v>3.65</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-04 20:29:13</t>
+          <t>2026-07-04 22:42:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="G2" t="n">
         <v>3.3</v>
       </c>
       <c r="H2" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="I2" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
         <v>3</v>
@@ -875,7 +875,7 @@
         <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
@@ -887,7 +887,7 @@
         <v>1.4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q2" t="n">
         <v>2.16</v>
@@ -896,10 +896,10 @@
         <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="T2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U2" t="n">
         <v>1.92</v>
@@ -908,7 +908,7 @@
         <v>1.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X2" t="n">
         <v>11.5</v>
@@ -917,10 +917,10 @@
         <v>10.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AA2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB2" t="n">
         <v>11</v>
@@ -941,7 +941,7 @@
         <v>14.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI2" t="n">
         <v>65</v>
@@ -971,7 +971,7 @@
         <v>5.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AS2" t="n">
         <v>6.6</v>
@@ -980,7 +980,7 @@
         <v>5.1</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AV2" t="n">
         <v>5.3</v>
@@ -989,19 +989,19 @@
         <v>6.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.9</v>
+        <v>11.5</v>
       </c>
       <c r="BA2" t="n">
         <v>6.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC2" t="n">
         <v>6.4</v>
@@ -1010,7 +1010,7 @@
         <v>6.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.2</v>
+        <v>120</v>
       </c>
       <c r="BF2" t="n">
         <v>6.6</v>
@@ -1022,7 +1022,7 @@
         <v>3.15</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="BJ2" t="n">
         <v>11</v>
@@ -1034,13 +1034,13 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>2.34</v>
+        <v>140</v>
       </c>
       <c r="BN2" t="n">
         <v>6.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BP2" t="n">
         <v>27</v>
@@ -1052,13 +1052,13 @@
         <v>44</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.24</v>
+        <v>7.8</v>
       </c>
       <c r="BT2" t="n">
         <v>5.9</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="BV2" t="n">
         <v>24</v>
@@ -1070,17 +1070,17 @@
         <v>42</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.24</v>
+        <v>7.8</v>
       </c>
       <c r="BZ2" t="n">
         <v>40</v>
       </c>
       <c r="CA2" t="n">
-        <v>2.24</v>
+        <v>7.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -1111,58 +1111,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I3" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="L3" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="P3" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="R3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
         <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="U3" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="X3" t="n">
         <v>18</v>
@@ -1177,7 +1177,7 @@
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AC3" t="n">
         <v>9.199999999999999</v>
@@ -1189,7 +1189,7 @@
         <v>700</v>
       </c>
       <c r="AF3" t="n">
-        <v>40</v>
+        <v>970</v>
       </c>
       <c r="AG3" t="n">
         <v>970</v>
@@ -1213,13 +1213,13 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AO3" t="n">
         <v>700</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AQ3" t="n">
         <v>6.2</v>
@@ -1228,19 +1228,19 @@
         <v>6.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.88</v>
+        <v>2.36</v>
       </c>
       <c r="AT3" t="n">
         <v>4.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AX3" t="n">
         <v>6.2</v>
@@ -1249,34 +1249,34 @@
         <v>7.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="BB3" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.7</v>
+        <v>120</v>
       </c>
       <c r="BF3" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.85</v>
+        <v>2.76</v>
       </c>
       <c r="BH3" t="n">
         <v>3.1</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN3" t="n">
         <v>4.6</v>
@@ -1300,7 +1300,7 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="G4" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K4" t="n">
         <v>3.7</v>
@@ -1389,22 +1389,22 @@
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P4" t="n">
         <v>1.83</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R4" t="n">
         <v>1.31</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T4" t="n">
         <v>1.94</v>
@@ -1419,7 +1419,7 @@
         <v>1.98</v>
       </c>
       <c r="X4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y4" t="n">
         <v>15</v>
@@ -1440,13 +1440,13 @@
         <v>18.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="AF4" t="n">
         <v>12</v>
       </c>
       <c r="AG4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH4" t="n">
         <v>22</v>
@@ -1455,7 +1455,7 @@
         <v>150</v>
       </c>
       <c r="AJ4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AK4" t="n">
         <v>24</v>
@@ -1467,7 +1467,7 @@
         <v>440</v>
       </c>
       <c r="AN4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO4" t="n">
         <v>170</v>
@@ -1476,7 +1476,7 @@
         <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR4" t="n">
         <v>28</v>
@@ -1485,7 +1485,7 @@
         <v>38</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU4" t="n">
         <v>7.2</v>
@@ -1494,10 +1494,10 @@
         <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AX4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY4" t="n">
         <v>9.4</v>
@@ -1515,80 +1515,80 @@
         <v>19.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BE4" t="n">
         <v>75</v>
       </c>
       <c r="BF4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BG4" t="n">
         <v>48</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.64</v>
+        <v>2.94</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO4" t="n">
         <v>4.1</v>
       </c>
       <c r="BP4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BT4" t="n">
         <v>7.8</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY4" t="n">
+        <v>14</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA4" t="n">
         <v>11.5</v>
       </c>
-      <c r="BZ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>10</v>
-      </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>2.56</v>
       </c>
       <c r="G5" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -1637,7 +1637,7 @@
         <v>3.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
@@ -1649,7 +1649,7 @@
         <v>1.38</v>
       </c>
       <c r="P5" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
         <v>2.14</v>
@@ -1658,10 +1658,10 @@
         <v>1.31</v>
       </c>
       <c r="S5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U5" t="n">
         <v>2.08</v>
@@ -1670,10 +1670,10 @@
         <v>1.47</v>
       </c>
       <c r="W5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y5" t="n">
         <v>11</v>
@@ -1685,7 +1685,7 @@
         <v>120</v>
       </c>
       <c r="AB5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC5" t="n">
         <v>7.6</v>
@@ -1694,28 +1694,28 @@
         <v>13.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
         <v>19.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK5" t="n">
         <v>32</v>
       </c>
       <c r="AL5" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
         <v>440</v>
@@ -1724,19 +1724,19 @@
         <v>28</v>
       </c>
       <c r="AO5" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="AP5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR5" t="n">
         <v>18</v>
       </c>
       <c r="AS5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AT5" t="n">
         <v>9.199999999999999</v>
@@ -1751,7 +1751,7 @@
         <v>27</v>
       </c>
       <c r="AX5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY5" t="n">
         <v>11</v>
@@ -1766,7 +1766,7 @@
         <v>29</v>
       </c>
       <c r="BC5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BD5" t="n">
         <v>34</v>
@@ -1781,13 +1781,13 @@
         <v>30</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="BJ5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK5" t="n">
         <v>7.8</v>
@@ -1796,53 +1796,53 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP5" t="n">
         <v>21</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT5" t="n">
         <v>6.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BV5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BZ5" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="G6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="J6" t="n">
         <v>4.5</v>
@@ -1891,7 +1891,7 @@
         <v>4.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1900,13 +1900,13 @@
         <v>3.75</v>
       </c>
       <c r="O6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P6" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R6" t="n">
         <v>1.34</v>
@@ -1915,22 +1915,22 @@
         <v>3.75</v>
       </c>
       <c r="T6" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V6" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="W6" t="n">
         <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Z6" t="n">
         <v>8.199999999999999</v>
@@ -1939,22 +1939,22 @@
         <v>13</v>
       </c>
       <c r="AB6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC6" t="n">
         <v>10</v>
       </c>
       <c r="AD6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AE6" t="n">
         <v>18.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AG6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AH6" t="n">
         <v>29</v>
@@ -1978,34 +1978,34 @@
         <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AP6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ6" t="n">
         <v>6.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS6" t="n">
         <v>11.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AU6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AV6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW6" t="n">
         <v>15.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AY6" t="n">
         <v>23</v>
@@ -2014,10 +2014,10 @@
         <v>23</v>
       </c>
       <c r="BA6" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BB6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BC6" t="n">
         <v>42</v>
@@ -2029,16 +2029,16 @@
         <v>70</v>
       </c>
       <c r="BF6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BG6" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="BJ6" t="n">
         <v>12.5</v>
@@ -2050,53 +2050,53 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
+        <v>19</v>
+      </c>
+      <c r="BN6" t="n">
         <v>11</v>
       </c>
-      <c r="BN6" t="n">
-        <v>12</v>
-      </c>
       <c r="BO6" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BP6" t="n">
         <v>85</v>
       </c>
       <c r="BQ6" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="BR6" t="n">
         <v>85</v>
       </c>
       <c r="BS6" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="BT6" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="BV6" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX6" t="n">
         <v>30</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>20</v>
       </c>
       <c r="CA6" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="G7" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I7" t="n">
         <v>4.9</v>
@@ -2163,7 +2163,7 @@
         <v>2.02</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S7" t="n">
         <v>3.65</v>
@@ -2175,10 +2175,10 @@
         <v>2.02</v>
       </c>
       <c r="V7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X7" t="n">
         <v>15.5</v>
@@ -2187,7 +2187,7 @@
         <v>16.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA7" t="n">
         <v>500</v>
@@ -2220,19 +2220,19 @@
         <v>25</v>
       </c>
       <c r="AK7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL7" t="n">
         <v>46</v>
       </c>
       <c r="AM7" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN7" t="n">
         <v>16</v>
       </c>
       <c r="AO7" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP7" t="n">
         <v>12</v>
@@ -2241,7 +2241,7 @@
         <v>13.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS7" t="n">
         <v>65</v>
@@ -2259,7 +2259,7 @@
         <v>46</v>
       </c>
       <c r="AX7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY7" t="n">
         <v>9.4</v>
@@ -2268,10 +2268,10 @@
         <v>16.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC7" t="n">
         <v>19</v>
@@ -2283,22 +2283,22 @@
         <v>75</v>
       </c>
       <c r="BF7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BH7" t="n">
         <v>3.35</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ7" t="n">
         <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2316,13 +2316,13 @@
         <v>13.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR7" t="n">
         <v>29</v>
       </c>
       <c r="BS7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT7" t="n">
         <v>8</v>
@@ -2337,7 +2337,7 @@
         <v>11.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY7" t="n">
         <v>12.5</v>
@@ -2346,11 +2346,11 @@
         <v>26</v>
       </c>
       <c r="CA7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -2387,10 +2387,10 @@
         <v>3.8</v>
       </c>
       <c r="H8" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="I8" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J8" t="n">
         <v>3.6</v>
@@ -2414,7 +2414,7 @@
         <v>2.06</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R8" t="n">
         <v>1.42</v>
@@ -2426,13 +2426,13 @@
         <v>1.68</v>
       </c>
       <c r="U8" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X8" t="n">
         <v>29</v>
@@ -2441,10 +2441,10 @@
         <v>11.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="AA8" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AB8" t="n">
         <v>26</v>
@@ -2456,10 +2456,10 @@
         <v>11.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AF8" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AG8" t="n">
         <v>23</v>
@@ -2468,22 +2468,22 @@
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ8" t="n">
         <v>500</v>
       </c>
       <c r="AK8" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AL8" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>600</v>
+        <v>60</v>
       </c>
       <c r="AO8" t="n">
         <v>17.5</v>
@@ -2492,7 +2492,7 @@
         <v>12.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AR8" t="n">
         <v>10.5</v>
@@ -2504,13 +2504,13 @@
         <v>12.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW8" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AX8" t="n">
         <v>13.5</v>
@@ -2522,10 +2522,10 @@
         <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BC8" t="n">
         <v>18</v>
@@ -2534,10 +2534,10 @@
         <v>8.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="BG8" t="n">
         <v>13</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -2635,16 +2635,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="G9" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="H9" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="I9" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="J9" t="n">
         <v>4.1</v>
@@ -2653,13 +2653,13 @@
         <v>4.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O9" t="n">
         <v>1.29</v>
@@ -2677,22 +2677,22 @@
         <v>3.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="U9" t="n">
         <v>1.96</v>
       </c>
       <c r="V9" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="W9" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X9" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Z9" t="n">
         <v>10</v>
@@ -2701,7 +2701,7 @@
         <v>16</v>
       </c>
       <c r="AB9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC9" t="n">
         <v>12</v>
@@ -2716,7 +2716,7 @@
         <v>70</v>
       </c>
       <c r="AG9" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AH9" t="n">
         <v>24</v>
@@ -2752,10 +2752,10 @@
         <v>8.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AT9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU9" t="n">
         <v>8.6</v>
@@ -2767,34 +2767,34 @@
         <v>15</v>
       </c>
       <c r="AX9" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="AY9" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>19</v>
       </c>
       <c r="BA9" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="BD9" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.2</v>
+        <v>29</v>
       </c>
       <c r="BF9" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="BG9" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BH9" t="n">
         <v>3.7</v>
@@ -2836,7 +2836,7 @@
         <v>4.2</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="BV9" t="n">
         <v>10.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -2892,25 +2892,25 @@
         <v>2.74</v>
       </c>
       <c r="G10" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H10" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J10" t="n">
         <v>3.2</v>
       </c>
       <c r="K10" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L10" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N10" t="n">
         <v>3.35</v>
@@ -2919,7 +2919,7 @@
         <v>1.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="Q10" t="n">
         <v>2.18</v>
@@ -2934,7 +2934,7 @@
         <v>1.88</v>
       </c>
       <c r="U10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V10" t="n">
         <v>1.49</v>
@@ -2946,10 +2946,10 @@
         <v>11.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA10" t="n">
         <v>55</v>
@@ -2958,16 +2958,16 @@
         <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD10" t="n">
         <v>13.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AG10" t="n">
         <v>13.5</v>
@@ -2976,25 +2976,25 @@
         <v>19.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AJ10" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK10" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AL10" t="n">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AM10" t="n">
-        <v>580</v>
+        <v>450</v>
       </c>
       <c r="AN10" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AO10" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AP10" t="n">
         <v>9.800000000000001</v>
@@ -3006,7 +3006,7 @@
         <v>16.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AT10" t="n">
         <v>8.800000000000001</v>
@@ -3036,10 +3036,10 @@
         <v>36</v>
       </c>
       <c r="BC10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE10" t="n">
         <v>70</v>
@@ -3051,22 +3051,22 @@
         <v>23</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN10" t="n">
         <v>5.8</v>
@@ -3078,13 +3078,13 @@
         <v>24</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR10" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BT10" t="n">
         <v>6.2</v>
@@ -3093,26 +3093,26 @@
         <v>4.6</v>
       </c>
       <c r="BV10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3215,7 @@
         <v>7.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE11" t="n">
         <v>60</v>
@@ -3251,19 +3251,19 @@
         <v>65</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>5.1</v>
       </c>
       <c r="AR11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AU11" t="n">
         <v>4.4</v>
@@ -3281,28 +3281,28 @@
         <v>6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC11" t="n">
         <v>7.8</v>
       </c>
-      <c r="BC11" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BD11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF11" t="n">
         <v>8</v>
       </c>
       <c r="BG11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH11" t="n">
         <v>2.72</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -3400,16 +3400,16 @@
         <v>1.52</v>
       </c>
       <c r="G12" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H12" t="n">
         <v>6.6</v>
       </c>
       <c r="I12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
         <v>4.3</v>
@@ -3421,7 +3421,7 @@
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O12" t="n">
         <v>1.47</v>
@@ -3448,7 +3448,7 @@
         <v>1.11</v>
       </c>
       <c r="W12" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="X12" t="n">
         <v>18.5</v>
@@ -3463,7 +3463,7 @@
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="AC12" t="n">
         <v>14</v>
@@ -3508,13 +3508,13 @@
         <v>4.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="AT12" t="n">
         <v>3.5</v>
@@ -3523,10 +3523,10 @@
         <v>5.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="AX12" t="n">
         <v>4.2</v>
@@ -3535,34 +3535,34 @@
         <v>7.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="BB12" t="n">
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BD12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="BH12" t="n">
         <v>2.96</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="G13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="I13" t="n">
         <v>1.64</v>
       </c>
       <c r="J13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L13" t="n">
         <v>1.32</v>
@@ -3675,16 +3675,16 @@
         <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R13" t="n">
         <v>1.58</v>
@@ -3693,19 +3693,19 @@
         <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="U13" t="n">
         <v>2.3</v>
       </c>
       <c r="V13" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="W13" t="n">
         <v>1.2</v>
       </c>
       <c r="X13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y13" t="n">
         <v>11.5</v>
@@ -3717,28 +3717,28 @@
         <v>16.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE13" t="n">
         <v>15.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AG13" t="n">
         <v>21</v>
       </c>
       <c r="AH13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ13" t="n">
         <v>690</v>
@@ -3771,7 +3771,7 @@
         <v>14.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU13" t="n">
         <v>9.6</v>
@@ -3798,7 +3798,7 @@
         <v>42</v>
       </c>
       <c r="BC13" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="BD13" t="n">
         <v>44</v>
@@ -3807,22 +3807,22 @@
         <v>50</v>
       </c>
       <c r="BF13" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH13" t="n">
         <v>4.2</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BJ13" t="n">
         <v>9.6</v>
       </c>
       <c r="BK13" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -4037,7 +4037,7 @@
         <v>2.54</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AY14" t="n">
         <v>4.4</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>6.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K15" t="n">
         <v>3.9</v>
@@ -4183,7 +4183,7 @@
         <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O15" t="n">
         <v>1.43</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G16" t="n">
         <v>2.04</v>
@@ -4431,22 +4431,22 @@
         <v>3.75</v>
       </c>
       <c r="L16" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M16" t="n">
         <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O16" t="n">
         <v>1.39</v>
       </c>
       <c r="P16" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R16" t="n">
         <v>1.28</v>
@@ -4455,10 +4455,10 @@
         <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="U16" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V16" t="n">
         <v>1.23</v>
@@ -4467,7 +4467,7 @@
         <v>1.96</v>
       </c>
       <c r="X16" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Y16" t="n">
         <v>970</v>
@@ -4479,7 +4479,7 @@
         <v>500</v>
       </c>
       <c r="AB16" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AC16" t="n">
         <v>8.4</v>
@@ -4494,10 +4494,10 @@
         <v>970</v>
       </c>
       <c r="AG16" t="n">
-        <v>36</v>
+        <v>19.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AI16" t="n">
         <v>500</v>
@@ -4524,13 +4524,13 @@
         <v>8.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AR16" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AT16" t="n">
         <v>6.8</v>
@@ -4539,13 +4539,13 @@
         <v>7</v>
       </c>
       <c r="AV16" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>8.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="AX16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AY16" t="n">
         <v>9</v>
@@ -4554,31 +4554,31 @@
         <v>13</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BC16" t="n">
         <v>7</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BH16" t="n">
         <v>3.2</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BJ16" t="n">
         <v>11</v>
@@ -4593,7 +4593,7 @@
         <v>10</v>
       </c>
       <c r="BN16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO16" t="n">
         <v>3.6</v>
@@ -4611,7 +4611,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU16" t="n">
         <v>4.7</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G17" t="n">
         <v>3.1</v>
@@ -4676,13 +4676,13 @@
         <v>2.38</v>
       </c>
       <c r="I17" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J17" t="n">
         <v>3.7</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L17" t="n">
         <v>1.27</v>
@@ -4700,13 +4700,13 @@
         <v>2.28</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R17" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S17" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T17" t="n">
         <v>1.59</v>
@@ -4715,13 +4715,13 @@
         <v>2.4</v>
       </c>
       <c r="V17" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W17" t="n">
         <v>1.48</v>
       </c>
       <c r="X17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y17" t="n">
         <v>14.5</v>
@@ -4736,10 +4736,10 @@
         <v>16</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD17" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE17" t="n">
         <v>26</v>
@@ -4757,22 +4757,22 @@
         <v>38</v>
       </c>
       <c r="AJ17" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK17" t="n">
         <v>32</v>
       </c>
       <c r="AL17" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM17" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN17" t="n">
         <v>22</v>
       </c>
       <c r="AO17" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP17" t="n">
         <v>15.5</v>
@@ -4784,10 +4784,10 @@
         <v>16</v>
       </c>
       <c r="AS17" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AT17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU17" t="n">
         <v>8</v>
@@ -4811,13 +4811,13 @@
         <v>25</v>
       </c>
       <c r="BB17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC17" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BD17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE17" t="n">
         <v>50</v>
@@ -4838,13 +4838,13 @@
         <v>9</v>
       </c>
       <c r="BK17" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN17" t="n">
         <v>6.6</v>
@@ -4856,7 +4856,7 @@
         <v>22</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
@@ -4865,7 +4865,7 @@
         <v>7.6</v>
       </c>
       <c r="BT17" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU17" t="n">
         <v>4.4</v>
@@ -4874,23 +4874,23 @@
         <v>18</v>
       </c>
       <c r="BW17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ17" t="n">
         <v>19.5</v>
       </c>
       <c r="CA17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -4924,13 +4924,13 @@
         <v>1.8</v>
       </c>
       <c r="G18" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="H18" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I18" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J18" t="n">
         <v>3.55</v>
@@ -4972,7 +4972,7 @@
         <v>1.22</v>
       </c>
       <c r="W18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X18" t="n">
         <v>14.5</v>
@@ -4984,10 +4984,10 @@
         <v>40</v>
       </c>
       <c r="AA18" t="n">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC18" t="n">
         <v>8.800000000000001</v>
@@ -4999,7 +4999,7 @@
         <v>110</v>
       </c>
       <c r="AF18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG18" t="n">
         <v>12</v>
@@ -5011,16 +5011,16 @@
         <v>120</v>
       </c>
       <c r="AJ18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL18" t="n">
         <v>40</v>
       </c>
       <c r="AM18" t="n">
-        <v>580</v>
+        <v>390</v>
       </c>
       <c r="AN18" t="n">
         <v>14.5</v>
@@ -5029,16 +5029,16 @@
         <v>600</v>
       </c>
       <c r="AP18" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AS18" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AT18" t="n">
         <v>7</v>
@@ -5047,7 +5047,7 @@
         <v>7.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AW18" t="n">
         <v>38</v>
@@ -5065,13 +5065,13 @@
         <v>40</v>
       </c>
       <c r="BB18" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BE18" t="n">
         <v>29</v>
@@ -5089,7 +5089,7 @@
         <v>2.74</v>
       </c>
       <c r="BJ18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK18" t="n">
         <v>5.5</v>
@@ -5098,53 +5098,53 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BN18" t="n">
         <v>4.6</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="BP18" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR18" t="n">
         <v>30</v>
       </c>
       <c r="BS18" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BT18" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU18" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV18" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW18" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
         <v>2.48</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>2.52</v>
       </c>
       <c r="BZ18" t="n">
         <v>27</v>
       </c>
       <c r="CA18" t="n">
-        <v>2.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G19" t="n">
         <v>1.77</v>
@@ -5184,10 +5184,10 @@
         <v>4.6</v>
       </c>
       <c r="I19" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J19" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K19" t="n">
         <v>4.8</v>
@@ -5199,31 +5199,31 @@
         <v>1.02</v>
       </c>
       <c r="N19" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="O19" t="n">
         <v>1.13</v>
       </c>
       <c r="P19" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R19" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="S19" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T19" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U19" t="n">
         <v>2.94</v>
       </c>
       <c r="V19" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W19" t="n">
         <v>2.3</v>
@@ -5232,10 +5232,10 @@
         <v>38</v>
       </c>
       <c r="Y19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z19" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AA19" t="n">
         <v>490</v>
@@ -5247,19 +5247,19 @@
         <v>12</v>
       </c>
       <c r="AD19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE19" t="n">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="AF19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG19" t="n">
         <v>11.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI19" t="n">
         <v>38</v>
@@ -5274,13 +5274,13 @@
         <v>22</v>
       </c>
       <c r="AM19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN19" t="n">
         <v>5.8</v>
       </c>
       <c r="AO19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP19" t="n">
         <v>28</v>
@@ -5289,10 +5289,10 @@
         <v>26</v>
       </c>
       <c r="AR19" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AS19" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AT19" t="n">
         <v>15.5</v>
@@ -5301,19 +5301,19 @@
         <v>10.5</v>
       </c>
       <c r="AV19" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AW19" t="n">
         <v>30</v>
       </c>
       <c r="AX19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY19" t="n">
         <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA19" t="n">
         <v>27</v>
@@ -5322,7 +5322,7 @@
         <v>18</v>
       </c>
       <c r="BC19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD19" t="n">
         <v>19</v>
@@ -5331,16 +5331,16 @@
         <v>29</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BH19" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BI19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BJ19" t="n">
         <v>8.800000000000001</v>
@@ -5352,7 +5352,7 @@
         <v>65</v>
       </c>
       <c r="BM19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN19" t="n">
         <v>5.2</v>
@@ -5373,10 +5373,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU19" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV19" t="n">
         <v>29</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -5435,7 +5435,7 @@
         <v>2.3</v>
       </c>
       <c r="H20" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I20" t="n">
         <v>3.45</v>
@@ -5465,10 +5465,10 @@
         <v>1.74</v>
       </c>
       <c r="R20" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T20" t="n">
         <v>1.64</v>
@@ -5480,13 +5480,13 @@
         <v>1.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="X20" t="n">
         <v>19</v>
       </c>
       <c r="Y20" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z20" t="n">
         <v>26</v>
@@ -5555,7 +5555,7 @@
         <v>7.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW20" t="n">
         <v>30</v>
@@ -5582,7 +5582,7 @@
         <v>28</v>
       </c>
       <c r="BE20" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="BF20" t="n">
         <v>12.5</v>
@@ -5630,7 +5630,7 @@
         <v>7</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV20" t="n">
         <v>25</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G21" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="H21" t="n">
         <v>6.6</v>
@@ -5701,13 +5701,13 @@
         <v>4.9</v>
       </c>
       <c r="L21" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M21" t="n">
         <v>1.04</v>
       </c>
       <c r="N21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O21" t="n">
         <v>1.23</v>
@@ -5716,7 +5716,7 @@
         <v>2.36</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R21" t="n">
         <v>1.54</v>
@@ -5731,7 +5731,7 @@
         <v>2.14</v>
       </c>
       <c r="V21" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W21" t="n">
         <v>2.78</v>
@@ -5770,7 +5770,7 @@
         <v>22</v>
       </c>
       <c r="AI21" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ21" t="n">
         <v>14</v>
@@ -5800,10 +5800,10 @@
         <v>50</v>
       </c>
       <c r="AS21" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AT21" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU21" t="n">
         <v>9.800000000000001</v>
@@ -5836,7 +5836,7 @@
         <v>26</v>
       </c>
       <c r="BE21" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="BF21" t="n">
         <v>6.2</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G22" t="n">
         <v>2.36</v>
@@ -5955,7 +5955,7 @@
         <v>3.85</v>
       </c>
       <c r="L22" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="M22" t="n">
         <v>1.06</v>
@@ -5967,7 +5967,7 @@
         <v>1.29</v>
       </c>
       <c r="P22" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="Q22" t="n">
         <v>1.91</v>
@@ -5976,10 +5976,10 @@
         <v>1.37</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U22" t="n">
         <v>2.16</v>
@@ -5988,7 +5988,7 @@
         <v>1.34</v>
       </c>
       <c r="W22" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X22" t="n">
         <v>16</v>
@@ -6015,7 +6015,7 @@
         <v>44</v>
       </c>
       <c r="AF22" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG22" t="n">
         <v>13</v>
@@ -6087,7 +6087,7 @@
         <v>19.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE22" t="n">
         <v>7.4</v>
@@ -6096,7 +6096,7 @@
         <v>14</v>
       </c>
       <c r="BG22" t="n">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BH22" t="n">
         <v>3.6</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -6197,19 +6197,19 @@
         <v>2.66</v>
       </c>
       <c r="H23" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I23" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="J23" t="n">
         <v>3.9</v>
       </c>
       <c r="K23" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L23" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M23" t="n">
         <v>1.02</v>
@@ -6221,7 +6221,7 @@
         <v>1.12</v>
       </c>
       <c r="P23" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q23" t="n">
         <v>1.4</v>
@@ -6245,16 +6245,16 @@
         <v>1.6</v>
       </c>
       <c r="X23" t="n">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="Y23" t="n">
         <v>32</v>
       </c>
       <c r="Z23" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="AA23" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AB23" t="n">
         <v>23</v>
@@ -6263,61 +6263,61 @@
         <v>12</v>
       </c>
       <c r="AD23" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF23" t="n">
         <v>26</v>
       </c>
       <c r="AG23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH23" t="n">
         <v>14</v>
       </c>
       <c r="AI23" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AJ23" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AK23" t="n">
         <v>25</v>
       </c>
       <c r="AL23" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AM23" t="n">
-        <v>580</v>
+        <v>55</v>
       </c>
       <c r="AN23" t="n">
         <v>10.5</v>
       </c>
       <c r="AO23" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP23" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="AQ23" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AR23" t="n">
-        <v>9.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="AS23" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="AT23" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AV23" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW23" t="n">
         <v>21</v>
@@ -6329,31 +6329,31 @@
         <v>11</v>
       </c>
       <c r="AZ23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA23" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BB23" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="BC23" t="n">
         <v>19</v>
       </c>
       <c r="BD23" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BE23" t="n">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="BF23" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG23" t="n">
         <v>9.6</v>
       </c>
       <c r="BH23" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BI23" t="n">
         <v>4.2</v>
@@ -6362,7 +6362,7 @@
         <v>8.4</v>
       </c>
       <c r="BK23" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
@@ -6374,7 +6374,7 @@
         <v>6.8</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BP23" t="n">
         <v>16.5</v>
@@ -6392,7 +6392,7 @@
         <v>7</v>
       </c>
       <c r="BU23" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BV23" t="n">
         <v>17.5</v>
@@ -6401,10 +6401,10 @@
         <v>6.4</v>
       </c>
       <c r="BX23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BY23" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BZ23" t="n">
         <v>11.5</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -6448,37 +6448,37 @@
         <v>2.28</v>
       </c>
       <c r="G24" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H24" t="n">
         <v>3.05</v>
       </c>
       <c r="I24" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J24" t="n">
         <v>3.2</v>
       </c>
       <c r="K24" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L24" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M24" t="n">
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P24" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R24" t="n">
         <v>1.33</v>
@@ -6490,19 +6490,19 @@
         <v>1.74</v>
       </c>
       <c r="U24" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V24" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W24" t="n">
         <v>1.63</v>
       </c>
       <c r="X24" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z24" t="n">
         <v>25</v>
@@ -6511,13 +6511,13 @@
         <v>150</v>
       </c>
       <c r="AB24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD24" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE24" t="n">
         <v>50</v>
@@ -6535,7 +6535,7 @@
         <v>60</v>
       </c>
       <c r="AJ24" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK24" t="n">
         <v>34</v>
@@ -6553,16 +6553,16 @@
         <v>46</v>
       </c>
       <c r="AP24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR24" t="n">
         <v>19</v>
       </c>
       <c r="AS24" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="AT24" t="n">
         <v>8.4</v>
@@ -6571,25 +6571,25 @@
         <v>6.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AW24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX24" t="n">
         <v>11</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>6.6</v>
+        <v>23</v>
       </c>
       <c r="BB24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC24" t="n">
         <v>20</v>
@@ -6598,34 +6598,34 @@
         <v>25</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF24" t="n">
         <v>18</v>
       </c>
       <c r="BG24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH24" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BJ24" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK24" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BN24" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO24" t="n">
         <v>4</v>
@@ -6634,13 +6634,13 @@
         <v>19</v>
       </c>
       <c r="BQ24" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BT24" t="n">
         <v>6.8</v>
@@ -6652,13 +6652,13 @@
         <v>28</v>
       </c>
       <c r="BW24" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -6699,10 +6699,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G25" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="H25" t="n">
         <v>5</v>
@@ -6717,43 +6717,43 @@
         <v>4.3</v>
       </c>
       <c r="L25" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M25" t="n">
         <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P25" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R25" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T25" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U25" t="n">
         <v>1.87</v>
       </c>
       <c r="V25" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W25" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X25" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y25" t="n">
         <v>970</v>
@@ -6765,10 +6765,10 @@
         <v>900</v>
       </c>
       <c r="AB25" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="AC25" t="n">
-        <v>42</v>
+        <v>16.5</v>
       </c>
       <c r="AD25" t="n">
         <v>500</v>
@@ -6777,10 +6777,10 @@
         <v>700</v>
       </c>
       <c r="AF25" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG25" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH25" t="n">
         <v>500</v>
@@ -6804,19 +6804,19 @@
         <v>55</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP25" t="n">
         <v>6.2</v>
       </c>
       <c r="AQ25" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.92</v>
+        <v>3.2</v>
       </c>
       <c r="AT25" t="n">
         <v>4.4</v>
@@ -6825,10 +6825,10 @@
         <v>5.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.46</v>
+        <v>4.2</v>
       </c>
       <c r="AX25" t="n">
         <v>4.9</v>
@@ -6837,34 +6837,34 @@
         <v>7</v>
       </c>
       <c r="AZ25" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.46</v>
+        <v>4.4</v>
       </c>
       <c r="BB25" t="n">
         <v>7</v>
       </c>
       <c r="BC25" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BD25" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.91</v>
+        <v>3.15</v>
       </c>
       <c r="BF25" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.9</v>
+        <v>2.86</v>
       </c>
       <c r="BH25" t="n">
         <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BJ25" t="n">
         <v>1000</v>
@@ -6882,7 +6882,7 @@
         <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -6953,19 +6953,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G26" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="H26" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J26" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K26" t="n">
         <v>3.4</v>
@@ -6977,7 +6977,7 @@
         <v>1.11</v>
       </c>
       <c r="N26" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="O26" t="n">
         <v>1.48</v>
@@ -6986,7 +6986,7 @@
         <v>1.54</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R26" t="n">
         <v>1.19</v>
@@ -7001,10 +7001,10 @@
         <v>1.73</v>
       </c>
       <c r="V26" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W26" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="X26" t="n">
         <v>9.4</v>
@@ -7013,7 +7013,7 @@
         <v>12</v>
       </c>
       <c r="Z26" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA26" t="n">
         <v>900</v>
@@ -7034,7 +7034,7 @@
         <v>12</v>
       </c>
       <c r="AG26" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH26" t="n">
         <v>26</v>
@@ -7049,7 +7049,7 @@
         <v>30</v>
       </c>
       <c r="AL26" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM26" t="n">
         <v>580</v>
@@ -7058,19 +7058,19 @@
         <v>28</v>
       </c>
       <c r="AO26" t="n">
-        <v>130</v>
+        <v>600</v>
       </c>
       <c r="AP26" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR26" t="n">
         <v>23</v>
       </c>
       <c r="AS26" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT26" t="n">
         <v>6.4</v>
@@ -7079,10 +7079,10 @@
         <v>6.4</v>
       </c>
       <c r="AV26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW26" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX26" t="n">
         <v>10</v>
@@ -7091,22 +7091,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA26" t="n">
-        <v>9.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="BB26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC26" t="n">
         <v>23</v>
       </c>
       <c r="BD26" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BE26" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF26" t="n">
         <v>21</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -7210,19 +7210,19 @@
         <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H27" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="J27" t="n">
         <v>3.85</v>
       </c>
       <c r="K27" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L27" t="n">
         <v>1.35</v>
@@ -7231,7 +7231,7 @@
         <v>1.05</v>
       </c>
       <c r="N27" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O27" t="n">
         <v>1.25</v>
@@ -7240,34 +7240,34 @@
         <v>2.28</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="T27" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U27" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V27" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="W27" t="n">
         <v>1.31</v>
       </c>
       <c r="X27" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Y27" t="n">
         <v>11.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA27" t="n">
         <v>23</v>
@@ -7279,7 +7279,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE27" t="n">
         <v>19</v>
@@ -7288,28 +7288,28 @@
         <v>32</v>
       </c>
       <c r="AG27" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI27" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AJ27" t="n">
         <v>95</v>
       </c>
       <c r="AK27" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="AL27" t="n">
         <v>55</v>
       </c>
       <c r="AM27" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AN27" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AO27" t="n">
         <v>11</v>
@@ -7318,28 +7318,28 @@
         <v>17</v>
       </c>
       <c r="AQ27" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT27" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU27" t="n">
         <v>8</v>
       </c>
       <c r="AV27" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW27" t="n">
         <v>17</v>
       </c>
       <c r="AX27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY27" t="n">
         <v>14.5</v>
@@ -7348,37 +7348,37 @@
         <v>15</v>
       </c>
       <c r="BA27" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BB27" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BC27" t="n">
         <v>38</v>
       </c>
       <c r="BD27" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE27" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BF27" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BG27" t="n">
         <v>10</v>
       </c>
       <c r="BH27" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BI27" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="BJ27" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK27" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
@@ -7393,10 +7393,10 @@
         <v>5.7</v>
       </c>
       <c r="BP27" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BQ27" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BR27" t="n">
         <v>38</v>
@@ -7408,7 +7408,7 @@
         <v>4.9</v>
       </c>
       <c r="BU27" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BV27" t="n">
         <v>13.5</v>
@@ -7417,20 +7417,20 @@
         <v>7.2</v>
       </c>
       <c r="BX27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BY27" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ27" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="CA27" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -7461,10 +7461,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G28" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="H28" t="n">
         <v>2.96</v>
@@ -7479,7 +7479,7 @@
         <v>3.6</v>
       </c>
       <c r="L28" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M28" t="n">
         <v>1.07</v>
@@ -7494,10 +7494,10 @@
         <v>1.83</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R28" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
         <v>3.55</v>
@@ -7569,7 +7569,7 @@
         <v>36</v>
       </c>
       <c r="AP28" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="AQ28" t="n">
         <v>10.5</v>
@@ -7581,10 +7581,10 @@
         <v>8.6</v>
       </c>
       <c r="AT28" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU28" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AV28" t="n">
         <v>8.4</v>
@@ -7596,7 +7596,7 @@
         <v>6.4</v>
       </c>
       <c r="AY28" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AZ28" t="n">
         <v>6.4</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="G29" t="n">
         <v>1.35</v>
@@ -7748,7 +7748,7 @@
         <v>2.08</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R29" t="n">
         <v>1.42</v>
@@ -7781,7 +7781,7 @@
         <v>810</v>
       </c>
       <c r="AB29" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AC29" t="n">
         <v>14</v>
@@ -7817,10 +7817,10 @@
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="AO29" t="n">
-        <v>430</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
         <v>14.5</v>
@@ -7832,7 +7832,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AT29" t="n">
         <v>6.8</v>
@@ -7841,10 +7841,10 @@
         <v>5.5</v>
       </c>
       <c r="AV29" t="n">
-        <v>34</v>
+        <v>7.2</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX29" t="n">
         <v>6.2</v>
@@ -7853,10 +7853,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ29" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="BB29" t="n">
         <v>8.6</v>
@@ -7868,7 +7868,7 @@
         <v>32</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="BF29" t="n">
         <v>5</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -7969,67 +7969,67 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="G30" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="H30" t="n">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="I30" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="J30" t="n">
         <v>3.65</v>
       </c>
       <c r="K30" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L30" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M30" t="n">
         <v>1.05</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O30" t="n">
         <v>1.25</v>
       </c>
       <c r="P30" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R30" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S30" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T30" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="U30" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V30" t="n">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="W30" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="X30" t="n">
         <v>500</v>
       </c>
       <c r="Y30" t="n">
+        <v>500</v>
+      </c>
+      <c r="Z30" t="n">
         <v>970</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>500</v>
       </c>
       <c r="AA30" t="n">
         <v>900</v>
@@ -8047,7 +8047,7 @@
         <v>970</v>
       </c>
       <c r="AF30" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AG30" t="n">
         <v>970</v>
@@ -8071,118 +8071,118 @@
         <v>580</v>
       </c>
       <c r="AN30" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO30" t="n">
         <v>55</v>
       </c>
       <c r="AP30" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AQ30" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AR30" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU30" t="n">
         <v>4.7</v>
       </c>
-      <c r="AS30" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AV30" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="AW30" t="n">
         <v>16.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="AY30" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AZ30" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="BA30" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BB30" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC30" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD30" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="BE30" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="BF30" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH30" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BJ30" t="n">
         <v>1000</v>
       </c>
       <c r="BK30" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BN30" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="BO30" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP30" t="n">
         <v>1000</v>
       </c>
       <c r="BQ30" t="n">
-        <v>4.3</v>
+        <v>8.4</v>
       </c>
       <c r="BR30" t="n">
         <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="BT30" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="BU30" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BV30" t="n">
         <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BZ30" t="n">
         <v>0</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G31" t="n">
         <v>2.94</v>
@@ -8241,19 +8241,19 @@
         <v>3.05</v>
       </c>
       <c r="L31" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="M31" t="n">
         <v>1.18</v>
       </c>
       <c r="N31" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="O31" t="n">
         <v>1.75</v>
       </c>
       <c r="P31" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Q31" t="n">
         <v>3.3</v>
@@ -8262,13 +8262,13 @@
         <v>1.11</v>
       </c>
       <c r="S31" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="T31" t="n">
         <v>2.42</v>
       </c>
       <c r="U31" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="V31" t="n">
         <v>1.32</v>
@@ -8280,10 +8280,10 @@
         <v>6.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA31" t="n">
         <v>110</v>
@@ -8295,7 +8295,7 @@
         <v>7.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE31" t="n">
         <v>200</v>
@@ -8322,16 +8322,16 @@
         <v>540</v>
       </c>
       <c r="AM31" t="n">
-        <v>410</v>
+        <v>380</v>
       </c>
       <c r="AN31" t="n">
         <v>180</v>
       </c>
       <c r="AO31" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AP31" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AQ31" t="n">
         <v>7</v>
@@ -8340,19 +8340,19 @@
         <v>19.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT31" t="n">
         <v>5.5</v>
       </c>
       <c r="AU31" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV31" t="n">
         <v>15.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX31" t="n">
         <v>11.5</v>
@@ -8361,10 +8361,10 @@
         <v>12</v>
       </c>
       <c r="AZ31" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB31" t="n">
         <v>36</v>
@@ -8373,7 +8373,7 @@
         <v>38</v>
       </c>
       <c r="BD31" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BE31" t="n">
         <v>55</v>
@@ -8382,13 +8382,13 @@
         <v>10</v>
       </c>
       <c r="BG31" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH31" t="n">
         <v>2.4</v>
       </c>
       <c r="BI31" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="BJ31" t="n">
         <v>14.5</v>
@@ -8424,7 +8424,7 @@
         <v>7</v>
       </c>
       <c r="BU31" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -8731,19 +8731,19 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="G33" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="H33" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="I33" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="J33" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K33" t="n">
         <v>4.7</v>
@@ -8767,7 +8767,7 @@
         <v>1.57</v>
       </c>
       <c r="R33" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S33" t="n">
         <v>2.42</v>
@@ -8776,13 +8776,13 @@
         <v>1.54</v>
       </c>
       <c r="U33" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V33" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W33" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="X33" t="n">
         <v>27</v>
@@ -8794,10 +8794,10 @@
         <v>32</v>
       </c>
       <c r="AA33" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AB33" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC33" t="n">
         <v>11</v>
@@ -8809,10 +8809,10 @@
         <v>40</v>
       </c>
       <c r="AF33" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH33" t="n">
         <v>17.5</v>
@@ -8821,10 +8821,10 @@
         <v>44</v>
       </c>
       <c r="AJ33" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK33" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL33" t="n">
         <v>32</v>
@@ -8833,67 +8833,67 @@
         <v>70</v>
       </c>
       <c r="AN33" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO33" t="n">
         <v>32</v>
       </c>
       <c r="AP33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ33" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ33" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS33" t="n">
+      <c r="BA33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD33" t="n">
         <v>4.7</v>
       </c>
-      <c r="AT33" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW33" t="n">
+      <c r="BE33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BH33" t="n">
         <v>4.5</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BH33" t="n">
-        <v>4.6</v>
       </c>
       <c r="BI33" t="n">
         <v>2.76</v>
@@ -8902,59 +8902,59 @@
         <v>9.6</v>
       </c>
       <c r="BK33" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BN33" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO33" t="n">
         <v>3.15</v>
       </c>
       <c r="BP33" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ33" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BR33" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS33" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BT33" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU33" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BV33" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BW33" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BX33" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BY33" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BZ33" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="CA33" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -9000,10 +9000,10 @@
         <v>3.1</v>
       </c>
       <c r="K34" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L34" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="M34" t="n">
         <v>1.1</v>
@@ -9045,7 +9045,7 @@
         <v>13.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AA34" t="n">
         <v>500</v>
@@ -9063,10 +9063,10 @@
         <v>500</v>
       </c>
       <c r="AF34" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AG34" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH34" t="n">
         <v>60</v>
@@ -9078,7 +9078,7 @@
         <v>900</v>
       </c>
       <c r="AK34" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AL34" t="n">
         <v>500</v>
@@ -9102,10 +9102,10 @@
         <v>14.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AT34" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AU34" t="n">
         <v>5.7</v>
@@ -9114,37 +9114,37 @@
         <v>10</v>
       </c>
       <c r="AW34" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AX34" t="n">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="AY34" t="n">
         <v>10</v>
       </c>
       <c r="AZ34" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BA34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB34" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC34" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BD34" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF34" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BG34" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH34" t="n">
         <v>3</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -9239,49 +9239,49 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="G35" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H35" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I35" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J35" t="n">
         <v>3.25</v>
       </c>
       <c r="K35" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L35" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="M35" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N35" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O35" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P35" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="R35" t="n">
         <v>1.32</v>
       </c>
       <c r="S35" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T35" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="U35" t="n">
         <v>1.99</v>
@@ -9290,37 +9290,37 @@
         <v>1.27</v>
       </c>
       <c r="W35" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X35" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AA35" t="n">
         <v>900</v>
       </c>
       <c r="AB35" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD35" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE35" t="n">
         <v>130</v>
       </c>
       <c r="AF35" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG35" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH35" t="n">
         <v>20</v>
@@ -9329,7 +9329,7 @@
         <v>160</v>
       </c>
       <c r="AJ35" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK35" t="n">
         <v>25</v>
@@ -9341,118 +9341,118 @@
         <v>580</v>
       </c>
       <c r="AN35" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO35" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP35" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY35" t="n">
         <v>4.3</v>
       </c>
-      <c r="AQ35" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR35" t="n">
+      <c r="AZ35" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF35" t="n">
         <v>5</v>
       </c>
-      <c r="AS35" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC35" t="n">
+      <c r="BG35" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK35" t="n">
         <v>4.8</v>
       </c>
-      <c r="BD35" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG35" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BH35" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BI35" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BJ35" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK35" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BL35" t="n">
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>6.8</v>
+        <v>2.46</v>
       </c>
       <c r="BN35" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO35" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BP35" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BQ35" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BR35" t="n">
         <v>32</v>
       </c>
       <c r="BS35" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BT35" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU35" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BV35" t="n">
         <v>38</v>
       </c>
       <c r="BW35" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BX35" t="n">
         <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ35" t="n">
         <v>0</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -9499,13 +9499,13 @@
         <v>1000</v>
       </c>
       <c r="H36" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="I36" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J36" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="K36" t="n">
         <v>1000</v>
@@ -9517,7 +9517,7 @@
         <v>1.05</v>
       </c>
       <c r="N36" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="O36" t="n">
         <v>1.29</v>
@@ -9532,7 +9532,7 @@
         <v>1.08</v>
       </c>
       <c r="S36" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="T36" t="n">
         <v>1.01</v>
@@ -9541,10 +9541,10 @@
         <v>1.04</v>
       </c>
       <c r="V36" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W36" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X36" t="n">
         <v>970</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -9756,7 +9756,7 @@
         <v>1.21</v>
       </c>
       <c r="I37" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="J37" t="n">
         <v>3.15</v>
@@ -9768,25 +9768,25 @@
         <v>1.01</v>
       </c>
       <c r="M37" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.19</v>
+        <v>1.8</v>
       </c>
       <c r="O37" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="P37" t="n">
-        <v>1.19</v>
+        <v>1.58</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S37" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="T37" t="n">
         <v>1.11</v>
@@ -9795,7 +9795,7 @@
         <v>1.11</v>
       </c>
       <c r="V37" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="W37" t="n">
         <v>1.03</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -10001,22 +10001,22 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="G38" t="n">
-        <v>6.2</v>
+        <v>2.5</v>
       </c>
       <c r="H38" t="n">
-        <v>2.48</v>
+        <v>2.92</v>
       </c>
       <c r="I38" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J38" t="n">
         <v>2.54</v>
       </c>
       <c r="K38" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
@@ -10025,22 +10025,22 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>1.08</v>
+        <v>1.95</v>
       </c>
       <c r="O38" t="n">
         <v>1.02</v>
       </c>
       <c r="P38" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="R38" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S38" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="T38" t="n">
         <v>1.61</v>
@@ -10052,7 +10052,7 @@
         <v>1.26</v>
       </c>
       <c r="W38" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="X38" t="n">
         <v>970</v>
@@ -10112,7 +10112,7 @@
         <v>4.4</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.53</v>
+        <v>5.8</v>
       </c>
       <c r="AR38" t="n">
         <v>1.6</v>
@@ -10157,7 +10157,7 @@
         <v>1.62</v>
       </c>
       <c r="BF38" t="n">
-        <v>4.6</v>
+        <v>1.59</v>
       </c>
       <c r="BG38" t="n">
         <v>1.62</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="G39" t="n">
         <v>1.91</v>
@@ -10267,7 +10267,7 @@
         <v>1000</v>
       </c>
       <c r="J39" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="K39" t="n">
         <v>100</v>
@@ -10279,22 +10279,22 @@
         <v>1.02</v>
       </c>
       <c r="N39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R39" t="n">
         <v>1.08</v>
       </c>
-      <c r="O39" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.07</v>
-      </c>
       <c r="S39" t="n">
-        <v>1.39</v>
+        <v>1.95</v>
       </c>
       <c r="T39" t="n">
         <v>1.01</v>
@@ -10363,7 +10363,7 @@
         <v>700</v>
       </c>
       <c r="AP39" t="n">
-        <v>4.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.73</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -10539,16 +10539,16 @@
         <v>1.34</v>
       </c>
       <c r="P40" t="n">
-        <v>1.09</v>
+        <v>1.79</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="R40" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S40" t="n">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="T40" t="n">
         <v>1.11</v>
@@ -10632,7 +10632,7 @@
         <v>3.85</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.51</v>
+        <v>5.8</v>
       </c>
       <c r="AV40" t="n">
         <v>1.57</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -10763,22 +10763,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.52</v>
+        <v>1.79</v>
       </c>
       <c r="G41" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
         <v>3.8</v>
       </c>
       <c r="I41" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="J41" t="n">
         <v>2.8</v>
       </c>
       <c r="K41" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
@@ -10787,22 +10787,22 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>1.08</v>
+        <v>2.04</v>
       </c>
       <c r="O41" t="n">
         <v>1.02</v>
       </c>
       <c r="P41" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.05</v>
+        <v>1.77</v>
       </c>
       <c r="R41" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S41" t="n">
-        <v>1.07</v>
+        <v>1.77</v>
       </c>
       <c r="T41" t="n">
         <v>1.78</v>
@@ -10814,7 +10814,7 @@
         <v>1.11</v>
       </c>
       <c r="W41" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="X41" t="n">
         <v>970</v>
@@ -10880,7 +10880,7 @@
         <v>1.84</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AT41" t="n">
         <v>3.85</v>
@@ -10892,7 +10892,7 @@
         <v>1.81</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AX41" t="n">
         <v>4.9</v>
@@ -10904,7 +10904,7 @@
         <v>1.81</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="BB41" t="n">
         <v>1.81</v>
@@ -10922,7 +10922,7 @@
         <v>4.4</v>
       </c>
       <c r="BG41" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="BH41" t="n">
         <v>1000</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -11017,22 +11017,22 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.84</v>
+        <v>2.36</v>
       </c>
       <c r="G42" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="H42" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="I42" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="J42" t="n">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="K42" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
@@ -11041,34 +11041,34 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>1.08</v>
+        <v>1.93</v>
       </c>
       <c r="O42" t="n">
         <v>1.02</v>
       </c>
       <c r="P42" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R42" t="n">
         <v>1.08</v>
       </c>
-      <c r="Q42" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.07</v>
-      </c>
       <c r="S42" t="n">
-        <v>1.02</v>
+        <v>1.87</v>
       </c>
       <c r="T42" t="n">
         <v>1.57</v>
       </c>
       <c r="U42" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="V42" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W42" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="X42" t="n">
         <v>970</v>
@@ -11125,13 +11125,13 @@
         <v>500</v>
       </c>
       <c r="AP42" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ42" t="n">
         <v>3.85</v>
       </c>
       <c r="AR42" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AS42" t="n">
         <v>1.63</v>
@@ -11140,7 +11140,7 @@
         <v>1.55</v>
       </c>
       <c r="AU42" t="n">
-        <v>4.2</v>
+        <v>1.48</v>
       </c>
       <c r="AV42" t="n">
         <v>1.56</v>
@@ -11194,7 +11194,7 @@
         <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BN42" t="n">
         <v>1000</v>
@@ -11206,13 +11206,13 @@
         <v>1000</v>
       </c>
       <c r="BQ42" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR42" t="n">
         <v>1000</v>
       </c>
       <c r="BS42" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT42" t="n">
         <v>1000</v>
@@ -11224,23 +11224,23 @@
         <v>1000</v>
       </c>
       <c r="BW42" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BX42" t="n">
         <v>1000</v>
       </c>
       <c r="BY42" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ42" t="n">
         <v>1000</v>
       </c>
       <c r="CA42" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -11304,7 +11304,7 @@
         <v>1.93</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R43" t="n">
         <v>1.36</v>
@@ -11328,7 +11328,7 @@
         <v>17</v>
       </c>
       <c r="Y43" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z43" t="n">
         <v>12</v>
@@ -11337,7 +11337,7 @@
         <v>21</v>
       </c>
       <c r="AB43" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AC43" t="n">
         <v>9.4</v>
@@ -11376,7 +11376,7 @@
         <v>700</v>
       </c>
       <c r="AO43" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AP43" t="n">
         <v>11.5</v>
@@ -11415,22 +11415,22 @@
         <v>18</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.55</v>
+        <v>6.4</v>
       </c>
       <c r="BG43" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BH43" t="n">
         <v>1000</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -11534,7 +11534,7 @@
         <v>1.73</v>
       </c>
       <c r="I44" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="J44" t="n">
         <v>3.1</v>
@@ -11549,22 +11549,22 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.33</v>
+        <v>1.93</v>
       </c>
       <c r="O44" t="n">
         <v>1.03</v>
       </c>
       <c r="P44" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.48</v>
+        <v>1.87</v>
       </c>
       <c r="R44" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S44" t="n">
-        <v>5.1</v>
+        <v>1.87</v>
       </c>
       <c r="T44" t="n">
         <v>1.01</v>
@@ -11585,43 +11585,43 @@
         <v>8.4</v>
       </c>
       <c r="Z44" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA44" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AB44" t="n">
         <v>21</v>
       </c>
       <c r="AC44" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AD44" t="n">
-        <v>16.5</v>
+        <v>25</v>
       </c>
       <c r="AE44" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AF44" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AG44" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AH44" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AI44" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AJ44" t="n">
-        <v>520</v>
+        <v>900</v>
       </c>
       <c r="AK44" t="n">
-        <v>370</v>
+        <v>700</v>
       </c>
       <c r="AL44" t="n">
-        <v>510</v>
+        <v>700</v>
       </c>
       <c r="AM44" t="n">
         <v>700</v>
@@ -11630,22 +11630,22 @@
         <v>700</v>
       </c>
       <c r="AO44" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="AP44" t="n">
         <v>4.4</v>
       </c>
       <c r="AQ44" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="AR44" t="n">
         <v>6.4</v>
       </c>
       <c r="AS44" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AT44" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU44" t="n">
         <v>6.6</v>
@@ -11660,28 +11660,28 @@
         <v>32</v>
       </c>
       <c r="AY44" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AZ44" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA44" t="n">
         <v>38</v>
       </c>
       <c r="BB44" t="n">
-        <v>2.84</v>
+        <v>2.26</v>
       </c>
       <c r="BC44" t="n">
-        <v>2.82</v>
+        <v>2.26</v>
       </c>
       <c r="BD44" t="n">
-        <v>2.84</v>
+        <v>2.26</v>
       </c>
       <c r="BE44" t="n">
-        <v>2.84</v>
+        <v>2.26</v>
       </c>
       <c r="BF44" t="n">
-        <v>2.84</v>
+        <v>2.26</v>
       </c>
       <c r="BG44" t="n">
         <v>12.5</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -12033,16 +12033,16 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="G46" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H46" t="n">
         <v>2.76</v>
       </c>
       <c r="I46" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J46" t="n">
         <v>2.72</v>
@@ -12051,85 +12051,85 @@
         <v>3.35</v>
       </c>
       <c r="L46" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="M46" t="n">
         <v>1.15</v>
       </c>
       <c r="N46" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S46" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T46" t="n">
         <v>2.2</v>
       </c>
-      <c r="O46" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S46" t="n">
-        <v>6</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.22</v>
-      </c>
       <c r="U46" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="V46" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W46" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X46" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Y46" t="n">
         <v>970</v>
       </c>
       <c r="Z46" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AA46" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AB46" t="n">
         <v>970</v>
       </c>
       <c r="AC46" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD46" t="n">
         <v>970</v>
       </c>
       <c r="AE46" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AF46" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="AG46" t="n">
         <v>970</v>
       </c>
       <c r="AH46" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="AI46" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AK46" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AL46" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AM46" t="n">
         <v>1000</v>
@@ -12138,79 +12138,79 @@
         <v>1000</v>
       </c>
       <c r="AO46" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP46" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AQ46" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.37</v>
+        <v>5.9</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.43</v>
+        <v>1.9</v>
       </c>
       <c r="AT46" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AU46" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.46</v>
+        <v>5.5</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.46</v>
+        <v>1.94</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.37</v>
+        <v>6</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.46</v>
+        <v>5.6</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="BA46" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.46</v>
+        <v>1.9</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.46</v>
+        <v>1.94</v>
       </c>
       <c r="BD46" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.46</v>
+        <v>1.91</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.44</v>
+        <v>1.88</v>
       </c>
       <c r="BG46" t="n">
-        <v>1.44</v>
+        <v>1.87</v>
       </c>
       <c r="BH46" t="n">
-        <v>2.58</v>
+        <v>3.35</v>
       </c>
       <c r="BI46" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BJ46" t="n">
         <v>1000</v>
       </c>
       <c r="BK46" t="n">
-        <v>2.74</v>
+        <v>1.31</v>
       </c>
       <c r="BL46" t="n">
         <v>1000</v>
       </c>
       <c r="BM46" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BN46" t="n">
         <v>1000</v>
@@ -12222,13 +12222,13 @@
         <v>1000</v>
       </c>
       <c r="BQ46" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BR46" t="n">
         <v>1000</v>
       </c>
       <c r="BS46" t="n">
-        <v>2.36</v>
+        <v>1.22</v>
       </c>
       <c r="BT46" t="n">
         <v>1000</v>
@@ -12240,23 +12240,23 @@
         <v>1000</v>
       </c>
       <c r="BW46" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BX46" t="n">
         <v>1000</v>
       </c>
       <c r="BY46" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BZ46" t="n">
         <v>1000</v>
       </c>
       <c r="CA46" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -12287,7 +12287,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G47" t="n">
         <v>3.1</v>
@@ -12299,7 +12299,7 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="K47" t="n">
         <v>7</v>
@@ -12311,22 +12311,22 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="O47" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="P47" t="n">
         <v>1.03</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="R47" t="n">
         <v>1.08</v>
       </c>
       <c r="S47" t="n">
-        <v>1.43</v>
+        <v>1.02</v>
       </c>
       <c r="T47" t="n">
         <v>1.01</v>
@@ -12341,10 +12341,10 @@
         <v>1.49</v>
       </c>
       <c r="X47" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Y47" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z47" t="n">
         <v>500</v>
@@ -12356,7 +12356,7 @@
         <v>500</v>
       </c>
       <c r="AC47" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AD47" t="n">
         <v>500</v>
@@ -12395,58 +12395,58 @@
         <v>500</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AV47" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="BA47" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="BD47" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="BG47" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BH47" t="n">
         <v>1000</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -12541,7 +12541,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="G48" t="n">
         <v>1000</v>
@@ -12556,7 +12556,7 @@
         <v>1.09</v>
       </c>
       <c r="K48" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L48" t="n">
         <v>1.01</v>
@@ -12589,10 +12589,10 @@
         <v>1.01</v>
       </c>
       <c r="V48" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W48" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X48" t="n">
         <v>500</v>
@@ -12697,10 +12697,10 @@
         <v>1.01</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG48" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH48" t="n">
         <v>1000</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -12795,16 +12795,16 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="G49" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="H49" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I49" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="J49" t="n">
         <v>3.2</v>
@@ -12813,19 +12813,19 @@
         <v>3.45</v>
       </c>
       <c r="L49" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M49" t="n">
         <v>1.09</v>
       </c>
       <c r="N49" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O49" t="n">
         <v>1.43</v>
       </c>
       <c r="P49" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q49" t="n">
         <v>2.26</v>
@@ -12834,31 +12834,31 @@
         <v>1.25</v>
       </c>
       <c r="S49" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T49" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="U49" t="n">
         <v>1.91</v>
       </c>
       <c r="V49" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="W49" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X49" t="n">
         <v>13.5</v>
       </c>
       <c r="Y49" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z49" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA49" t="n">
-        <v>40</v>
+        <v>900</v>
       </c>
       <c r="AB49" t="n">
         <v>14.5</v>
@@ -12876,7 +12876,7 @@
         <v>32</v>
       </c>
       <c r="AG49" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AH49" t="n">
         <v>25</v>
@@ -12888,16 +12888,16 @@
         <v>900</v>
       </c>
       <c r="AK49" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AL49" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AM49" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN49" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AO49" t="n">
         <v>32</v>
@@ -12912,10 +12912,10 @@
         <v>11.5</v>
       </c>
       <c r="AS49" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AT49" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU49" t="n">
         <v>6.6</v>
@@ -12924,7 +12924,7 @@
         <v>9.6</v>
       </c>
       <c r="AW49" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AX49" t="n">
         <v>18</v>
@@ -12936,22 +12936,22 @@
         <v>17</v>
       </c>
       <c r="BA49" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BB49" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BC49" t="n">
         <v>40</v>
       </c>
       <c r="BD49" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BE49" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BF49" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BG49" t="n">
         <v>19</v>
@@ -12960,10 +12960,10 @@
         <v>3.05</v>
       </c>
       <c r="BI49" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="BJ49" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK49" t="n">
         <v>7.8</v>
@@ -12972,53 +12972,53 @@
         <v>1000</v>
       </c>
       <c r="BM49" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN49" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BO49" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BP49" t="n">
         <v>1000</v>
       </c>
       <c r="BQ49" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR49" t="n">
         <v>1000</v>
       </c>
       <c r="BS49" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BT49" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BU49" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BV49" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BW49" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BX49" t="n">
         <v>1000</v>
       </c>
       <c r="BY49" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ49" t="n">
         <v>1000</v>
       </c>
       <c r="CA49" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -13049,13 +13049,13 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="G50" t="n">
         <v>1000</v>
       </c>
       <c r="H50" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="I50" t="n">
         <v>1000</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -13327,7 +13327,7 @@
         <v>1.1</v>
       </c>
       <c r="N51" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O51" t="n">
         <v>1.42</v>
@@ -13339,7 +13339,7 @@
         <v>2.24</v>
       </c>
       <c r="R51" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S51" t="n">
         <v>4.3</v>
@@ -13366,7 +13366,7 @@
         <v>23</v>
       </c>
       <c r="AA51" t="n">
-        <v>65</v>
+        <v>900</v>
       </c>
       <c r="AB51" t="n">
         <v>11.5</v>
@@ -13384,7 +13384,7 @@
         <v>22</v>
       </c>
       <c r="AG51" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH51" t="n">
         <v>24</v>
@@ -13405,13 +13405,13 @@
         <v>500</v>
       </c>
       <c r="AN51" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO51" t="n">
         <v>55</v>
       </c>
       <c r="AP51" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ51" t="n">
         <v>7.2</v>
@@ -13432,7 +13432,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW51" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AX51" t="n">
         <v>13</v>
@@ -13444,28 +13444,28 @@
         <v>14</v>
       </c>
       <c r="BA51" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB51" t="n">
         <v>4</v>
       </c>
-      <c r="BB51" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BC51" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BD51" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF51" t="n">
         <v>4</v>
       </c>
-      <c r="BE51" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF51" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BG51" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BH51" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI51" t="n">
         <v>2.4</v>
@@ -13474,13 +13474,13 @@
         <v>11</v>
       </c>
       <c r="BK51" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL51" t="n">
         <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BN51" t="n">
         <v>5.9</v>
@@ -13492,13 +13492,13 @@
         <v>25</v>
       </c>
       <c r="BQ51" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR51" t="n">
         <v>1000</v>
       </c>
       <c r="BS51" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT51" t="n">
         <v>6.2</v>
@@ -13510,13 +13510,13 @@
         <v>27</v>
       </c>
       <c r="BW51" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX51" t="n">
         <v>1000</v>
       </c>
       <c r="BY51" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BZ51" t="n">
         <v>0</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -13557,22 +13557,22 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="G52" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="H52" t="n">
-        <v>2.6</v>
+        <v>2.98</v>
       </c>
       <c r="I52" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="J52" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K52" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L52" t="n">
         <v>1.27</v>
@@ -13584,10 +13584,10 @@
         <v>4.7</v>
       </c>
       <c r="O52" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P52" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q52" t="n">
         <v>1.65</v>
@@ -13596,19 +13596,19 @@
         <v>1.5</v>
       </c>
       <c r="S52" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T52" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U52" t="n">
         <v>2.4</v>
       </c>
       <c r="V52" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="W52" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="X52" t="n">
         <v>24</v>
@@ -13617,22 +13617,22 @@
         <v>16.5</v>
       </c>
       <c r="Z52" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AA52" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AB52" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AC52" t="n">
         <v>10.5</v>
       </c>
       <c r="AD52" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE52" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF52" t="n">
         <v>21</v>
@@ -13647,10 +13647,10 @@
         <v>42</v>
       </c>
       <c r="AJ52" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AK52" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AL52" t="n">
         <v>34</v>
@@ -13659,10 +13659,10 @@
         <v>65</v>
       </c>
       <c r="AN52" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO52" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AP52" t="n">
         <v>14</v>
@@ -13689,7 +13689,7 @@
         <v>18.5</v>
       </c>
       <c r="AX52" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY52" t="n">
         <v>9.6</v>
@@ -13704,7 +13704,7 @@
         <v>1.03</v>
       </c>
       <c r="BC52" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BD52" t="n">
         <v>1.03</v>
@@ -13713,7 +13713,7 @@
         <v>1.03</v>
       </c>
       <c r="BF52" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BG52" t="n">
         <v>12.5</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -13811,22 +13811,22 @@
         </is>
       </c>
       <c r="F53" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I53" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J53" t="n">
         <v>2.84</v>
       </c>
-      <c r="G53" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="H53" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I53" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J53" t="n">
-        <v>2.8</v>
-      </c>
       <c r="K53" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L53" t="n">
         <v>1.53</v>
@@ -13835,7 +13835,7 @@
         <v>1.14</v>
       </c>
       <c r="N53" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O53" t="n">
         <v>1.57</v>
@@ -13844,7 +13844,7 @@
         <v>1.47</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="R53" t="n">
         <v>1.18</v>
@@ -13856,13 +13856,13 @@
         <v>2.12</v>
       </c>
       <c r="U53" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V53" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W53" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="X53" t="n">
         <v>8.199999999999999</v>
@@ -13880,13 +13880,13 @@
         <v>8.6</v>
       </c>
       <c r="AC53" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD53" t="n">
         <v>15</v>
       </c>
       <c r="AE53" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF53" t="n">
         <v>19.5</v>
@@ -13925,13 +13925,13 @@
         <v>7</v>
       </c>
       <c r="AR53" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS53" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT53" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AU53" t="n">
         <v>6</v>
@@ -13940,7 +13940,7 @@
         <v>12</v>
       </c>
       <c r="AW53" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX53" t="n">
         <v>15.5</v>
@@ -13952,28 +13952,28 @@
         <v>20</v>
       </c>
       <c r="BA53" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB53" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC53" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD53" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BD53" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BE53" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF53" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG53" t="n">
-        <v>8.4</v>
+        <v>42</v>
       </c>
       <c r="BH53" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BI53" t="n">
         <v>2.22</v>
@@ -13982,13 +13982,13 @@
         <v>12</v>
       </c>
       <c r="BK53" t="n">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="BL53" t="n">
         <v>1000</v>
       </c>
       <c r="BM53" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN53" t="n">
         <v>6</v>
@@ -14000,41 +14000,41 @@
         <v>1000</v>
       </c>
       <c r="BQ53" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR53" t="n">
         <v>1000</v>
       </c>
       <c r="BS53" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT53" t="n">
         <v>5.9</v>
       </c>
       <c r="BU53" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BV53" t="n">
         <v>1000</v>
       </c>
       <c r="BW53" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX53" t="n">
         <v>1000</v>
       </c>
       <c r="BY53" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ53" t="n">
         <v>1000</v>
       </c>
       <c r="CA53" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -14319,61 +14319,61 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G55" t="n">
         <v>2.52</v>
       </c>
       <c r="H55" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I55" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J55" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K55" t="n">
         <v>3.35</v>
       </c>
       <c r="L55" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M55" t="n">
         <v>1.12</v>
       </c>
       <c r="N55" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O55" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="P55" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="R55" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S55" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="T55" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U55" t="n">
         <v>1.8</v>
       </c>
       <c r="V55" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W55" t="n">
         <v>1.65</v>
       </c>
       <c r="X55" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y55" t="n">
         <v>12</v>
@@ -14385,7 +14385,7 @@
         <v>95</v>
       </c>
       <c r="AB55" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC55" t="n">
         <v>8.199999999999999</v>
@@ -14424,7 +14424,7 @@
         <v>38</v>
       </c>
       <c r="AO55" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP55" t="n">
         <v>7</v>
@@ -14436,7 +14436,7 @@
         <v>19</v>
       </c>
       <c r="AS55" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AT55" t="n">
         <v>6</v>
@@ -14448,7 +14448,7 @@
         <v>12.5</v>
       </c>
       <c r="AW55" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AX55" t="n">
         <v>10.5</v>
@@ -14460,49 +14460,49 @@
         <v>17</v>
       </c>
       <c r="BA55" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB55" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BC55" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BD55" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF55" t="n">
         <v>5</v>
       </c>
-      <c r="BE55" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF55" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BG55" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BH55" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BI55" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BJ55" t="n">
         <v>11.5</v>
       </c>
       <c r="BK55" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL55" t="n">
         <v>1000</v>
       </c>
       <c r="BM55" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN55" t="n">
         <v>5.1</v>
       </c>
       <c r="BO55" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP55" t="n">
         <v>21</v>
@@ -14514,25 +14514,25 @@
         <v>44</v>
       </c>
       <c r="BS55" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT55" t="n">
         <v>7</v>
       </c>
       <c r="BU55" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV55" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BW55" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX55" t="n">
         <v>60</v>
       </c>
       <c r="BY55" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ55" t="n">
         <v>0</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -14573,16 +14573,16 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G56" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H56" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I56" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J56" t="n">
         <v>3.1</v>
@@ -14594,37 +14594,37 @@
         <v>1.44</v>
       </c>
       <c r="M56" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N56" t="n">
         <v>2.88</v>
       </c>
       <c r="O56" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P56" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="R56" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
       </c>
       <c r="T56" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U56" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V56" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W56" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="X56" t="n">
         <v>11.5</v>
@@ -14684,7 +14684,7 @@
         <v>3.9</v>
       </c>
       <c r="AQ56" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR56" t="n">
         <v>19</v>
@@ -14738,65 +14738,65 @@
         <v>2.84</v>
       </c>
       <c r="BI56" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="BJ56" t="n">
         <v>11</v>
       </c>
       <c r="BK56" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BL56" t="n">
         <v>1000</v>
       </c>
       <c r="BM56" t="n">
-        <v>15.5</v>
+        <v>4.8</v>
       </c>
       <c r="BN56" t="n">
         <v>5</v>
       </c>
       <c r="BO56" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BP56" t="n">
         <v>1000</v>
       </c>
       <c r="BQ56" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR56" t="n">
         <v>1000</v>
       </c>
       <c r="BS56" t="n">
+        <v>13</v>
+      </c>
+      <c r="BT56" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU56" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW56" t="n">
         <v>12</v>
       </c>
-      <c r="BT56" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU56" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW56" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BX56" t="n">
         <v>1000</v>
       </c>
       <c r="BY56" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BZ56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA56" t="n">
         <v>13</v>
       </c>
-      <c r="BZ56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA56" t="n">
-        <v>12</v>
-      </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>
@@ -14842,7 +14842,7 @@
         <v>3.2</v>
       </c>
       <c r="K57" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L57" t="n">
         <v>1.38</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-04 22:42:06</t>
+          <t>2026-07-05 00:54:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,180 +843,180 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tacuarembo</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cerrito</t>
+          <t>HFX Wanderers</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.85</v>
+        <v>9.6</v>
       </c>
       <c r="G2" t="n">
+        <v>11</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K2" t="n">
         <v>4.7</v>
       </c>
-      <c r="H2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.92</v>
-      </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.19</v>
+        <v>4.7</v>
       </c>
       <c r="O2" t="n">
-        <v>4.4</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>2.14</v>
       </c>
       <c r="R2" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>110</v>
+        <v>4.8</v>
       </c>
       <c r="T2" t="n">
-        <v>6.8</v>
+        <v>1.72</v>
       </c>
       <c r="U2" t="n">
-        <v>1.13</v>
+        <v>2.12</v>
       </c>
       <c r="V2" t="n">
-        <v>1.22</v>
+        <v>3.05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>2.4</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="Z2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB2" t="n">
         <v>1000</v>
       </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>6</v>
-      </c>
       <c r="AC2" t="n">
-        <v>11.5</v>
+        <v>6.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>990</v>
+        <v>7.6</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF2" t="n">
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.16</v>
+        <v>16</v>
       </c>
       <c r="AQ2" t="n">
         <v>4.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AS2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>55</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>140</v>
+      </c>
+      <c r="BF2" t="n">
         <v>110</v>
       </c>
-      <c r="AT2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>280</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>85</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>170</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>130</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>290</v>
-      </c>
       <c r="BG2" t="n">
-        <v>5.6</v>
+        <v>18</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-05 18:20:14</t>
+          <t>2026-07-05 20:28:02</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1102,246 +1102,246 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Delfin</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
         <v>2.64</v>
       </c>
-      <c r="G3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="AD3" t="n">
         <v>4.6</v>
       </c>
-      <c r="O3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA3" t="n">
+      <c r="AE3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
         <v>42</v>
       </c>
-      <c r="AB3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>27</v>
-      </c>
       <c r="AL3" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AM3" t="n">
-        <v>65</v>
+        <v>300</v>
       </c>
       <c r="AN3" t="n">
-        <v>19</v>
+        <v>220</v>
       </c>
       <c r="AO3" t="n">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="AP3" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR3" t="n">
         <v>17.5</v>
       </c>
       <c r="AS3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA3" t="n">
         <v>34</v>
       </c>
-      <c r="AT3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>30</v>
-      </c>
       <c r="BB3" t="n">
-        <v>34</v>
+        <v>16.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BD3" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="BE3" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="BF3" t="n">
-        <v>16.5</v>
+        <v>110</v>
       </c>
       <c r="BG3" t="n">
-        <v>16.5</v>
+        <v>48</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-05 18:20:14</t>
+          <t>2026-07-05 20:28:02</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Delfin</t>
+          <t>Miami FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Birmingham Legion FC</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S4" t="n">
         <v>3.15</v>
       </c>
-      <c r="G4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S4" t="n">
-        <v>6</v>
-      </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="U4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W4" t="n">
         <v>1.77</v>
       </c>
-      <c r="V4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.45</v>
-      </c>
       <c r="X4" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK4" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>460</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>170</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>40</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>140</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>38</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>36</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>170</v>
+        <v>4.2</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BP4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS4" t="n">
-        <v>10.5</v>
+        <v>24</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY4" t="n">
-        <v>10.5</v>
+        <v>24</v>
       </c>
       <c r="BZ4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="CA4" t="n">
-        <v>10.5</v>
+        <v>24</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-05 18:20:14</t>
+          <t>2026-07-05 20:28:02</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1610,246 +1610,246 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Miami FC</t>
+          <t>Colon FC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Birmingham Legion FC</t>
+          <t>Uruguay Montevideo FC</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="G5" t="n">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="H5" t="n">
-        <v>2.82</v>
+        <v>4.2</v>
       </c>
       <c r="I5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K5" t="n">
         <v>3</v>
       </c>
-      <c r="J5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4</v>
-      </c>
       <c r="L5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P5" t="n">
         <v>1.33</v>
       </c>
-      <c r="M5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.32</v>
-      </c>
       <c r="Q5" t="n">
-        <v>1.7</v>
+        <v>3.85</v>
       </c>
       <c r="R5" t="n">
-        <v>1.51</v>
+        <v>1.1</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>1.61</v>
+        <v>2.76</v>
       </c>
       <c r="U5" t="n">
-        <v>2.46</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="W5" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="X5" t="n">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="Y5" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG5" t="n">
         <v>15</v>
       </c>
-      <c r="Z5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA5" t="n">
+      <c r="AH5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>220</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>280</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>34</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>140</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>350</v>
+      </c>
+      <c r="BF5" t="n">
         <v>48</v>
       </c>
-      <c r="AB5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK5" t="n">
+      <c r="BG5" t="n">
+        <v>150</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>32</v>
+      </c>
+      <c r="BK5" t="n">
         <v>25</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>14</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>7</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BO5" t="n">
         <v>5.1</v>
       </c>
       <c r="BP5" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="BR5" t="n">
-        <v>27</v>
+        <v>910</v>
       </c>
       <c r="BS5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BV5" t="n">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="BW5" t="n">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="BX5" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="BY5" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="BZ5" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-05 18:20:14</t>
+          <t>2026-07-05 20:28:02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,183 +1859,183 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Colon FC</t>
+          <t>Nautico PE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Uruguay Montevideo FC</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.08</v>
+        <v>2.48</v>
       </c>
       <c r="G6" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="I6" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="L6" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="M6" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="O6" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="P6" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="R6" t="n">
         <v>1.21</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="X6" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>11</v>
-      </c>
       <c r="AH6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI6" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AK6" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AL6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM6" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AN6" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AO6" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AP6" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR6" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AS6" t="n">
         <v>65</v>
       </c>
       <c r="AT6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU6" t="n">
         <v>6.4</v>
       </c>
-      <c r="AU6" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AV6" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW6" t="n">
         <v>48</v>
       </c>
       <c r="AX6" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ6" t="n">
         <v>21</v>
       </c>
       <c r="BA6" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BB6" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BC6" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BD6" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BE6" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="BF6" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BG6" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="BI6" t="n">
         <v>2.62</v>
@@ -2044,66 +2044,66 @@
         <v>11</v>
       </c>
       <c r="BK6" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BL6" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="BM6" t="n">
+        <v>150</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>12</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>42</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>36</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY6" t="n">
         <v>15</v>
       </c>
-      <c r="BN6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>38</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>40</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-05 18:20:14</t>
+          <t>2026-07-05 20:28:02</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,498 +2113,244 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Anapolis GO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G7" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="H7" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="I7" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="M7" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.84</v>
+        <v>3.55</v>
       </c>
       <c r="O7" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="P7" t="n">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.58</v>
+        <v>2.04</v>
       </c>
       <c r="R7" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>5.3</v>
+        <v>3.75</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="U7" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W7" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="X7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Y7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA7" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC7" t="n">
         <v>7.8</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>7.2</v>
       </c>
       <c r="AD7" t="n">
         <v>15.5</v>
       </c>
       <c r="AE7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI7" t="n">
         <v>55</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AJ7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>14.5</v>
       </c>
-      <c r="AG7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN7" t="n">
+      <c r="BA7" t="n">
         <v>36</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="BB7" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE7" t="n">
         <v>70</v>
       </c>
-      <c r="AP7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR7" t="n">
+      <c r="BF7" t="n">
         <v>20</v>
       </c>
-      <c r="AS7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>30</v>
-      </c>
       <c r="BG7" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.58</v>
+        <v>2.92</v>
       </c>
       <c r="BJ7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BK7" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BO7" t="n">
         <v>4.7</v>
       </c>
       <c r="BP7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ7" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BR7" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BS7" t="n">
-        <v>14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT7" t="n">
         <v>6.4</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BV7" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BW7" t="n">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="BX7" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="BY7" t="n">
-        <v>15.5</v>
+        <v>8.4</v>
       </c>
       <c r="BZ7" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-05 18:20:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Brazilian Serie C</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Anapolis GO</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Botafogo PB</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="X8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>70</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>32</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>65</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>27</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>40</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>2026-07-05 18:20:14</t>
+          <t>2026-07-05 20:28:02</t>
         </is>
       </c>
     </row>
